--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -1981,13 +1981,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46108.590050300925</v>
+        <v>46108.75671696759</v>
       </c>
       <c r="C4" s="5">
-        <v>46112.30827043981</v>
+        <v>46112.47493710648</v>
       </c>
       <c r="D4" s="5">
-        <v>46135.47863081019</v>
+        <v>46135.64529747685</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2030,13 +2030,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46108.59013304398</v>
+        <v>46108.75679971065</v>
       </c>
       <c r="C5" s="8">
-        <v>46112.30816390047</v>
+        <v>46112.47483056713</v>
       </c>
       <c r="D5" s="8">
-        <v>46112.30818222222</v>
+        <v>46112.47484888889</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2093,13 +2093,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46108.59013730324</v>
+        <v>46108.75680396991</v>
       </c>
       <c r="C6" s="5">
-        <v>46112.30820663195</v>
+        <v>46112.47487329861</v>
       </c>
       <c r="D6" s="5">
-        <v>46112.30822237268</v>
+        <v>46112.47488903935</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -2156,13 +2156,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8">
-        <v>46108.59014104167</v>
+        <v>46108.756807708334</v>
       </c>
       <c r="C7" s="8">
-        <v>46112.30822040509</v>
+        <v>46112.47488707176</v>
       </c>
       <c r="D7" s="8">
-        <v>46112.30823634259</v>
+        <v>46112.474903009264</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>36</v>
@@ -2219,13 +2219,13 @@
         <v>37</v>
       </c>
       <c r="B8" s="5">
-        <v>46108.59014988426</v>
+        <v>46108.75681655093</v>
       </c>
       <c r="C8" s="5">
-        <v>46112.3082394213</v>
+        <v>46112.47490608796</v>
       </c>
       <c r="D8" s="5">
-        <v>46112.30827072916</v>
+        <v>46112.47493739583</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>38</v>
@@ -2282,13 +2282,13 @@
         <v>40</v>
       </c>
       <c r="B9" s="8">
-        <v>46108.59015527778</v>
+        <v>46108.756821944444</v>
       </c>
       <c r="C9" s="8">
-        <v>46112.30825949074</v>
+        <v>46112.4749261574</v>
       </c>
       <c r="D9" s="8">
-        <v>46112.30827738426</v>
+        <v>46112.474944050926</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>41</v>
@@ -2345,11 +2345,11 @@
         <v>42</v>
       </c>
       <c r="B10" s="5">
-        <v>46108.590055740744</v>
+        <v>46108.75672240741</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46134.72758210648</v>
+        <v>46134.89424877315</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>43</v>
@@ -2392,13 +2392,13 @@
         <v>45</v>
       </c>
       <c r="B11" s="8">
-        <v>46108.590159328705</v>
+        <v>46108.75682599537</v>
       </c>
       <c r="C11" s="8">
-        <v>46134.72757178241</v>
+        <v>46134.89423844907</v>
       </c>
       <c r="D11" s="8">
-        <v>46134.727589560185</v>
+        <v>46134.89425622685</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>46</v>
@@ -2457,11 +2457,11 @@
         <v>50</v>
       </c>
       <c r="B12" s="5">
-        <v>46108.5901654051</v>
+        <v>46108.756832071755</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46111.41252525463</v>
+        <v>46111.57919192129</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -2520,11 +2520,11 @@
         <v>55</v>
       </c>
       <c r="B13" s="8">
-        <v>46111.362621168984</v>
+        <v>46111.52928783565</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46111.412670578706</v>
+        <v>46111.57933724537</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>56</v>
@@ -2573,11 +2573,11 @@
         <v>59</v>
       </c>
       <c r="B14" s="5">
-        <v>46111.36284828704</v>
+        <v>46111.529514953705</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46111.41266780093</v>
+        <v>46111.57933446759</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>60</v>
@@ -2626,11 +2626,11 @@
         <v>62</v>
       </c>
       <c r="B15" s="8">
-        <v>46111.362902650464</v>
+        <v>46111.52956931713</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="8">
-        <v>46111.41266497685</v>
+        <v>46111.579331643516</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>63</v>
@@ -2679,11 +2679,11 @@
         <v>65</v>
       </c>
       <c r="B16" s="5">
-        <v>46111.362951585645</v>
+        <v>46111.529618252316</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46111.41266065973</v>
+        <v>46111.579327326384</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>66</v>
@@ -2732,13 +2732,13 @@
         <v>68</v>
       </c>
       <c r="B17" s="8">
-        <v>46108.59006069445</v>
+        <v>46108.756727361106</v>
       </c>
       <c r="C17" s="8">
-        <v>46112.30866109954</v>
+        <v>46112.4753277662</v>
       </c>
       <c r="D17" s="8">
-        <v>46135.47865769676</v>
+        <v>46135.645324363424</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>69</v>
@@ -2781,13 +2781,13 @@
         <v>71</v>
       </c>
       <c r="B18" s="5">
-        <v>46108.59017084491</v>
+        <v>46108.75683751157</v>
       </c>
       <c r="C18" s="5">
-        <v>46112.30849111111</v>
+        <v>46112.47515777778</v>
       </c>
       <c r="D18" s="5">
-        <v>46113.983714988426</v>
+        <v>46114.1503816551</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>72</v>
@@ -2846,13 +2846,13 @@
         <v>74</v>
       </c>
       <c r="B19" s="8">
-        <v>46108.59018086806</v>
+        <v>46108.75684753472</v>
       </c>
       <c r="C19" s="8">
-        <v>46112.308508773145</v>
+        <v>46112.47517543982</v>
       </c>
       <c r="D19" s="8">
-        <v>46121.00810387731</v>
+        <v>46121.17477054398</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>75</v>
@@ -2911,13 +2911,13 @@
         <v>77</v>
       </c>
       <c r="B20" s="5">
-        <v>46108.590186574074</v>
+        <v>46108.756853240746</v>
       </c>
       <c r="C20" s="5">
-        <v>46112.30856804398</v>
+        <v>46112.47523471065</v>
       </c>
       <c r="D20" s="5">
-        <v>46121.00810381945</v>
+        <v>46121.17477048611</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>78</v>
@@ -2976,13 +2976,13 @@
         <v>80</v>
       </c>
       <c r="B21" s="8">
-        <v>46108.59019297454</v>
+        <v>46108.7568596412</v>
       </c>
       <c r="C21" s="8">
-        <v>46112.30862387731</v>
+        <v>46112.47529054398</v>
       </c>
       <c r="D21" s="8">
-        <v>46121.0081040625</v>
+        <v>46121.174770729165</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>81</v>
@@ -3041,13 +3041,13 @@
         <v>84</v>
       </c>
       <c r="B22" s="5">
-        <v>46108.62263557871</v>
+        <v>46108.78930224537</v>
       </c>
       <c r="C22" s="5">
-        <v>46112.30864754629</v>
+        <v>46112.47531421296</v>
       </c>
       <c r="D22" s="5">
-        <v>46121.0081037037</v>
+        <v>46121.17477037037</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>85</v>
@@ -3106,11 +3106,11 @@
         <v>87</v>
       </c>
       <c r="B23" s="8">
-        <v>46108.59006707176</v>
+        <v>46108.756733738424</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="8">
-        <v>46135.37941291666</v>
+        <v>46135.546079583335</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>88</v>
@@ -3153,13 +3153,13 @@
         <v>90</v>
       </c>
       <c r="B24" s="5">
-        <v>46108.59020194445</v>
+        <v>46108.75686861111</v>
       </c>
       <c r="C24" s="5">
-        <v>46112.308853090275</v>
+        <v>46112.47551975695</v>
       </c>
       <c r="D24" s="5">
-        <v>46115.96251511574</v>
+        <v>46116.12918178241</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>91</v>
@@ -3218,13 +3218,13 @@
         <v>93</v>
       </c>
       <c r="B25" s="8">
-        <v>46108.59020821759</v>
+        <v>46108.75687488426</v>
       </c>
       <c r="C25" s="8">
-        <v>46112.30882164351</v>
+        <v>46112.475488310185</v>
       </c>
       <c r="D25" s="8">
-        <v>46123.02682134259</v>
+        <v>46123.19348800926</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>94</v>
@@ -3283,11 +3283,11 @@
         <v>96</v>
       </c>
       <c r="B26" s="5">
-        <v>46108.59021409722</v>
+        <v>46108.75688076389</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46169.68626451389</v>
+        <v>46169.852931180554</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>97</v>
@@ -3346,13 +3346,13 @@
         <v>101</v>
       </c>
       <c r="B27" s="8">
-        <v>46108.59021996528</v>
+        <v>46108.75688663195</v>
       </c>
       <c r="C27" s="8">
-        <v>46135.37940633102</v>
+        <v>46135.546072997684</v>
       </c>
       <c r="D27" s="8">
-        <v>46135.37953547454</v>
+        <v>46135.5462021412</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>102</v>
@@ -3411,11 +3411,11 @@
         <v>104</v>
       </c>
       <c r="B28" s="5">
-        <v>46108.59023068287</v>
+        <v>46108.756897349536</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46185.01189069444</v>
+        <v>46185.17855736111</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3474,13 +3474,13 @@
         <v>111</v>
       </c>
       <c r="B29" s="8">
-        <v>46108.590235682874</v>
+        <v>46108.75690234954</v>
       </c>
       <c r="C29" s="8">
-        <v>46112.309146307874</v>
+        <v>46112.47581297454</v>
       </c>
       <c r="D29" s="8">
-        <v>46123.02682138889</v>
+        <v>46123.19348805556</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>112</v>
@@ -3539,11 +3539,11 @@
         <v>114</v>
       </c>
       <c r="B30" s="5">
-        <v>46108.59024174769</v>
+        <v>46108.75690841435</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46185.011889166664</v>
+        <v>46185.178555833336</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>115</v>
@@ -3602,13 +3602,13 @@
         <v>117</v>
       </c>
       <c r="B31" s="8">
-        <v>46108.61981157407</v>
+        <v>46108.78647824074</v>
       </c>
       <c r="C31" s="8">
-        <v>46112.30910100695</v>
+        <v>46112.47576767361</v>
       </c>
       <c r="D31" s="8">
-        <v>46123.0268209375</v>
+        <v>46123.19348760416</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>86</v>
@@ -3667,11 +3667,11 @@
         <v>119</v>
       </c>
       <c r="B32" s="5">
-        <v>46108.5900744213</v>
+        <v>46108.756741087964</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46154.70118263889</v>
+        <v>46154.867849305556</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>120</v>
@@ -3714,11 +3714,11 @@
         <v>122</v>
       </c>
       <c r="B33" s="8">
-        <v>46108.59028607639</v>
+        <v>46108.75695274306</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="8">
-        <v>46182.52670556713</v>
+        <v>46182.6933722338</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>123</v>
@@ -3777,13 +3777,13 @@
         <v>127</v>
       </c>
       <c r="B34" s="5">
-        <v>46108.59029108797</v>
+        <v>46108.75695775463</v>
       </c>
       <c r="C34" s="5">
-        <v>46182.52669886574</v>
+        <v>46182.69336553241</v>
       </c>
       <c r="D34" s="5">
-        <v>46182.52670059028</v>
+        <v>46182.69336725694</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>128</v>
@@ -3842,11 +3842,11 @@
         <v>130</v>
       </c>
       <c r="B35" s="8">
-        <v>46108.590296759256</v>
+        <v>46108.75696342593</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46182.52670665509</v>
+        <v>46182.69337332176</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>131</v>
@@ -3905,11 +3905,11 @@
         <v>133</v>
       </c>
       <c r="B36" s="5">
-        <v>46108.59030648148</v>
+        <v>46108.75697314815</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.6876652662</v>
+        <v>46169.854331932875</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>134</v>
@@ -3968,11 +3968,11 @@
         <v>136</v>
       </c>
       <c r="B37" s="8">
-        <v>46108.5903112963</v>
+        <v>46108.75697796296</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46135.37941498843</v>
+        <v>46135.54608165509</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>137</v>
@@ -4031,11 +4031,11 @@
         <v>139</v>
       </c>
       <c r="B38" s="5">
-        <v>46108.590316863425</v>
+        <v>46108.7569835301</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46111.41535784722</v>
+        <v>46111.58202451389</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>140</v>
@@ -4092,11 +4092,11 @@
         <v>142</v>
       </c>
       <c r="B39" s="8">
-        <v>46108.590321655094</v>
+        <v>46108.75698832176</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46183.000833576385</v>
+        <v>46183.16750024306</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>143</v>
@@ -4155,11 +4155,11 @@
         <v>145</v>
       </c>
       <c r="B40" s="5">
-        <v>46108.59032644676</v>
+        <v>46108.75699311343</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46169.683875891205</v>
+        <v>46169.85054255787</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>146</v>
@@ -4218,11 +4218,11 @@
         <v>148</v>
       </c>
       <c r="B41" s="8">
-        <v>46108.59033180556</v>
+        <v>46108.75699847222</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46182.00132953704</v>
+        <v>46182.1679962037</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>149</v>
@@ -4281,11 +4281,11 @@
         <v>151</v>
       </c>
       <c r="B42" s="5">
-        <v>46108.59033690972</v>
+        <v>46108.75700357639</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46182.52677877314</v>
+        <v>46182.693445439814</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>152</v>
@@ -4344,13 +4344,13 @@
         <v>154</v>
       </c>
       <c r="B43" s="8">
-        <v>46108.59034189815</v>
+        <v>46108.75700856482</v>
       </c>
       <c r="C43" s="8">
-        <v>46182.52677163194</v>
+        <v>46182.69343829861</v>
       </c>
       <c r="D43" s="8">
-        <v>46182.52677309028</v>
+        <v>46182.69343975694</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>155</v>
@@ -4409,11 +4409,11 @@
         <v>157</v>
       </c>
       <c r="B44" s="5">
-        <v>46108.59034976852</v>
+        <v>46108.757016435186</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46182.526779803244</v>
+        <v>46182.69344646991</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>158</v>
@@ -4472,11 +4472,11 @@
         <v>160</v>
       </c>
       <c r="B45" s="8">
-        <v>46108.590355162036</v>
+        <v>46108.7570218287</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46182.52678069445</v>
+        <v>46182.69344736111</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>161</v>
@@ -4535,11 +4535,11 @@
         <v>163</v>
       </c>
       <c r="B46" s="5">
-        <v>46108.590360532406</v>
+        <v>46108.75702719907</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46169.6841436574</v>
+        <v>46169.850810324075</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>164</v>
@@ -4598,11 +4598,11 @@
         <v>168</v>
       </c>
       <c r="B47" s="8">
-        <v>46108.59036534722</v>
+        <v>46108.75703201389</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46169.68407221065</v>
+        <v>46169.850738877314</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>109</v>
@@ -4661,11 +4661,11 @@
         <v>170</v>
       </c>
       <c r="B48" s="5">
-        <v>46108.590370949074</v>
+        <v>46108.75703761574</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46169.68410056713</v>
+        <v>46169.850767233795</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>171</v>
@@ -4724,13 +4724,13 @@
         <v>173</v>
       </c>
       <c r="B49" s="8">
-        <v>46108.59037640046</v>
+        <v>46108.75704306713</v>
       </c>
       <c r="C49" s="8">
-        <v>46154.701175821756</v>
+        <v>46154.86784248843</v>
       </c>
       <c r="D49" s="8">
-        <v>46154.70117755787</v>
+        <v>46154.86784422454</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>174</v>
@@ -4789,13 +4789,13 @@
         <v>176</v>
       </c>
       <c r="B50" s="5">
-        <v>46108.59038365741</v>
+        <v>46108.75705032407</v>
       </c>
       <c r="C50" s="5">
-        <v>46154.70079945602</v>
+        <v>46154.86746612268</v>
       </c>
       <c r="D50" s="5">
-        <v>46154.70080144676</v>
+        <v>46154.86746811343</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>177</v>
@@ -4844,13 +4844,13 @@
         <v>179</v>
       </c>
       <c r="B51" s="8">
-        <v>46108.590390613426</v>
+        <v>46108.75705728009</v>
       </c>
       <c r="C51" s="8">
-        <v>46154.70109605324</v>
+        <v>46154.86776271991</v>
       </c>
       <c r="D51" s="8">
-        <v>46154.70109744213</v>
+        <v>46154.8677641088</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>180</v>
@@ -4899,11 +4899,11 @@
         <v>182</v>
       </c>
       <c r="B52" s="5">
-        <v>46108.590394768515</v>
+        <v>46108.757061435186</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46169.68575747685</v>
+        <v>46169.85242414352</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>183</v>
@@ -4962,11 +4962,11 @@
         <v>187</v>
       </c>
       <c r="B53" s="8">
-        <v>46108.590440300926</v>
+        <v>46108.75710696759</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46169.6857249537</v>
+        <v>46169.85239162037</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>116</v>
@@ -5021,11 +5021,11 @@
         <v>189</v>
       </c>
       <c r="B54" s="5">
-        <v>46108.59044626157</v>
+        <v>46108.757112928244</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46169.6857443287</v>
+        <v>46169.85241099537</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -5074,13 +5074,13 @@
         <v>193</v>
       </c>
       <c r="B55" s="8">
-        <v>46111.341939791666</v>
+        <v>46111.50860645833</v>
       </c>
       <c r="C55" s="8">
-        <v>46182.52738331018</v>
+        <v>46182.69404997685</v>
       </c>
       <c r="D55" s="8">
-        <v>46182.52739695602</v>
+        <v>46182.69406362269</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>194</v>
@@ -5139,13 +5139,13 @@
         <v>196</v>
       </c>
       <c r="B56" s="5">
-        <v>46111.34208927084</v>
+        <v>46111.508755937495</v>
       </c>
       <c r="C56" s="5">
-        <v>46182.52684064815</v>
+        <v>46182.69350731482</v>
       </c>
       <c r="D56" s="5">
-        <v>46182.52684210648</v>
+        <v>46182.69350877315</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>197</v>
@@ -5194,13 +5194,13 @@
         <v>199</v>
       </c>
       <c r="B57" s="8">
-        <v>46111.34218010417</v>
+        <v>46111.508846770834</v>
       </c>
       <c r="C57" s="8">
-        <v>46182.52736954861</v>
+        <v>46182.69403621528</v>
       </c>
       <c r="D57" s="8">
-        <v>46182.52737082176</v>
+        <v>46182.69403748843</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>200</v>
@@ -5249,11 +5249,11 @@
         <v>202</v>
       </c>
       <c r="B58" s="5">
-        <v>46108.59045233796</v>
+        <v>46108.75711900463</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46141.36111729167</v>
+        <v>46141.52778395833</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>203</v>
@@ -5296,11 +5296,11 @@
         <v>205</v>
       </c>
       <c r="B59" s="8">
-        <v>46108.59045658565</v>
+        <v>46108.75712325232</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46141.361117673616</v>
+        <v>46141.52778434027</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>206</v>
@@ -5357,11 +5357,11 @@
         <v>211</v>
       </c>
       <c r="B60" s="5">
-        <v>46114.3859125</v>
+        <v>46114.552579166666</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46127.00489599537</v>
+        <v>46127.171562662035</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>212</v>
@@ -5410,11 +5410,11 @@
         <v>216</v>
       </c>
       <c r="B61" s="8">
-        <v>46114.38610657408</v>
+        <v>46114.552773240735</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46127.00489753472</v>
+        <v>46127.17156420139</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>217</v>
@@ -5463,11 +5463,11 @@
         <v>219</v>
       </c>
       <c r="B62" s="5">
-        <v>46108.590461886575</v>
+        <v>46108.75712855324</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46182.02170063657</v>
+        <v>46182.18836730324</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>220</v>
@@ -5526,11 +5526,11 @@
         <v>223</v>
       </c>
       <c r="B63" s="8">
-        <v>46114.386197858796</v>
+        <v>46114.55286452547</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46114.45154746527</v>
+        <v>46114.618214131944</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>212</v>
@@ -5579,11 +5579,11 @@
         <v>226</v>
       </c>
       <c r="B64" s="5">
-        <v>46114.38629995371</v>
+        <v>46114.552966620366</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46114.45154405093</v>
+        <v>46114.61821071759</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>217</v>
@@ -5632,11 +5632,11 @@
         <v>229</v>
       </c>
       <c r="B65" s="8">
-        <v>46108.59046716435</v>
+        <v>46108.75713383102</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46183.01246226852</v>
+        <v>46183.17912893518</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>108</v>
@@ -5695,11 +5695,11 @@
         <v>232</v>
       </c>
       <c r="B66" s="5">
-        <v>46114.386456319444</v>
+        <v>46114.55312298611</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46114.45180700232</v>
+        <v>46114.61847366898</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>212</v>
@@ -5746,11 +5746,11 @@
         <v>233</v>
       </c>
       <c r="B67" s="8">
-        <v>46114.38657800926</v>
+        <v>46114.553244675924</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46114.45180384259</v>
+        <v>46114.61847050926</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>234</v>
@@ -5797,11 +5797,11 @@
         <v>235</v>
       </c>
       <c r="B68" s="5">
-        <v>46108.590472094904</v>
+        <v>46108.757138761575</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46114.46471738426</v>
+        <v>46114.631384050925</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>236</v>
@@ -5860,11 +5860,11 @@
         <v>240</v>
       </c>
       <c r="B69" s="8">
-        <v>46111.386135231485</v>
+        <v>46111.55280189815</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46114.46184366898</v>
+        <v>46114.62851033565</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>212</v>
@@ -5911,11 +5911,11 @@
         <v>242</v>
       </c>
       <c r="B70" s="5">
-        <v>46111.386185787036</v>
+        <v>46111.55285245371</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46114.46184373843</v>
+        <v>46114.62851040509</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>243</v>
@@ -5962,11 +5962,11 @@
         <v>245</v>
       </c>
       <c r="B71" s="8">
-        <v>46108.590475000005</v>
+        <v>46108.75714166666</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46118.378899930554</v>
+        <v>46118.545566597226</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>246</v>
@@ -6009,11 +6009,11 @@
         <v>248</v>
       </c>
       <c r="B72" s="5">
-        <v>46108.590477881946</v>
+        <v>46108.75714454861</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46118.38465878472</v>
+        <v>46118.55132545139</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>247</v>
@@ -6070,11 +6070,11 @@
         <v>252</v>
       </c>
       <c r="B73" s="8">
-        <v>46111.33692341435</v>
+        <v>46111.50359008102</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46114.452684918986</v>
+        <v>46114.61935158564</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>253</v>
@@ -6117,11 +6117,11 @@
         <v>255</v>
       </c>
       <c r="B74" s="5">
-        <v>46111.337379502314</v>
+        <v>46111.50404616898</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46114.46662025463</v>
+        <v>46114.63328692129</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>256</v>
@@ -6180,11 +6180,11 @@
         <v>260</v>
       </c>
       <c r="B75" s="8">
-        <v>46111.33739503472</v>
+        <v>46111.50406170139</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46114.46676979167</v>
+        <v>46114.63343645833</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>261</v>
@@ -6243,11 +6243,11 @@
         <v>263</v>
       </c>
       <c r="B76" s="5">
-        <v>46111.33877189815</v>
+        <v>46111.50543856481</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46114.45509847222</v>
+        <v>46114.62176513889</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>264</v>
@@ -6290,11 +6290,11 @@
         <v>266</v>
       </c>
       <c r="B77" s="8">
-        <v>46111.33882837963</v>
+        <v>46111.505495046295</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46114.4672025926</v>
+        <v>46114.633869259254</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>267</v>
@@ -6353,11 +6353,11 @@
         <v>271</v>
       </c>
       <c r="B78" s="5">
-        <v>46111.33893648148</v>
+        <v>46111.50560314815</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46114.46730556713</v>
+        <v>46114.6339722338</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>272</v>
@@ -6416,11 +6416,11 @@
         <v>273</v>
       </c>
       <c r="B79" s="8">
-        <v>46111.35966650463</v>
+        <v>46111.52633317129</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46114.46034972223</v>
+        <v>46114.627016388884</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>212</v>
@@ -6469,11 +6469,11 @@
         <v>276</v>
       </c>
       <c r="B80" s="5">
-        <v>46111.35997770833</v>
+        <v>46111.526644375</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46114.46035050926</v>
+        <v>46114.627017175924</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>217</v>
@@ -6522,11 +6522,11 @@
         <v>278</v>
       </c>
       <c r="B81" s="8">
-        <v>46111.33896791667</v>
+        <v>46111.50563458333</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46114.467399016205</v>
+        <v>46114.63406568287</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>279</v>
@@ -6585,11 +6585,11 @@
         <v>280</v>
       </c>
       <c r="B82" s="5">
-        <v>46111.36024980324</v>
+        <v>46111.526916469906</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46114.460489212965</v>
+        <v>46114.62715587963</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>212</v>
@@ -6638,11 +6638,11 @@
         <v>283</v>
       </c>
       <c r="B83" s="8">
-        <v>46111.360331620366</v>
+        <v>46111.52699828704</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46114.46049005787</v>
+        <v>46114.62715672454</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>217</v>
@@ -6691,11 +6691,11 @@
         <v>286</v>
       </c>
       <c r="B84" s="5">
-        <v>46108.590482175925</v>
+        <v>46108.75714884259</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46118.37890002315</v>
+        <v>46118.54556668982</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>287</v>
@@ -6738,11 +6738,11 @@
         <v>289</v>
       </c>
       <c r="B85" s="8">
-        <v>46108.59048576389</v>
+        <v>46108.75715243055</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46185.01829324074</v>
+        <v>46185.184959907405</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>290</v>
@@ -6801,11 +6801,11 @@
         <v>292</v>
       </c>
       <c r="B86" s="5">
-        <v>46108.59049106481</v>
+        <v>46108.75715773148</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46118.38559032408</v>
+        <v>46118.55225699074</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>57</v>
@@ -6864,11 +6864,11 @@
         <v>294</v>
       </c>
       <c r="B87" s="8">
-        <v>46108.59049682871</v>
+        <v>46108.75716349537</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46111.43095715278</v>
+        <v>46111.59762381944</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>295</v>
@@ -6927,11 +6927,11 @@
         <v>297</v>
       </c>
       <c r="B88" s="5">
-        <v>46108.59050208333</v>
+        <v>46108.75716875</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46111.43116314815</v>
+        <v>46111.59782981481</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>298</v>
@@ -6990,11 +6990,11 @@
         <v>299</v>
       </c>
       <c r="B89" s="8">
-        <v>46108.59050763889</v>
+        <v>46108.75717430556</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46154.7011133912</v>
+        <v>46154.86778005787</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>300</v>
@@ -7053,11 +7053,11 @@
         <v>301</v>
       </c>
       <c r="B90" s="5">
-        <v>46108.590512106486</v>
+        <v>46108.75717877314</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46118.37890193287</v>
+        <v>46118.54556859954</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>302</v>
@@ -7114,11 +7114,11 @@
         <v>304</v>
       </c>
       <c r="B91" s="8">
-        <v>46108.65537042824</v>
+        <v>46108.822037094906</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46185.01829278935</v>
+        <v>46185.18495945602</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>305</v>
@@ -7177,11 +7177,11 @@
         <v>307</v>
       </c>
       <c r="B92" s="5">
-        <v>46108.59051645834</v>
+        <v>46108.757183124995</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46114.45928084491</v>
+        <v>46114.62594751157</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>308</v>
@@ -7224,11 +7224,11 @@
         <v>310</v>
       </c>
       <c r="B93" s="8">
-        <v>46108.59051962963</v>
+        <v>46108.757186296294</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46114.46852113426</v>
+        <v>46114.63518780093</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>311</v>
@@ -7287,11 +7287,11 @@
         <v>312</v>
       </c>
       <c r="B94" s="5">
-        <v>46111.36053535879</v>
+        <v>46111.52720202546</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46118.37890077547</v>
+        <v>46118.545567442125</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>212</v>
@@ -7340,11 +7340,11 @@
         <v>315</v>
       </c>
       <c r="B95" s="8">
-        <v>46111.360671284725</v>
+        <v>46111.52733795139</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46118.37890146991</v>
+        <v>46118.54556813657</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>217</v>
@@ -7393,11 +7393,11 @@
         <v>318</v>
       </c>
       <c r="B96" s="5">
-        <v>46108.59054331019</v>
+        <v>46108.75720997685</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46114.46976324074</v>
+        <v>46114.636429907405</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>319</v>
@@ -7456,11 +7456,11 @@
         <v>320</v>
       </c>
       <c r="B97" s="8">
-        <v>46111.361234131946</v>
+        <v>46111.52790079861</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46114.46109891204</v>
+        <v>46114.627765578705</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>212</v>
@@ -7509,11 +7509,11 @@
         <v>323</v>
       </c>
       <c r="B98" s="5">
-        <v>46111.361294375005</v>
+        <v>46111.52796104166</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46114.4610996875</v>
+        <v>46114.62776635417</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>217</v>
@@ -7562,11 +7562,11 @@
         <v>326</v>
       </c>
       <c r="B99" s="8">
-        <v>46108.59053100694</v>
+        <v>46108.75719767361</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46114.469869988425</v>
+        <v>46114.63653665509</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>327</v>
@@ -7625,11 +7625,11 @@
         <v>328</v>
       </c>
       <c r="B100" s="5">
-        <v>46111.36089966435</v>
+        <v>46111.52756633102</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46118.37890564815</v>
+        <v>46118.54557231482</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>212</v>
@@ -7678,11 +7678,11 @@
         <v>331</v>
       </c>
       <c r="B101" s="8">
-        <v>46111.360955729164</v>
+        <v>46111.527622395835</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46118.37890216435</v>
+        <v>46118.54556883102</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>217</v>
@@ -7731,11 +7731,11 @@
         <v>334</v>
       </c>
       <c r="B102" s="5">
-        <v>46108.59053674768</v>
+        <v>46108.75720341435</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46114.47000480324</v>
+        <v>46114.63667146991</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>335</v>
@@ -7794,11 +7794,11 @@
         <v>336</v>
       </c>
       <c r="B103" s="8">
-        <v>46111.361091377315</v>
+        <v>46111.52775804398</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46118.37890427084</v>
+        <v>46118.545570937495</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>212</v>
@@ -7847,11 +7847,11 @@
         <v>338</v>
       </c>
       <c r="B104" s="5">
-        <v>46111.36114163195</v>
+        <v>46111.52780829861</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46118.37890494213</v>
+        <v>46118.545571608796</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>217</v>
@@ -7900,11 +7900,11 @@
         <v>340</v>
       </c>
       <c r="B105" s="8">
-        <v>46108.59052474537</v>
+        <v>46108.757191412034</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46114.47013482639</v>
+        <v>46114.636801493056</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>341</v>
@@ -7963,11 +7963,11 @@
         <v>342</v>
       </c>
       <c r="B106" s="5">
-        <v>46111.360779826384</v>
+        <v>46111.527446493055</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46118.378902881945</v>
+        <v>46118.545569548616</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>212</v>
@@ -8016,11 +8016,11 @@
         <v>345</v>
       </c>
       <c r="B107" s="8">
-        <v>46111.3607934375</v>
+        <v>46111.52746010417</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46118.37890357639</v>
+        <v>46118.545570243055</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>217</v>
@@ -8069,11 +8069,11 @@
         <v>348</v>
       </c>
       <c r="B108" s="5">
-        <v>46108.5905503588</v>
+        <v>46108.757217025464</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46114.47019792824</v>
+        <v>46114.63686459491</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>349</v>
@@ -8132,11 +8132,11 @@
         <v>350</v>
       </c>
       <c r="B109" s="8">
-        <v>46111.3613652662</v>
+        <v>46111.528031932874</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46114.46184315972</v>
+        <v>46114.62850982639</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>212</v>
@@ -8183,11 +8183,11 @@
         <v>352</v>
       </c>
       <c r="B110" s="5">
-        <v>46111.36144461806</v>
+        <v>46111.52811128472</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46114.46184398148</v>
+        <v>46114.62851064815</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>217</v>
@@ -8234,11 +8234,11 @@
         <v>354</v>
       </c>
       <c r="B111" s="8">
-        <v>46108.590609189814</v>
+        <v>46108.75727585648</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46114.47028635417</v>
+        <v>46114.63695302083</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>355</v>
@@ -8295,11 +8295,11 @@
         <v>357</v>
       </c>
       <c r="B112" s="5">
-        <v>46111.36151453704</v>
+        <v>46111.5281812037</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46114.461976701394</v>
+        <v>46114.62864336805</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>212</v>
@@ -8346,11 +8346,11 @@
         <v>359</v>
       </c>
       <c r="B113" s="8">
-        <v>46111.36159975694</v>
+        <v>46111.528266423615</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46114.461977430554</v>
+        <v>46114.62864409722</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>217</v>
@@ -8397,11 +8397,11 @@
         <v>361</v>
       </c>
       <c r="B114" s="5">
-        <v>46108.59061655092</v>
+        <v>46108.757283217594</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46114.4629612037</v>
+        <v>46114.62962787037</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>362</v>
@@ -8444,11 +8444,11 @@
         <v>364</v>
       </c>
       <c r="B115" s="8">
-        <v>46108.59062076389</v>
+        <v>46108.757287430555</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46114.47057226852</v>
+        <v>46114.63723893519</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>365</v>
@@ -8507,11 +8507,11 @@
         <v>369</v>
       </c>
       <c r="B116" s="5">
-        <v>46111.36179929398</v>
+        <v>46111.52846596065</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46114.46221721065</v>
+        <v>46114.62888387732</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>212</v>
@@ -8558,11 +8558,11 @@
         <v>371</v>
       </c>
       <c r="B117" s="8">
-        <v>46111.36185140046</v>
+        <v>46111.528518067134</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46114.46221803241</v>
+        <v>46114.62888469908</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>217</v>
@@ -8609,11 +8609,11 @@
         <v>373</v>
       </c>
       <c r="B118" s="5">
-        <v>46111.36454934027</v>
+        <v>46111.531216006944</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46114.462218761575</v>
+        <v>46114.62888542824</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>56</v>
@@ -8660,11 +8660,11 @@
         <v>375</v>
       </c>
       <c r="B119" s="8">
-        <v>46111.36462608796</v>
+        <v>46111.53129275463</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46114.46221949074</v>
+        <v>46114.62888615741</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>60</v>
@@ -8711,11 +8711,11 @@
         <v>377</v>
       </c>
       <c r="B120" s="5">
-        <v>46111.36468155093</v>
+        <v>46111.53134821759</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46114.46222025463</v>
+        <v>46114.628886921295</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>378</v>
@@ -8762,11 +8762,11 @@
         <v>380</v>
       </c>
       <c r="B121" s="8">
-        <v>46111.364732754635</v>
+        <v>46111.53139942129</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46114.46222100694</v>
+        <v>46114.62888767361</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>66</v>
@@ -8813,11 +8813,11 @@
         <v>382</v>
       </c>
       <c r="B122" s="5">
-        <v>46111.36677152778</v>
+        <v>46111.53343819444</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46114.46222177084</v>
+        <v>46114.628888437495</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>306</v>
@@ -8864,11 +8864,11 @@
         <v>384</v>
       </c>
       <c r="B123" s="8">
-        <v>46108.590626226855</v>
+        <v>46108.75729289352</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46114.47070795139</v>
+        <v>46114.637374618054</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>385</v>
@@ -8927,11 +8927,11 @@
         <v>387</v>
       </c>
       <c r="B124" s="5">
-        <v>46111.36190743056</v>
+        <v>46111.52857409722</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46114.46243561343</v>
+        <v>46114.629102280094</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>212</v>
@@ -8980,11 +8980,11 @@
         <v>389</v>
       </c>
       <c r="B125" s="8">
-        <v>46111.36200734954</v>
+        <v>46111.528674016205</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46114.462436354166</v>
+        <v>46114.62910302084</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>217</v>
@@ -9033,11 +9033,11 @@
         <v>391</v>
       </c>
       <c r="B126" s="5">
-        <v>46111.364885625</v>
+        <v>46111.531552291664</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46114.462437118054</v>
+        <v>46114.629103784726</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>56</v>
@@ -9086,11 +9086,11 @@
         <v>393</v>
       </c>
       <c r="B127" s="8">
-        <v>46111.36493667824</v>
+        <v>46111.531603344905</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46114.4624378588</v>
+        <v>46114.62910452546</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>60</v>
@@ -9139,11 +9139,11 @@
         <v>395</v>
       </c>
       <c r="B128" s="5">
-        <v>46111.36498171296</v>
+        <v>46111.531648379634</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46114.462438622686</v>
+        <v>46114.62910528935</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>378</v>
@@ -9192,11 +9192,11 @@
         <v>397</v>
       </c>
       <c r="B129" s="8">
-        <v>46111.36503925926</v>
+        <v>46111.531705925925</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46114.462439386574</v>
+        <v>46114.62910605324</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>66</v>
@@ -9245,11 +9245,11 @@
         <v>399</v>
       </c>
       <c r="B130" s="5">
-        <v>46111.36690346064</v>
+        <v>46111.533570127314</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46114.46244017361</v>
+        <v>46114.62910684028</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>306</v>
@@ -9298,11 +9298,11 @@
         <v>401</v>
       </c>
       <c r="B131" s="8">
-        <v>46108.590632638894</v>
+        <v>46108.75729930555</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46114.4708202662</v>
+        <v>46114.63748693287</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>402</v>
@@ -9361,11 +9361,11 @@
         <v>404</v>
       </c>
       <c r="B132" s="5">
-        <v>46111.362133206014</v>
+        <v>46111.528799872685</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46114.46264680555</v>
+        <v>46114.62931347222</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>212</v>
@@ -9412,11 +9412,11 @@
         <v>406</v>
       </c>
       <c r="B133" s="8">
-        <v>46111.36218512732</v>
+        <v>46111.52885179398</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46114.46264762731</v>
+        <v>46114.62931429398</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>217</v>
@@ -9463,11 +9463,11 @@
         <v>408</v>
       </c>
       <c r="B134" s="5">
-        <v>46111.365487731484</v>
+        <v>46111.53215439815</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46114.46264837963</v>
+        <v>46114.629315046295</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>56</v>
@@ -9514,11 +9514,11 @@
         <v>410</v>
       </c>
       <c r="B135" s="8">
-        <v>46111.365539756946</v>
+        <v>46111.53220642361</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46114.4626491088</v>
+        <v>46114.62931577546</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>60</v>
@@ -9565,11 +9565,11 @@
         <v>412</v>
       </c>
       <c r="B136" s="5">
-        <v>46111.36559162037</v>
+        <v>46111.532258287036</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46114.46264986111</v>
+        <v>46114.629316527775</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>378</v>
@@ -9616,11 +9616,11 @@
         <v>414</v>
       </c>
       <c r="B137" s="8">
-        <v>46111.36564334491</v>
+        <v>46111.53231001158</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46114.462650625</v>
+        <v>46114.62931729166</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>66</v>
@@ -9667,11 +9667,11 @@
         <v>416</v>
       </c>
       <c r="B138" s="5">
-        <v>46111.36701570602</v>
+        <v>46111.53368237268</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46114.462651388894</v>
+        <v>46114.62931805555</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>417</v>
@@ -9718,11 +9718,11 @@
         <v>419</v>
       </c>
       <c r="B139" s="8">
-        <v>46108.59063791667</v>
+        <v>46108.757304583334</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46114.47088356482</v>
+        <v>46114.63755023148</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>420</v>
@@ -9781,11 +9781,11 @@
         <v>422</v>
       </c>
       <c r="B140" s="5">
-        <v>46111.36227834491</v>
+        <v>46111.528945011574</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46114.66361440972</v>
+        <v>46114.830281076385</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>212</v>
@@ -9834,11 +9834,11 @@
         <v>424</v>
       </c>
       <c r="B141" s="8">
-        <v>46111.36234425926</v>
+        <v>46111.52901092592</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46114.663636122685</v>
+        <v>46114.830302789356</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>217</v>
@@ -9887,11 +9887,11 @@
         <v>425</v>
       </c>
       <c r="B142" s="5">
-        <v>46111.36580612269</v>
+        <v>46111.53247278935</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46114.66365253473</v>
+        <v>46114.830319201385</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>56</v>
@@ -9940,11 +9940,11 @@
         <v>426</v>
       </c>
       <c r="B143" s="8">
-        <v>46111.36586684028</v>
+        <v>46111.53253350694</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46114.66366907407</v>
+        <v>46114.83033574074</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>60</v>
@@ -9993,11 +9993,11 @@
         <v>427</v>
       </c>
       <c r="B144" s="5">
-        <v>46111.365971747684</v>
+        <v>46111.532638414355</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46114.66368572917</v>
+        <v>46114.83035239583</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>66</v>
@@ -10046,11 +10046,11 @@
         <v>428</v>
       </c>
       <c r="B145" s="8">
-        <v>46111.36591445602</v>
+        <v>46111.53258112269</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46114.66370447917</v>
+        <v>46114.83037114583</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>378</v>
@@ -10099,11 +10099,11 @@
         <v>429</v>
       </c>
       <c r="B146" s="5">
-        <v>46111.36718960648</v>
+        <v>46111.53385627315</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46114.663727604166</v>
+        <v>46114.83039427083</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>306</v>
@@ -10152,11 +10152,11 @@
         <v>430</v>
       </c>
       <c r="B147" s="8">
-        <v>46108.59064383102</v>
+        <v>46108.757310497684</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46114.46296130787</v>
+        <v>46114.62962797454</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>431</v>
@@ -10199,11 +10199,11 @@
         <v>433</v>
       </c>
       <c r="B148" s="5">
-        <v>46108.59064700232</v>
+        <v>46108.75731366898</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46114.470976944445</v>
+        <v>46114.63764361111</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>434</v>
@@ -10262,11 +10262,11 @@
         <v>437</v>
       </c>
       <c r="B149" s="8">
-        <v>46108.59065334491</v>
+        <v>46108.75732001157</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46119.58174862269</v>
+        <v>46119.74841528935</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>438</v>
@@ -10325,11 +10325,11 @@
         <v>440</v>
       </c>
       <c r="B150" s="5">
-        <v>46108.59066239583</v>
+        <v>46108.7573290625</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46114.462961701385</v>
+        <v>46114.62962836806</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>441</v>
@@ -10372,11 +10372,11 @@
         <v>443</v>
       </c>
       <c r="B151" s="8">
-        <v>46108.59066638889</v>
+        <v>46108.75733305556</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46119.581792349534</v>
+        <v>46119.748459016206</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>444</v>
@@ -10435,11 +10435,11 @@
         <v>446</v>
       </c>
       <c r="B152" s="5">
-        <v>46108.59067203704</v>
+        <v>46108.757338703705</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46119.58183587963</v>
+        <v>46119.748502546296</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>447</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -5467,7 +5467,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46182.18836730324</v>
+        <v>46189.16797456019</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>220</v>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46114.618214131944</v>
+        <v>46189.16802</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>212</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46114.61821071759</v>
+        <v>46189.16802199074</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>217</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -5636,7 +5636,7 @@
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46183.17912893518</v>
+        <v>46190.167973020834</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>108</v>
@@ -5699,7 +5699,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46114.61847366898</v>
+        <v>46190.16810163195</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>212</v>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46114.61847050926</v>
+        <v>46190.168103460644</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>234</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -5467,7 +5467,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46189.16797456019</v>
+        <v>46190.19261076389</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>220</v>
@@ -5514,8 +5514,8 @@
       <c r="S62" s="6">
         <v>0</v>
       </c>
-      <c r="T62" s="12" t="s">
-        <v>110</v>
+      <c r="T62" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U62" s="10" t="s">
         <v>54</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -5636,7 +5636,7 @@
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46190.167973020834</v>
+        <v>46191.171331157406</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>108</v>
@@ -5683,8 +5683,8 @@
       <c r="S65" s="9">
         <v>0</v>
       </c>
-      <c r="T65" s="12" t="s">
-        <v>110</v>
+      <c r="T65" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U65" s="10" t="s">
         <v>54</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -3415,7 +3415,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46185.17855736111</v>
+        <v>46192.16898982639</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3543,7 +3543,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46185.178555833336</v>
+        <v>46192.169004641204</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>115</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="447">
   <si>
     <t>50001525- ZITRON PERU METRO DE LIMA  ESTACION 07</t>
   </si>
@@ -341,9 +341,6 @@
   </si>
   <si>
     <t>Generación OC materiales ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213833777470493</t>
@@ -3415,7 +3412,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46192.16898982639</v>
+        <v>46193.195807870376</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3462,8 +3459,8 @@
       <c r="S28" s="6">
         <v>0</v>
       </c>
-      <c r="T28" s="12" t="s">
-        <v>110</v>
+      <c r="T28" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U28" s="12" t="s">
         <v>100</v>
@@ -3471,7 +3468,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B29" s="8">
         <v>46108.75690234954</v>
@@ -3483,7 +3480,7 @@
         <v>46123.19348805556</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3516,7 +3513,7 @@
         <v>78</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q29" s="8">
         <v>46121</v>
@@ -3536,17 +3533,17 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B30" s="5">
         <v>46108.75690841435</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46192.169004641204</v>
+        <v>46193.19580785879</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3579,7 +3576,7 @@
         <v>108</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q30" s="5">
         <v>46191</v>
@@ -3590,8 +3587,8 @@
       <c r="S30" s="6">
         <v>0</v>
       </c>
-      <c r="T30" s="12" t="s">
-        <v>110</v>
+      <c r="T30" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U30" s="12" t="s">
         <v>100</v>
@@ -3599,7 +3596,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B31" s="8">
         <v>46108.78647824074</v>
@@ -3644,7 +3641,7 @@
         <v>85</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q31" s="8">
         <v>46121</v>
@@ -3664,7 +3661,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B32" s="5">
         <v>46108.756741087964</v>
@@ -3674,7 +3671,7 @@
         <v>46154.867849305556</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>25</v>
@@ -3698,7 +3695,7 @@
         <v>26</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3711,7 +3708,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B33" s="8">
         <v>46108.75695274306</v>
@@ -3721,16 +3718,16 @@
         <v>46182.6933722338</v>
       </c>
       <c r="E33" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="F33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="9" t="s">
+      <c r="H33" s="9" t="s">
         <v>124</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>125</v>
       </c>
       <c r="I33" s="8">
         <v>46125</v>
@@ -3748,13 +3745,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q33" s="8">
         <v>46125</v>
@@ -3774,7 +3771,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B34" s="5">
         <v>46108.75695775463</v>
@@ -3786,16 +3783,16 @@
         <v>46182.69336725694</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I34" s="5">
         <v>46125</v>
@@ -3813,13 +3810,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>94</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Q34" s="5">
         <v>45985</v>
@@ -3839,7 +3836,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B35" s="8">
         <v>46108.75696342593</v>
@@ -3849,16 +3846,16 @@
         <v>46182.69337332176</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="H35" s="9" t="s">
         <v>124</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>125</v>
       </c>
       <c r="I35" s="8">
         <v>46127</v>
@@ -3876,13 +3873,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q35" s="8">
         <v>45987</v>
@@ -3902,7 +3899,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B36" s="5">
         <v>46108.75697314815</v>
@@ -3912,16 +3909,16 @@
         <v>46169.854331932875</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I36" s="5">
         <v>46125</v>
@@ -3939,13 +3936,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q36" s="5">
         <v>46125</v>
@@ -3965,7 +3962,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B37" s="8">
         <v>46108.75697796296</v>
@@ -3975,16 +3972,16 @@
         <v>46135.54608165509</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="H37" s="9" t="s">
         <v>124</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>125</v>
       </c>
       <c r="I37" s="8">
         <v>46125</v>
@@ -4002,13 +3999,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>102</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q37" s="8">
         <v>45979</v>
@@ -4028,7 +4025,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B38" s="5">
         <v>46108.7569835301</v>
@@ -4038,16 +4035,16 @@
         <v>46111.58202451389</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I38" s="5">
         <v>46134</v>
@@ -4065,13 +4062,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q38" s="5">
         <v>45988</v>
@@ -4089,7 +4086,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B39" s="8">
         <v>46108.75698832176</v>
@@ -4099,16 +4096,16 @@
         <v>46183.16750024306</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="H39" s="9" t="s">
         <v>124</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>125</v>
       </c>
       <c r="I39" s="8">
         <v>46125</v>
@@ -4126,13 +4123,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q39" s="8">
         <v>46125</v>
@@ -4152,7 +4149,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B40" s="5">
         <v>46108.75699311343</v>
@@ -4162,16 +4159,16 @@
         <v>46169.85054255787</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I40" s="5">
         <v>46125</v>
@@ -4189,13 +4186,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>97</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q40" s="5">
         <v>45985</v>
@@ -4215,7 +4212,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B41" s="8">
         <v>46108.75699847222</v>
@@ -4225,16 +4222,16 @@
         <v>46182.1679962037</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>124</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>125</v>
       </c>
       <c r="I41" s="8">
         <v>46127</v>
@@ -4252,13 +4249,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Q41" s="8">
         <v>45987</v>
@@ -4278,7 +4275,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B42" s="5">
         <v>46108.75700357639</v>
@@ -4288,16 +4285,16 @@
         <v>46182.693445439814</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I42" s="5">
         <v>46118</v>
@@ -4315,13 +4312,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q42" s="5">
         <v>46118</v>
@@ -4341,7 +4338,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B43" s="8">
         <v>46108.75700856482</v>
@@ -4353,16 +4350,16 @@
         <v>46182.69343975694</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="H43" s="9" t="s">
         <v>124</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>125</v>
       </c>
       <c r="I43" s="8">
         <v>46118</v>
@@ -4380,13 +4377,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>91</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q43" s="8">
         <v>45978</v>
@@ -4406,7 +4403,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B44" s="5">
         <v>46108.757016435186</v>
@@ -4416,16 +4413,16 @@
         <v>46182.69344646991</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I44" s="5">
         <v>46139</v>
@@ -4443,13 +4440,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q44" s="5">
         <v>45999</v>
@@ -4469,7 +4466,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B45" s="8">
         <v>46108.7570218287</v>
@@ -4479,16 +4476,16 @@
         <v>46182.69344736111</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="H45" s="9" t="s">
         <v>124</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>125</v>
       </c>
       <c r="I45" s="8">
         <v>46139</v>
@@ -4506,13 +4503,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q45" s="8">
         <v>45999</v>
@@ -4532,7 +4529,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B46" s="5">
         <v>46108.75702719907</v>
@@ -4542,16 +4539,16 @@
         <v>46169.850810324075</v>
       </c>
       <c r="E46" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="6" t="s">
+      <c r="H46" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>166</v>
       </c>
       <c r="I46" s="5">
         <v>46195</v>
@@ -4569,13 +4566,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q46" s="5">
         <v>46195</v>
@@ -4595,7 +4592,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B47" s="8">
         <v>46108.75703201389</v>
@@ -4611,10 +4608,10 @@
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H47" s="9" t="s">
         <v>165</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>166</v>
       </c>
       <c r="I47" s="8">
         <v>46195</v>
@@ -4632,13 +4629,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>105</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q47" s="8">
         <v>45985</v>
@@ -4658,7 +4655,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B48" s="5">
         <v>46108.75703761574</v>
@@ -4668,16 +4665,16 @@
         <v>46169.850767233795</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>166</v>
       </c>
       <c r="I48" s="5">
         <v>46202</v>
@@ -4695,13 +4692,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>109</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q48" s="5">
         <v>46007</v>
@@ -4721,7 +4718,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B49" s="8">
         <v>46108.75704306713</v>
@@ -4733,16 +4730,16 @@
         <v>46154.86784422454</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H49" s="9" t="s">
         <v>165</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>166</v>
       </c>
       <c r="I49" s="8">
         <v>46125</v>
@@ -4760,13 +4757,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q49" s="8">
         <v>46125</v>
@@ -4786,7 +4783,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B50" s="5">
         <v>46108.75705032407</v>
@@ -4798,16 +4795,16 @@
         <v>46154.86746811343</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>166</v>
       </c>
       <c r="I50" s="5">
         <v>46125</v>
@@ -4825,13 +4822,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4841,7 +4838,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B51" s="8">
         <v>46108.75705728009</v>
@@ -4853,16 +4850,16 @@
         <v>46154.8677641088</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>165</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>166</v>
       </c>
       <c r="I51" s="8">
         <v>46135</v>
@@ -4880,13 +4877,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4896,7 +4893,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B52" s="5">
         <v>46108.757061435186</v>
@@ -4906,16 +4903,16 @@
         <v>46169.85242414352</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
+      <c r="H52" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I52" s="5">
         <v>46195</v>
@@ -4933,13 +4930,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q52" s="5">
         <v>46195</v>
@@ -4959,7 +4956,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B53" s="8">
         <v>46108.75710696759</v>
@@ -4969,16 +4966,16 @@
         <v>46169.85239162037</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="H53" s="9" t="s">
         <v>184</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>185</v>
       </c>
       <c r="I53" s="8">
         <v>46195</v>
@@ -4996,13 +4993,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5018,7 +5015,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B54" s="5">
         <v>46108.757112928244</v>
@@ -5028,16 +5025,16 @@
         <v>46169.85241099537</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I54" s="5">
         <v>46210</v>
@@ -5055,13 +5052,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O54" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="P54" s="6" t="s">
         <v>191</v>
-      </c>
-      <c r="P54" s="6" t="s">
-        <v>192</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5071,7 +5068,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B55" s="8">
         <v>46111.50860645833</v>
@@ -5083,16 +5080,16 @@
         <v>46182.69406362269</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="H55" s="9" t="s">
         <v>124</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>125</v>
       </c>
       <c r="I55" s="8">
         <v>46125</v>
@@ -5110,10 +5107,10 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5136,7 +5133,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B56" s="5">
         <v>46111.508755937495</v>
@@ -5148,16 +5145,16 @@
         <v>46182.69350877315</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I56" s="5">
         <v>46125</v>
@@ -5175,13 +5172,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>86</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5191,7 +5188,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B57" s="8">
         <v>46111.508846770834</v>
@@ -5203,16 +5200,16 @@
         <v>46182.69403748843</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>124</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>125</v>
       </c>
       <c r="I57" s="8">
         <v>46132</v>
@@ -5230,13 +5227,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5246,7 +5243,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B58" s="5">
         <v>46108.75711900463</v>
@@ -5256,7 +5253,7 @@
         <v>46141.52778395833</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -5280,7 +5277,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5293,7 +5290,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B59" s="8">
         <v>46108.75712325232</v>
@@ -5303,16 +5300,16 @@
         <v>46141.52778434027</v>
       </c>
       <c r="E59" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="F59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="9" t="s">
+      <c r="H59" s="9" t="s">
         <v>207</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>208</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="8">
@@ -5328,13 +5325,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O59" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="P59" s="9" t="s">
         <v>209</v>
-      </c>
-      <c r="P59" s="9" t="s">
-        <v>210</v>
       </c>
       <c r="Q59" s="8">
         <v>46121</v>
@@ -5354,7 +5351,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B60" s="5">
         <v>46114.552579166666</v>
@@ -5364,16 +5361,16 @@
         <v>46127.171562662035</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
+      <c r="H60" s="6" t="s">
         <v>213</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>214</v>
       </c>
       <c r="I60" s="5">
         <v>46121</v>
@@ -5391,13 +5388,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5407,7 +5404,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B61" s="8">
         <v>46114.552773240735</v>
@@ -5417,16 +5414,16 @@
         <v>46127.17156420139</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>213</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>214</v>
       </c>
       <c r="I61" s="8">
         <v>46121</v>
@@ -5444,13 +5441,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>78</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5460,7 +5457,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B62" s="5">
         <v>46108.75712855324</v>
@@ -5470,16 +5467,16 @@
         <v>46190.19261076389</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>207</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>208</v>
       </c>
       <c r="I62" s="5">
         <v>46183</v>
@@ -5497,13 +5494,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O62" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="P62" s="6" t="s">
         <v>221</v>
-      </c>
-      <c r="P62" s="6" t="s">
-        <v>222</v>
       </c>
       <c r="Q62" s="5">
         <v>46183</v>
@@ -5523,7 +5520,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B63" s="8">
         <v>46114.55286452547</v>
@@ -5533,16 +5530,16 @@
         <v>46189.16802</v>
       </c>
       <c r="E63" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="F63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="9" t="s">
+      <c r="H63" s="9" t="s">
         <v>213</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>214</v>
       </c>
       <c r="I63" s="8">
         <v>46183</v>
@@ -5560,13 +5557,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O63" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="P63" s="9" t="s">
         <v>224</v>
-      </c>
-      <c r="P63" s="9" t="s">
-        <v>225</v>
       </c>
       <c r="Q63" s="9"/>
       <c r="R63" s="9"/>
@@ -5576,7 +5573,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B64" s="5">
         <v>46114.552966620366</v>
@@ -5586,16 +5583,16 @@
         <v>46189.16802199074</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>213</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>214</v>
       </c>
       <c r="I64" s="5">
         <v>46183</v>
@@ -5613,13 +5610,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O64" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>227</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>228</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5629,7 +5626,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B65" s="8">
         <v>46108.75713383102</v>
@@ -5645,10 +5642,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>213</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>214</v>
       </c>
       <c r="I65" s="8">
         <v>46190</v>
@@ -5666,13 +5663,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O65" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="P65" s="9" t="s">
         <v>230</v>
-      </c>
-      <c r="P65" s="9" t="s">
-        <v>231</v>
       </c>
       <c r="Q65" s="8">
         <v>46190</v>
@@ -5692,7 +5689,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B66" s="5">
         <v>46114.55312298611</v>
@@ -5702,16 +5699,16 @@
         <v>46190.16810163195</v>
       </c>
       <c r="E66" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G66" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="F66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G66" s="6" t="s">
+      <c r="H66" s="6" t="s">
         <v>213</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>214</v>
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="5">
@@ -5730,7 +5727,7 @@
         <v>108</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5743,7 +5740,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B67" s="8">
         <v>46114.553244675924</v>
@@ -5753,16 +5750,16 @@
         <v>46190.168103460644</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>213</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>214</v>
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="8">
@@ -5781,7 +5778,7 @@
         <v>108</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>26</v>
@@ -5794,7 +5791,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B68" s="5">
         <v>46108.757138761575</v>
@@ -5804,16 +5801,16 @@
         <v>46114.631384050925</v>
       </c>
       <c r="E68" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G68" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="F68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G68" s="6" t="s">
+      <c r="H68" s="6" t="s">
         <v>237</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>238</v>
       </c>
       <c r="I68" s="5">
         <v>46281</v>
@@ -5831,10 +5828,10 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5857,7 +5854,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B69" s="8">
         <v>46111.55280189815</v>
@@ -5867,16 +5864,16 @@
         <v>46114.62851033565</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -5892,13 +5889,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5908,7 +5905,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B70" s="5">
         <v>46111.55285245371</v>
@@ -5918,16 +5915,16 @@
         <v>46114.62851040509</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>237</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>238</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -5943,13 +5940,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5959,7 +5956,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B71" s="8">
         <v>46108.75714166666</v>
@@ -5969,7 +5966,7 @@
         <v>46118.545566597226</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -5993,7 +5990,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -6006,7 +6003,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B72" s="5">
         <v>46108.75714454861</v>
@@ -6016,16 +6013,16 @@
         <v>46118.55132545139</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -6041,13 +6038,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Q72" s="5">
         <v>46231</v>
@@ -6067,7 +6064,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B73" s="8">
         <v>46111.50359008102</v>
@@ -6077,7 +6074,7 @@
         <v>46114.61935158564</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -6101,7 +6098,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -6114,7 +6111,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B74" s="5">
         <v>46111.50404616898</v>
@@ -6124,16 +6121,16 @@
         <v>46114.63328692129</v>
       </c>
       <c r="E74" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G74" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="F74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G74" s="6" t="s">
+      <c r="H74" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I74" s="5">
         <v>46211</v>
@@ -6151,13 +6148,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q74" s="5">
         <v>46211</v>
@@ -6177,7 +6174,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B75" s="8">
         <v>46111.50406170139</v>
@@ -6187,16 +6184,16 @@
         <v>46114.63343645833</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="H75" s="9" t="s">
         <v>249</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>250</v>
       </c>
       <c r="I75" s="8">
         <v>46213</v>
@@ -6214,13 +6211,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q75" s="8">
         <v>46213</v>
@@ -6240,7 +6237,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B76" s="5">
         <v>46111.50543856481</v>
@@ -6250,7 +6247,7 @@
         <v>46114.62176513889</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -6274,7 +6271,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -6287,7 +6284,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B77" s="8">
         <v>46111.505495046295</v>
@@ -6297,16 +6294,16 @@
         <v>46114.633869259254</v>
       </c>
       <c r="E77" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G77" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="F77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G77" s="9" t="s">
+      <c r="H77" s="9" t="s">
         <v>268</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>269</v>
       </c>
       <c r="I77" s="8">
         <v>46217</v>
@@ -6324,13 +6321,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q77" s="8">
         <v>46217</v>
@@ -6350,7 +6347,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B78" s="5">
         <v>46111.50560314815</v>
@@ -6360,16 +6357,16 @@
         <v>46114.6339722338</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="I78" s="5">
         <v>46226</v>
@@ -6387,13 +6384,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q78" s="5">
         <v>46226</v>
@@ -6413,7 +6410,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B79" s="8">
         <v>46111.52633317129</v>
@@ -6423,16 +6420,16 @@
         <v>46114.627016388884</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="H79" s="9" t="s">
         <v>268</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>269</v>
       </c>
       <c r="I79" s="8">
         <v>46226</v>
@@ -6450,13 +6447,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O79" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="P79" s="9" t="s">
         <v>274</v>
-      </c>
-      <c r="P79" s="9" t="s">
-        <v>275</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6466,7 +6463,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B80" s="5">
         <v>46111.526644375</v>
@@ -6476,16 +6473,16 @@
         <v>46114.627017175924</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="I80" s="5">
         <v>46226</v>
@@ -6503,13 +6500,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6519,7 +6516,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B81" s="8">
         <v>46111.50563458333</v>
@@ -6529,16 +6526,16 @@
         <v>46114.63406568287</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="H81" s="9" t="s">
         <v>249</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>250</v>
       </c>
       <c r="I81" s="8">
         <v>46246</v>
@@ -6556,13 +6553,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q81" s="8">
         <v>46246</v>
@@ -6582,7 +6579,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B82" s="5">
         <v>46111.526916469906</v>
@@ -6592,16 +6589,16 @@
         <v>46114.62715587963</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I82" s="5">
         <v>46246</v>
@@ -6619,13 +6616,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O82" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="P82" s="6" t="s">
         <v>281</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>282</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6635,7 +6632,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B83" s="8">
         <v>46111.52699828704</v>
@@ -6645,16 +6642,16 @@
         <v>46114.62715672454</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="H83" s="9" t="s">
         <v>249</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>250</v>
       </c>
       <c r="I83" s="8">
         <v>46246</v>
@@ -6672,13 +6669,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O83" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="P83" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="P83" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6688,7 +6685,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B84" s="5">
         <v>46108.75714884259</v>
@@ -6698,7 +6695,7 @@
         <v>46118.54556668982</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -6722,7 +6719,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6735,7 +6732,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B85" s="8">
         <v>46108.75715243055</v>
@@ -6745,16 +6742,16 @@
         <v>46185.184959907405</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="H85" s="9" t="s">
         <v>257</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>258</v>
       </c>
       <c r="I85" s="8">
         <v>46183</v>
@@ -6772,13 +6769,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q85" s="8">
         <v>46183</v>
@@ -6798,7 +6795,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B86" s="5">
         <v>46108.75715773148</v>
@@ -6814,10 +6811,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I86" s="5">
         <v>46239</v>
@@ -6835,13 +6832,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q86" s="5">
         <v>46239</v>
@@ -6861,7 +6858,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B87" s="8">
         <v>46108.75716349537</v>
@@ -6871,16 +6868,16 @@
         <v>46111.59762381944</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="H87" s="9" t="s">
         <v>257</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>258</v>
       </c>
       <c r="I87" s="8">
         <v>46246</v>
@@ -6898,13 +6895,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q87" s="8">
         <v>46246</v>
@@ -6924,7 +6921,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B88" s="5">
         <v>46108.75716875</v>
@@ -6934,16 +6931,16 @@
         <v>46111.59782981481</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I88" s="5">
         <v>46273</v>
@@ -6961,13 +6958,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q88" s="5">
         <v>46273</v>
@@ -6987,7 +6984,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B89" s="8">
         <v>46108.75717430556</v>
@@ -6997,16 +6994,16 @@
         <v>46154.86778005787</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="H89" s="9" t="s">
         <v>257</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>258</v>
       </c>
       <c r="I89" s="8">
         <v>46220</v>
@@ -7024,13 +7021,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q89" s="8">
         <v>46220</v>
@@ -7050,7 +7047,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B90" s="5">
         <v>46108.75717877314</v>
@@ -7060,16 +7057,16 @@
         <v>46118.54556859954</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
@@ -7085,13 +7082,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Q90" s="5">
         <v>46231</v>
@@ -7111,7 +7108,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B91" s="8">
         <v>46108.822037094906</v>
@@ -7121,16 +7118,16 @@
         <v>46185.18495945602</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="H91" s="9" t="s">
         <v>257</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>258</v>
       </c>
       <c r="I91" s="8">
         <v>46181</v>
@@ -7148,13 +7145,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q91" s="8">
         <v>46183</v>
@@ -7174,7 +7171,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B92" s="5">
         <v>46108.757183124995</v>
@@ -7184,7 +7181,7 @@
         <v>46114.62594751157</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>25</v>
@@ -7208,7 +7205,7 @@
         <v>26</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>26</v>
@@ -7221,7 +7218,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B93" s="8">
         <v>46108.757186296294</v>
@@ -7231,7 +7228,7 @@
         <v>46114.63518780093</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7258,13 +7255,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q93" s="8">
         <v>46248</v>
@@ -7284,7 +7281,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B94" s="5">
         <v>46111.52720202546</v>
@@ -7294,7 +7291,7 @@
         <v>46118.545567442125</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7321,13 +7318,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="O94" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="P94" s="6" t="s">
         <v>313</v>
-      </c>
-      <c r="P94" s="6" t="s">
-        <v>314</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7337,7 +7334,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B95" s="8">
         <v>46111.52733795139</v>
@@ -7347,7 +7344,7 @@
         <v>46118.54556813657</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7374,13 +7371,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="O95" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="P95" s="9" t="s">
         <v>316</v>
-      </c>
-      <c r="P95" s="9" t="s">
-        <v>317</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7390,7 +7387,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B96" s="5">
         <v>46108.75720997685</v>
@@ -7400,7 +7397,7 @@
         <v>46114.636429907405</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7427,13 +7424,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q96" s="5">
         <v>46268</v>
@@ -7453,7 +7450,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B97" s="8">
         <v>46111.52790079861</v>
@@ -7463,7 +7460,7 @@
         <v>46114.627765578705</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7490,13 +7487,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O97" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="P97" s="9" t="s">
         <v>321</v>
-      </c>
-      <c r="P97" s="9" t="s">
-        <v>322</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7506,7 +7503,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B98" s="5">
         <v>46111.52796104166</v>
@@ -7516,7 +7513,7 @@
         <v>46114.62776635417</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7543,13 +7540,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O98" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="P98" s="6" t="s">
         <v>324</v>
-      </c>
-      <c r="P98" s="6" t="s">
-        <v>325</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7559,7 +7556,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B99" s="8">
         <v>46108.75719767361</v>
@@ -7569,7 +7566,7 @@
         <v>46114.63653665509</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7596,13 +7593,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q99" s="8">
         <v>46272</v>
@@ -7622,7 +7619,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B100" s="5">
         <v>46111.52756633102</v>
@@ -7632,7 +7629,7 @@
         <v>46118.54557231482</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7659,13 +7656,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O100" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="P100" s="6" t="s">
         <v>329</v>
-      </c>
-      <c r="P100" s="6" t="s">
-        <v>330</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7675,7 +7672,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B101" s="8">
         <v>46111.527622395835</v>
@@ -7685,7 +7682,7 @@
         <v>46118.54556883102</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7712,13 +7709,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O101" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="P101" s="9" t="s">
         <v>332</v>
-      </c>
-      <c r="P101" s="9" t="s">
-        <v>333</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7728,7 +7725,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B102" s="5">
         <v>46108.75720341435</v>
@@ -7738,7 +7735,7 @@
         <v>46114.63667146991</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7765,13 +7762,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q102" s="5">
         <v>46274</v>
@@ -7791,7 +7788,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B103" s="8">
         <v>46111.52775804398</v>
@@ -7801,7 +7798,7 @@
         <v>46118.545570937495</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7828,13 +7825,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -7844,7 +7841,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B104" s="5">
         <v>46111.52780829861</v>
@@ -7854,7 +7851,7 @@
         <v>46118.545571608796</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7881,13 +7878,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7897,7 +7894,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B105" s="8">
         <v>46108.757191412034</v>
@@ -7907,7 +7904,7 @@
         <v>46114.636801493056</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -7934,13 +7931,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q105" s="8">
         <v>46276</v>
@@ -7960,7 +7957,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B106" s="5">
         <v>46111.527446493055</v>
@@ -7970,7 +7967,7 @@
         <v>46118.545569548616</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7997,13 +7994,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="O106" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="P106" s="6" t="s">
         <v>343</v>
-      </c>
-      <c r="P106" s="6" t="s">
-        <v>344</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8013,7 +8010,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B107" s="8">
         <v>46111.52746010417</v>
@@ -8023,7 +8020,7 @@
         <v>46118.545570243055</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -8050,13 +8047,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="O107" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="P107" s="9" t="s">
         <v>346</v>
-      </c>
-      <c r="P107" s="9" t="s">
-        <v>347</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -8066,7 +8063,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B108" s="5">
         <v>46108.757217025464</v>
@@ -8076,7 +8073,7 @@
         <v>46114.63686459491</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8103,13 +8100,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q108" s="5">
         <v>46280</v>
@@ -8129,7 +8126,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B109" s="8">
         <v>46111.528031932874</v>
@@ -8139,7 +8136,7 @@
         <v>46114.62850982639</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8164,13 +8161,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8180,7 +8177,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B110" s="5">
         <v>46111.52811128472</v>
@@ -8190,7 +8187,7 @@
         <v>46114.62851064815</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8215,13 +8212,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8231,7 +8228,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B111" s="8">
         <v>46108.75727585648</v>
@@ -8241,7 +8238,7 @@
         <v>46114.63695302083</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8266,13 +8263,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q111" s="8">
         <v>46286</v>
@@ -8292,7 +8289,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B112" s="5">
         <v>46111.5281812037</v>
@@ -8302,7 +8299,7 @@
         <v>46114.62864336805</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8327,13 +8324,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8343,7 +8340,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B113" s="8">
         <v>46111.528266423615</v>
@@ -8353,7 +8350,7 @@
         <v>46114.62864409722</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8378,13 +8375,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8394,7 +8391,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B114" s="5">
         <v>46108.757283217594</v>
@@ -8404,7 +8401,7 @@
         <v>46114.62962787037</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>25</v>
@@ -8428,7 +8425,7 @@
         <v>26</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>26</v>
@@ -8441,7 +8438,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B115" s="8">
         <v>46108.757287430555</v>
@@ -8451,16 +8448,16 @@
         <v>46114.63723893519</v>
       </c>
       <c r="E115" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="F115" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G115" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="F115" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G115" s="9" t="s">
+      <c r="H115" s="9" t="s">
         <v>366</v>
-      </c>
-      <c r="H115" s="9" t="s">
-        <v>367</v>
       </c>
       <c r="I115" s="8">
         <v>46287</v>
@@ -8478,13 +8475,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="Q115" s="8">
         <v>46287</v>
@@ -8504,7 +8501,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B116" s="5">
         <v>46111.52846596065</v>
@@ -8514,16 +8511,16 @@
         <v>46114.62888387732</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="H116" s="6" t="s">
         <v>366</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>367</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8539,13 +8536,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8555,7 +8552,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B117" s="8">
         <v>46111.528518067134</v>
@@ -8565,16 +8562,16 @@
         <v>46114.62888469908</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="H117" s="9" t="s">
         <v>366</v>
-      </c>
-      <c r="H117" s="9" t="s">
-        <v>367</v>
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="8">
@@ -8590,13 +8587,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8606,7 +8603,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B118" s="5">
         <v>46111.531216006944</v>
@@ -8622,10 +8619,10 @@
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="H118" s="6" t="s">
         <v>366</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>367</v>
       </c>
       <c r="I118" s="6"/>
       <c r="J118" s="5">
@@ -8641,13 +8638,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8657,7 +8654,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B119" s="8">
         <v>46111.53129275463</v>
@@ -8673,10 +8670,10 @@
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="H119" s="9" t="s">
         <v>366</v>
-      </c>
-      <c r="H119" s="9" t="s">
-        <v>367</v>
       </c>
       <c r="I119" s="9"/>
       <c r="J119" s="8">
@@ -8692,13 +8689,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="O119" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8708,7 +8705,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B120" s="5">
         <v>46111.53134821759</v>
@@ -8718,16 +8715,16 @@
         <v>46114.628886921295</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="H120" s="6" t="s">
         <v>366</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>367</v>
       </c>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
@@ -8743,13 +8740,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8759,7 +8756,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B121" s="8">
         <v>46111.53139942129</v>
@@ -8775,10 +8772,10 @@
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="H121" s="9" t="s">
         <v>366</v>
-      </c>
-      <c r="H121" s="9" t="s">
-        <v>367</v>
       </c>
       <c r="I121" s="9"/>
       <c r="J121" s="8">
@@ -8794,13 +8791,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="O121" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8810,7 +8807,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B122" s="5">
         <v>46111.53343819444</v>
@@ -8820,16 +8817,16 @@
         <v>46114.628888437495</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="H122" s="6" t="s">
         <v>366</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>367</v>
       </c>
       <c r="I122" s="6"/>
       <c r="J122" s="5">
@@ -8845,13 +8842,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8861,7 +8858,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B123" s="8">
         <v>46108.75729289352</v>
@@ -8871,7 +8868,7 @@
         <v>46114.637374618054</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -8898,13 +8895,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="Q123" s="8">
         <v>46288</v>
@@ -8924,7 +8921,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B124" s="5">
         <v>46111.52857409722</v>
@@ -8934,7 +8931,7 @@
         <v>46114.629102280094</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8961,13 +8958,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8977,7 +8974,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B125" s="8">
         <v>46111.528674016205</v>
@@ -8987,7 +8984,7 @@
         <v>46114.62910302084</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -9014,13 +9011,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -9030,7 +9027,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B126" s="5">
         <v>46111.531552291664</v>
@@ -9067,13 +9064,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9083,7 +9080,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B127" s="8">
         <v>46111.531603344905</v>
@@ -9120,13 +9117,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="O127" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9136,7 +9133,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B128" s="5">
         <v>46111.531648379634</v>
@@ -9146,7 +9143,7 @@
         <v>46114.62910528935</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9173,13 +9170,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9189,7 +9186,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B129" s="8">
         <v>46111.531705925925</v>
@@ -9226,13 +9223,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="O129" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9242,7 +9239,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B130" s="5">
         <v>46111.533570127314</v>
@@ -9252,7 +9249,7 @@
         <v>46114.62910684028</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9279,13 +9276,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9295,7 +9292,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B131" s="8">
         <v>46108.75729930555</v>
@@ -9305,16 +9302,16 @@
         <v>46114.63748693287</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="H131" s="9" t="s">
         <v>268</v>
-      </c>
-      <c r="H131" s="9" t="s">
-        <v>269</v>
       </c>
       <c r="I131" s="8">
         <v>46293</v>
@@ -9332,13 +9329,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="Q131" s="8">
         <v>46293</v>
@@ -9358,7 +9355,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B132" s="5">
         <v>46111.528799872685</v>
@@ -9368,16 +9365,16 @@
         <v>46114.62931347222</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="H132" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9393,13 +9390,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9409,7 +9406,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B133" s="8">
         <v>46111.52885179398</v>
@@ -9419,16 +9416,16 @@
         <v>46114.62931429398</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="H133" s="9" t="s">
         <v>268</v>
-      </c>
-      <c r="H133" s="9" t="s">
-        <v>269</v>
       </c>
       <c r="I133" s="9"/>
       <c r="J133" s="8">
@@ -9444,13 +9441,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9460,7 +9457,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B134" s="5">
         <v>46111.53215439815</v>
@@ -9476,10 +9473,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="H134" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9495,13 +9492,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9511,7 +9508,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B135" s="8">
         <v>46111.53220642361</v>
@@ -9527,10 +9524,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="H135" s="9" t="s">
         <v>268</v>
-      </c>
-      <c r="H135" s="9" t="s">
-        <v>269</v>
       </c>
       <c r="I135" s="9"/>
       <c r="J135" s="8">
@@ -9546,13 +9543,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="O135" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9562,7 +9559,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B136" s="5">
         <v>46111.532258287036</v>
@@ -9572,16 +9569,16 @@
         <v>46114.629316527775</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="H136" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="H136" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9597,13 +9594,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9613,7 +9610,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B137" s="8">
         <v>46111.53231001158</v>
@@ -9629,10 +9626,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="H137" s="9" t="s">
         <v>268</v>
-      </c>
-      <c r="H137" s="9" t="s">
-        <v>269</v>
       </c>
       <c r="I137" s="9"/>
       <c r="J137" s="8">
@@ -9648,13 +9645,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="O137" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -9664,7 +9661,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B138" s="5">
         <v>46111.53368237268</v>
@@ -9674,16 +9671,16 @@
         <v>46114.62931805555</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="H138" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="H138" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
@@ -9699,13 +9696,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9715,7 +9712,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B139" s="8">
         <v>46108.757304583334</v>
@@ -9725,16 +9722,16 @@
         <v>46114.63755023148</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="H139" s="9" t="s">
         <v>268</v>
-      </c>
-      <c r="H139" s="9" t="s">
-        <v>269</v>
       </c>
       <c r="I139" s="8">
         <v>46294</v>
@@ -9752,13 +9749,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="Q139" s="8">
         <v>46294</v>
@@ -9778,7 +9775,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B140" s="5">
         <v>46111.528945011574</v>
@@ -9788,16 +9785,16 @@
         <v>46114.830281076385</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="H140" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="I140" s="5">
         <v>46294</v>
@@ -9815,13 +9812,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9831,7 +9828,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B141" s="8">
         <v>46111.52901092592</v>
@@ -9841,16 +9838,16 @@
         <v>46114.830302789356</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="H141" s="9" t="s">
         <v>268</v>
-      </c>
-      <c r="H141" s="9" t="s">
-        <v>269</v>
       </c>
       <c r="I141" s="8">
         <v>46294</v>
@@ -9868,13 +9865,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -9884,7 +9881,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B142" s="5">
         <v>46111.53247278935</v>
@@ -9900,10 +9897,10 @@
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="H142" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="H142" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="I142" s="5">
         <v>46294</v>
@@ -9921,13 +9918,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9937,7 +9934,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B143" s="8">
         <v>46111.53253350694</v>
@@ -9953,10 +9950,10 @@
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="H143" s="9" t="s">
         <v>268</v>
-      </c>
-      <c r="H143" s="9" t="s">
-        <v>269</v>
       </c>
       <c r="I143" s="8">
         <v>46294</v>
@@ -9974,13 +9971,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="O143" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -9990,7 +9987,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B144" s="5">
         <v>46111.532638414355</v>
@@ -10006,10 +10003,10 @@
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="H144" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="H144" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="I144" s="5">
         <v>46294</v>
@@ -10027,13 +10024,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10043,7 +10040,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B145" s="8">
         <v>46111.53258112269</v>
@@ -10053,16 +10050,16 @@
         <v>46114.83037114583</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="H145" s="9" t="s">
         <v>268</v>
-      </c>
-      <c r="H145" s="9" t="s">
-        <v>269</v>
       </c>
       <c r="I145" s="8">
         <v>46294</v>
@@ -10080,13 +10077,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -10096,7 +10093,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B146" s="5">
         <v>46111.53385627315</v>
@@ -10106,16 +10103,16 @@
         <v>46114.83039427083</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="H146" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="H146" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="I146" s="5">
         <v>46294</v>
@@ -10133,13 +10130,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10149,7 +10146,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B147" s="8">
         <v>46108.757310497684</v>
@@ -10159,7 +10156,7 @@
         <v>46114.62962797454</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>25</v>
@@ -10183,7 +10180,7 @@
         <v>26</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="P147" s="9" t="s">
         <v>26</v>
@@ -10196,7 +10193,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B148" s="5">
         <v>46108.75731366898</v>
@@ -10206,16 +10203,16 @@
         <v>46114.63764361111</v>
       </c>
       <c r="E148" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="F148" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G148" s="6" t="s">
         <v>434</v>
       </c>
-      <c r="F148" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G148" s="6" t="s">
+      <c r="H148" s="6" t="s">
         <v>435</v>
-      </c>
-      <c r="H148" s="6" t="s">
-        <v>436</v>
       </c>
       <c r="I148" s="5">
         <v>46295</v>
@@ -10233,13 +10230,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="Q148" s="5">
         <v>46295</v>
@@ -10259,7 +10256,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B149" s="8">
         <v>46108.75732001157</v>
@@ -10269,16 +10266,16 @@
         <v>46119.74841528935</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="H149" s="9" t="s">
         <v>435</v>
-      </c>
-      <c r="H149" s="9" t="s">
-        <v>436</v>
       </c>
       <c r="I149" s="8">
         <v>46295</v>
@@ -10296,13 +10293,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="Q149" s="8">
         <v>46295</v>
@@ -10322,7 +10319,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B150" s="5">
         <v>46108.7573290625</v>
@@ -10332,7 +10329,7 @@
         <v>46114.62962836806</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>25</v>
@@ -10356,7 +10353,7 @@
         <v>26</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="P150" s="6" t="s">
         <v>26</v>
@@ -10369,7 +10366,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B151" s="8">
         <v>46108.75733305556</v>
@@ -10379,7 +10376,7 @@
         <v>46119.748459016206</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
@@ -10406,13 +10403,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Q151" s="8">
         <v>46295</v>
@@ -10432,7 +10429,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B152" s="5">
         <v>46108.757338703705</v>
@@ -10442,7 +10439,7 @@
         <v>46119.748502546296</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10469,13 +10466,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q152" s="5">
         <v>46304</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -3284,7 +3284,7 @@
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46169.852931180554</v>
+        <v>46197.60055238426</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>97</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -3284,7 +3284,7 @@
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46197.60055238426</v>
+        <v>46197.61952591436</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>97</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -1978,13 +1978,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46108.75671696759</v>
+        <v>46108.590050300925</v>
       </c>
       <c r="C4" s="5">
-        <v>46112.47493710648</v>
+        <v>46112.30827043981</v>
       </c>
       <c r="D4" s="5">
-        <v>46135.64529747685</v>
+        <v>46135.47863081019</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2027,13 +2027,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46108.75679971065</v>
+        <v>46108.59013304398</v>
       </c>
       <c r="C5" s="8">
-        <v>46112.47483056713</v>
+        <v>46112.30816390047</v>
       </c>
       <c r="D5" s="8">
-        <v>46112.47484888889</v>
+        <v>46112.30818222222</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2090,13 +2090,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46108.75680396991</v>
+        <v>46108.59013730324</v>
       </c>
       <c r="C6" s="5">
-        <v>46112.47487329861</v>
+        <v>46112.30820663195</v>
       </c>
       <c r="D6" s="5">
-        <v>46112.47488903935</v>
+        <v>46112.30822237268</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -2153,13 +2153,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8">
-        <v>46108.756807708334</v>
+        <v>46108.59014104167</v>
       </c>
       <c r="C7" s="8">
-        <v>46112.47488707176</v>
+        <v>46112.30822040509</v>
       </c>
       <c r="D7" s="8">
-        <v>46112.474903009264</v>
+        <v>46112.30823634259</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>36</v>
@@ -2216,13 +2216,13 @@
         <v>37</v>
       </c>
       <c r="B8" s="5">
-        <v>46108.75681655093</v>
+        <v>46108.59014988426</v>
       </c>
       <c r="C8" s="5">
-        <v>46112.47490608796</v>
+        <v>46112.3082394213</v>
       </c>
       <c r="D8" s="5">
-        <v>46112.47493739583</v>
+        <v>46112.30827072916</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>38</v>
@@ -2279,13 +2279,13 @@
         <v>40</v>
       </c>
       <c r="B9" s="8">
-        <v>46108.756821944444</v>
+        <v>46108.59015527778</v>
       </c>
       <c r="C9" s="8">
-        <v>46112.4749261574</v>
+        <v>46112.30825949074</v>
       </c>
       <c r="D9" s="8">
-        <v>46112.474944050926</v>
+        <v>46112.30827738426</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>41</v>
@@ -2342,11 +2342,11 @@
         <v>42</v>
       </c>
       <c r="B10" s="5">
-        <v>46108.75672240741</v>
+        <v>46108.590055740744</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46134.89424877315</v>
+        <v>46134.72758210648</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>43</v>
@@ -2389,13 +2389,13 @@
         <v>45</v>
       </c>
       <c r="B11" s="8">
-        <v>46108.75682599537</v>
+        <v>46108.590159328705</v>
       </c>
       <c r="C11" s="8">
-        <v>46134.89423844907</v>
+        <v>46134.72757178241</v>
       </c>
       <c r="D11" s="8">
-        <v>46134.89425622685</v>
+        <v>46134.727589560185</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>46</v>
@@ -2454,11 +2454,11 @@
         <v>50</v>
       </c>
       <c r="B12" s="5">
-        <v>46108.756832071755</v>
+        <v>46108.5901654051</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46111.57919192129</v>
+        <v>46111.41252525463</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -2517,11 +2517,11 @@
         <v>55</v>
       </c>
       <c r="B13" s="8">
-        <v>46111.52928783565</v>
+        <v>46111.362621168984</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46111.57933724537</v>
+        <v>46111.412670578706</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>56</v>
@@ -2570,11 +2570,11 @@
         <v>59</v>
       </c>
       <c r="B14" s="5">
-        <v>46111.529514953705</v>
+        <v>46111.36284828704</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46111.57933446759</v>
+        <v>46111.41266780093</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>60</v>
@@ -2623,11 +2623,11 @@
         <v>62</v>
       </c>
       <c r="B15" s="8">
-        <v>46111.52956931713</v>
+        <v>46111.362902650464</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="8">
-        <v>46111.579331643516</v>
+        <v>46111.41266497685</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>63</v>
@@ -2676,11 +2676,11 @@
         <v>65</v>
       </c>
       <c r="B16" s="5">
-        <v>46111.529618252316</v>
+        <v>46111.362951585645</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46111.579327326384</v>
+        <v>46111.41266065973</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>66</v>
@@ -2729,13 +2729,13 @@
         <v>68</v>
       </c>
       <c r="B17" s="8">
-        <v>46108.756727361106</v>
+        <v>46108.59006069445</v>
       </c>
       <c r="C17" s="8">
-        <v>46112.4753277662</v>
+        <v>46112.30866109954</v>
       </c>
       <c r="D17" s="8">
-        <v>46135.645324363424</v>
+        <v>46135.47865769676</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>69</v>
@@ -2778,13 +2778,13 @@
         <v>71</v>
       </c>
       <c r="B18" s="5">
-        <v>46108.75683751157</v>
+        <v>46108.59017084491</v>
       </c>
       <c r="C18" s="5">
-        <v>46112.47515777778</v>
+        <v>46112.30849111111</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.1503816551</v>
+        <v>46113.983714988426</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>72</v>
@@ -2843,13 +2843,13 @@
         <v>74</v>
       </c>
       <c r="B19" s="8">
-        <v>46108.75684753472</v>
+        <v>46108.59018086806</v>
       </c>
       <c r="C19" s="8">
-        <v>46112.47517543982</v>
+        <v>46112.308508773145</v>
       </c>
       <c r="D19" s="8">
-        <v>46121.17477054398</v>
+        <v>46121.00810387731</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>75</v>
@@ -2908,13 +2908,13 @@
         <v>77</v>
       </c>
       <c r="B20" s="5">
-        <v>46108.756853240746</v>
+        <v>46108.590186574074</v>
       </c>
       <c r="C20" s="5">
-        <v>46112.47523471065</v>
+        <v>46112.30856804398</v>
       </c>
       <c r="D20" s="5">
-        <v>46121.17477048611</v>
+        <v>46121.00810381945</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>78</v>
@@ -2973,13 +2973,13 @@
         <v>80</v>
       </c>
       <c r="B21" s="8">
-        <v>46108.7568596412</v>
+        <v>46108.59019297454</v>
       </c>
       <c r="C21" s="8">
-        <v>46112.47529054398</v>
+        <v>46112.30862387731</v>
       </c>
       <c r="D21" s="8">
-        <v>46121.174770729165</v>
+        <v>46121.0081040625</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>81</v>
@@ -3038,13 +3038,13 @@
         <v>84</v>
       </c>
       <c r="B22" s="5">
-        <v>46108.78930224537</v>
+        <v>46108.62263557871</v>
       </c>
       <c r="C22" s="5">
-        <v>46112.47531421296</v>
+        <v>46112.30864754629</v>
       </c>
       <c r="D22" s="5">
-        <v>46121.17477037037</v>
+        <v>46121.0081037037</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>85</v>
@@ -3103,11 +3103,11 @@
         <v>87</v>
       </c>
       <c r="B23" s="8">
-        <v>46108.756733738424</v>
+        <v>46108.59006707176</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="8">
-        <v>46135.546079583335</v>
+        <v>46135.37941291666</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>88</v>
@@ -3150,13 +3150,13 @@
         <v>90</v>
       </c>
       <c r="B24" s="5">
-        <v>46108.75686861111</v>
+        <v>46108.59020194445</v>
       </c>
       <c r="C24" s="5">
-        <v>46112.47551975695</v>
+        <v>46112.308853090275</v>
       </c>
       <c r="D24" s="5">
-        <v>46116.12918178241</v>
+        <v>46115.96251511574</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>91</v>
@@ -3215,13 +3215,13 @@
         <v>93</v>
       </c>
       <c r="B25" s="8">
-        <v>46108.75687488426</v>
+        <v>46108.59020821759</v>
       </c>
       <c r="C25" s="8">
-        <v>46112.475488310185</v>
+        <v>46112.30882164351</v>
       </c>
       <c r="D25" s="8">
-        <v>46123.19348800926</v>
+        <v>46123.02682134259</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>94</v>
@@ -3280,11 +3280,11 @@
         <v>96</v>
       </c>
       <c r="B26" s="5">
-        <v>46108.75688076389</v>
+        <v>46108.59021409722</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46197.61952591436</v>
+        <v>46197.452859247685</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>97</v>
@@ -3343,13 +3343,13 @@
         <v>101</v>
       </c>
       <c r="B27" s="8">
-        <v>46108.75688663195</v>
+        <v>46108.59021996528</v>
       </c>
       <c r="C27" s="8">
-        <v>46135.546072997684</v>
+        <v>46135.37940633102</v>
       </c>
       <c r="D27" s="8">
-        <v>46135.5462021412</v>
+        <v>46135.37953547454</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>102</v>
@@ -3408,11 +3408,11 @@
         <v>104</v>
       </c>
       <c r="B28" s="5">
-        <v>46108.756897349536</v>
+        <v>46108.59023068287</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46193.195807870376</v>
+        <v>46193.029141203704</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3471,13 +3471,13 @@
         <v>110</v>
       </c>
       <c r="B29" s="8">
-        <v>46108.75690234954</v>
+        <v>46108.590235682874</v>
       </c>
       <c r="C29" s="8">
-        <v>46112.47581297454</v>
+        <v>46112.309146307874</v>
       </c>
       <c r="D29" s="8">
-        <v>46123.19348805556</v>
+        <v>46123.02682138889</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>111</v>
@@ -3536,11 +3536,11 @@
         <v>113</v>
       </c>
       <c r="B30" s="5">
-        <v>46108.75690841435</v>
+        <v>46108.59024174769</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46193.19580785879</v>
+        <v>46193.02914119213</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>114</v>
@@ -3599,13 +3599,13 @@
         <v>116</v>
       </c>
       <c r="B31" s="8">
-        <v>46108.78647824074</v>
+        <v>46108.61981157407</v>
       </c>
       <c r="C31" s="8">
-        <v>46112.47576767361</v>
+        <v>46112.30910100695</v>
       </c>
       <c r="D31" s="8">
-        <v>46123.19348760416</v>
+        <v>46123.0268209375</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>86</v>
@@ -3664,11 +3664,11 @@
         <v>118</v>
       </c>
       <c r="B32" s="5">
-        <v>46108.756741087964</v>
+        <v>46108.5900744213</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46154.867849305556</v>
+        <v>46154.70118263889</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>119</v>
@@ -3711,11 +3711,11 @@
         <v>121</v>
       </c>
       <c r="B33" s="8">
-        <v>46108.75695274306</v>
+        <v>46108.59028607639</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="8">
-        <v>46182.6933722338</v>
+        <v>46182.52670556713</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>122</v>
@@ -3774,13 +3774,13 @@
         <v>126</v>
       </c>
       <c r="B34" s="5">
-        <v>46108.75695775463</v>
+        <v>46108.59029108797</v>
       </c>
       <c r="C34" s="5">
-        <v>46182.69336553241</v>
+        <v>46182.52669886574</v>
       </c>
       <c r="D34" s="5">
-        <v>46182.69336725694</v>
+        <v>46182.52670059028</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>127</v>
@@ -3839,11 +3839,11 @@
         <v>129</v>
       </c>
       <c r="B35" s="8">
-        <v>46108.75696342593</v>
+        <v>46108.590296759256</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46182.69337332176</v>
+        <v>46182.52670665509</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>130</v>
@@ -3902,11 +3902,11 @@
         <v>132</v>
       </c>
       <c r="B36" s="5">
-        <v>46108.75697314815</v>
+        <v>46108.59030648148</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.854331932875</v>
+        <v>46169.6876652662</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>133</v>
@@ -3965,11 +3965,11 @@
         <v>135</v>
       </c>
       <c r="B37" s="8">
-        <v>46108.75697796296</v>
+        <v>46108.5903112963</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46135.54608165509</v>
+        <v>46135.37941498843</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>136</v>
@@ -4028,11 +4028,11 @@
         <v>138</v>
       </c>
       <c r="B38" s="5">
-        <v>46108.7569835301</v>
+        <v>46108.590316863425</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46111.58202451389</v>
+        <v>46111.41535784722</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>139</v>
@@ -4089,11 +4089,11 @@
         <v>141</v>
       </c>
       <c r="B39" s="8">
-        <v>46108.75698832176</v>
+        <v>46108.590321655094</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46183.16750024306</v>
+        <v>46183.000833576385</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>142</v>
@@ -4152,11 +4152,11 @@
         <v>144</v>
       </c>
       <c r="B40" s="5">
-        <v>46108.75699311343</v>
+        <v>46108.59032644676</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46169.85054255787</v>
+        <v>46169.683875891205</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>145</v>
@@ -4215,11 +4215,11 @@
         <v>147</v>
       </c>
       <c r="B41" s="8">
-        <v>46108.75699847222</v>
+        <v>46108.59033180556</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46182.1679962037</v>
+        <v>46182.00132953704</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>148</v>
@@ -4278,11 +4278,11 @@
         <v>150</v>
       </c>
       <c r="B42" s="5">
-        <v>46108.75700357639</v>
+        <v>46108.59033690972</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46182.693445439814</v>
+        <v>46182.52677877314</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>151</v>
@@ -4341,13 +4341,13 @@
         <v>153</v>
       </c>
       <c r="B43" s="8">
-        <v>46108.75700856482</v>
+        <v>46108.59034189815</v>
       </c>
       <c r="C43" s="8">
-        <v>46182.69343829861</v>
+        <v>46182.52677163194</v>
       </c>
       <c r="D43" s="8">
-        <v>46182.69343975694</v>
+        <v>46182.52677309028</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>154</v>
@@ -4406,11 +4406,11 @@
         <v>156</v>
       </c>
       <c r="B44" s="5">
-        <v>46108.757016435186</v>
+        <v>46108.59034976852</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46182.69344646991</v>
+        <v>46182.526779803244</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>157</v>
@@ -4469,11 +4469,11 @@
         <v>159</v>
       </c>
       <c r="B45" s="8">
-        <v>46108.7570218287</v>
+        <v>46108.590355162036</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46182.69344736111</v>
+        <v>46182.52678069445</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>160</v>
@@ -4532,11 +4532,11 @@
         <v>162</v>
       </c>
       <c r="B46" s="5">
-        <v>46108.75702719907</v>
+        <v>46108.590360532406</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46169.850810324075</v>
+        <v>46169.6841436574</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>163</v>
@@ -4595,11 +4595,11 @@
         <v>167</v>
       </c>
       <c r="B47" s="8">
-        <v>46108.75703201389</v>
+        <v>46108.59036534722</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46169.850738877314</v>
+        <v>46169.68407221065</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>109</v>
@@ -4658,11 +4658,11 @@
         <v>169</v>
       </c>
       <c r="B48" s="5">
-        <v>46108.75703761574</v>
+        <v>46108.590370949074</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46169.850767233795</v>
+        <v>46169.68410056713</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>170</v>
@@ -4721,13 +4721,13 @@
         <v>172</v>
       </c>
       <c r="B49" s="8">
-        <v>46108.75704306713</v>
+        <v>46108.59037640046</v>
       </c>
       <c r="C49" s="8">
-        <v>46154.86784248843</v>
+        <v>46154.701175821756</v>
       </c>
       <c r="D49" s="8">
-        <v>46154.86784422454</v>
+        <v>46154.70117755787</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>173</v>
@@ -4786,13 +4786,13 @@
         <v>175</v>
       </c>
       <c r="B50" s="5">
-        <v>46108.75705032407</v>
+        <v>46108.59038365741</v>
       </c>
       <c r="C50" s="5">
-        <v>46154.86746612268</v>
+        <v>46154.70079945602</v>
       </c>
       <c r="D50" s="5">
-        <v>46154.86746811343</v>
+        <v>46154.70080144676</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>176</v>
@@ -4841,13 +4841,13 @@
         <v>178</v>
       </c>
       <c r="B51" s="8">
-        <v>46108.75705728009</v>
+        <v>46108.590390613426</v>
       </c>
       <c r="C51" s="8">
-        <v>46154.86776271991</v>
+        <v>46154.70109605324</v>
       </c>
       <c r="D51" s="8">
-        <v>46154.8677641088</v>
+        <v>46154.70109744213</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>179</v>
@@ -4896,11 +4896,11 @@
         <v>181</v>
       </c>
       <c r="B52" s="5">
-        <v>46108.757061435186</v>
+        <v>46108.590394768515</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46169.85242414352</v>
+        <v>46169.68575747685</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>182</v>
@@ -4959,11 +4959,11 @@
         <v>186</v>
       </c>
       <c r="B53" s="8">
-        <v>46108.75710696759</v>
+        <v>46108.590440300926</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46169.85239162037</v>
+        <v>46169.6857249537</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>115</v>
@@ -5018,11 +5018,11 @@
         <v>188</v>
       </c>
       <c r="B54" s="5">
-        <v>46108.757112928244</v>
+        <v>46108.59044626157</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46169.85241099537</v>
+        <v>46169.6857443287</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>189</v>
@@ -5071,13 +5071,13 @@
         <v>192</v>
       </c>
       <c r="B55" s="8">
-        <v>46111.50860645833</v>
+        <v>46111.341939791666</v>
       </c>
       <c r="C55" s="8">
-        <v>46182.69404997685</v>
+        <v>46182.52738331018</v>
       </c>
       <c r="D55" s="8">
-        <v>46182.69406362269</v>
+        <v>46182.52739695602</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>193</v>
@@ -5136,13 +5136,13 @@
         <v>195</v>
       </c>
       <c r="B56" s="5">
-        <v>46111.508755937495</v>
+        <v>46111.34208927084</v>
       </c>
       <c r="C56" s="5">
-        <v>46182.69350731482</v>
+        <v>46182.52684064815</v>
       </c>
       <c r="D56" s="5">
-        <v>46182.69350877315</v>
+        <v>46182.52684210648</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>196</v>
@@ -5191,13 +5191,13 @@
         <v>198</v>
       </c>
       <c r="B57" s="8">
-        <v>46111.508846770834</v>
+        <v>46111.34218010417</v>
       </c>
       <c r="C57" s="8">
-        <v>46182.69403621528</v>
+        <v>46182.52736954861</v>
       </c>
       <c r="D57" s="8">
-        <v>46182.69403748843</v>
+        <v>46182.52737082176</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>199</v>
@@ -5246,11 +5246,11 @@
         <v>201</v>
       </c>
       <c r="B58" s="5">
-        <v>46108.75711900463</v>
+        <v>46108.59045233796</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46141.52778395833</v>
+        <v>46141.36111729167</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>202</v>
@@ -5293,11 +5293,11 @@
         <v>204</v>
       </c>
       <c r="B59" s="8">
-        <v>46108.75712325232</v>
+        <v>46108.59045658565</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46141.52778434027</v>
+        <v>46141.361117673616</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>205</v>
@@ -5354,11 +5354,11 @@
         <v>210</v>
       </c>
       <c r="B60" s="5">
-        <v>46114.552579166666</v>
+        <v>46114.3859125</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46127.171562662035</v>
+        <v>46127.00489599537</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>211</v>
@@ -5407,11 +5407,11 @@
         <v>215</v>
       </c>
       <c r="B61" s="8">
-        <v>46114.552773240735</v>
+        <v>46114.38610657408</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46127.17156420139</v>
+        <v>46127.00489753472</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>216</v>
@@ -5460,11 +5460,11 @@
         <v>218</v>
       </c>
       <c r="B62" s="5">
-        <v>46108.75712855324</v>
+        <v>46108.590461886575</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46190.19261076389</v>
+        <v>46190.02594409722</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>219</v>
@@ -5523,11 +5523,11 @@
         <v>222</v>
       </c>
       <c r="B63" s="8">
-        <v>46114.55286452547</v>
+        <v>46114.386197858796</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46189.16802</v>
+        <v>46189.00135333333</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>211</v>
@@ -5576,11 +5576,11 @@
         <v>225</v>
       </c>
       <c r="B64" s="5">
-        <v>46114.552966620366</v>
+        <v>46114.38629995371</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46189.16802199074</v>
+        <v>46189.00135532407</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>216</v>
@@ -5629,11 +5629,11 @@
         <v>228</v>
       </c>
       <c r="B65" s="8">
-        <v>46108.75713383102</v>
+        <v>46108.59046716435</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46191.171331157406</v>
+        <v>46191.00466449074</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>108</v>
@@ -5692,11 +5692,11 @@
         <v>231</v>
       </c>
       <c r="B66" s="5">
-        <v>46114.55312298611</v>
+        <v>46114.386456319444</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46190.16810163195</v>
+        <v>46190.00143496528</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>211</v>
@@ -5743,11 +5743,11 @@
         <v>232</v>
       </c>
       <c r="B67" s="8">
-        <v>46114.553244675924</v>
+        <v>46114.38657800926</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46190.168103460644</v>
+        <v>46190.00143679398</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>233</v>
@@ -5794,11 +5794,11 @@
         <v>234</v>
       </c>
       <c r="B68" s="5">
-        <v>46108.757138761575</v>
+        <v>46108.590472094904</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46114.631384050925</v>
+        <v>46114.46471738426</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>235</v>
@@ -5857,11 +5857,11 @@
         <v>239</v>
       </c>
       <c r="B69" s="8">
-        <v>46111.55280189815</v>
+        <v>46111.386135231485</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46114.62851033565</v>
+        <v>46114.46184366898</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>211</v>
@@ -5908,11 +5908,11 @@
         <v>241</v>
       </c>
       <c r="B70" s="5">
-        <v>46111.55285245371</v>
+        <v>46111.386185787036</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46114.62851040509</v>
+        <v>46114.46184373843</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>242</v>
@@ -5959,11 +5959,11 @@
         <v>244</v>
       </c>
       <c r="B71" s="8">
-        <v>46108.75714166666</v>
+        <v>46108.590475000005</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46118.545566597226</v>
+        <v>46118.378899930554</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>245</v>
@@ -6006,11 +6006,11 @@
         <v>247</v>
       </c>
       <c r="B72" s="5">
-        <v>46108.75714454861</v>
+        <v>46108.590477881946</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46118.55132545139</v>
+        <v>46118.38465878472</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>246</v>
@@ -6067,11 +6067,11 @@
         <v>251</v>
       </c>
       <c r="B73" s="8">
-        <v>46111.50359008102</v>
+        <v>46111.33692341435</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46114.61935158564</v>
+        <v>46114.452684918986</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>252</v>
@@ -6114,11 +6114,11 @@
         <v>254</v>
       </c>
       <c r="B74" s="5">
-        <v>46111.50404616898</v>
+        <v>46111.337379502314</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46114.63328692129</v>
+        <v>46114.46662025463</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>255</v>
@@ -6177,11 +6177,11 @@
         <v>259</v>
       </c>
       <c r="B75" s="8">
-        <v>46111.50406170139</v>
+        <v>46111.33739503472</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46114.63343645833</v>
+        <v>46114.46676979167</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>260</v>
@@ -6240,11 +6240,11 @@
         <v>262</v>
       </c>
       <c r="B76" s="5">
-        <v>46111.50543856481</v>
+        <v>46111.33877189815</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46114.62176513889</v>
+        <v>46114.45509847222</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>263</v>
@@ -6287,11 +6287,11 @@
         <v>265</v>
       </c>
       <c r="B77" s="8">
-        <v>46111.505495046295</v>
+        <v>46111.33882837963</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46114.633869259254</v>
+        <v>46114.4672025926</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>266</v>
@@ -6350,11 +6350,11 @@
         <v>270</v>
       </c>
       <c r="B78" s="5">
-        <v>46111.50560314815</v>
+        <v>46111.33893648148</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46114.6339722338</v>
+        <v>46114.46730556713</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>271</v>
@@ -6413,11 +6413,11 @@
         <v>272</v>
       </c>
       <c r="B79" s="8">
-        <v>46111.52633317129</v>
+        <v>46111.35966650463</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46114.627016388884</v>
+        <v>46114.46034972223</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>211</v>
@@ -6466,11 +6466,11 @@
         <v>275</v>
       </c>
       <c r="B80" s="5">
-        <v>46111.526644375</v>
+        <v>46111.35997770833</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46114.627017175924</v>
+        <v>46114.46035050926</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>216</v>
@@ -6519,11 +6519,11 @@
         <v>277</v>
       </c>
       <c r="B81" s="8">
-        <v>46111.50563458333</v>
+        <v>46111.33896791667</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46114.63406568287</v>
+        <v>46114.467399016205</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>278</v>
@@ -6582,11 +6582,11 @@
         <v>279</v>
       </c>
       <c r="B82" s="5">
-        <v>46111.526916469906</v>
+        <v>46111.36024980324</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46114.62715587963</v>
+        <v>46114.460489212965</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>211</v>
@@ -6635,11 +6635,11 @@
         <v>282</v>
       </c>
       <c r="B83" s="8">
-        <v>46111.52699828704</v>
+        <v>46111.360331620366</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46114.62715672454</v>
+        <v>46114.46049005787</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>216</v>
@@ -6688,11 +6688,11 @@
         <v>285</v>
       </c>
       <c r="B84" s="5">
-        <v>46108.75714884259</v>
+        <v>46108.590482175925</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46118.54556668982</v>
+        <v>46118.37890002315</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>286</v>
@@ -6735,11 +6735,11 @@
         <v>288</v>
       </c>
       <c r="B85" s="8">
-        <v>46108.75715243055</v>
+        <v>46108.59048576389</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46185.184959907405</v>
+        <v>46185.01829324074</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>289</v>
@@ -6798,11 +6798,11 @@
         <v>291</v>
       </c>
       <c r="B86" s="5">
-        <v>46108.75715773148</v>
+        <v>46108.59049106481</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46118.55225699074</v>
+        <v>46118.38559032408</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>57</v>
@@ -6861,11 +6861,11 @@
         <v>293</v>
       </c>
       <c r="B87" s="8">
-        <v>46108.75716349537</v>
+        <v>46108.59049682871</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46111.59762381944</v>
+        <v>46111.43095715278</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>294</v>
@@ -6924,11 +6924,11 @@
         <v>296</v>
       </c>
       <c r="B88" s="5">
-        <v>46108.75716875</v>
+        <v>46108.59050208333</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46111.59782981481</v>
+        <v>46111.43116314815</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>297</v>
@@ -6987,11 +6987,11 @@
         <v>298</v>
       </c>
       <c r="B89" s="8">
-        <v>46108.75717430556</v>
+        <v>46108.59050763889</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46154.86778005787</v>
+        <v>46154.7011133912</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>299</v>
@@ -7050,11 +7050,11 @@
         <v>300</v>
       </c>
       <c r="B90" s="5">
-        <v>46108.75717877314</v>
+        <v>46108.590512106486</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46118.54556859954</v>
+        <v>46118.37890193287</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>301</v>
@@ -7111,11 +7111,11 @@
         <v>303</v>
       </c>
       <c r="B91" s="8">
-        <v>46108.822037094906</v>
+        <v>46108.65537042824</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46185.18495945602</v>
+        <v>46185.01829278935</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>304</v>
@@ -7174,11 +7174,11 @@
         <v>306</v>
       </c>
       <c r="B92" s="5">
-        <v>46108.757183124995</v>
+        <v>46108.59051645834</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46114.62594751157</v>
+        <v>46114.45928084491</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>307</v>
@@ -7221,11 +7221,11 @@
         <v>309</v>
       </c>
       <c r="B93" s="8">
-        <v>46108.757186296294</v>
+        <v>46108.59051962963</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46114.63518780093</v>
+        <v>46114.46852113426</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>310</v>
@@ -7284,11 +7284,11 @@
         <v>311</v>
       </c>
       <c r="B94" s="5">
-        <v>46111.52720202546</v>
+        <v>46111.36053535879</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46118.545567442125</v>
+        <v>46118.37890077547</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>211</v>
@@ -7337,11 +7337,11 @@
         <v>314</v>
       </c>
       <c r="B95" s="8">
-        <v>46111.52733795139</v>
+        <v>46111.360671284725</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46118.54556813657</v>
+        <v>46118.37890146991</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>216</v>
@@ -7390,11 +7390,11 @@
         <v>317</v>
       </c>
       <c r="B96" s="5">
-        <v>46108.75720997685</v>
+        <v>46108.59054331019</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46114.636429907405</v>
+        <v>46114.46976324074</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>318</v>
@@ -7453,11 +7453,11 @@
         <v>319</v>
       </c>
       <c r="B97" s="8">
-        <v>46111.52790079861</v>
+        <v>46111.361234131946</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46114.627765578705</v>
+        <v>46114.46109891204</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>211</v>
@@ -7506,11 +7506,11 @@
         <v>322</v>
       </c>
       <c r="B98" s="5">
-        <v>46111.52796104166</v>
+        <v>46111.361294375005</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46114.62776635417</v>
+        <v>46114.4610996875</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>216</v>
@@ -7559,11 +7559,11 @@
         <v>325</v>
       </c>
       <c r="B99" s="8">
-        <v>46108.75719767361</v>
+        <v>46108.59053100694</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46114.63653665509</v>
+        <v>46114.469869988425</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>326</v>
@@ -7622,11 +7622,11 @@
         <v>327</v>
       </c>
       <c r="B100" s="5">
-        <v>46111.52756633102</v>
+        <v>46111.36089966435</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46118.54557231482</v>
+        <v>46118.37890564815</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>211</v>
@@ -7675,11 +7675,11 @@
         <v>330</v>
       </c>
       <c r="B101" s="8">
-        <v>46111.527622395835</v>
+        <v>46111.360955729164</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46118.54556883102</v>
+        <v>46118.37890216435</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>216</v>
@@ -7728,11 +7728,11 @@
         <v>333</v>
       </c>
       <c r="B102" s="5">
-        <v>46108.75720341435</v>
+        <v>46108.59053674768</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46114.63667146991</v>
+        <v>46114.47000480324</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>334</v>
@@ -7791,11 +7791,11 @@
         <v>335</v>
       </c>
       <c r="B103" s="8">
-        <v>46111.52775804398</v>
+        <v>46111.361091377315</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46118.545570937495</v>
+        <v>46118.37890427084</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>211</v>
@@ -7844,11 +7844,11 @@
         <v>337</v>
       </c>
       <c r="B104" s="5">
-        <v>46111.52780829861</v>
+        <v>46111.36114163195</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46118.545571608796</v>
+        <v>46118.37890494213</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>216</v>
@@ -7897,11 +7897,11 @@
         <v>339</v>
       </c>
       <c r="B105" s="8">
-        <v>46108.757191412034</v>
+        <v>46108.59052474537</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46114.636801493056</v>
+        <v>46114.47013482639</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>340</v>
@@ -7960,11 +7960,11 @@
         <v>341</v>
       </c>
       <c r="B106" s="5">
-        <v>46111.527446493055</v>
+        <v>46111.360779826384</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46118.545569548616</v>
+        <v>46118.378902881945</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>211</v>
@@ -8013,11 +8013,11 @@
         <v>344</v>
       </c>
       <c r="B107" s="8">
-        <v>46111.52746010417</v>
+        <v>46111.3607934375</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46118.545570243055</v>
+        <v>46118.37890357639</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>216</v>
@@ -8066,11 +8066,11 @@
         <v>347</v>
       </c>
       <c r="B108" s="5">
-        <v>46108.757217025464</v>
+        <v>46108.5905503588</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46114.63686459491</v>
+        <v>46114.47019792824</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>348</v>
@@ -8129,11 +8129,11 @@
         <v>349</v>
       </c>
       <c r="B109" s="8">
-        <v>46111.528031932874</v>
+        <v>46111.3613652662</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46114.62850982639</v>
+        <v>46114.46184315972</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>211</v>
@@ -8180,11 +8180,11 @@
         <v>351</v>
       </c>
       <c r="B110" s="5">
-        <v>46111.52811128472</v>
+        <v>46111.36144461806</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46114.62851064815</v>
+        <v>46114.46184398148</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>216</v>
@@ -8231,11 +8231,11 @@
         <v>353</v>
       </c>
       <c r="B111" s="8">
-        <v>46108.75727585648</v>
+        <v>46108.590609189814</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46114.63695302083</v>
+        <v>46114.47028635417</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>354</v>
@@ -8292,11 +8292,11 @@
         <v>356</v>
       </c>
       <c r="B112" s="5">
-        <v>46111.5281812037</v>
+        <v>46111.36151453704</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46114.62864336805</v>
+        <v>46114.461976701394</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>211</v>
@@ -8343,11 +8343,11 @@
         <v>358</v>
       </c>
       <c r="B113" s="8">
-        <v>46111.528266423615</v>
+        <v>46111.36159975694</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46114.62864409722</v>
+        <v>46114.461977430554</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>216</v>
@@ -8394,11 +8394,11 @@
         <v>360</v>
       </c>
       <c r="B114" s="5">
-        <v>46108.757283217594</v>
+        <v>46108.59061655092</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46114.62962787037</v>
+        <v>46114.4629612037</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>361</v>
@@ -8441,11 +8441,11 @@
         <v>363</v>
       </c>
       <c r="B115" s="8">
-        <v>46108.757287430555</v>
+        <v>46108.59062076389</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46114.63723893519</v>
+        <v>46114.47057226852</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>364</v>
@@ -8504,11 +8504,11 @@
         <v>368</v>
       </c>
       <c r="B116" s="5">
-        <v>46111.52846596065</v>
+        <v>46111.36179929398</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46114.62888387732</v>
+        <v>46114.46221721065</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>211</v>
@@ -8555,11 +8555,11 @@
         <v>370</v>
       </c>
       <c r="B117" s="8">
-        <v>46111.528518067134</v>
+        <v>46111.36185140046</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46114.62888469908</v>
+        <v>46114.46221803241</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>216</v>
@@ -8606,11 +8606,11 @@
         <v>372</v>
       </c>
       <c r="B118" s="5">
-        <v>46111.531216006944</v>
+        <v>46111.36454934027</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46114.62888542824</v>
+        <v>46114.462218761575</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>56</v>
@@ -8657,11 +8657,11 @@
         <v>374</v>
       </c>
       <c r="B119" s="8">
-        <v>46111.53129275463</v>
+        <v>46111.36462608796</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46114.62888615741</v>
+        <v>46114.46221949074</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>60</v>
@@ -8708,11 +8708,11 @@
         <v>376</v>
       </c>
       <c r="B120" s="5">
-        <v>46111.53134821759</v>
+        <v>46111.36468155093</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46114.628886921295</v>
+        <v>46114.46222025463</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>377</v>
@@ -8759,11 +8759,11 @@
         <v>379</v>
       </c>
       <c r="B121" s="8">
-        <v>46111.53139942129</v>
+        <v>46111.364732754635</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46114.62888767361</v>
+        <v>46114.46222100694</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>66</v>
@@ -8810,11 +8810,11 @@
         <v>381</v>
       </c>
       <c r="B122" s="5">
-        <v>46111.53343819444</v>
+        <v>46111.36677152778</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46114.628888437495</v>
+        <v>46114.46222177084</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>305</v>
@@ -8861,11 +8861,11 @@
         <v>383</v>
       </c>
       <c r="B123" s="8">
-        <v>46108.75729289352</v>
+        <v>46108.590626226855</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46114.637374618054</v>
+        <v>46114.47070795139</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>384</v>
@@ -8924,11 +8924,11 @@
         <v>386</v>
       </c>
       <c r="B124" s="5">
-        <v>46111.52857409722</v>
+        <v>46111.36190743056</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46114.629102280094</v>
+        <v>46114.46243561343</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>211</v>
@@ -8977,11 +8977,11 @@
         <v>388</v>
       </c>
       <c r="B125" s="8">
-        <v>46111.528674016205</v>
+        <v>46111.36200734954</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46114.62910302084</v>
+        <v>46114.462436354166</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>216</v>
@@ -9030,11 +9030,11 @@
         <v>390</v>
       </c>
       <c r="B126" s="5">
-        <v>46111.531552291664</v>
+        <v>46111.364885625</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46114.629103784726</v>
+        <v>46114.462437118054</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>56</v>
@@ -9083,11 +9083,11 @@
         <v>392</v>
       </c>
       <c r="B127" s="8">
-        <v>46111.531603344905</v>
+        <v>46111.36493667824</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46114.62910452546</v>
+        <v>46114.4624378588</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>60</v>
@@ -9136,11 +9136,11 @@
         <v>394</v>
       </c>
       <c r="B128" s="5">
-        <v>46111.531648379634</v>
+        <v>46111.36498171296</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46114.62910528935</v>
+        <v>46114.462438622686</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>377</v>
@@ -9189,11 +9189,11 @@
         <v>396</v>
       </c>
       <c r="B129" s="8">
-        <v>46111.531705925925</v>
+        <v>46111.36503925926</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46114.62910605324</v>
+        <v>46114.462439386574</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>66</v>
@@ -9242,11 +9242,11 @@
         <v>398</v>
       </c>
       <c r="B130" s="5">
-        <v>46111.533570127314</v>
+        <v>46111.36690346064</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46114.62910684028</v>
+        <v>46114.46244017361</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>305</v>
@@ -9295,11 +9295,11 @@
         <v>400</v>
       </c>
       <c r="B131" s="8">
-        <v>46108.75729930555</v>
+        <v>46108.590632638894</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46114.63748693287</v>
+        <v>46114.4708202662</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>401</v>
@@ -9358,11 +9358,11 @@
         <v>403</v>
       </c>
       <c r="B132" s="5">
-        <v>46111.528799872685</v>
+        <v>46111.362133206014</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46114.62931347222</v>
+        <v>46114.46264680555</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>211</v>
@@ -9409,11 +9409,11 @@
         <v>405</v>
       </c>
       <c r="B133" s="8">
-        <v>46111.52885179398</v>
+        <v>46111.36218512732</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46114.62931429398</v>
+        <v>46114.46264762731</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>216</v>
@@ -9460,11 +9460,11 @@
         <v>407</v>
       </c>
       <c r="B134" s="5">
-        <v>46111.53215439815</v>
+        <v>46111.365487731484</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46114.629315046295</v>
+        <v>46114.46264837963</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>56</v>
@@ -9511,11 +9511,11 @@
         <v>409</v>
       </c>
       <c r="B135" s="8">
-        <v>46111.53220642361</v>
+        <v>46111.365539756946</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46114.62931577546</v>
+        <v>46114.4626491088</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>60</v>
@@ -9562,11 +9562,11 @@
         <v>411</v>
       </c>
       <c r="B136" s="5">
-        <v>46111.532258287036</v>
+        <v>46111.36559162037</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46114.629316527775</v>
+        <v>46114.46264986111</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>377</v>
@@ -9613,11 +9613,11 @@
         <v>413</v>
       </c>
       <c r="B137" s="8">
-        <v>46111.53231001158</v>
+        <v>46111.36564334491</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46114.62931729166</v>
+        <v>46114.462650625</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>66</v>
@@ -9664,11 +9664,11 @@
         <v>415</v>
       </c>
       <c r="B138" s="5">
-        <v>46111.53368237268</v>
+        <v>46111.36701570602</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46114.62931805555</v>
+        <v>46114.462651388894</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>416</v>
@@ -9715,11 +9715,11 @@
         <v>418</v>
       </c>
       <c r="B139" s="8">
-        <v>46108.757304583334</v>
+        <v>46108.59063791667</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46114.63755023148</v>
+        <v>46114.47088356482</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>419</v>
@@ -9778,11 +9778,11 @@
         <v>421</v>
       </c>
       <c r="B140" s="5">
-        <v>46111.528945011574</v>
+        <v>46111.36227834491</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46114.830281076385</v>
+        <v>46114.66361440972</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>211</v>
@@ -9831,11 +9831,11 @@
         <v>423</v>
       </c>
       <c r="B141" s="8">
-        <v>46111.52901092592</v>
+        <v>46111.36234425926</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46114.830302789356</v>
+        <v>46114.663636122685</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>216</v>
@@ -9884,11 +9884,11 @@
         <v>424</v>
       </c>
       <c r="B142" s="5">
-        <v>46111.53247278935</v>
+        <v>46111.36580612269</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46114.830319201385</v>
+        <v>46114.66365253473</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>56</v>
@@ -9937,11 +9937,11 @@
         <v>425</v>
       </c>
       <c r="B143" s="8">
-        <v>46111.53253350694</v>
+        <v>46111.36586684028</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46114.83033574074</v>
+        <v>46114.66366907407</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>60</v>
@@ -9990,11 +9990,11 @@
         <v>426</v>
       </c>
       <c r="B144" s="5">
-        <v>46111.532638414355</v>
+        <v>46111.365971747684</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46114.83035239583</v>
+        <v>46114.66368572917</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>66</v>
@@ -10043,11 +10043,11 @@
         <v>427</v>
       </c>
       <c r="B145" s="8">
-        <v>46111.53258112269</v>
+        <v>46111.36591445602</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46114.83037114583</v>
+        <v>46114.66370447917</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>377</v>
@@ -10096,11 +10096,11 @@
         <v>428</v>
       </c>
       <c r="B146" s="5">
-        <v>46111.53385627315</v>
+        <v>46111.36718960648</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46114.83039427083</v>
+        <v>46114.663727604166</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>305</v>
@@ -10149,11 +10149,11 @@
         <v>429</v>
       </c>
       <c r="B147" s="8">
-        <v>46108.757310497684</v>
+        <v>46108.59064383102</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46114.62962797454</v>
+        <v>46114.46296130787</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>430</v>
@@ -10196,11 +10196,11 @@
         <v>432</v>
       </c>
       <c r="B148" s="5">
-        <v>46108.75731366898</v>
+        <v>46108.59064700232</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46114.63764361111</v>
+        <v>46114.470976944445</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>433</v>
@@ -10259,11 +10259,11 @@
         <v>436</v>
       </c>
       <c r="B149" s="8">
-        <v>46108.75732001157</v>
+        <v>46108.59065334491</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46119.74841528935</v>
+        <v>46119.58174862269</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>437</v>
@@ -10322,11 +10322,11 @@
         <v>439</v>
       </c>
       <c r="B150" s="5">
-        <v>46108.7573290625</v>
+        <v>46108.59066239583</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46114.62962836806</v>
+        <v>46114.462961701385</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>440</v>
@@ -10369,11 +10369,11 @@
         <v>442</v>
       </c>
       <c r="B151" s="8">
-        <v>46108.75733305556</v>
+        <v>46108.59066638889</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46119.748459016206</v>
+        <v>46119.581792349534</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>443</v>
@@ -10432,11 +10432,11 @@
         <v>445</v>
       </c>
       <c r="B152" s="5">
-        <v>46108.757338703705</v>
+        <v>46108.59067203704</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46119.748502546296</v>
+        <v>46119.58183587963</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>446</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -1978,13 +1978,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46108.590050300925</v>
+        <v>46108.75671696759</v>
       </c>
       <c r="C4" s="5">
-        <v>46112.30827043981</v>
+        <v>46112.47493710648</v>
       </c>
       <c r="D4" s="5">
-        <v>46135.47863081019</v>
+        <v>46135.64529747685</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2027,13 +2027,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46108.59013304398</v>
+        <v>46108.75679971065</v>
       </c>
       <c r="C5" s="8">
-        <v>46112.30816390047</v>
+        <v>46112.47483056713</v>
       </c>
       <c r="D5" s="8">
-        <v>46112.30818222222</v>
+        <v>46112.47484888889</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2090,13 +2090,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46108.59013730324</v>
+        <v>46108.75680396991</v>
       </c>
       <c r="C6" s="5">
-        <v>46112.30820663195</v>
+        <v>46112.47487329861</v>
       </c>
       <c r="D6" s="5">
-        <v>46112.30822237268</v>
+        <v>46112.47488903935</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -2153,13 +2153,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8">
-        <v>46108.59014104167</v>
+        <v>46108.756807708334</v>
       </c>
       <c r="C7" s="8">
-        <v>46112.30822040509</v>
+        <v>46112.47488707176</v>
       </c>
       <c r="D7" s="8">
-        <v>46112.30823634259</v>
+        <v>46112.474903009264</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>36</v>
@@ -2216,13 +2216,13 @@
         <v>37</v>
       </c>
       <c r="B8" s="5">
-        <v>46108.59014988426</v>
+        <v>46108.75681655093</v>
       </c>
       <c r="C8" s="5">
-        <v>46112.3082394213</v>
+        <v>46112.47490608796</v>
       </c>
       <c r="D8" s="5">
-        <v>46112.30827072916</v>
+        <v>46112.47493739583</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>38</v>
@@ -2279,13 +2279,13 @@
         <v>40</v>
       </c>
       <c r="B9" s="8">
-        <v>46108.59015527778</v>
+        <v>46108.756821944444</v>
       </c>
       <c r="C9" s="8">
-        <v>46112.30825949074</v>
+        <v>46112.4749261574</v>
       </c>
       <c r="D9" s="8">
-        <v>46112.30827738426</v>
+        <v>46112.474944050926</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>41</v>
@@ -2342,11 +2342,11 @@
         <v>42</v>
       </c>
       <c r="B10" s="5">
-        <v>46108.590055740744</v>
+        <v>46108.75672240741</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46134.72758210648</v>
+        <v>46134.89424877315</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>43</v>
@@ -2389,13 +2389,13 @@
         <v>45</v>
       </c>
       <c r="B11" s="8">
-        <v>46108.590159328705</v>
+        <v>46108.75682599537</v>
       </c>
       <c r="C11" s="8">
-        <v>46134.72757178241</v>
+        <v>46134.89423844907</v>
       </c>
       <c r="D11" s="8">
-        <v>46134.727589560185</v>
+        <v>46134.89425622685</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>46</v>
@@ -2454,11 +2454,11 @@
         <v>50</v>
       </c>
       <c r="B12" s="5">
-        <v>46108.5901654051</v>
+        <v>46108.756832071755</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46111.41252525463</v>
+        <v>46111.57919192129</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -2517,11 +2517,11 @@
         <v>55</v>
       </c>
       <c r="B13" s="8">
-        <v>46111.362621168984</v>
+        <v>46111.52928783565</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46111.412670578706</v>
+        <v>46111.57933724537</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>56</v>
@@ -2570,11 +2570,11 @@
         <v>59</v>
       </c>
       <c r="B14" s="5">
-        <v>46111.36284828704</v>
+        <v>46111.529514953705</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46111.41266780093</v>
+        <v>46111.57933446759</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>60</v>
@@ -2623,11 +2623,11 @@
         <v>62</v>
       </c>
       <c r="B15" s="8">
-        <v>46111.362902650464</v>
+        <v>46111.52956931713</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="8">
-        <v>46111.41266497685</v>
+        <v>46111.579331643516</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>63</v>
@@ -2676,11 +2676,11 @@
         <v>65</v>
       </c>
       <c r="B16" s="5">
-        <v>46111.362951585645</v>
+        <v>46111.529618252316</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46111.41266065973</v>
+        <v>46111.579327326384</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>66</v>
@@ -2729,13 +2729,13 @@
         <v>68</v>
       </c>
       <c r="B17" s="8">
-        <v>46108.59006069445</v>
+        <v>46108.756727361106</v>
       </c>
       <c r="C17" s="8">
-        <v>46112.30866109954</v>
+        <v>46112.4753277662</v>
       </c>
       <c r="D17" s="8">
-        <v>46135.47865769676</v>
+        <v>46135.645324363424</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>69</v>
@@ -2778,13 +2778,13 @@
         <v>71</v>
       </c>
       <c r="B18" s="5">
-        <v>46108.59017084491</v>
+        <v>46108.75683751157</v>
       </c>
       <c r="C18" s="5">
-        <v>46112.30849111111</v>
+        <v>46112.47515777778</v>
       </c>
       <c r="D18" s="5">
-        <v>46113.983714988426</v>
+        <v>46114.1503816551</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>72</v>
@@ -2843,13 +2843,13 @@
         <v>74</v>
       </c>
       <c r="B19" s="8">
-        <v>46108.59018086806</v>
+        <v>46108.75684753472</v>
       </c>
       <c r="C19" s="8">
-        <v>46112.308508773145</v>
+        <v>46112.47517543982</v>
       </c>
       <c r="D19" s="8">
-        <v>46121.00810387731</v>
+        <v>46121.17477054398</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>75</v>
@@ -2908,13 +2908,13 @@
         <v>77</v>
       </c>
       <c r="B20" s="5">
-        <v>46108.590186574074</v>
+        <v>46108.756853240746</v>
       </c>
       <c r="C20" s="5">
-        <v>46112.30856804398</v>
+        <v>46112.47523471065</v>
       </c>
       <c r="D20" s="5">
-        <v>46121.00810381945</v>
+        <v>46121.17477048611</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>78</v>
@@ -2973,13 +2973,13 @@
         <v>80</v>
       </c>
       <c r="B21" s="8">
-        <v>46108.59019297454</v>
+        <v>46108.7568596412</v>
       </c>
       <c r="C21" s="8">
-        <v>46112.30862387731</v>
+        <v>46112.47529054398</v>
       </c>
       <c r="D21" s="8">
-        <v>46121.0081040625</v>
+        <v>46121.174770729165</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>81</v>
@@ -3038,13 +3038,13 @@
         <v>84</v>
       </c>
       <c r="B22" s="5">
-        <v>46108.62263557871</v>
+        <v>46108.78930224537</v>
       </c>
       <c r="C22" s="5">
-        <v>46112.30864754629</v>
+        <v>46112.47531421296</v>
       </c>
       <c r="D22" s="5">
-        <v>46121.0081037037</v>
+        <v>46121.17477037037</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>85</v>
@@ -3103,11 +3103,11 @@
         <v>87</v>
       </c>
       <c r="B23" s="8">
-        <v>46108.59006707176</v>
+        <v>46108.756733738424</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="8">
-        <v>46135.37941291666</v>
+        <v>46135.546079583335</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>88</v>
@@ -3150,13 +3150,13 @@
         <v>90</v>
       </c>
       <c r="B24" s="5">
-        <v>46108.59020194445</v>
+        <v>46108.75686861111</v>
       </c>
       <c r="C24" s="5">
-        <v>46112.308853090275</v>
+        <v>46112.47551975695</v>
       </c>
       <c r="D24" s="5">
-        <v>46115.96251511574</v>
+        <v>46116.12918178241</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>91</v>
@@ -3215,13 +3215,13 @@
         <v>93</v>
       </c>
       <c r="B25" s="8">
-        <v>46108.59020821759</v>
+        <v>46108.75687488426</v>
       </c>
       <c r="C25" s="8">
-        <v>46112.30882164351</v>
+        <v>46112.475488310185</v>
       </c>
       <c r="D25" s="8">
-        <v>46123.02682134259</v>
+        <v>46123.19348800926</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>94</v>
@@ -3280,11 +3280,11 @@
         <v>96</v>
       </c>
       <c r="B26" s="5">
-        <v>46108.59021409722</v>
+        <v>46108.75688076389</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46197.452859247685</v>
+        <v>46197.61952591436</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>97</v>
@@ -3343,13 +3343,13 @@
         <v>101</v>
       </c>
       <c r="B27" s="8">
-        <v>46108.59021996528</v>
+        <v>46108.75688663195</v>
       </c>
       <c r="C27" s="8">
-        <v>46135.37940633102</v>
+        <v>46135.546072997684</v>
       </c>
       <c r="D27" s="8">
-        <v>46135.37953547454</v>
+        <v>46135.5462021412</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>102</v>
@@ -3408,11 +3408,11 @@
         <v>104</v>
       </c>
       <c r="B28" s="5">
-        <v>46108.59023068287</v>
+        <v>46108.756897349536</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46193.029141203704</v>
+        <v>46193.195807870376</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3471,13 +3471,13 @@
         <v>110</v>
       </c>
       <c r="B29" s="8">
-        <v>46108.590235682874</v>
+        <v>46108.75690234954</v>
       </c>
       <c r="C29" s="8">
-        <v>46112.309146307874</v>
+        <v>46112.47581297454</v>
       </c>
       <c r="D29" s="8">
-        <v>46123.02682138889</v>
+        <v>46123.19348805556</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>111</v>
@@ -3536,11 +3536,11 @@
         <v>113</v>
       </c>
       <c r="B30" s="5">
-        <v>46108.59024174769</v>
+        <v>46108.75690841435</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46193.02914119213</v>
+        <v>46193.19580785879</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>114</v>
@@ -3599,13 +3599,13 @@
         <v>116</v>
       </c>
       <c r="B31" s="8">
-        <v>46108.61981157407</v>
+        <v>46108.78647824074</v>
       </c>
       <c r="C31" s="8">
-        <v>46112.30910100695</v>
+        <v>46112.47576767361</v>
       </c>
       <c r="D31" s="8">
-        <v>46123.0268209375</v>
+        <v>46123.19348760416</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>86</v>
@@ -3664,11 +3664,11 @@
         <v>118</v>
       </c>
       <c r="B32" s="5">
-        <v>46108.5900744213</v>
+        <v>46108.756741087964</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46154.70118263889</v>
+        <v>46154.867849305556</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>119</v>
@@ -3711,11 +3711,11 @@
         <v>121</v>
       </c>
       <c r="B33" s="8">
-        <v>46108.59028607639</v>
+        <v>46108.75695274306</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="8">
-        <v>46182.52670556713</v>
+        <v>46182.6933722338</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>122</v>
@@ -3774,13 +3774,13 @@
         <v>126</v>
       </c>
       <c r="B34" s="5">
-        <v>46108.59029108797</v>
+        <v>46108.75695775463</v>
       </c>
       <c r="C34" s="5">
-        <v>46182.52669886574</v>
+        <v>46182.69336553241</v>
       </c>
       <c r="D34" s="5">
-        <v>46182.52670059028</v>
+        <v>46182.69336725694</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>127</v>
@@ -3839,11 +3839,11 @@
         <v>129</v>
       </c>
       <c r="B35" s="8">
-        <v>46108.590296759256</v>
+        <v>46108.75696342593</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46182.52670665509</v>
+        <v>46182.69337332176</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>130</v>
@@ -3902,11 +3902,11 @@
         <v>132</v>
       </c>
       <c r="B36" s="5">
-        <v>46108.59030648148</v>
+        <v>46108.75697314815</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.6876652662</v>
+        <v>46169.854331932875</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>133</v>
@@ -3965,11 +3965,11 @@
         <v>135</v>
       </c>
       <c r="B37" s="8">
-        <v>46108.5903112963</v>
+        <v>46108.75697796296</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46135.37941498843</v>
+        <v>46135.54608165509</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>136</v>
@@ -4028,11 +4028,11 @@
         <v>138</v>
       </c>
       <c r="B38" s="5">
-        <v>46108.590316863425</v>
+        <v>46108.7569835301</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46111.41535784722</v>
+        <v>46111.58202451389</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>139</v>
@@ -4089,11 +4089,11 @@
         <v>141</v>
       </c>
       <c r="B39" s="8">
-        <v>46108.590321655094</v>
+        <v>46108.75698832176</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46183.000833576385</v>
+        <v>46183.16750024306</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>142</v>
@@ -4152,11 +4152,11 @@
         <v>144</v>
       </c>
       <c r="B40" s="5">
-        <v>46108.59032644676</v>
+        <v>46108.75699311343</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46169.683875891205</v>
+        <v>46169.85054255787</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>145</v>
@@ -4215,11 +4215,11 @@
         <v>147</v>
       </c>
       <c r="B41" s="8">
-        <v>46108.59033180556</v>
+        <v>46108.75699847222</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46182.00132953704</v>
+        <v>46182.1679962037</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>148</v>
@@ -4278,11 +4278,11 @@
         <v>150</v>
       </c>
       <c r="B42" s="5">
-        <v>46108.59033690972</v>
+        <v>46108.75700357639</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46182.52677877314</v>
+        <v>46182.693445439814</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>151</v>
@@ -4341,13 +4341,13 @@
         <v>153</v>
       </c>
       <c r="B43" s="8">
-        <v>46108.59034189815</v>
+        <v>46108.75700856482</v>
       </c>
       <c r="C43" s="8">
-        <v>46182.52677163194</v>
+        <v>46182.69343829861</v>
       </c>
       <c r="D43" s="8">
-        <v>46182.52677309028</v>
+        <v>46182.69343975694</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>154</v>
@@ -4406,11 +4406,11 @@
         <v>156</v>
       </c>
       <c r="B44" s="5">
-        <v>46108.59034976852</v>
+        <v>46108.757016435186</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46182.526779803244</v>
+        <v>46182.69344646991</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>157</v>
@@ -4469,11 +4469,11 @@
         <v>159</v>
       </c>
       <c r="B45" s="8">
-        <v>46108.590355162036</v>
+        <v>46108.7570218287</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46182.52678069445</v>
+        <v>46182.69344736111</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>160</v>
@@ -4532,11 +4532,11 @@
         <v>162</v>
       </c>
       <c r="B46" s="5">
-        <v>46108.590360532406</v>
+        <v>46108.75702719907</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46169.6841436574</v>
+        <v>46169.850810324075</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>163</v>
@@ -4595,11 +4595,11 @@
         <v>167</v>
       </c>
       <c r="B47" s="8">
-        <v>46108.59036534722</v>
+        <v>46108.75703201389</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46169.68407221065</v>
+        <v>46169.850738877314</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>109</v>
@@ -4658,11 +4658,11 @@
         <v>169</v>
       </c>
       <c r="B48" s="5">
-        <v>46108.590370949074</v>
+        <v>46108.75703761574</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46169.68410056713</v>
+        <v>46169.850767233795</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>170</v>
@@ -4721,13 +4721,13 @@
         <v>172</v>
       </c>
       <c r="B49" s="8">
-        <v>46108.59037640046</v>
+        <v>46108.75704306713</v>
       </c>
       <c r="C49" s="8">
-        <v>46154.701175821756</v>
+        <v>46154.86784248843</v>
       </c>
       <c r="D49" s="8">
-        <v>46154.70117755787</v>
+        <v>46154.86784422454</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>173</v>
@@ -4786,13 +4786,13 @@
         <v>175</v>
       </c>
       <c r="B50" s="5">
-        <v>46108.59038365741</v>
+        <v>46108.75705032407</v>
       </c>
       <c r="C50" s="5">
-        <v>46154.70079945602</v>
+        <v>46154.86746612268</v>
       </c>
       <c r="D50" s="5">
-        <v>46154.70080144676</v>
+        <v>46154.86746811343</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>176</v>
@@ -4841,13 +4841,13 @@
         <v>178</v>
       </c>
       <c r="B51" s="8">
-        <v>46108.590390613426</v>
+        <v>46108.75705728009</v>
       </c>
       <c r="C51" s="8">
-        <v>46154.70109605324</v>
+        <v>46154.86776271991</v>
       </c>
       <c r="D51" s="8">
-        <v>46154.70109744213</v>
+        <v>46154.8677641088</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>179</v>
@@ -4896,11 +4896,11 @@
         <v>181</v>
       </c>
       <c r="B52" s="5">
-        <v>46108.590394768515</v>
+        <v>46108.757061435186</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46169.68575747685</v>
+        <v>46169.85242414352</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>182</v>
@@ -4959,11 +4959,11 @@
         <v>186</v>
       </c>
       <c r="B53" s="8">
-        <v>46108.590440300926</v>
+        <v>46108.75710696759</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46169.6857249537</v>
+        <v>46169.85239162037</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>115</v>
@@ -5018,11 +5018,11 @@
         <v>188</v>
       </c>
       <c r="B54" s="5">
-        <v>46108.59044626157</v>
+        <v>46108.757112928244</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46169.6857443287</v>
+        <v>46169.85241099537</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>189</v>
@@ -5071,13 +5071,13 @@
         <v>192</v>
       </c>
       <c r="B55" s="8">
-        <v>46111.341939791666</v>
+        <v>46111.50860645833</v>
       </c>
       <c r="C55" s="8">
-        <v>46182.52738331018</v>
+        <v>46182.69404997685</v>
       </c>
       <c r="D55" s="8">
-        <v>46182.52739695602</v>
+        <v>46182.69406362269</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>193</v>
@@ -5136,13 +5136,13 @@
         <v>195</v>
       </c>
       <c r="B56" s="5">
-        <v>46111.34208927084</v>
+        <v>46111.508755937495</v>
       </c>
       <c r="C56" s="5">
-        <v>46182.52684064815</v>
+        <v>46182.69350731482</v>
       </c>
       <c r="D56" s="5">
-        <v>46182.52684210648</v>
+        <v>46182.69350877315</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>196</v>
@@ -5191,13 +5191,13 @@
         <v>198</v>
       </c>
       <c r="B57" s="8">
-        <v>46111.34218010417</v>
+        <v>46111.508846770834</v>
       </c>
       <c r="C57" s="8">
-        <v>46182.52736954861</v>
+        <v>46182.69403621528</v>
       </c>
       <c r="D57" s="8">
-        <v>46182.52737082176</v>
+        <v>46182.69403748843</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>199</v>
@@ -5246,11 +5246,11 @@
         <v>201</v>
       </c>
       <c r="B58" s="5">
-        <v>46108.59045233796</v>
+        <v>46108.75711900463</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46141.36111729167</v>
+        <v>46141.52778395833</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>202</v>
@@ -5293,11 +5293,11 @@
         <v>204</v>
       </c>
       <c r="B59" s="8">
-        <v>46108.59045658565</v>
+        <v>46108.75712325232</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46141.361117673616</v>
+        <v>46141.52778434027</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>205</v>
@@ -5354,11 +5354,11 @@
         <v>210</v>
       </c>
       <c r="B60" s="5">
-        <v>46114.3859125</v>
+        <v>46114.552579166666</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46127.00489599537</v>
+        <v>46127.171562662035</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>211</v>
@@ -5407,11 +5407,11 @@
         <v>215</v>
       </c>
       <c r="B61" s="8">
-        <v>46114.38610657408</v>
+        <v>46114.552773240735</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46127.00489753472</v>
+        <v>46127.17156420139</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>216</v>
@@ -5460,11 +5460,11 @@
         <v>218</v>
       </c>
       <c r="B62" s="5">
-        <v>46108.590461886575</v>
+        <v>46108.75712855324</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46190.02594409722</v>
+        <v>46190.19261076389</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>219</v>
@@ -5523,11 +5523,11 @@
         <v>222</v>
       </c>
       <c r="B63" s="8">
-        <v>46114.386197858796</v>
+        <v>46114.55286452547</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46189.00135333333</v>
+        <v>46189.16802</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>211</v>
@@ -5576,11 +5576,11 @@
         <v>225</v>
       </c>
       <c r="B64" s="5">
-        <v>46114.38629995371</v>
+        <v>46114.552966620366</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46189.00135532407</v>
+        <v>46189.16802199074</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>216</v>
@@ -5629,11 +5629,11 @@
         <v>228</v>
       </c>
       <c r="B65" s="8">
-        <v>46108.59046716435</v>
+        <v>46108.75713383102</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46191.00466449074</v>
+        <v>46191.171331157406</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>108</v>
@@ -5692,11 +5692,11 @@
         <v>231</v>
       </c>
       <c r="B66" s="5">
-        <v>46114.386456319444</v>
+        <v>46114.55312298611</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46190.00143496528</v>
+        <v>46190.16810163195</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>211</v>
@@ -5743,11 +5743,11 @@
         <v>232</v>
       </c>
       <c r="B67" s="8">
-        <v>46114.38657800926</v>
+        <v>46114.553244675924</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46190.00143679398</v>
+        <v>46190.168103460644</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>233</v>
@@ -5794,11 +5794,11 @@
         <v>234</v>
       </c>
       <c r="B68" s="5">
-        <v>46108.590472094904</v>
+        <v>46108.757138761575</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46114.46471738426</v>
+        <v>46114.631384050925</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>235</v>
@@ -5857,11 +5857,11 @@
         <v>239</v>
       </c>
       <c r="B69" s="8">
-        <v>46111.386135231485</v>
+        <v>46111.55280189815</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46114.46184366898</v>
+        <v>46114.62851033565</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>211</v>
@@ -5908,11 +5908,11 @@
         <v>241</v>
       </c>
       <c r="B70" s="5">
-        <v>46111.386185787036</v>
+        <v>46111.55285245371</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46114.46184373843</v>
+        <v>46114.62851040509</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>242</v>
@@ -5959,11 +5959,11 @@
         <v>244</v>
       </c>
       <c r="B71" s="8">
-        <v>46108.590475000005</v>
+        <v>46108.75714166666</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46118.378899930554</v>
+        <v>46118.545566597226</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>245</v>
@@ -6006,11 +6006,11 @@
         <v>247</v>
       </c>
       <c r="B72" s="5">
-        <v>46108.590477881946</v>
+        <v>46108.75714454861</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46118.38465878472</v>
+        <v>46118.55132545139</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>246</v>
@@ -6067,11 +6067,11 @@
         <v>251</v>
       </c>
       <c r="B73" s="8">
-        <v>46111.33692341435</v>
+        <v>46111.50359008102</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46114.452684918986</v>
+        <v>46114.61935158564</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>252</v>
@@ -6114,11 +6114,11 @@
         <v>254</v>
       </c>
       <c r="B74" s="5">
-        <v>46111.337379502314</v>
+        <v>46111.50404616898</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46114.46662025463</v>
+        <v>46114.63328692129</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>255</v>
@@ -6177,11 +6177,11 @@
         <v>259</v>
       </c>
       <c r="B75" s="8">
-        <v>46111.33739503472</v>
+        <v>46111.50406170139</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46114.46676979167</v>
+        <v>46114.63343645833</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>260</v>
@@ -6240,11 +6240,11 @@
         <v>262</v>
       </c>
       <c r="B76" s="5">
-        <v>46111.33877189815</v>
+        <v>46111.50543856481</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46114.45509847222</v>
+        <v>46114.62176513889</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>263</v>
@@ -6287,11 +6287,11 @@
         <v>265</v>
       </c>
       <c r="B77" s="8">
-        <v>46111.33882837963</v>
+        <v>46111.505495046295</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46114.4672025926</v>
+        <v>46114.633869259254</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>266</v>
@@ -6350,11 +6350,11 @@
         <v>270</v>
       </c>
       <c r="B78" s="5">
-        <v>46111.33893648148</v>
+        <v>46111.50560314815</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46114.46730556713</v>
+        <v>46114.6339722338</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>271</v>
@@ -6413,11 +6413,11 @@
         <v>272</v>
       </c>
       <c r="B79" s="8">
-        <v>46111.35966650463</v>
+        <v>46111.52633317129</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46114.46034972223</v>
+        <v>46114.627016388884</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>211</v>
@@ -6466,11 +6466,11 @@
         <v>275</v>
       </c>
       <c r="B80" s="5">
-        <v>46111.35997770833</v>
+        <v>46111.526644375</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46114.46035050926</v>
+        <v>46114.627017175924</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>216</v>
@@ -6519,11 +6519,11 @@
         <v>277</v>
       </c>
       <c r="B81" s="8">
-        <v>46111.33896791667</v>
+        <v>46111.50563458333</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46114.467399016205</v>
+        <v>46114.63406568287</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>278</v>
@@ -6582,11 +6582,11 @@
         <v>279</v>
       </c>
       <c r="B82" s="5">
-        <v>46111.36024980324</v>
+        <v>46111.526916469906</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46114.460489212965</v>
+        <v>46114.62715587963</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>211</v>
@@ -6635,11 +6635,11 @@
         <v>282</v>
       </c>
       <c r="B83" s="8">
-        <v>46111.360331620366</v>
+        <v>46111.52699828704</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46114.46049005787</v>
+        <v>46114.62715672454</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>216</v>
@@ -6688,11 +6688,11 @@
         <v>285</v>
       </c>
       <c r="B84" s="5">
-        <v>46108.590482175925</v>
+        <v>46108.75714884259</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46118.37890002315</v>
+        <v>46118.54556668982</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>286</v>
@@ -6735,11 +6735,11 @@
         <v>288</v>
       </c>
       <c r="B85" s="8">
-        <v>46108.59048576389</v>
+        <v>46108.75715243055</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46185.01829324074</v>
+        <v>46185.184959907405</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>289</v>
@@ -6798,11 +6798,11 @@
         <v>291</v>
       </c>
       <c r="B86" s="5">
-        <v>46108.59049106481</v>
+        <v>46108.75715773148</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46118.38559032408</v>
+        <v>46118.55225699074</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>57</v>
@@ -6861,11 +6861,11 @@
         <v>293</v>
       </c>
       <c r="B87" s="8">
-        <v>46108.59049682871</v>
+        <v>46108.75716349537</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46111.43095715278</v>
+        <v>46111.59762381944</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>294</v>
@@ -6924,11 +6924,11 @@
         <v>296</v>
       </c>
       <c r="B88" s="5">
-        <v>46108.59050208333</v>
+        <v>46108.75716875</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46111.43116314815</v>
+        <v>46111.59782981481</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>297</v>
@@ -6987,11 +6987,11 @@
         <v>298</v>
       </c>
       <c r="B89" s="8">
-        <v>46108.59050763889</v>
+        <v>46108.75717430556</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46154.7011133912</v>
+        <v>46154.86778005787</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>299</v>
@@ -7050,11 +7050,11 @@
         <v>300</v>
       </c>
       <c r="B90" s="5">
-        <v>46108.590512106486</v>
+        <v>46108.75717877314</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46118.37890193287</v>
+        <v>46118.54556859954</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>301</v>
@@ -7111,11 +7111,11 @@
         <v>303</v>
       </c>
       <c r="B91" s="8">
-        <v>46108.65537042824</v>
+        <v>46108.822037094906</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46185.01829278935</v>
+        <v>46185.18495945602</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>304</v>
@@ -7174,11 +7174,11 @@
         <v>306</v>
       </c>
       <c r="B92" s="5">
-        <v>46108.59051645834</v>
+        <v>46108.757183124995</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46114.45928084491</v>
+        <v>46114.62594751157</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>307</v>
@@ -7221,11 +7221,11 @@
         <v>309</v>
       </c>
       <c r="B93" s="8">
-        <v>46108.59051962963</v>
+        <v>46108.757186296294</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46114.46852113426</v>
+        <v>46114.63518780093</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>310</v>
@@ -7284,11 +7284,11 @@
         <v>311</v>
       </c>
       <c r="B94" s="5">
-        <v>46111.36053535879</v>
+        <v>46111.52720202546</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46118.37890077547</v>
+        <v>46118.545567442125</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>211</v>
@@ -7337,11 +7337,11 @@
         <v>314</v>
       </c>
       <c r="B95" s="8">
-        <v>46111.360671284725</v>
+        <v>46111.52733795139</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46118.37890146991</v>
+        <v>46118.54556813657</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>216</v>
@@ -7390,11 +7390,11 @@
         <v>317</v>
       </c>
       <c r="B96" s="5">
-        <v>46108.59054331019</v>
+        <v>46108.75720997685</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46114.46976324074</v>
+        <v>46114.636429907405</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>318</v>
@@ -7453,11 +7453,11 @@
         <v>319</v>
       </c>
       <c r="B97" s="8">
-        <v>46111.361234131946</v>
+        <v>46111.52790079861</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46114.46109891204</v>
+        <v>46114.627765578705</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>211</v>
@@ -7506,11 +7506,11 @@
         <v>322</v>
       </c>
       <c r="B98" s="5">
-        <v>46111.361294375005</v>
+        <v>46111.52796104166</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46114.4610996875</v>
+        <v>46114.62776635417</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>216</v>
@@ -7559,11 +7559,11 @@
         <v>325</v>
       </c>
       <c r="B99" s="8">
-        <v>46108.59053100694</v>
+        <v>46108.75719767361</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46114.469869988425</v>
+        <v>46114.63653665509</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>326</v>
@@ -7622,11 +7622,11 @@
         <v>327</v>
       </c>
       <c r="B100" s="5">
-        <v>46111.36089966435</v>
+        <v>46111.52756633102</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46118.37890564815</v>
+        <v>46118.54557231482</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>211</v>
@@ -7675,11 +7675,11 @@
         <v>330</v>
       </c>
       <c r="B101" s="8">
-        <v>46111.360955729164</v>
+        <v>46111.527622395835</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46118.37890216435</v>
+        <v>46118.54556883102</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>216</v>
@@ -7728,11 +7728,11 @@
         <v>333</v>
       </c>
       <c r="B102" s="5">
-        <v>46108.59053674768</v>
+        <v>46108.75720341435</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46114.47000480324</v>
+        <v>46114.63667146991</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>334</v>
@@ -7791,11 +7791,11 @@
         <v>335</v>
       </c>
       <c r="B103" s="8">
-        <v>46111.361091377315</v>
+        <v>46111.52775804398</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46118.37890427084</v>
+        <v>46118.545570937495</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>211</v>
@@ -7844,11 +7844,11 @@
         <v>337</v>
       </c>
       <c r="B104" s="5">
-        <v>46111.36114163195</v>
+        <v>46111.52780829861</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46118.37890494213</v>
+        <v>46118.545571608796</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>216</v>
@@ -7897,11 +7897,11 @@
         <v>339</v>
       </c>
       <c r="B105" s="8">
-        <v>46108.59052474537</v>
+        <v>46108.757191412034</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46114.47013482639</v>
+        <v>46114.636801493056</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>340</v>
@@ -7960,11 +7960,11 @@
         <v>341</v>
       </c>
       <c r="B106" s="5">
-        <v>46111.360779826384</v>
+        <v>46111.527446493055</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46118.378902881945</v>
+        <v>46118.545569548616</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>211</v>
@@ -8013,11 +8013,11 @@
         <v>344</v>
       </c>
       <c r="B107" s="8">
-        <v>46111.3607934375</v>
+        <v>46111.52746010417</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46118.37890357639</v>
+        <v>46118.545570243055</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>216</v>
@@ -8066,11 +8066,11 @@
         <v>347</v>
       </c>
       <c r="B108" s="5">
-        <v>46108.5905503588</v>
+        <v>46108.757217025464</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46114.47019792824</v>
+        <v>46114.63686459491</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>348</v>
@@ -8129,11 +8129,11 @@
         <v>349</v>
       </c>
       <c r="B109" s="8">
-        <v>46111.3613652662</v>
+        <v>46111.528031932874</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46114.46184315972</v>
+        <v>46114.62850982639</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>211</v>
@@ -8180,11 +8180,11 @@
         <v>351</v>
       </c>
       <c r="B110" s="5">
-        <v>46111.36144461806</v>
+        <v>46111.52811128472</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46114.46184398148</v>
+        <v>46114.62851064815</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>216</v>
@@ -8231,11 +8231,11 @@
         <v>353</v>
       </c>
       <c r="B111" s="8">
-        <v>46108.590609189814</v>
+        <v>46108.75727585648</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46114.47028635417</v>
+        <v>46114.63695302083</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>354</v>
@@ -8292,11 +8292,11 @@
         <v>356</v>
       </c>
       <c r="B112" s="5">
-        <v>46111.36151453704</v>
+        <v>46111.5281812037</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46114.461976701394</v>
+        <v>46114.62864336805</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>211</v>
@@ -8343,11 +8343,11 @@
         <v>358</v>
       </c>
       <c r="B113" s="8">
-        <v>46111.36159975694</v>
+        <v>46111.528266423615</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46114.461977430554</v>
+        <v>46114.62864409722</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>216</v>
@@ -8394,11 +8394,11 @@
         <v>360</v>
       </c>
       <c r="B114" s="5">
-        <v>46108.59061655092</v>
+        <v>46108.757283217594</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46114.4629612037</v>
+        <v>46114.62962787037</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>361</v>
@@ -8441,11 +8441,11 @@
         <v>363</v>
       </c>
       <c r="B115" s="8">
-        <v>46108.59062076389</v>
+        <v>46108.757287430555</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46114.47057226852</v>
+        <v>46114.63723893519</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>364</v>
@@ -8504,11 +8504,11 @@
         <v>368</v>
       </c>
       <c r="B116" s="5">
-        <v>46111.36179929398</v>
+        <v>46111.52846596065</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46114.46221721065</v>
+        <v>46114.62888387732</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>211</v>
@@ -8555,11 +8555,11 @@
         <v>370</v>
       </c>
       <c r="B117" s="8">
-        <v>46111.36185140046</v>
+        <v>46111.528518067134</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46114.46221803241</v>
+        <v>46114.62888469908</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>216</v>
@@ -8606,11 +8606,11 @@
         <v>372</v>
       </c>
       <c r="B118" s="5">
-        <v>46111.36454934027</v>
+        <v>46111.531216006944</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46114.462218761575</v>
+        <v>46114.62888542824</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>56</v>
@@ -8657,11 +8657,11 @@
         <v>374</v>
       </c>
       <c r="B119" s="8">
-        <v>46111.36462608796</v>
+        <v>46111.53129275463</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46114.46221949074</v>
+        <v>46114.62888615741</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>60</v>
@@ -8708,11 +8708,11 @@
         <v>376</v>
       </c>
       <c r="B120" s="5">
-        <v>46111.36468155093</v>
+        <v>46111.53134821759</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46114.46222025463</v>
+        <v>46114.628886921295</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>377</v>
@@ -8759,11 +8759,11 @@
         <v>379</v>
       </c>
       <c r="B121" s="8">
-        <v>46111.364732754635</v>
+        <v>46111.53139942129</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46114.46222100694</v>
+        <v>46114.62888767361</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>66</v>
@@ -8810,11 +8810,11 @@
         <v>381</v>
       </c>
       <c r="B122" s="5">
-        <v>46111.36677152778</v>
+        <v>46111.53343819444</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46114.46222177084</v>
+        <v>46114.628888437495</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>305</v>
@@ -8861,11 +8861,11 @@
         <v>383</v>
       </c>
       <c r="B123" s="8">
-        <v>46108.590626226855</v>
+        <v>46108.75729289352</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46114.47070795139</v>
+        <v>46114.637374618054</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>384</v>
@@ -8924,11 +8924,11 @@
         <v>386</v>
       </c>
       <c r="B124" s="5">
-        <v>46111.36190743056</v>
+        <v>46111.52857409722</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46114.46243561343</v>
+        <v>46114.629102280094</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>211</v>
@@ -8977,11 +8977,11 @@
         <v>388</v>
       </c>
       <c r="B125" s="8">
-        <v>46111.36200734954</v>
+        <v>46111.528674016205</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46114.462436354166</v>
+        <v>46114.62910302084</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>216</v>
@@ -9030,11 +9030,11 @@
         <v>390</v>
       </c>
       <c r="B126" s="5">
-        <v>46111.364885625</v>
+        <v>46111.531552291664</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46114.462437118054</v>
+        <v>46114.629103784726</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>56</v>
@@ -9083,11 +9083,11 @@
         <v>392</v>
       </c>
       <c r="B127" s="8">
-        <v>46111.36493667824</v>
+        <v>46111.531603344905</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46114.4624378588</v>
+        <v>46114.62910452546</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>60</v>
@@ -9136,11 +9136,11 @@
         <v>394</v>
       </c>
       <c r="B128" s="5">
-        <v>46111.36498171296</v>
+        <v>46111.531648379634</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46114.462438622686</v>
+        <v>46114.62910528935</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>377</v>
@@ -9189,11 +9189,11 @@
         <v>396</v>
       </c>
       <c r="B129" s="8">
-        <v>46111.36503925926</v>
+        <v>46111.531705925925</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46114.462439386574</v>
+        <v>46114.62910605324</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>66</v>
@@ -9242,11 +9242,11 @@
         <v>398</v>
       </c>
       <c r="B130" s="5">
-        <v>46111.36690346064</v>
+        <v>46111.533570127314</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46114.46244017361</v>
+        <v>46114.62910684028</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>305</v>
@@ -9295,11 +9295,11 @@
         <v>400</v>
       </c>
       <c r="B131" s="8">
-        <v>46108.590632638894</v>
+        <v>46108.75729930555</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46114.4708202662</v>
+        <v>46114.63748693287</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>401</v>
@@ -9358,11 +9358,11 @@
         <v>403</v>
       </c>
       <c r="B132" s="5">
-        <v>46111.362133206014</v>
+        <v>46111.528799872685</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46114.46264680555</v>
+        <v>46114.62931347222</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>211</v>
@@ -9409,11 +9409,11 @@
         <v>405</v>
       </c>
       <c r="B133" s="8">
-        <v>46111.36218512732</v>
+        <v>46111.52885179398</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46114.46264762731</v>
+        <v>46114.62931429398</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>216</v>
@@ -9460,11 +9460,11 @@
         <v>407</v>
       </c>
       <c r="B134" s="5">
-        <v>46111.365487731484</v>
+        <v>46111.53215439815</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46114.46264837963</v>
+        <v>46114.629315046295</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>56</v>
@@ -9511,11 +9511,11 @@
         <v>409</v>
       </c>
       <c r="B135" s="8">
-        <v>46111.365539756946</v>
+        <v>46111.53220642361</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46114.4626491088</v>
+        <v>46114.62931577546</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>60</v>
@@ -9562,11 +9562,11 @@
         <v>411</v>
       </c>
       <c r="B136" s="5">
-        <v>46111.36559162037</v>
+        <v>46111.532258287036</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46114.46264986111</v>
+        <v>46114.629316527775</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>377</v>
@@ -9613,11 +9613,11 @@
         <v>413</v>
       </c>
       <c r="B137" s="8">
-        <v>46111.36564334491</v>
+        <v>46111.53231001158</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46114.462650625</v>
+        <v>46114.62931729166</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>66</v>
@@ -9664,11 +9664,11 @@
         <v>415</v>
       </c>
       <c r="B138" s="5">
-        <v>46111.36701570602</v>
+        <v>46111.53368237268</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46114.462651388894</v>
+        <v>46114.62931805555</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>416</v>
@@ -9715,11 +9715,11 @@
         <v>418</v>
       </c>
       <c r="B139" s="8">
-        <v>46108.59063791667</v>
+        <v>46108.757304583334</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46114.47088356482</v>
+        <v>46114.63755023148</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>419</v>
@@ -9778,11 +9778,11 @@
         <v>421</v>
       </c>
       <c r="B140" s="5">
-        <v>46111.36227834491</v>
+        <v>46111.528945011574</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46114.66361440972</v>
+        <v>46114.830281076385</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>211</v>
@@ -9831,11 +9831,11 @@
         <v>423</v>
       </c>
       <c r="B141" s="8">
-        <v>46111.36234425926</v>
+        <v>46111.52901092592</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46114.663636122685</v>
+        <v>46114.830302789356</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>216</v>
@@ -9884,11 +9884,11 @@
         <v>424</v>
       </c>
       <c r="B142" s="5">
-        <v>46111.36580612269</v>
+        <v>46111.53247278935</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46114.66365253473</v>
+        <v>46114.830319201385</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>56</v>
@@ -9937,11 +9937,11 @@
         <v>425</v>
       </c>
       <c r="B143" s="8">
-        <v>46111.36586684028</v>
+        <v>46111.53253350694</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46114.66366907407</v>
+        <v>46114.83033574074</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>60</v>
@@ -9990,11 +9990,11 @@
         <v>426</v>
       </c>
       <c r="B144" s="5">
-        <v>46111.365971747684</v>
+        <v>46111.532638414355</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46114.66368572917</v>
+        <v>46114.83035239583</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>66</v>
@@ -10043,11 +10043,11 @@
         <v>427</v>
       </c>
       <c r="B145" s="8">
-        <v>46111.36591445602</v>
+        <v>46111.53258112269</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46114.66370447917</v>
+        <v>46114.83037114583</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>377</v>
@@ -10096,11 +10096,11 @@
         <v>428</v>
       </c>
       <c r="B146" s="5">
-        <v>46111.36718960648</v>
+        <v>46111.53385627315</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46114.663727604166</v>
+        <v>46114.83039427083</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>305</v>
@@ -10149,11 +10149,11 @@
         <v>429</v>
       </c>
       <c r="B147" s="8">
-        <v>46108.59064383102</v>
+        <v>46108.757310497684</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46114.46296130787</v>
+        <v>46114.62962797454</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>430</v>
@@ -10196,11 +10196,11 @@
         <v>432</v>
       </c>
       <c r="B148" s="5">
-        <v>46108.59064700232</v>
+        <v>46108.75731366898</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46114.470976944445</v>
+        <v>46114.63764361111</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>433</v>
@@ -10259,11 +10259,11 @@
         <v>436</v>
       </c>
       <c r="B149" s="8">
-        <v>46108.59065334491</v>
+        <v>46108.75732001157</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46119.58174862269</v>
+        <v>46119.74841528935</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>437</v>
@@ -10322,11 +10322,11 @@
         <v>439</v>
       </c>
       <c r="B150" s="5">
-        <v>46108.59066239583</v>
+        <v>46108.7573290625</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46114.462961701385</v>
+        <v>46114.62962836806</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>440</v>
@@ -10369,11 +10369,11 @@
         <v>442</v>
       </c>
       <c r="B151" s="8">
-        <v>46108.59066638889</v>
+        <v>46108.75733305556</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46119.581792349534</v>
+        <v>46119.748459016206</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>443</v>
@@ -10432,11 +10432,11 @@
         <v>445</v>
       </c>
       <c r="B152" s="5">
-        <v>46108.59067203704</v>
+        <v>46108.757338703705</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46119.58183587963</v>
+        <v>46119.748502546296</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>446</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -3284,7 +3284,7 @@
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46197.61952591436</v>
+        <v>46198.619161863426</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>97</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -1978,13 +1978,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46108.75671696759</v>
+        <v>46108.590050300925</v>
       </c>
       <c r="C4" s="5">
-        <v>46112.47493710648</v>
+        <v>46112.30827043981</v>
       </c>
       <c r="D4" s="5">
-        <v>46135.64529747685</v>
+        <v>46135.47863081019</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2027,13 +2027,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46108.75679971065</v>
+        <v>46108.59013304398</v>
       </c>
       <c r="C5" s="8">
-        <v>46112.47483056713</v>
+        <v>46112.30816390047</v>
       </c>
       <c r="D5" s="8">
-        <v>46112.47484888889</v>
+        <v>46112.30818222222</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2090,13 +2090,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46108.75680396991</v>
+        <v>46108.59013730324</v>
       </c>
       <c r="C6" s="5">
-        <v>46112.47487329861</v>
+        <v>46112.30820663195</v>
       </c>
       <c r="D6" s="5">
-        <v>46112.47488903935</v>
+        <v>46112.30822237268</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -2153,13 +2153,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8">
-        <v>46108.756807708334</v>
+        <v>46108.59014104167</v>
       </c>
       <c r="C7" s="8">
-        <v>46112.47488707176</v>
+        <v>46112.30822040509</v>
       </c>
       <c r="D7" s="8">
-        <v>46112.474903009264</v>
+        <v>46112.30823634259</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>36</v>
@@ -2216,13 +2216,13 @@
         <v>37</v>
       </c>
       <c r="B8" s="5">
-        <v>46108.75681655093</v>
+        <v>46108.59014988426</v>
       </c>
       <c r="C8" s="5">
-        <v>46112.47490608796</v>
+        <v>46112.3082394213</v>
       </c>
       <c r="D8" s="5">
-        <v>46112.47493739583</v>
+        <v>46112.30827072916</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>38</v>
@@ -2279,13 +2279,13 @@
         <v>40</v>
       </c>
       <c r="B9" s="8">
-        <v>46108.756821944444</v>
+        <v>46108.59015527778</v>
       </c>
       <c r="C9" s="8">
-        <v>46112.4749261574</v>
+        <v>46112.30825949074</v>
       </c>
       <c r="D9" s="8">
-        <v>46112.474944050926</v>
+        <v>46112.30827738426</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>41</v>
@@ -2342,11 +2342,11 @@
         <v>42</v>
       </c>
       <c r="B10" s="5">
-        <v>46108.75672240741</v>
+        <v>46108.590055740744</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46134.89424877315</v>
+        <v>46134.72758210648</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>43</v>
@@ -2389,13 +2389,13 @@
         <v>45</v>
       </c>
       <c r="B11" s="8">
-        <v>46108.75682599537</v>
+        <v>46108.590159328705</v>
       </c>
       <c r="C11" s="8">
-        <v>46134.89423844907</v>
+        <v>46134.72757178241</v>
       </c>
       <c r="D11" s="8">
-        <v>46134.89425622685</v>
+        <v>46134.727589560185</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>46</v>
@@ -2454,11 +2454,11 @@
         <v>50</v>
       </c>
       <c r="B12" s="5">
-        <v>46108.756832071755</v>
+        <v>46108.5901654051</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46111.57919192129</v>
+        <v>46111.41252525463</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -2517,11 +2517,11 @@
         <v>55</v>
       </c>
       <c r="B13" s="8">
-        <v>46111.52928783565</v>
+        <v>46111.362621168984</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46111.57933724537</v>
+        <v>46111.412670578706</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>56</v>
@@ -2570,11 +2570,11 @@
         <v>59</v>
       </c>
       <c r="B14" s="5">
-        <v>46111.529514953705</v>
+        <v>46111.36284828704</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46111.57933446759</v>
+        <v>46111.41266780093</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>60</v>
@@ -2623,11 +2623,11 @@
         <v>62</v>
       </c>
       <c r="B15" s="8">
-        <v>46111.52956931713</v>
+        <v>46111.362902650464</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="8">
-        <v>46111.579331643516</v>
+        <v>46111.41266497685</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>63</v>
@@ -2676,11 +2676,11 @@
         <v>65</v>
       </c>
       <c r="B16" s="5">
-        <v>46111.529618252316</v>
+        <v>46111.362951585645</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46111.579327326384</v>
+        <v>46111.41266065973</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>66</v>
@@ -2729,13 +2729,13 @@
         <v>68</v>
       </c>
       <c r="B17" s="8">
-        <v>46108.756727361106</v>
+        <v>46108.59006069445</v>
       </c>
       <c r="C17" s="8">
-        <v>46112.4753277662</v>
+        <v>46112.30866109954</v>
       </c>
       <c r="D17" s="8">
-        <v>46135.645324363424</v>
+        <v>46135.47865769676</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>69</v>
@@ -2778,13 +2778,13 @@
         <v>71</v>
       </c>
       <c r="B18" s="5">
-        <v>46108.75683751157</v>
+        <v>46108.59017084491</v>
       </c>
       <c r="C18" s="5">
-        <v>46112.47515777778</v>
+        <v>46112.30849111111</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.1503816551</v>
+        <v>46113.983714988426</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>72</v>
@@ -2843,13 +2843,13 @@
         <v>74</v>
       </c>
       <c r="B19" s="8">
-        <v>46108.75684753472</v>
+        <v>46108.59018086806</v>
       </c>
       <c r="C19" s="8">
-        <v>46112.47517543982</v>
+        <v>46112.308508773145</v>
       </c>
       <c r="D19" s="8">
-        <v>46121.17477054398</v>
+        <v>46121.00810387731</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>75</v>
@@ -2908,13 +2908,13 @@
         <v>77</v>
       </c>
       <c r="B20" s="5">
-        <v>46108.756853240746</v>
+        <v>46108.590186574074</v>
       </c>
       <c r="C20" s="5">
-        <v>46112.47523471065</v>
+        <v>46112.30856804398</v>
       </c>
       <c r="D20" s="5">
-        <v>46121.17477048611</v>
+        <v>46121.00810381945</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>78</v>
@@ -2973,13 +2973,13 @@
         <v>80</v>
       </c>
       <c r="B21" s="8">
-        <v>46108.7568596412</v>
+        <v>46108.59019297454</v>
       </c>
       <c r="C21" s="8">
-        <v>46112.47529054398</v>
+        <v>46112.30862387731</v>
       </c>
       <c r="D21" s="8">
-        <v>46121.174770729165</v>
+        <v>46121.0081040625</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>81</v>
@@ -3038,13 +3038,13 @@
         <v>84</v>
       </c>
       <c r="B22" s="5">
-        <v>46108.78930224537</v>
+        <v>46108.62263557871</v>
       </c>
       <c r="C22" s="5">
-        <v>46112.47531421296</v>
+        <v>46112.30864754629</v>
       </c>
       <c r="D22" s="5">
-        <v>46121.17477037037</v>
+        <v>46121.0081037037</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>85</v>
@@ -3103,11 +3103,11 @@
         <v>87</v>
       </c>
       <c r="B23" s="8">
-        <v>46108.756733738424</v>
+        <v>46108.59006707176</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="8">
-        <v>46135.546079583335</v>
+        <v>46135.37941291666</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>88</v>
@@ -3150,13 +3150,13 @@
         <v>90</v>
       </c>
       <c r="B24" s="5">
-        <v>46108.75686861111</v>
+        <v>46108.59020194445</v>
       </c>
       <c r="C24" s="5">
-        <v>46112.47551975695</v>
+        <v>46112.308853090275</v>
       </c>
       <c r="D24" s="5">
-        <v>46116.12918178241</v>
+        <v>46115.96251511574</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>91</v>
@@ -3215,13 +3215,13 @@
         <v>93</v>
       </c>
       <c r="B25" s="8">
-        <v>46108.75687488426</v>
+        <v>46108.59020821759</v>
       </c>
       <c r="C25" s="8">
-        <v>46112.475488310185</v>
+        <v>46112.30882164351</v>
       </c>
       <c r="D25" s="8">
-        <v>46123.19348800926</v>
+        <v>46123.02682134259</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>94</v>
@@ -3280,11 +3280,11 @@
         <v>96</v>
       </c>
       <c r="B26" s="5">
-        <v>46108.75688076389</v>
+        <v>46108.59021409722</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46198.619161863426</v>
+        <v>46198.45249519676</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>97</v>
@@ -3343,13 +3343,13 @@
         <v>101</v>
       </c>
       <c r="B27" s="8">
-        <v>46108.75688663195</v>
+        <v>46108.59021996528</v>
       </c>
       <c r="C27" s="8">
-        <v>46135.546072997684</v>
+        <v>46135.37940633102</v>
       </c>
       <c r="D27" s="8">
-        <v>46135.5462021412</v>
+        <v>46135.37953547454</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>102</v>
@@ -3408,11 +3408,11 @@
         <v>104</v>
       </c>
       <c r="B28" s="5">
-        <v>46108.756897349536</v>
+        <v>46108.59023068287</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46193.195807870376</v>
+        <v>46193.029141203704</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3471,13 +3471,13 @@
         <v>110</v>
       </c>
       <c r="B29" s="8">
-        <v>46108.75690234954</v>
+        <v>46108.590235682874</v>
       </c>
       <c r="C29" s="8">
-        <v>46112.47581297454</v>
+        <v>46112.309146307874</v>
       </c>
       <c r="D29" s="8">
-        <v>46123.19348805556</v>
+        <v>46123.02682138889</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>111</v>
@@ -3536,11 +3536,11 @@
         <v>113</v>
       </c>
       <c r="B30" s="5">
-        <v>46108.75690841435</v>
+        <v>46108.59024174769</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46193.19580785879</v>
+        <v>46193.02914119213</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>114</v>
@@ -3599,13 +3599,13 @@
         <v>116</v>
       </c>
       <c r="B31" s="8">
-        <v>46108.78647824074</v>
+        <v>46108.61981157407</v>
       </c>
       <c r="C31" s="8">
-        <v>46112.47576767361</v>
+        <v>46112.30910100695</v>
       </c>
       <c r="D31" s="8">
-        <v>46123.19348760416</v>
+        <v>46123.0268209375</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>86</v>
@@ -3664,11 +3664,11 @@
         <v>118</v>
       </c>
       <c r="B32" s="5">
-        <v>46108.756741087964</v>
+        <v>46108.5900744213</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46154.867849305556</v>
+        <v>46154.70118263889</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>119</v>
@@ -3711,11 +3711,11 @@
         <v>121</v>
       </c>
       <c r="B33" s="8">
-        <v>46108.75695274306</v>
+        <v>46108.59028607639</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="8">
-        <v>46182.6933722338</v>
+        <v>46182.52670556713</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>122</v>
@@ -3774,13 +3774,13 @@
         <v>126</v>
       </c>
       <c r="B34" s="5">
-        <v>46108.75695775463</v>
+        <v>46108.59029108797</v>
       </c>
       <c r="C34" s="5">
-        <v>46182.69336553241</v>
+        <v>46182.52669886574</v>
       </c>
       <c r="D34" s="5">
-        <v>46182.69336725694</v>
+        <v>46182.52670059028</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>127</v>
@@ -3839,11 +3839,11 @@
         <v>129</v>
       </c>
       <c r="B35" s="8">
-        <v>46108.75696342593</v>
+        <v>46108.590296759256</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46182.69337332176</v>
+        <v>46182.52670665509</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>130</v>
@@ -3902,11 +3902,11 @@
         <v>132</v>
       </c>
       <c r="B36" s="5">
-        <v>46108.75697314815</v>
+        <v>46108.59030648148</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.854331932875</v>
+        <v>46169.6876652662</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>133</v>
@@ -3965,11 +3965,11 @@
         <v>135</v>
       </c>
       <c r="B37" s="8">
-        <v>46108.75697796296</v>
+        <v>46108.5903112963</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46135.54608165509</v>
+        <v>46135.37941498843</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>136</v>
@@ -4028,11 +4028,11 @@
         <v>138</v>
       </c>
       <c r="B38" s="5">
-        <v>46108.7569835301</v>
+        <v>46108.590316863425</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46111.58202451389</v>
+        <v>46111.41535784722</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>139</v>
@@ -4089,11 +4089,11 @@
         <v>141</v>
       </c>
       <c r="B39" s="8">
-        <v>46108.75698832176</v>
+        <v>46108.590321655094</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46183.16750024306</v>
+        <v>46183.000833576385</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>142</v>
@@ -4152,11 +4152,11 @@
         <v>144</v>
       </c>
       <c r="B40" s="5">
-        <v>46108.75699311343</v>
+        <v>46108.59032644676</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46169.85054255787</v>
+        <v>46169.683875891205</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>145</v>
@@ -4215,11 +4215,11 @@
         <v>147</v>
       </c>
       <c r="B41" s="8">
-        <v>46108.75699847222</v>
+        <v>46108.59033180556</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46182.1679962037</v>
+        <v>46182.00132953704</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>148</v>
@@ -4278,11 +4278,11 @@
         <v>150</v>
       </c>
       <c r="B42" s="5">
-        <v>46108.75700357639</v>
+        <v>46108.59033690972</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46182.693445439814</v>
+        <v>46182.52677877314</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>151</v>
@@ -4341,13 +4341,13 @@
         <v>153</v>
       </c>
       <c r="B43" s="8">
-        <v>46108.75700856482</v>
+        <v>46108.59034189815</v>
       </c>
       <c r="C43" s="8">
-        <v>46182.69343829861</v>
+        <v>46182.52677163194</v>
       </c>
       <c r="D43" s="8">
-        <v>46182.69343975694</v>
+        <v>46182.52677309028</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>154</v>
@@ -4406,11 +4406,11 @@
         <v>156</v>
       </c>
       <c r="B44" s="5">
-        <v>46108.757016435186</v>
+        <v>46108.59034976852</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46182.69344646991</v>
+        <v>46182.526779803244</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>157</v>
@@ -4469,11 +4469,11 @@
         <v>159</v>
       </c>
       <c r="B45" s="8">
-        <v>46108.7570218287</v>
+        <v>46108.590355162036</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46182.69344736111</v>
+        <v>46182.52678069445</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>160</v>
@@ -4532,11 +4532,11 @@
         <v>162</v>
       </c>
       <c r="B46" s="5">
-        <v>46108.75702719907</v>
+        <v>46108.590360532406</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46169.850810324075</v>
+        <v>46169.6841436574</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>163</v>
@@ -4595,11 +4595,11 @@
         <v>167</v>
       </c>
       <c r="B47" s="8">
-        <v>46108.75703201389</v>
+        <v>46108.59036534722</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46169.850738877314</v>
+        <v>46169.68407221065</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>109</v>
@@ -4658,11 +4658,11 @@
         <v>169</v>
       </c>
       <c r="B48" s="5">
-        <v>46108.75703761574</v>
+        <v>46108.590370949074</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46169.850767233795</v>
+        <v>46169.68410056713</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>170</v>
@@ -4721,13 +4721,13 @@
         <v>172</v>
       </c>
       <c r="B49" s="8">
-        <v>46108.75704306713</v>
+        <v>46108.59037640046</v>
       </c>
       <c r="C49" s="8">
-        <v>46154.86784248843</v>
+        <v>46154.701175821756</v>
       </c>
       <c r="D49" s="8">
-        <v>46154.86784422454</v>
+        <v>46154.70117755787</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>173</v>
@@ -4786,13 +4786,13 @@
         <v>175</v>
       </c>
       <c r="B50" s="5">
-        <v>46108.75705032407</v>
+        <v>46108.59038365741</v>
       </c>
       <c r="C50" s="5">
-        <v>46154.86746612268</v>
+        <v>46154.70079945602</v>
       </c>
       <c r="D50" s="5">
-        <v>46154.86746811343</v>
+        <v>46154.70080144676</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>176</v>
@@ -4841,13 +4841,13 @@
         <v>178</v>
       </c>
       <c r="B51" s="8">
-        <v>46108.75705728009</v>
+        <v>46108.590390613426</v>
       </c>
       <c r="C51" s="8">
-        <v>46154.86776271991</v>
+        <v>46154.70109605324</v>
       </c>
       <c r="D51" s="8">
-        <v>46154.8677641088</v>
+        <v>46154.70109744213</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>179</v>
@@ -4896,11 +4896,11 @@
         <v>181</v>
       </c>
       <c r="B52" s="5">
-        <v>46108.757061435186</v>
+        <v>46108.590394768515</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46169.85242414352</v>
+        <v>46169.68575747685</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>182</v>
@@ -4959,11 +4959,11 @@
         <v>186</v>
       </c>
       <c r="B53" s="8">
-        <v>46108.75710696759</v>
+        <v>46108.590440300926</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46169.85239162037</v>
+        <v>46169.6857249537</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>115</v>
@@ -5018,11 +5018,11 @@
         <v>188</v>
       </c>
       <c r="B54" s="5">
-        <v>46108.757112928244</v>
+        <v>46108.59044626157</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46169.85241099537</v>
+        <v>46169.6857443287</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>189</v>
@@ -5071,13 +5071,13 @@
         <v>192</v>
       </c>
       <c r="B55" s="8">
-        <v>46111.50860645833</v>
+        <v>46111.341939791666</v>
       </c>
       <c r="C55" s="8">
-        <v>46182.69404997685</v>
+        <v>46182.52738331018</v>
       </c>
       <c r="D55" s="8">
-        <v>46182.69406362269</v>
+        <v>46182.52739695602</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>193</v>
@@ -5136,13 +5136,13 @@
         <v>195</v>
       </c>
       <c r="B56" s="5">
-        <v>46111.508755937495</v>
+        <v>46111.34208927084</v>
       </c>
       <c r="C56" s="5">
-        <v>46182.69350731482</v>
+        <v>46182.52684064815</v>
       </c>
       <c r="D56" s="5">
-        <v>46182.69350877315</v>
+        <v>46182.52684210648</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>196</v>
@@ -5191,13 +5191,13 @@
         <v>198</v>
       </c>
       <c r="B57" s="8">
-        <v>46111.508846770834</v>
+        <v>46111.34218010417</v>
       </c>
       <c r="C57" s="8">
-        <v>46182.69403621528</v>
+        <v>46182.52736954861</v>
       </c>
       <c r="D57" s="8">
-        <v>46182.69403748843</v>
+        <v>46182.52737082176</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>199</v>
@@ -5246,11 +5246,11 @@
         <v>201</v>
       </c>
       <c r="B58" s="5">
-        <v>46108.75711900463</v>
+        <v>46108.59045233796</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46141.52778395833</v>
+        <v>46141.36111729167</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>202</v>
@@ -5293,11 +5293,11 @@
         <v>204</v>
       </c>
       <c r="B59" s="8">
-        <v>46108.75712325232</v>
+        <v>46108.59045658565</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46141.52778434027</v>
+        <v>46141.361117673616</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>205</v>
@@ -5354,11 +5354,11 @@
         <v>210</v>
       </c>
       <c r="B60" s="5">
-        <v>46114.552579166666</v>
+        <v>46114.3859125</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46127.171562662035</v>
+        <v>46127.00489599537</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>211</v>
@@ -5407,11 +5407,11 @@
         <v>215</v>
       </c>
       <c r="B61" s="8">
-        <v>46114.552773240735</v>
+        <v>46114.38610657408</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46127.17156420139</v>
+        <v>46127.00489753472</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>216</v>
@@ -5460,11 +5460,11 @@
         <v>218</v>
       </c>
       <c r="B62" s="5">
-        <v>46108.75712855324</v>
+        <v>46108.590461886575</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46190.19261076389</v>
+        <v>46190.02594409722</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>219</v>
@@ -5523,11 +5523,11 @@
         <v>222</v>
       </c>
       <c r="B63" s="8">
-        <v>46114.55286452547</v>
+        <v>46114.386197858796</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46189.16802</v>
+        <v>46189.00135333333</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>211</v>
@@ -5576,11 +5576,11 @@
         <v>225</v>
       </c>
       <c r="B64" s="5">
-        <v>46114.552966620366</v>
+        <v>46114.38629995371</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46189.16802199074</v>
+        <v>46189.00135532407</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>216</v>
@@ -5629,11 +5629,11 @@
         <v>228</v>
       </c>
       <c r="B65" s="8">
-        <v>46108.75713383102</v>
+        <v>46108.59046716435</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46191.171331157406</v>
+        <v>46191.00466449074</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>108</v>
@@ -5692,11 +5692,11 @@
         <v>231</v>
       </c>
       <c r="B66" s="5">
-        <v>46114.55312298611</v>
+        <v>46114.386456319444</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46190.16810163195</v>
+        <v>46190.00143496528</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>211</v>
@@ -5743,11 +5743,11 @@
         <v>232</v>
       </c>
       <c r="B67" s="8">
-        <v>46114.553244675924</v>
+        <v>46114.38657800926</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46190.168103460644</v>
+        <v>46190.00143679398</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>233</v>
@@ -5794,11 +5794,11 @@
         <v>234</v>
       </c>
       <c r="B68" s="5">
-        <v>46108.757138761575</v>
+        <v>46108.590472094904</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46114.631384050925</v>
+        <v>46114.46471738426</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>235</v>
@@ -5857,11 +5857,11 @@
         <v>239</v>
       </c>
       <c r="B69" s="8">
-        <v>46111.55280189815</v>
+        <v>46111.386135231485</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46114.62851033565</v>
+        <v>46114.46184366898</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>211</v>
@@ -5908,11 +5908,11 @@
         <v>241</v>
       </c>
       <c r="B70" s="5">
-        <v>46111.55285245371</v>
+        <v>46111.386185787036</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46114.62851040509</v>
+        <v>46114.46184373843</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>242</v>
@@ -5959,11 +5959,11 @@
         <v>244</v>
       </c>
       <c r="B71" s="8">
-        <v>46108.75714166666</v>
+        <v>46108.590475000005</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46118.545566597226</v>
+        <v>46118.378899930554</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>245</v>
@@ -6006,11 +6006,11 @@
         <v>247</v>
       </c>
       <c r="B72" s="5">
-        <v>46108.75714454861</v>
+        <v>46108.590477881946</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46118.55132545139</v>
+        <v>46118.38465878472</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>246</v>
@@ -6067,11 +6067,11 @@
         <v>251</v>
       </c>
       <c r="B73" s="8">
-        <v>46111.50359008102</v>
+        <v>46111.33692341435</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46114.61935158564</v>
+        <v>46114.452684918986</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>252</v>
@@ -6114,11 +6114,11 @@
         <v>254</v>
       </c>
       <c r="B74" s="5">
-        <v>46111.50404616898</v>
+        <v>46111.337379502314</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46114.63328692129</v>
+        <v>46114.46662025463</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>255</v>
@@ -6177,11 +6177,11 @@
         <v>259</v>
       </c>
       <c r="B75" s="8">
-        <v>46111.50406170139</v>
+        <v>46111.33739503472</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46114.63343645833</v>
+        <v>46114.46676979167</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>260</v>
@@ -6240,11 +6240,11 @@
         <v>262</v>
       </c>
       <c r="B76" s="5">
-        <v>46111.50543856481</v>
+        <v>46111.33877189815</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46114.62176513889</v>
+        <v>46114.45509847222</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>263</v>
@@ -6287,11 +6287,11 @@
         <v>265</v>
       </c>
       <c r="B77" s="8">
-        <v>46111.505495046295</v>
+        <v>46111.33882837963</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46114.633869259254</v>
+        <v>46114.4672025926</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>266</v>
@@ -6350,11 +6350,11 @@
         <v>270</v>
       </c>
       <c r="B78" s="5">
-        <v>46111.50560314815</v>
+        <v>46111.33893648148</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46114.6339722338</v>
+        <v>46114.46730556713</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>271</v>
@@ -6413,11 +6413,11 @@
         <v>272</v>
       </c>
       <c r="B79" s="8">
-        <v>46111.52633317129</v>
+        <v>46111.35966650463</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46114.627016388884</v>
+        <v>46114.46034972223</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>211</v>
@@ -6466,11 +6466,11 @@
         <v>275</v>
       </c>
       <c r="B80" s="5">
-        <v>46111.526644375</v>
+        <v>46111.35997770833</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46114.627017175924</v>
+        <v>46114.46035050926</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>216</v>
@@ -6519,11 +6519,11 @@
         <v>277</v>
       </c>
       <c r="B81" s="8">
-        <v>46111.50563458333</v>
+        <v>46111.33896791667</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46114.63406568287</v>
+        <v>46114.467399016205</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>278</v>
@@ -6582,11 +6582,11 @@
         <v>279</v>
       </c>
       <c r="B82" s="5">
-        <v>46111.526916469906</v>
+        <v>46111.36024980324</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46114.62715587963</v>
+        <v>46114.460489212965</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>211</v>
@@ -6635,11 +6635,11 @@
         <v>282</v>
       </c>
       <c r="B83" s="8">
-        <v>46111.52699828704</v>
+        <v>46111.360331620366</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46114.62715672454</v>
+        <v>46114.46049005787</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>216</v>
@@ -6688,11 +6688,11 @@
         <v>285</v>
       </c>
       <c r="B84" s="5">
-        <v>46108.75714884259</v>
+        <v>46108.590482175925</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46118.54556668982</v>
+        <v>46118.37890002315</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>286</v>
@@ -6735,11 +6735,11 @@
         <v>288</v>
       </c>
       <c r="B85" s="8">
-        <v>46108.75715243055</v>
+        <v>46108.59048576389</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46185.184959907405</v>
+        <v>46185.01829324074</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>289</v>
@@ -6798,11 +6798,11 @@
         <v>291</v>
       </c>
       <c r="B86" s="5">
-        <v>46108.75715773148</v>
+        <v>46108.59049106481</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46118.55225699074</v>
+        <v>46118.38559032408</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>57</v>
@@ -6861,11 +6861,11 @@
         <v>293</v>
       </c>
       <c r="B87" s="8">
-        <v>46108.75716349537</v>
+        <v>46108.59049682871</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46111.59762381944</v>
+        <v>46111.43095715278</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>294</v>
@@ -6924,11 +6924,11 @@
         <v>296</v>
       </c>
       <c r="B88" s="5">
-        <v>46108.75716875</v>
+        <v>46108.59050208333</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46111.59782981481</v>
+        <v>46111.43116314815</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>297</v>
@@ -6987,11 +6987,11 @@
         <v>298</v>
       </c>
       <c r="B89" s="8">
-        <v>46108.75717430556</v>
+        <v>46108.59050763889</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46154.86778005787</v>
+        <v>46154.7011133912</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>299</v>
@@ -7050,11 +7050,11 @@
         <v>300</v>
       </c>
       <c r="B90" s="5">
-        <v>46108.75717877314</v>
+        <v>46108.590512106486</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46118.54556859954</v>
+        <v>46118.37890193287</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>301</v>
@@ -7111,11 +7111,11 @@
         <v>303</v>
       </c>
       <c r="B91" s="8">
-        <v>46108.822037094906</v>
+        <v>46108.65537042824</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46185.18495945602</v>
+        <v>46185.01829278935</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>304</v>
@@ -7174,11 +7174,11 @@
         <v>306</v>
       </c>
       <c r="B92" s="5">
-        <v>46108.757183124995</v>
+        <v>46108.59051645834</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46114.62594751157</v>
+        <v>46114.45928084491</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>307</v>
@@ -7221,11 +7221,11 @@
         <v>309</v>
       </c>
       <c r="B93" s="8">
-        <v>46108.757186296294</v>
+        <v>46108.59051962963</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46114.63518780093</v>
+        <v>46114.46852113426</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>310</v>
@@ -7284,11 +7284,11 @@
         <v>311</v>
       </c>
       <c r="B94" s="5">
-        <v>46111.52720202546</v>
+        <v>46111.36053535879</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46118.545567442125</v>
+        <v>46118.37890077547</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>211</v>
@@ -7337,11 +7337,11 @@
         <v>314</v>
       </c>
       <c r="B95" s="8">
-        <v>46111.52733795139</v>
+        <v>46111.360671284725</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46118.54556813657</v>
+        <v>46118.37890146991</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>216</v>
@@ -7390,11 +7390,11 @@
         <v>317</v>
       </c>
       <c r="B96" s="5">
-        <v>46108.75720997685</v>
+        <v>46108.59054331019</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46114.636429907405</v>
+        <v>46114.46976324074</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>318</v>
@@ -7453,11 +7453,11 @@
         <v>319</v>
       </c>
       <c r="B97" s="8">
-        <v>46111.52790079861</v>
+        <v>46111.361234131946</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46114.627765578705</v>
+        <v>46114.46109891204</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>211</v>
@@ -7506,11 +7506,11 @@
         <v>322</v>
       </c>
       <c r="B98" s="5">
-        <v>46111.52796104166</v>
+        <v>46111.361294375005</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46114.62776635417</v>
+        <v>46114.4610996875</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>216</v>
@@ -7559,11 +7559,11 @@
         <v>325</v>
       </c>
       <c r="B99" s="8">
-        <v>46108.75719767361</v>
+        <v>46108.59053100694</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46114.63653665509</v>
+        <v>46114.469869988425</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>326</v>
@@ -7622,11 +7622,11 @@
         <v>327</v>
       </c>
       <c r="B100" s="5">
-        <v>46111.52756633102</v>
+        <v>46111.36089966435</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46118.54557231482</v>
+        <v>46118.37890564815</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>211</v>
@@ -7675,11 +7675,11 @@
         <v>330</v>
       </c>
       <c r="B101" s="8">
-        <v>46111.527622395835</v>
+        <v>46111.360955729164</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46118.54556883102</v>
+        <v>46118.37890216435</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>216</v>
@@ -7728,11 +7728,11 @@
         <v>333</v>
       </c>
       <c r="B102" s="5">
-        <v>46108.75720341435</v>
+        <v>46108.59053674768</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46114.63667146991</v>
+        <v>46114.47000480324</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>334</v>
@@ -7791,11 +7791,11 @@
         <v>335</v>
       </c>
       <c r="B103" s="8">
-        <v>46111.52775804398</v>
+        <v>46111.361091377315</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46118.545570937495</v>
+        <v>46118.37890427084</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>211</v>
@@ -7844,11 +7844,11 @@
         <v>337</v>
       </c>
       <c r="B104" s="5">
-        <v>46111.52780829861</v>
+        <v>46111.36114163195</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46118.545571608796</v>
+        <v>46118.37890494213</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>216</v>
@@ -7897,11 +7897,11 @@
         <v>339</v>
       </c>
       <c r="B105" s="8">
-        <v>46108.757191412034</v>
+        <v>46108.59052474537</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46114.636801493056</v>
+        <v>46114.47013482639</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>340</v>
@@ -7960,11 +7960,11 @@
         <v>341</v>
       </c>
       <c r="B106" s="5">
-        <v>46111.527446493055</v>
+        <v>46111.360779826384</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46118.545569548616</v>
+        <v>46118.378902881945</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>211</v>
@@ -8013,11 +8013,11 @@
         <v>344</v>
       </c>
       <c r="B107" s="8">
-        <v>46111.52746010417</v>
+        <v>46111.3607934375</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46118.545570243055</v>
+        <v>46118.37890357639</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>216</v>
@@ -8066,11 +8066,11 @@
         <v>347</v>
       </c>
       <c r="B108" s="5">
-        <v>46108.757217025464</v>
+        <v>46108.5905503588</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46114.63686459491</v>
+        <v>46114.47019792824</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>348</v>
@@ -8129,11 +8129,11 @@
         <v>349</v>
       </c>
       <c r="B109" s="8">
-        <v>46111.528031932874</v>
+        <v>46111.3613652662</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46114.62850982639</v>
+        <v>46114.46184315972</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>211</v>
@@ -8180,11 +8180,11 @@
         <v>351</v>
       </c>
       <c r="B110" s="5">
-        <v>46111.52811128472</v>
+        <v>46111.36144461806</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46114.62851064815</v>
+        <v>46114.46184398148</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>216</v>
@@ -8231,11 +8231,11 @@
         <v>353</v>
       </c>
       <c r="B111" s="8">
-        <v>46108.75727585648</v>
+        <v>46108.590609189814</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46114.63695302083</v>
+        <v>46114.47028635417</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>354</v>
@@ -8292,11 +8292,11 @@
         <v>356</v>
       </c>
       <c r="B112" s="5">
-        <v>46111.5281812037</v>
+        <v>46111.36151453704</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46114.62864336805</v>
+        <v>46114.461976701394</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>211</v>
@@ -8343,11 +8343,11 @@
         <v>358</v>
       </c>
       <c r="B113" s="8">
-        <v>46111.528266423615</v>
+        <v>46111.36159975694</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46114.62864409722</v>
+        <v>46114.461977430554</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>216</v>
@@ -8394,11 +8394,11 @@
         <v>360</v>
       </c>
       <c r="B114" s="5">
-        <v>46108.757283217594</v>
+        <v>46108.59061655092</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46114.62962787037</v>
+        <v>46114.4629612037</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>361</v>
@@ -8441,11 +8441,11 @@
         <v>363</v>
       </c>
       <c r="B115" s="8">
-        <v>46108.757287430555</v>
+        <v>46108.59062076389</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46114.63723893519</v>
+        <v>46114.47057226852</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>364</v>
@@ -8504,11 +8504,11 @@
         <v>368</v>
       </c>
       <c r="B116" s="5">
-        <v>46111.52846596065</v>
+        <v>46111.36179929398</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46114.62888387732</v>
+        <v>46114.46221721065</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>211</v>
@@ -8555,11 +8555,11 @@
         <v>370</v>
       </c>
       <c r="B117" s="8">
-        <v>46111.528518067134</v>
+        <v>46111.36185140046</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46114.62888469908</v>
+        <v>46114.46221803241</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>216</v>
@@ -8606,11 +8606,11 @@
         <v>372</v>
       </c>
       <c r="B118" s="5">
-        <v>46111.531216006944</v>
+        <v>46111.36454934027</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46114.62888542824</v>
+        <v>46114.462218761575</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>56</v>
@@ -8657,11 +8657,11 @@
         <v>374</v>
       </c>
       <c r="B119" s="8">
-        <v>46111.53129275463</v>
+        <v>46111.36462608796</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46114.62888615741</v>
+        <v>46114.46221949074</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>60</v>
@@ -8708,11 +8708,11 @@
         <v>376</v>
       </c>
       <c r="B120" s="5">
-        <v>46111.53134821759</v>
+        <v>46111.36468155093</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46114.628886921295</v>
+        <v>46114.46222025463</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>377</v>
@@ -8759,11 +8759,11 @@
         <v>379</v>
       </c>
       <c r="B121" s="8">
-        <v>46111.53139942129</v>
+        <v>46111.364732754635</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46114.62888767361</v>
+        <v>46114.46222100694</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>66</v>
@@ -8810,11 +8810,11 @@
         <v>381</v>
       </c>
       <c r="B122" s="5">
-        <v>46111.53343819444</v>
+        <v>46111.36677152778</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46114.628888437495</v>
+        <v>46114.46222177084</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>305</v>
@@ -8861,11 +8861,11 @@
         <v>383</v>
       </c>
       <c r="B123" s="8">
-        <v>46108.75729289352</v>
+        <v>46108.590626226855</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46114.637374618054</v>
+        <v>46114.47070795139</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>384</v>
@@ -8924,11 +8924,11 @@
         <v>386</v>
       </c>
       <c r="B124" s="5">
-        <v>46111.52857409722</v>
+        <v>46111.36190743056</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46114.629102280094</v>
+        <v>46114.46243561343</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>211</v>
@@ -8977,11 +8977,11 @@
         <v>388</v>
       </c>
       <c r="B125" s="8">
-        <v>46111.528674016205</v>
+        <v>46111.36200734954</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46114.62910302084</v>
+        <v>46114.462436354166</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>216</v>
@@ -9030,11 +9030,11 @@
         <v>390</v>
       </c>
       <c r="B126" s="5">
-        <v>46111.531552291664</v>
+        <v>46111.364885625</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46114.629103784726</v>
+        <v>46114.462437118054</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>56</v>
@@ -9083,11 +9083,11 @@
         <v>392</v>
       </c>
       <c r="B127" s="8">
-        <v>46111.531603344905</v>
+        <v>46111.36493667824</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46114.62910452546</v>
+        <v>46114.4624378588</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>60</v>
@@ -9136,11 +9136,11 @@
         <v>394</v>
       </c>
       <c r="B128" s="5">
-        <v>46111.531648379634</v>
+        <v>46111.36498171296</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46114.62910528935</v>
+        <v>46114.462438622686</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>377</v>
@@ -9189,11 +9189,11 @@
         <v>396</v>
       </c>
       <c r="B129" s="8">
-        <v>46111.531705925925</v>
+        <v>46111.36503925926</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46114.62910605324</v>
+        <v>46114.462439386574</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>66</v>
@@ -9242,11 +9242,11 @@
         <v>398</v>
       </c>
       <c r="B130" s="5">
-        <v>46111.533570127314</v>
+        <v>46111.36690346064</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46114.62910684028</v>
+        <v>46114.46244017361</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>305</v>
@@ -9295,11 +9295,11 @@
         <v>400</v>
       </c>
       <c r="B131" s="8">
-        <v>46108.75729930555</v>
+        <v>46108.590632638894</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46114.63748693287</v>
+        <v>46114.4708202662</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>401</v>
@@ -9358,11 +9358,11 @@
         <v>403</v>
       </c>
       <c r="B132" s="5">
-        <v>46111.528799872685</v>
+        <v>46111.362133206014</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46114.62931347222</v>
+        <v>46114.46264680555</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>211</v>
@@ -9409,11 +9409,11 @@
         <v>405</v>
       </c>
       <c r="B133" s="8">
-        <v>46111.52885179398</v>
+        <v>46111.36218512732</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46114.62931429398</v>
+        <v>46114.46264762731</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>216</v>
@@ -9460,11 +9460,11 @@
         <v>407</v>
       </c>
       <c r="B134" s="5">
-        <v>46111.53215439815</v>
+        <v>46111.365487731484</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46114.629315046295</v>
+        <v>46114.46264837963</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>56</v>
@@ -9511,11 +9511,11 @@
         <v>409</v>
       </c>
       <c r="B135" s="8">
-        <v>46111.53220642361</v>
+        <v>46111.365539756946</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46114.62931577546</v>
+        <v>46114.4626491088</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>60</v>
@@ -9562,11 +9562,11 @@
         <v>411</v>
       </c>
       <c r="B136" s="5">
-        <v>46111.532258287036</v>
+        <v>46111.36559162037</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46114.629316527775</v>
+        <v>46114.46264986111</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>377</v>
@@ -9613,11 +9613,11 @@
         <v>413</v>
       </c>
       <c r="B137" s="8">
-        <v>46111.53231001158</v>
+        <v>46111.36564334491</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46114.62931729166</v>
+        <v>46114.462650625</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>66</v>
@@ -9664,11 +9664,11 @@
         <v>415</v>
       </c>
       <c r="B138" s="5">
-        <v>46111.53368237268</v>
+        <v>46111.36701570602</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46114.62931805555</v>
+        <v>46114.462651388894</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>416</v>
@@ -9715,11 +9715,11 @@
         <v>418</v>
       </c>
       <c r="B139" s="8">
-        <v>46108.757304583334</v>
+        <v>46108.59063791667</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46114.63755023148</v>
+        <v>46114.47088356482</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>419</v>
@@ -9778,11 +9778,11 @@
         <v>421</v>
       </c>
       <c r="B140" s="5">
-        <v>46111.528945011574</v>
+        <v>46111.36227834491</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46114.830281076385</v>
+        <v>46114.66361440972</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>211</v>
@@ -9831,11 +9831,11 @@
         <v>423</v>
       </c>
       <c r="B141" s="8">
-        <v>46111.52901092592</v>
+        <v>46111.36234425926</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46114.830302789356</v>
+        <v>46114.663636122685</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>216</v>
@@ -9884,11 +9884,11 @@
         <v>424</v>
       </c>
       <c r="B142" s="5">
-        <v>46111.53247278935</v>
+        <v>46111.36580612269</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46114.830319201385</v>
+        <v>46114.66365253473</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>56</v>
@@ -9937,11 +9937,11 @@
         <v>425</v>
       </c>
       <c r="B143" s="8">
-        <v>46111.53253350694</v>
+        <v>46111.36586684028</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46114.83033574074</v>
+        <v>46114.66366907407</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>60</v>
@@ -9990,11 +9990,11 @@
         <v>426</v>
       </c>
       <c r="B144" s="5">
-        <v>46111.532638414355</v>
+        <v>46111.365971747684</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46114.83035239583</v>
+        <v>46114.66368572917</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>66</v>
@@ -10043,11 +10043,11 @@
         <v>427</v>
       </c>
       <c r="B145" s="8">
-        <v>46111.53258112269</v>
+        <v>46111.36591445602</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46114.83037114583</v>
+        <v>46114.66370447917</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>377</v>
@@ -10096,11 +10096,11 @@
         <v>428</v>
       </c>
       <c r="B146" s="5">
-        <v>46111.53385627315</v>
+        <v>46111.36718960648</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46114.83039427083</v>
+        <v>46114.663727604166</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>305</v>
@@ -10149,11 +10149,11 @@
         <v>429</v>
       </c>
       <c r="B147" s="8">
-        <v>46108.757310497684</v>
+        <v>46108.59064383102</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46114.62962797454</v>
+        <v>46114.46296130787</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>430</v>
@@ -10196,11 +10196,11 @@
         <v>432</v>
       </c>
       <c r="B148" s="5">
-        <v>46108.75731366898</v>
+        <v>46108.59064700232</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46114.63764361111</v>
+        <v>46114.470976944445</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>433</v>
@@ -10259,11 +10259,11 @@
         <v>436</v>
       </c>
       <c r="B149" s="8">
-        <v>46108.75732001157</v>
+        <v>46108.59065334491</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46119.74841528935</v>
+        <v>46119.58174862269</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>437</v>
@@ -10322,11 +10322,11 @@
         <v>439</v>
       </c>
       <c r="B150" s="5">
-        <v>46108.7573290625</v>
+        <v>46108.59066239583</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46114.62962836806</v>
+        <v>46114.462961701385</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>440</v>
@@ -10369,11 +10369,11 @@
         <v>442</v>
       </c>
       <c r="B151" s="8">
-        <v>46108.75733305556</v>
+        <v>46108.59066638889</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46119.748459016206</v>
+        <v>46119.581792349534</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>443</v>
@@ -10432,11 +10432,11 @@
         <v>445</v>
       </c>
       <c r="B152" s="5">
-        <v>46108.757338703705</v>
+        <v>46108.59067203704</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46119.748502546296</v>
+        <v>46119.58183587963</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>446</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -1978,13 +1978,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46108.590050300925</v>
+        <v>46108.75671696759</v>
       </c>
       <c r="C4" s="5">
-        <v>46112.30827043981</v>
+        <v>46112.47493710648</v>
       </c>
       <c r="D4" s="5">
-        <v>46135.47863081019</v>
+        <v>46135.64529747685</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2027,13 +2027,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46108.59013304398</v>
+        <v>46108.75679971065</v>
       </c>
       <c r="C5" s="8">
-        <v>46112.30816390047</v>
+        <v>46112.47483056713</v>
       </c>
       <c r="D5" s="8">
-        <v>46112.30818222222</v>
+        <v>46112.47484888889</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2090,13 +2090,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46108.59013730324</v>
+        <v>46108.75680396991</v>
       </c>
       <c r="C6" s="5">
-        <v>46112.30820663195</v>
+        <v>46112.47487329861</v>
       </c>
       <c r="D6" s="5">
-        <v>46112.30822237268</v>
+        <v>46112.47488903935</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -2153,13 +2153,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8">
-        <v>46108.59014104167</v>
+        <v>46108.756807708334</v>
       </c>
       <c r="C7" s="8">
-        <v>46112.30822040509</v>
+        <v>46112.47488707176</v>
       </c>
       <c r="D7" s="8">
-        <v>46112.30823634259</v>
+        <v>46112.474903009264</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>36</v>
@@ -2216,13 +2216,13 @@
         <v>37</v>
       </c>
       <c r="B8" s="5">
-        <v>46108.59014988426</v>
+        <v>46108.75681655093</v>
       </c>
       <c r="C8" s="5">
-        <v>46112.3082394213</v>
+        <v>46112.47490608796</v>
       </c>
       <c r="D8" s="5">
-        <v>46112.30827072916</v>
+        <v>46112.47493739583</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>38</v>
@@ -2279,13 +2279,13 @@
         <v>40</v>
       </c>
       <c r="B9" s="8">
-        <v>46108.59015527778</v>
+        <v>46108.756821944444</v>
       </c>
       <c r="C9" s="8">
-        <v>46112.30825949074</v>
+        <v>46112.4749261574</v>
       </c>
       <c r="D9" s="8">
-        <v>46112.30827738426</v>
+        <v>46112.474944050926</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>41</v>
@@ -2342,11 +2342,11 @@
         <v>42</v>
       </c>
       <c r="B10" s="5">
-        <v>46108.590055740744</v>
+        <v>46108.75672240741</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46134.72758210648</v>
+        <v>46134.89424877315</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>43</v>
@@ -2389,13 +2389,13 @@
         <v>45</v>
       </c>
       <c r="B11" s="8">
-        <v>46108.590159328705</v>
+        <v>46108.75682599537</v>
       </c>
       <c r="C11" s="8">
-        <v>46134.72757178241</v>
+        <v>46134.89423844907</v>
       </c>
       <c r="D11" s="8">
-        <v>46134.727589560185</v>
+        <v>46134.89425622685</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>46</v>
@@ -2454,11 +2454,11 @@
         <v>50</v>
       </c>
       <c r="B12" s="5">
-        <v>46108.5901654051</v>
+        <v>46108.756832071755</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46111.41252525463</v>
+        <v>46111.57919192129</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -2517,11 +2517,11 @@
         <v>55</v>
       </c>
       <c r="B13" s="8">
-        <v>46111.362621168984</v>
+        <v>46111.52928783565</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46111.412670578706</v>
+        <v>46111.57933724537</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>56</v>
@@ -2570,11 +2570,11 @@
         <v>59</v>
       </c>
       <c r="B14" s="5">
-        <v>46111.36284828704</v>
+        <v>46111.529514953705</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46111.41266780093</v>
+        <v>46111.57933446759</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>60</v>
@@ -2623,11 +2623,11 @@
         <v>62</v>
       </c>
       <c r="B15" s="8">
-        <v>46111.362902650464</v>
+        <v>46111.52956931713</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="8">
-        <v>46111.41266497685</v>
+        <v>46111.579331643516</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>63</v>
@@ -2676,11 +2676,11 @@
         <v>65</v>
       </c>
       <c r="B16" s="5">
-        <v>46111.362951585645</v>
+        <v>46111.529618252316</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46111.41266065973</v>
+        <v>46111.579327326384</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>66</v>
@@ -2729,13 +2729,13 @@
         <v>68</v>
       </c>
       <c r="B17" s="8">
-        <v>46108.59006069445</v>
+        <v>46108.756727361106</v>
       </c>
       <c r="C17" s="8">
-        <v>46112.30866109954</v>
+        <v>46112.4753277662</v>
       </c>
       <c r="D17" s="8">
-        <v>46135.47865769676</v>
+        <v>46135.645324363424</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>69</v>
@@ -2778,13 +2778,13 @@
         <v>71</v>
       </c>
       <c r="B18" s="5">
-        <v>46108.59017084491</v>
+        <v>46108.75683751157</v>
       </c>
       <c r="C18" s="5">
-        <v>46112.30849111111</v>
+        <v>46112.47515777778</v>
       </c>
       <c r="D18" s="5">
-        <v>46113.983714988426</v>
+        <v>46114.1503816551</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>72</v>
@@ -2843,13 +2843,13 @@
         <v>74</v>
       </c>
       <c r="B19" s="8">
-        <v>46108.59018086806</v>
+        <v>46108.75684753472</v>
       </c>
       <c r="C19" s="8">
-        <v>46112.308508773145</v>
+        <v>46112.47517543982</v>
       </c>
       <c r="D19" s="8">
-        <v>46121.00810387731</v>
+        <v>46121.17477054398</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>75</v>
@@ -2908,13 +2908,13 @@
         <v>77</v>
       </c>
       <c r="B20" s="5">
-        <v>46108.590186574074</v>
+        <v>46108.756853240746</v>
       </c>
       <c r="C20" s="5">
-        <v>46112.30856804398</v>
+        <v>46112.47523471065</v>
       </c>
       <c r="D20" s="5">
-        <v>46121.00810381945</v>
+        <v>46121.17477048611</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>78</v>
@@ -2973,13 +2973,13 @@
         <v>80</v>
       </c>
       <c r="B21" s="8">
-        <v>46108.59019297454</v>
+        <v>46108.7568596412</v>
       </c>
       <c r="C21" s="8">
-        <v>46112.30862387731</v>
+        <v>46112.47529054398</v>
       </c>
       <c r="D21" s="8">
-        <v>46121.0081040625</v>
+        <v>46121.174770729165</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>81</v>
@@ -3038,13 +3038,13 @@
         <v>84</v>
       </c>
       <c r="B22" s="5">
-        <v>46108.62263557871</v>
+        <v>46108.78930224537</v>
       </c>
       <c r="C22" s="5">
-        <v>46112.30864754629</v>
+        <v>46112.47531421296</v>
       </c>
       <c r="D22" s="5">
-        <v>46121.0081037037</v>
+        <v>46121.17477037037</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>85</v>
@@ -3103,11 +3103,11 @@
         <v>87</v>
       </c>
       <c r="B23" s="8">
-        <v>46108.59006707176</v>
+        <v>46108.756733738424</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="8">
-        <v>46135.37941291666</v>
+        <v>46135.546079583335</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>88</v>
@@ -3150,13 +3150,13 @@
         <v>90</v>
       </c>
       <c r="B24" s="5">
-        <v>46108.59020194445</v>
+        <v>46108.75686861111</v>
       </c>
       <c r="C24" s="5">
-        <v>46112.308853090275</v>
+        <v>46112.47551975695</v>
       </c>
       <c r="D24" s="5">
-        <v>46115.96251511574</v>
+        <v>46116.12918178241</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>91</v>
@@ -3215,13 +3215,13 @@
         <v>93</v>
       </c>
       <c r="B25" s="8">
-        <v>46108.59020821759</v>
+        <v>46108.75687488426</v>
       </c>
       <c r="C25" s="8">
-        <v>46112.30882164351</v>
+        <v>46112.475488310185</v>
       </c>
       <c r="D25" s="8">
-        <v>46123.02682134259</v>
+        <v>46123.19348800926</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>94</v>
@@ -3280,11 +3280,11 @@
         <v>96</v>
       </c>
       <c r="B26" s="5">
-        <v>46108.59021409722</v>
+        <v>46108.75688076389</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46198.45249519676</v>
+        <v>46198.619161863426</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>97</v>
@@ -3343,13 +3343,13 @@
         <v>101</v>
       </c>
       <c r="B27" s="8">
-        <v>46108.59021996528</v>
+        <v>46108.75688663195</v>
       </c>
       <c r="C27" s="8">
-        <v>46135.37940633102</v>
+        <v>46135.546072997684</v>
       </c>
       <c r="D27" s="8">
-        <v>46135.37953547454</v>
+        <v>46135.5462021412</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>102</v>
@@ -3408,11 +3408,11 @@
         <v>104</v>
       </c>
       <c r="B28" s="5">
-        <v>46108.59023068287</v>
+        <v>46108.756897349536</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46193.029141203704</v>
+        <v>46193.195807870376</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3471,13 +3471,13 @@
         <v>110</v>
       </c>
       <c r="B29" s="8">
-        <v>46108.590235682874</v>
+        <v>46108.75690234954</v>
       </c>
       <c r="C29" s="8">
-        <v>46112.309146307874</v>
+        <v>46112.47581297454</v>
       </c>
       <c r="D29" s="8">
-        <v>46123.02682138889</v>
+        <v>46123.19348805556</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>111</v>
@@ -3536,11 +3536,11 @@
         <v>113</v>
       </c>
       <c r="B30" s="5">
-        <v>46108.59024174769</v>
+        <v>46108.75690841435</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46193.02914119213</v>
+        <v>46193.19580785879</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>114</v>
@@ -3599,13 +3599,13 @@
         <v>116</v>
       </c>
       <c r="B31" s="8">
-        <v>46108.61981157407</v>
+        <v>46108.78647824074</v>
       </c>
       <c r="C31" s="8">
-        <v>46112.30910100695</v>
+        <v>46112.47576767361</v>
       </c>
       <c r="D31" s="8">
-        <v>46123.0268209375</v>
+        <v>46123.19348760416</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>86</v>
@@ -3664,11 +3664,11 @@
         <v>118</v>
       </c>
       <c r="B32" s="5">
-        <v>46108.5900744213</v>
+        <v>46108.756741087964</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46154.70118263889</v>
+        <v>46154.867849305556</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>119</v>
@@ -3711,11 +3711,11 @@
         <v>121</v>
       </c>
       <c r="B33" s="8">
-        <v>46108.59028607639</v>
+        <v>46108.75695274306</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="8">
-        <v>46182.52670556713</v>
+        <v>46182.6933722338</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>122</v>
@@ -3774,13 +3774,13 @@
         <v>126</v>
       </c>
       <c r="B34" s="5">
-        <v>46108.59029108797</v>
+        <v>46108.75695775463</v>
       </c>
       <c r="C34" s="5">
-        <v>46182.52669886574</v>
+        <v>46182.69336553241</v>
       </c>
       <c r="D34" s="5">
-        <v>46182.52670059028</v>
+        <v>46182.69336725694</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>127</v>
@@ -3839,11 +3839,11 @@
         <v>129</v>
       </c>
       <c r="B35" s="8">
-        <v>46108.590296759256</v>
+        <v>46108.75696342593</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46182.52670665509</v>
+        <v>46182.69337332176</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>130</v>
@@ -3902,11 +3902,11 @@
         <v>132</v>
       </c>
       <c r="B36" s="5">
-        <v>46108.59030648148</v>
+        <v>46108.75697314815</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.6876652662</v>
+        <v>46169.854331932875</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>133</v>
@@ -3965,11 +3965,11 @@
         <v>135</v>
       </c>
       <c r="B37" s="8">
-        <v>46108.5903112963</v>
+        <v>46108.75697796296</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46135.37941498843</v>
+        <v>46135.54608165509</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>136</v>
@@ -4028,11 +4028,11 @@
         <v>138</v>
       </c>
       <c r="B38" s="5">
-        <v>46108.590316863425</v>
+        <v>46108.7569835301</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46111.41535784722</v>
+        <v>46111.58202451389</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>139</v>
@@ -4089,11 +4089,11 @@
         <v>141</v>
       </c>
       <c r="B39" s="8">
-        <v>46108.590321655094</v>
+        <v>46108.75698832176</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46183.000833576385</v>
+        <v>46183.16750024306</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>142</v>
@@ -4152,11 +4152,11 @@
         <v>144</v>
       </c>
       <c r="B40" s="5">
-        <v>46108.59032644676</v>
+        <v>46108.75699311343</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46169.683875891205</v>
+        <v>46169.85054255787</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>145</v>
@@ -4215,11 +4215,11 @@
         <v>147</v>
       </c>
       <c r="B41" s="8">
-        <v>46108.59033180556</v>
+        <v>46108.75699847222</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46182.00132953704</v>
+        <v>46182.1679962037</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>148</v>
@@ -4278,11 +4278,11 @@
         <v>150</v>
       </c>
       <c r="B42" s="5">
-        <v>46108.59033690972</v>
+        <v>46108.75700357639</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46182.52677877314</v>
+        <v>46182.693445439814</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>151</v>
@@ -4341,13 +4341,13 @@
         <v>153</v>
       </c>
       <c r="B43" s="8">
-        <v>46108.59034189815</v>
+        <v>46108.75700856482</v>
       </c>
       <c r="C43" s="8">
-        <v>46182.52677163194</v>
+        <v>46182.69343829861</v>
       </c>
       <c r="D43" s="8">
-        <v>46182.52677309028</v>
+        <v>46182.69343975694</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>154</v>
@@ -4406,11 +4406,11 @@
         <v>156</v>
       </c>
       <c r="B44" s="5">
-        <v>46108.59034976852</v>
+        <v>46108.757016435186</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46182.526779803244</v>
+        <v>46182.69344646991</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>157</v>
@@ -4469,11 +4469,11 @@
         <v>159</v>
       </c>
       <c r="B45" s="8">
-        <v>46108.590355162036</v>
+        <v>46108.7570218287</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46182.52678069445</v>
+        <v>46182.69344736111</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>160</v>
@@ -4532,11 +4532,11 @@
         <v>162</v>
       </c>
       <c r="B46" s="5">
-        <v>46108.590360532406</v>
+        <v>46108.75702719907</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46169.6841436574</v>
+        <v>46169.850810324075</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>163</v>
@@ -4595,11 +4595,11 @@
         <v>167</v>
       </c>
       <c r="B47" s="8">
-        <v>46108.59036534722</v>
+        <v>46108.75703201389</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46169.68407221065</v>
+        <v>46169.850738877314</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>109</v>
@@ -4658,11 +4658,11 @@
         <v>169</v>
       </c>
       <c r="B48" s="5">
-        <v>46108.590370949074</v>
+        <v>46108.75703761574</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46169.68410056713</v>
+        <v>46169.850767233795</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>170</v>
@@ -4721,13 +4721,13 @@
         <v>172</v>
       </c>
       <c r="B49" s="8">
-        <v>46108.59037640046</v>
+        <v>46108.75704306713</v>
       </c>
       <c r="C49" s="8">
-        <v>46154.701175821756</v>
+        <v>46154.86784248843</v>
       </c>
       <c r="D49" s="8">
-        <v>46154.70117755787</v>
+        <v>46154.86784422454</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>173</v>
@@ -4786,13 +4786,13 @@
         <v>175</v>
       </c>
       <c r="B50" s="5">
-        <v>46108.59038365741</v>
+        <v>46108.75705032407</v>
       </c>
       <c r="C50" s="5">
-        <v>46154.70079945602</v>
+        <v>46154.86746612268</v>
       </c>
       <c r="D50" s="5">
-        <v>46154.70080144676</v>
+        <v>46154.86746811343</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>176</v>
@@ -4841,13 +4841,13 @@
         <v>178</v>
       </c>
       <c r="B51" s="8">
-        <v>46108.590390613426</v>
+        <v>46108.75705728009</v>
       </c>
       <c r="C51" s="8">
-        <v>46154.70109605324</v>
+        <v>46154.86776271991</v>
       </c>
       <c r="D51" s="8">
-        <v>46154.70109744213</v>
+        <v>46154.8677641088</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>179</v>
@@ -4896,11 +4896,11 @@
         <v>181</v>
       </c>
       <c r="B52" s="5">
-        <v>46108.590394768515</v>
+        <v>46108.757061435186</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46169.68575747685</v>
+        <v>46169.85242414352</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>182</v>
@@ -4959,11 +4959,11 @@
         <v>186</v>
       </c>
       <c r="B53" s="8">
-        <v>46108.590440300926</v>
+        <v>46108.75710696759</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46169.6857249537</v>
+        <v>46169.85239162037</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>115</v>
@@ -5018,11 +5018,11 @@
         <v>188</v>
       </c>
       <c r="B54" s="5">
-        <v>46108.59044626157</v>
+        <v>46108.757112928244</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46169.6857443287</v>
+        <v>46169.85241099537</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>189</v>
@@ -5071,13 +5071,13 @@
         <v>192</v>
       </c>
       <c r="B55" s="8">
-        <v>46111.341939791666</v>
+        <v>46111.50860645833</v>
       </c>
       <c r="C55" s="8">
-        <v>46182.52738331018</v>
+        <v>46182.69404997685</v>
       </c>
       <c r="D55" s="8">
-        <v>46182.52739695602</v>
+        <v>46182.69406362269</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>193</v>
@@ -5136,13 +5136,13 @@
         <v>195</v>
       </c>
       <c r="B56" s="5">
-        <v>46111.34208927084</v>
+        <v>46111.508755937495</v>
       </c>
       <c r="C56" s="5">
-        <v>46182.52684064815</v>
+        <v>46182.69350731482</v>
       </c>
       <c r="D56" s="5">
-        <v>46182.52684210648</v>
+        <v>46182.69350877315</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>196</v>
@@ -5191,13 +5191,13 @@
         <v>198</v>
       </c>
       <c r="B57" s="8">
-        <v>46111.34218010417</v>
+        <v>46111.508846770834</v>
       </c>
       <c r="C57" s="8">
-        <v>46182.52736954861</v>
+        <v>46182.69403621528</v>
       </c>
       <c r="D57" s="8">
-        <v>46182.52737082176</v>
+        <v>46182.69403748843</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>199</v>
@@ -5246,11 +5246,11 @@
         <v>201</v>
       </c>
       <c r="B58" s="5">
-        <v>46108.59045233796</v>
+        <v>46108.75711900463</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46141.36111729167</v>
+        <v>46141.52778395833</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>202</v>
@@ -5293,11 +5293,11 @@
         <v>204</v>
       </c>
       <c r="B59" s="8">
-        <v>46108.59045658565</v>
+        <v>46108.75712325232</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46141.361117673616</v>
+        <v>46141.52778434027</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>205</v>
@@ -5354,11 +5354,11 @@
         <v>210</v>
       </c>
       <c r="B60" s="5">
-        <v>46114.3859125</v>
+        <v>46114.552579166666</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46127.00489599537</v>
+        <v>46127.171562662035</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>211</v>
@@ -5407,11 +5407,11 @@
         <v>215</v>
       </c>
       <c r="B61" s="8">
-        <v>46114.38610657408</v>
+        <v>46114.552773240735</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46127.00489753472</v>
+        <v>46127.17156420139</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>216</v>
@@ -5460,11 +5460,11 @@
         <v>218</v>
       </c>
       <c r="B62" s="5">
-        <v>46108.590461886575</v>
+        <v>46108.75712855324</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46190.02594409722</v>
+        <v>46190.19261076389</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>219</v>
@@ -5523,11 +5523,11 @@
         <v>222</v>
       </c>
       <c r="B63" s="8">
-        <v>46114.386197858796</v>
+        <v>46114.55286452547</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46189.00135333333</v>
+        <v>46189.16802</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>211</v>
@@ -5576,11 +5576,11 @@
         <v>225</v>
       </c>
       <c r="B64" s="5">
-        <v>46114.38629995371</v>
+        <v>46114.552966620366</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46189.00135532407</v>
+        <v>46189.16802199074</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>216</v>
@@ -5629,11 +5629,11 @@
         <v>228</v>
       </c>
       <c r="B65" s="8">
-        <v>46108.59046716435</v>
+        <v>46108.75713383102</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46191.00466449074</v>
+        <v>46191.171331157406</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>108</v>
@@ -5692,11 +5692,11 @@
         <v>231</v>
       </c>
       <c r="B66" s="5">
-        <v>46114.386456319444</v>
+        <v>46114.55312298611</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46190.00143496528</v>
+        <v>46190.16810163195</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>211</v>
@@ -5743,11 +5743,11 @@
         <v>232</v>
       </c>
       <c r="B67" s="8">
-        <v>46114.38657800926</v>
+        <v>46114.553244675924</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46190.00143679398</v>
+        <v>46190.168103460644</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>233</v>
@@ -5794,11 +5794,11 @@
         <v>234</v>
       </c>
       <c r="B68" s="5">
-        <v>46108.590472094904</v>
+        <v>46108.757138761575</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46114.46471738426</v>
+        <v>46114.631384050925</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>235</v>
@@ -5857,11 +5857,11 @@
         <v>239</v>
       </c>
       <c r="B69" s="8">
-        <v>46111.386135231485</v>
+        <v>46111.55280189815</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46114.46184366898</v>
+        <v>46114.62851033565</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>211</v>
@@ -5908,11 +5908,11 @@
         <v>241</v>
       </c>
       <c r="B70" s="5">
-        <v>46111.386185787036</v>
+        <v>46111.55285245371</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46114.46184373843</v>
+        <v>46114.62851040509</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>242</v>
@@ -5959,11 +5959,11 @@
         <v>244</v>
       </c>
       <c r="B71" s="8">
-        <v>46108.590475000005</v>
+        <v>46108.75714166666</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46118.378899930554</v>
+        <v>46118.545566597226</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>245</v>
@@ -6006,11 +6006,11 @@
         <v>247</v>
       </c>
       <c r="B72" s="5">
-        <v>46108.590477881946</v>
+        <v>46108.75714454861</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46118.38465878472</v>
+        <v>46118.55132545139</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>246</v>
@@ -6067,11 +6067,11 @@
         <v>251</v>
       </c>
       <c r="B73" s="8">
-        <v>46111.33692341435</v>
+        <v>46111.50359008102</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46114.452684918986</v>
+        <v>46114.61935158564</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>252</v>
@@ -6114,11 +6114,11 @@
         <v>254</v>
       </c>
       <c r="B74" s="5">
-        <v>46111.337379502314</v>
+        <v>46111.50404616898</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46114.46662025463</v>
+        <v>46114.63328692129</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>255</v>
@@ -6177,11 +6177,11 @@
         <v>259</v>
       </c>
       <c r="B75" s="8">
-        <v>46111.33739503472</v>
+        <v>46111.50406170139</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46114.46676979167</v>
+        <v>46114.63343645833</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>260</v>
@@ -6240,11 +6240,11 @@
         <v>262</v>
       </c>
       <c r="B76" s="5">
-        <v>46111.33877189815</v>
+        <v>46111.50543856481</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46114.45509847222</v>
+        <v>46114.62176513889</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>263</v>
@@ -6287,11 +6287,11 @@
         <v>265</v>
       </c>
       <c r="B77" s="8">
-        <v>46111.33882837963</v>
+        <v>46111.505495046295</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46114.4672025926</v>
+        <v>46114.633869259254</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>266</v>
@@ -6350,11 +6350,11 @@
         <v>270</v>
       </c>
       <c r="B78" s="5">
-        <v>46111.33893648148</v>
+        <v>46111.50560314815</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46114.46730556713</v>
+        <v>46114.6339722338</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>271</v>
@@ -6413,11 +6413,11 @@
         <v>272</v>
       </c>
       <c r="B79" s="8">
-        <v>46111.35966650463</v>
+        <v>46111.52633317129</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46114.46034972223</v>
+        <v>46114.627016388884</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>211</v>
@@ -6466,11 +6466,11 @@
         <v>275</v>
       </c>
       <c r="B80" s="5">
-        <v>46111.35997770833</v>
+        <v>46111.526644375</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46114.46035050926</v>
+        <v>46114.627017175924</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>216</v>
@@ -6519,11 +6519,11 @@
         <v>277</v>
       </c>
       <c r="B81" s="8">
-        <v>46111.33896791667</v>
+        <v>46111.50563458333</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46114.467399016205</v>
+        <v>46114.63406568287</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>278</v>
@@ -6582,11 +6582,11 @@
         <v>279</v>
       </c>
       <c r="B82" s="5">
-        <v>46111.36024980324</v>
+        <v>46111.526916469906</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46114.460489212965</v>
+        <v>46114.62715587963</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>211</v>
@@ -6635,11 +6635,11 @@
         <v>282</v>
       </c>
       <c r="B83" s="8">
-        <v>46111.360331620366</v>
+        <v>46111.52699828704</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46114.46049005787</v>
+        <v>46114.62715672454</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>216</v>
@@ -6688,11 +6688,11 @@
         <v>285</v>
       </c>
       <c r="B84" s="5">
-        <v>46108.590482175925</v>
+        <v>46108.75714884259</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46118.37890002315</v>
+        <v>46118.54556668982</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>286</v>
@@ -6735,11 +6735,11 @@
         <v>288</v>
       </c>
       <c r="B85" s="8">
-        <v>46108.59048576389</v>
+        <v>46108.75715243055</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46185.01829324074</v>
+        <v>46185.184959907405</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>289</v>
@@ -6798,11 +6798,11 @@
         <v>291</v>
       </c>
       <c r="B86" s="5">
-        <v>46108.59049106481</v>
+        <v>46108.75715773148</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46118.38559032408</v>
+        <v>46118.55225699074</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>57</v>
@@ -6861,11 +6861,11 @@
         <v>293</v>
       </c>
       <c r="B87" s="8">
-        <v>46108.59049682871</v>
+        <v>46108.75716349537</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46111.43095715278</v>
+        <v>46111.59762381944</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>294</v>
@@ -6924,11 +6924,11 @@
         <v>296</v>
       </c>
       <c r="B88" s="5">
-        <v>46108.59050208333</v>
+        <v>46108.75716875</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46111.43116314815</v>
+        <v>46111.59782981481</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>297</v>
@@ -6987,11 +6987,11 @@
         <v>298</v>
       </c>
       <c r="B89" s="8">
-        <v>46108.59050763889</v>
+        <v>46108.75717430556</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46154.7011133912</v>
+        <v>46154.86778005787</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>299</v>
@@ -7050,11 +7050,11 @@
         <v>300</v>
       </c>
       <c r="B90" s="5">
-        <v>46108.590512106486</v>
+        <v>46108.75717877314</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46118.37890193287</v>
+        <v>46118.54556859954</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>301</v>
@@ -7111,11 +7111,11 @@
         <v>303</v>
       </c>
       <c r="B91" s="8">
-        <v>46108.65537042824</v>
+        <v>46108.822037094906</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46185.01829278935</v>
+        <v>46185.18495945602</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>304</v>
@@ -7174,11 +7174,11 @@
         <v>306</v>
       </c>
       <c r="B92" s="5">
-        <v>46108.59051645834</v>
+        <v>46108.757183124995</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46114.45928084491</v>
+        <v>46114.62594751157</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>307</v>
@@ -7221,11 +7221,11 @@
         <v>309</v>
       </c>
       <c r="B93" s="8">
-        <v>46108.59051962963</v>
+        <v>46108.757186296294</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46114.46852113426</v>
+        <v>46114.63518780093</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>310</v>
@@ -7284,11 +7284,11 @@
         <v>311</v>
       </c>
       <c r="B94" s="5">
-        <v>46111.36053535879</v>
+        <v>46111.52720202546</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46118.37890077547</v>
+        <v>46118.545567442125</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>211</v>
@@ -7337,11 +7337,11 @@
         <v>314</v>
       </c>
       <c r="B95" s="8">
-        <v>46111.360671284725</v>
+        <v>46111.52733795139</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46118.37890146991</v>
+        <v>46118.54556813657</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>216</v>
@@ -7390,11 +7390,11 @@
         <v>317</v>
       </c>
       <c r="B96" s="5">
-        <v>46108.59054331019</v>
+        <v>46108.75720997685</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46114.46976324074</v>
+        <v>46114.636429907405</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>318</v>
@@ -7453,11 +7453,11 @@
         <v>319</v>
       </c>
       <c r="B97" s="8">
-        <v>46111.361234131946</v>
+        <v>46111.52790079861</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46114.46109891204</v>
+        <v>46114.627765578705</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>211</v>
@@ -7506,11 +7506,11 @@
         <v>322</v>
       </c>
       <c r="B98" s="5">
-        <v>46111.361294375005</v>
+        <v>46111.52796104166</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46114.4610996875</v>
+        <v>46114.62776635417</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>216</v>
@@ -7559,11 +7559,11 @@
         <v>325</v>
       </c>
       <c r="B99" s="8">
-        <v>46108.59053100694</v>
+        <v>46108.75719767361</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46114.469869988425</v>
+        <v>46114.63653665509</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>326</v>
@@ -7622,11 +7622,11 @@
         <v>327</v>
       </c>
       <c r="B100" s="5">
-        <v>46111.36089966435</v>
+        <v>46111.52756633102</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46118.37890564815</v>
+        <v>46118.54557231482</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>211</v>
@@ -7675,11 +7675,11 @@
         <v>330</v>
       </c>
       <c r="B101" s="8">
-        <v>46111.360955729164</v>
+        <v>46111.527622395835</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46118.37890216435</v>
+        <v>46118.54556883102</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>216</v>
@@ -7728,11 +7728,11 @@
         <v>333</v>
       </c>
       <c r="B102" s="5">
-        <v>46108.59053674768</v>
+        <v>46108.75720341435</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46114.47000480324</v>
+        <v>46114.63667146991</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>334</v>
@@ -7791,11 +7791,11 @@
         <v>335</v>
       </c>
       <c r="B103" s="8">
-        <v>46111.361091377315</v>
+        <v>46111.52775804398</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46118.37890427084</v>
+        <v>46118.545570937495</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>211</v>
@@ -7844,11 +7844,11 @@
         <v>337</v>
       </c>
       <c r="B104" s="5">
-        <v>46111.36114163195</v>
+        <v>46111.52780829861</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46118.37890494213</v>
+        <v>46118.545571608796</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>216</v>
@@ -7897,11 +7897,11 @@
         <v>339</v>
       </c>
       <c r="B105" s="8">
-        <v>46108.59052474537</v>
+        <v>46108.757191412034</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46114.47013482639</v>
+        <v>46114.636801493056</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>340</v>
@@ -7960,11 +7960,11 @@
         <v>341</v>
       </c>
       <c r="B106" s="5">
-        <v>46111.360779826384</v>
+        <v>46111.527446493055</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46118.378902881945</v>
+        <v>46118.545569548616</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>211</v>
@@ -8013,11 +8013,11 @@
         <v>344</v>
       </c>
       <c r="B107" s="8">
-        <v>46111.3607934375</v>
+        <v>46111.52746010417</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46118.37890357639</v>
+        <v>46118.545570243055</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>216</v>
@@ -8066,11 +8066,11 @@
         <v>347</v>
       </c>
       <c r="B108" s="5">
-        <v>46108.5905503588</v>
+        <v>46108.757217025464</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46114.47019792824</v>
+        <v>46114.63686459491</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>348</v>
@@ -8129,11 +8129,11 @@
         <v>349</v>
       </c>
       <c r="B109" s="8">
-        <v>46111.3613652662</v>
+        <v>46111.528031932874</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46114.46184315972</v>
+        <v>46114.62850982639</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>211</v>
@@ -8180,11 +8180,11 @@
         <v>351</v>
       </c>
       <c r="B110" s="5">
-        <v>46111.36144461806</v>
+        <v>46111.52811128472</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46114.46184398148</v>
+        <v>46114.62851064815</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>216</v>
@@ -8231,11 +8231,11 @@
         <v>353</v>
       </c>
       <c r="B111" s="8">
-        <v>46108.590609189814</v>
+        <v>46108.75727585648</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46114.47028635417</v>
+        <v>46114.63695302083</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>354</v>
@@ -8292,11 +8292,11 @@
         <v>356</v>
       </c>
       <c r="B112" s="5">
-        <v>46111.36151453704</v>
+        <v>46111.5281812037</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46114.461976701394</v>
+        <v>46114.62864336805</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>211</v>
@@ -8343,11 +8343,11 @@
         <v>358</v>
       </c>
       <c r="B113" s="8">
-        <v>46111.36159975694</v>
+        <v>46111.528266423615</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46114.461977430554</v>
+        <v>46114.62864409722</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>216</v>
@@ -8394,11 +8394,11 @@
         <v>360</v>
       </c>
       <c r="B114" s="5">
-        <v>46108.59061655092</v>
+        <v>46108.757283217594</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46114.4629612037</v>
+        <v>46114.62962787037</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>361</v>
@@ -8441,11 +8441,11 @@
         <v>363</v>
       </c>
       <c r="B115" s="8">
-        <v>46108.59062076389</v>
+        <v>46108.757287430555</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46114.47057226852</v>
+        <v>46114.63723893519</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>364</v>
@@ -8504,11 +8504,11 @@
         <v>368</v>
       </c>
       <c r="B116" s="5">
-        <v>46111.36179929398</v>
+        <v>46111.52846596065</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46114.46221721065</v>
+        <v>46114.62888387732</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>211</v>
@@ -8555,11 +8555,11 @@
         <v>370</v>
       </c>
       <c r="B117" s="8">
-        <v>46111.36185140046</v>
+        <v>46111.528518067134</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46114.46221803241</v>
+        <v>46114.62888469908</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>216</v>
@@ -8606,11 +8606,11 @@
         <v>372</v>
       </c>
       <c r="B118" s="5">
-        <v>46111.36454934027</v>
+        <v>46111.531216006944</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46114.462218761575</v>
+        <v>46114.62888542824</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>56</v>
@@ -8657,11 +8657,11 @@
         <v>374</v>
       </c>
       <c r="B119" s="8">
-        <v>46111.36462608796</v>
+        <v>46111.53129275463</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46114.46221949074</v>
+        <v>46114.62888615741</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>60</v>
@@ -8708,11 +8708,11 @@
         <v>376</v>
       </c>
       <c r="B120" s="5">
-        <v>46111.36468155093</v>
+        <v>46111.53134821759</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46114.46222025463</v>
+        <v>46114.628886921295</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>377</v>
@@ -8759,11 +8759,11 @@
         <v>379</v>
       </c>
       <c r="B121" s="8">
-        <v>46111.364732754635</v>
+        <v>46111.53139942129</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46114.46222100694</v>
+        <v>46114.62888767361</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>66</v>
@@ -8810,11 +8810,11 @@
         <v>381</v>
       </c>
       <c r="B122" s="5">
-        <v>46111.36677152778</v>
+        <v>46111.53343819444</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46114.46222177084</v>
+        <v>46114.628888437495</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>305</v>
@@ -8861,11 +8861,11 @@
         <v>383</v>
       </c>
       <c r="B123" s="8">
-        <v>46108.590626226855</v>
+        <v>46108.75729289352</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46114.47070795139</v>
+        <v>46114.637374618054</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>384</v>
@@ -8924,11 +8924,11 @@
         <v>386</v>
       </c>
       <c r="B124" s="5">
-        <v>46111.36190743056</v>
+        <v>46111.52857409722</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46114.46243561343</v>
+        <v>46114.629102280094</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>211</v>
@@ -8977,11 +8977,11 @@
         <v>388</v>
       </c>
       <c r="B125" s="8">
-        <v>46111.36200734954</v>
+        <v>46111.528674016205</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46114.462436354166</v>
+        <v>46114.62910302084</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>216</v>
@@ -9030,11 +9030,11 @@
         <v>390</v>
       </c>
       <c r="B126" s="5">
-        <v>46111.364885625</v>
+        <v>46111.531552291664</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46114.462437118054</v>
+        <v>46114.629103784726</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>56</v>
@@ -9083,11 +9083,11 @@
         <v>392</v>
       </c>
       <c r="B127" s="8">
-        <v>46111.36493667824</v>
+        <v>46111.531603344905</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46114.4624378588</v>
+        <v>46114.62910452546</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>60</v>
@@ -9136,11 +9136,11 @@
         <v>394</v>
       </c>
       <c r="B128" s="5">
-        <v>46111.36498171296</v>
+        <v>46111.531648379634</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46114.462438622686</v>
+        <v>46114.62910528935</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>377</v>
@@ -9189,11 +9189,11 @@
         <v>396</v>
       </c>
       <c r="B129" s="8">
-        <v>46111.36503925926</v>
+        <v>46111.531705925925</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46114.462439386574</v>
+        <v>46114.62910605324</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>66</v>
@@ -9242,11 +9242,11 @@
         <v>398</v>
       </c>
       <c r="B130" s="5">
-        <v>46111.36690346064</v>
+        <v>46111.533570127314</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46114.46244017361</v>
+        <v>46114.62910684028</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>305</v>
@@ -9295,11 +9295,11 @@
         <v>400</v>
       </c>
       <c r="B131" s="8">
-        <v>46108.590632638894</v>
+        <v>46108.75729930555</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46114.4708202662</v>
+        <v>46114.63748693287</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>401</v>
@@ -9358,11 +9358,11 @@
         <v>403</v>
       </c>
       <c r="B132" s="5">
-        <v>46111.362133206014</v>
+        <v>46111.528799872685</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46114.46264680555</v>
+        <v>46114.62931347222</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>211</v>
@@ -9409,11 +9409,11 @@
         <v>405</v>
       </c>
       <c r="B133" s="8">
-        <v>46111.36218512732</v>
+        <v>46111.52885179398</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46114.46264762731</v>
+        <v>46114.62931429398</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>216</v>
@@ -9460,11 +9460,11 @@
         <v>407</v>
       </c>
       <c r="B134" s="5">
-        <v>46111.365487731484</v>
+        <v>46111.53215439815</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46114.46264837963</v>
+        <v>46114.629315046295</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>56</v>
@@ -9511,11 +9511,11 @@
         <v>409</v>
       </c>
       <c r="B135" s="8">
-        <v>46111.365539756946</v>
+        <v>46111.53220642361</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46114.4626491088</v>
+        <v>46114.62931577546</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>60</v>
@@ -9562,11 +9562,11 @@
         <v>411</v>
       </c>
       <c r="B136" s="5">
-        <v>46111.36559162037</v>
+        <v>46111.532258287036</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46114.46264986111</v>
+        <v>46114.629316527775</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>377</v>
@@ -9613,11 +9613,11 @@
         <v>413</v>
       </c>
       <c r="B137" s="8">
-        <v>46111.36564334491</v>
+        <v>46111.53231001158</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46114.462650625</v>
+        <v>46114.62931729166</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>66</v>
@@ -9664,11 +9664,11 @@
         <v>415</v>
       </c>
       <c r="B138" s="5">
-        <v>46111.36701570602</v>
+        <v>46111.53368237268</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46114.462651388894</v>
+        <v>46114.62931805555</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>416</v>
@@ -9715,11 +9715,11 @@
         <v>418</v>
       </c>
       <c r="B139" s="8">
-        <v>46108.59063791667</v>
+        <v>46108.757304583334</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46114.47088356482</v>
+        <v>46114.63755023148</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>419</v>
@@ -9778,11 +9778,11 @@
         <v>421</v>
       </c>
       <c r="B140" s="5">
-        <v>46111.36227834491</v>
+        <v>46111.528945011574</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46114.66361440972</v>
+        <v>46114.830281076385</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>211</v>
@@ -9831,11 +9831,11 @@
         <v>423</v>
       </c>
       <c r="B141" s="8">
-        <v>46111.36234425926</v>
+        <v>46111.52901092592</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46114.663636122685</v>
+        <v>46114.830302789356</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>216</v>
@@ -9884,11 +9884,11 @@
         <v>424</v>
       </c>
       <c r="B142" s="5">
-        <v>46111.36580612269</v>
+        <v>46111.53247278935</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46114.66365253473</v>
+        <v>46114.830319201385</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>56</v>
@@ -9937,11 +9937,11 @@
         <v>425</v>
       </c>
       <c r="B143" s="8">
-        <v>46111.36586684028</v>
+        <v>46111.53253350694</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46114.66366907407</v>
+        <v>46114.83033574074</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>60</v>
@@ -9990,11 +9990,11 @@
         <v>426</v>
       </c>
       <c r="B144" s="5">
-        <v>46111.365971747684</v>
+        <v>46111.532638414355</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46114.66368572917</v>
+        <v>46114.83035239583</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>66</v>
@@ -10043,11 +10043,11 @@
         <v>427</v>
       </c>
       <c r="B145" s="8">
-        <v>46111.36591445602</v>
+        <v>46111.53258112269</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46114.66370447917</v>
+        <v>46114.83037114583</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>377</v>
@@ -10096,11 +10096,11 @@
         <v>428</v>
       </c>
       <c r="B146" s="5">
-        <v>46111.36718960648</v>
+        <v>46111.53385627315</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46114.663727604166</v>
+        <v>46114.83039427083</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>305</v>
@@ -10149,11 +10149,11 @@
         <v>429</v>
       </c>
       <c r="B147" s="8">
-        <v>46108.59064383102</v>
+        <v>46108.757310497684</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46114.46296130787</v>
+        <v>46114.62962797454</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>430</v>
@@ -10196,11 +10196,11 @@
         <v>432</v>
       </c>
       <c r="B148" s="5">
-        <v>46108.59064700232</v>
+        <v>46108.75731366898</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46114.470976944445</v>
+        <v>46114.63764361111</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>433</v>
@@ -10259,11 +10259,11 @@
         <v>436</v>
       </c>
       <c r="B149" s="8">
-        <v>46108.59065334491</v>
+        <v>46108.75732001157</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46119.58174862269</v>
+        <v>46119.74841528935</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>437</v>
@@ -10322,11 +10322,11 @@
         <v>439</v>
       </c>
       <c r="B150" s="5">
-        <v>46108.59066239583</v>
+        <v>46108.7573290625</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46114.462961701385</v>
+        <v>46114.62962836806</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>440</v>
@@ -10369,11 +10369,11 @@
         <v>442</v>
       </c>
       <c r="B151" s="8">
-        <v>46108.59066638889</v>
+        <v>46108.75733305556</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46119.581792349534</v>
+        <v>46119.748459016206</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>443</v>
@@ -10432,11 +10432,11 @@
         <v>445</v>
       </c>
       <c r="B152" s="5">
-        <v>46108.59067203704</v>
+        <v>46108.757338703705</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46119.58183587963</v>
+        <v>46119.748502546296</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>446</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -4473,7 +4473,7 @@
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46182.69344736111</v>
+        <v>46198.81105956019</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>160</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -4599,7 +4599,7 @@
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46169.850738877314</v>
+        <v>46199.16861097222</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>109</v>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46169.85239162037</v>
+        <v>46199.168608900465</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>115</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -4473,7 +4473,7 @@
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46198.81105956019</v>
+        <v>46199.811805694444</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>160</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="448">
   <si>
     <t>50001525- ZITRON PERU METRO DE LIMA  ESTACION 07</t>
   </si>
@@ -512,6 +512,9 @@
   </si>
   <si>
     <t>Generación OC materiales ot 4287 - 4288,Fabricacion a codigo y compras locales ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1213833777483168</t>
@@ -4536,7 +4539,7 @@
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46169.850810324075</v>
+        <v>46203.203189305554</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>163</v>
@@ -4583,8 +4586,8 @@
       <c r="S46" s="6">
         <v>0</v>
       </c>
-      <c r="T46" s="11" t="s">
-        <v>53</v>
+      <c r="T46" s="12" t="s">
+        <v>167</v>
       </c>
       <c r="U46" s="10" t="s">
         <v>54</v>
@@ -4592,7 +4595,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B47" s="8">
         <v>46108.75703201389</v>
@@ -4635,7 +4638,7 @@
         <v>105</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q47" s="8">
         <v>45985</v>
@@ -4655,7 +4658,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B48" s="5">
         <v>46108.75703761574</v>
@@ -4665,7 +4668,7 @@
         <v>46169.850767233795</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
@@ -4698,7 +4701,7 @@
         <v>109</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q48" s="5">
         <v>46007</v>
@@ -4718,7 +4721,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B49" s="8">
         <v>46108.75704306713</v>
@@ -4730,7 +4733,7 @@
         <v>46154.86784422454</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
@@ -4760,7 +4763,7 @@
         <v>119</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>119</v>
@@ -4783,7 +4786,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B50" s="5">
         <v>46108.75705032407</v>
@@ -4795,7 +4798,7 @@
         <v>46154.86746811343</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
@@ -4822,13 +4825,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>111</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4838,7 +4841,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B51" s="8">
         <v>46108.75705728009</v>
@@ -4850,7 +4853,7 @@
         <v>46154.8677641088</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
@@ -4877,13 +4880,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4893,7 +4896,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B52" s="5">
         <v>46108.757061435186</v>
@@ -4903,16 +4906,16 @@
         <v>46169.85242414352</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I52" s="5">
         <v>46195</v>
@@ -4933,7 +4936,7 @@
         <v>119</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>119</v>
@@ -4956,7 +4959,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B53" s="8">
         <v>46108.75710696759</v>
@@ -4972,10 +4975,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I53" s="8">
         <v>46195</v>
@@ -4993,13 +4996,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>114</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5015,7 +5018,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B54" s="5">
         <v>46108.757112928244</v>
@@ -5025,16 +5028,16 @@
         <v>46169.85241099537</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I54" s="5">
         <v>46210</v>
@@ -5052,13 +5055,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5068,7 +5071,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B55" s="8">
         <v>46111.50860645833</v>
@@ -5080,7 +5083,7 @@
         <v>46182.69406362269</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
@@ -5110,7 +5113,7 @@
         <v>119</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5133,7 +5136,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B56" s="5">
         <v>46111.508755937495</v>
@@ -5145,7 +5148,7 @@
         <v>46182.69350877315</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -5172,13 +5175,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>86</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5188,7 +5191,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B57" s="8">
         <v>46111.508846770834</v>
@@ -5200,7 +5203,7 @@
         <v>46182.69403748843</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
@@ -5227,13 +5230,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5243,7 +5246,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B58" s="5">
         <v>46108.75711900463</v>
@@ -5253,7 +5256,7 @@
         <v>46141.52778395833</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -5277,7 +5280,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5290,7 +5293,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B59" s="8">
         <v>46108.75712325232</v>
@@ -5300,16 +5303,16 @@
         <v>46141.52778434027</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="8">
@@ -5325,13 +5328,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q59" s="8">
         <v>46121</v>
@@ -5351,7 +5354,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B60" s="5">
         <v>46114.552579166666</v>
@@ -5361,16 +5364,16 @@
         <v>46127.171562662035</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I60" s="5">
         <v>46121</v>
@@ -5388,13 +5391,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5404,7 +5407,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B61" s="8">
         <v>46114.552773240735</v>
@@ -5414,16 +5417,16 @@
         <v>46127.17156420139</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I61" s="8">
         <v>46121</v>
@@ -5441,13 +5444,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>78</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5457,7 +5460,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B62" s="5">
         <v>46108.75712855324</v>
@@ -5467,16 +5470,16 @@
         <v>46190.19261076389</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I62" s="5">
         <v>46183</v>
@@ -5494,13 +5497,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q62" s="5">
         <v>46183</v>
@@ -5520,7 +5523,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B63" s="8">
         <v>46114.55286452547</v>
@@ -5530,16 +5533,16 @@
         <v>46189.16802</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I63" s="8">
         <v>46183</v>
@@ -5557,13 +5560,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q63" s="9"/>
       <c r="R63" s="9"/>
@@ -5573,7 +5576,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B64" s="5">
         <v>46114.552966620366</v>
@@ -5583,16 +5586,16 @@
         <v>46189.16802199074</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I64" s="5">
         <v>46183</v>
@@ -5610,13 +5613,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5626,7 +5629,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B65" s="8">
         <v>46108.75713383102</v>
@@ -5642,10 +5645,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I65" s="8">
         <v>46190</v>
@@ -5663,13 +5666,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q65" s="8">
         <v>46190</v>
@@ -5689,7 +5692,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B66" s="5">
         <v>46114.55312298611</v>
@@ -5699,16 +5702,16 @@
         <v>46190.16810163195</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="5">
@@ -5727,7 +5730,7 @@
         <v>108</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5740,7 +5743,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B67" s="8">
         <v>46114.553244675924</v>
@@ -5750,16 +5753,16 @@
         <v>46190.168103460644</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="8">
@@ -5778,7 +5781,7 @@
         <v>108</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>26</v>
@@ -5791,7 +5794,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B68" s="5">
         <v>46108.757138761575</v>
@@ -5801,16 +5804,16 @@
         <v>46114.631384050925</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I68" s="5">
         <v>46281</v>
@@ -5828,10 +5831,10 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5854,7 +5857,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B69" s="8">
         <v>46111.55280189815</v>
@@ -5864,16 +5867,16 @@
         <v>46114.62851033565</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -5889,13 +5892,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5905,7 +5908,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B70" s="5">
         <v>46111.55285245371</v>
@@ -5915,16 +5918,16 @@
         <v>46114.62851040509</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -5940,13 +5943,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5956,7 +5959,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B71" s="8">
         <v>46108.75714166666</v>
@@ -5966,7 +5969,7 @@
         <v>46118.545566597226</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -5990,7 +5993,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -6003,7 +6006,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B72" s="5">
         <v>46108.75714454861</v>
@@ -6013,16 +6016,16 @@
         <v>46118.55132545139</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -6038,13 +6041,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q72" s="5">
         <v>46231</v>
@@ -6064,7 +6067,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B73" s="8">
         <v>46111.50359008102</v>
@@ -6074,7 +6077,7 @@
         <v>46114.61935158564</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -6098,7 +6101,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -6111,7 +6114,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B74" s="5">
         <v>46111.50404616898</v>
@@ -6121,16 +6124,16 @@
         <v>46114.63328692129</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I74" s="5">
         <v>46211</v>
@@ -6148,13 +6151,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q74" s="5">
         <v>46211</v>
@@ -6174,7 +6177,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B75" s="8">
         <v>46111.50406170139</v>
@@ -6184,16 +6187,16 @@
         <v>46114.63343645833</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I75" s="8">
         <v>46213</v>
@@ -6211,13 +6214,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q75" s="8">
         <v>46213</v>
@@ -6237,7 +6240,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B76" s="5">
         <v>46111.50543856481</v>
@@ -6247,7 +6250,7 @@
         <v>46114.62176513889</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -6271,7 +6274,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -6284,7 +6287,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B77" s="8">
         <v>46111.505495046295</v>
@@ -6294,16 +6297,16 @@
         <v>46114.633869259254</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I77" s="8">
         <v>46217</v>
@@ -6321,13 +6324,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q77" s="8">
         <v>46217</v>
@@ -6347,7 +6350,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B78" s="5">
         <v>46111.50560314815</v>
@@ -6357,16 +6360,16 @@
         <v>46114.6339722338</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I78" s="5">
         <v>46226</v>
@@ -6384,13 +6387,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q78" s="5">
         <v>46226</v>
@@ -6410,7 +6413,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B79" s="8">
         <v>46111.52633317129</v>
@@ -6420,16 +6423,16 @@
         <v>46114.627016388884</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I79" s="8">
         <v>46226</v>
@@ -6447,13 +6450,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6463,7 +6466,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B80" s="5">
         <v>46111.526644375</v>
@@ -6473,16 +6476,16 @@
         <v>46114.627017175924</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I80" s="5">
         <v>46226</v>
@@ -6500,13 +6503,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6516,7 +6519,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B81" s="8">
         <v>46111.50563458333</v>
@@ -6526,16 +6529,16 @@
         <v>46114.63406568287</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I81" s="8">
         <v>46246</v>
@@ -6553,13 +6556,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q81" s="8">
         <v>46246</v>
@@ -6579,7 +6582,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B82" s="5">
         <v>46111.526916469906</v>
@@ -6589,16 +6592,16 @@
         <v>46114.62715587963</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I82" s="5">
         <v>46246</v>
@@ -6616,13 +6619,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6632,7 +6635,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B83" s="8">
         <v>46111.52699828704</v>
@@ -6642,16 +6645,16 @@
         <v>46114.62715672454</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I83" s="8">
         <v>46246</v>
@@ -6669,13 +6672,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6685,7 +6688,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B84" s="5">
         <v>46108.75714884259</v>
@@ -6695,7 +6698,7 @@
         <v>46118.54556668982</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -6719,7 +6722,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6732,7 +6735,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B85" s="8">
         <v>46108.75715243055</v>
@@ -6742,16 +6745,16 @@
         <v>46185.184959907405</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I85" s="8">
         <v>46183</v>
@@ -6769,13 +6772,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O85" s="9" t="s">
         <v>148</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q85" s="8">
         <v>46183</v>
@@ -6795,7 +6798,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B86" s="5">
         <v>46108.75715773148</v>
@@ -6811,10 +6814,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I86" s="5">
         <v>46239</v>
@@ -6832,13 +6835,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>139</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q86" s="5">
         <v>46239</v>
@@ -6858,7 +6861,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B87" s="8">
         <v>46108.75716349537</v>
@@ -6868,16 +6871,16 @@
         <v>46111.59762381944</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I87" s="8">
         <v>46246</v>
@@ -6895,13 +6898,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O87" s="9" t="s">
         <v>130</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q87" s="8">
         <v>46246</v>
@@ -6921,7 +6924,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B88" s="5">
         <v>46108.75716875</v>
@@ -6931,16 +6934,16 @@
         <v>46111.59782981481</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I88" s="5">
         <v>46273</v>
@@ -6958,13 +6961,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>157</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q88" s="5">
         <v>46273</v>
@@ -6984,7 +6987,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B89" s="8">
         <v>46108.75717430556</v>
@@ -6994,16 +6997,16 @@
         <v>46154.86778005787</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I89" s="8">
         <v>46220</v>
@@ -7021,13 +7024,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q89" s="8">
         <v>46220</v>
@@ -7047,7 +7050,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B90" s="5">
         <v>46108.75717877314</v>
@@ -7057,16 +7060,16 @@
         <v>46118.54556859954</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
@@ -7082,13 +7085,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q90" s="5">
         <v>46231</v>
@@ -7108,7 +7111,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B91" s="8">
         <v>46108.822037094906</v>
@@ -7118,16 +7121,16 @@
         <v>46185.18495945602</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I91" s="8">
         <v>46181</v>
@@ -7145,13 +7148,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q91" s="8">
         <v>46183</v>
@@ -7171,7 +7174,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B92" s="5">
         <v>46108.757183124995</v>
@@ -7181,7 +7184,7 @@
         <v>46114.62594751157</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>25</v>
@@ -7205,7 +7208,7 @@
         <v>26</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>26</v>
@@ -7218,7 +7221,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B93" s="8">
         <v>46108.757186296294</v>
@@ -7228,7 +7231,7 @@
         <v>46114.63518780093</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7255,13 +7258,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q93" s="8">
         <v>46248</v>
@@ -7281,7 +7284,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B94" s="5">
         <v>46111.52720202546</v>
@@ -7291,7 +7294,7 @@
         <v>46118.545567442125</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7318,13 +7321,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7334,7 +7337,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B95" s="8">
         <v>46111.52733795139</v>
@@ -7344,7 +7347,7 @@
         <v>46118.54556813657</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7371,13 +7374,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7387,7 +7390,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B96" s="5">
         <v>46108.75720997685</v>
@@ -7397,7 +7400,7 @@
         <v>46114.636429907405</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7424,13 +7427,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q96" s="5">
         <v>46268</v>
@@ -7450,7 +7453,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B97" s="8">
         <v>46111.52790079861</v>
@@ -7460,7 +7463,7 @@
         <v>46114.627765578705</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7487,13 +7490,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7503,7 +7506,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B98" s="5">
         <v>46111.52796104166</v>
@@ -7513,7 +7516,7 @@
         <v>46114.62776635417</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7540,13 +7543,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7556,7 +7559,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B99" s="8">
         <v>46108.75719767361</v>
@@ -7566,7 +7569,7 @@
         <v>46114.63653665509</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7593,13 +7596,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q99" s="8">
         <v>46272</v>
@@ -7619,7 +7622,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B100" s="5">
         <v>46111.52756633102</v>
@@ -7629,7 +7632,7 @@
         <v>46118.54557231482</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7656,13 +7659,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7672,7 +7675,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B101" s="8">
         <v>46111.527622395835</v>
@@ -7682,7 +7685,7 @@
         <v>46118.54556883102</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7709,13 +7712,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7725,7 +7728,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B102" s="5">
         <v>46108.75720341435</v>
@@ -7735,7 +7738,7 @@
         <v>46114.63667146991</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7762,13 +7765,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q102" s="5">
         <v>46274</v>
@@ -7788,7 +7791,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B103" s="8">
         <v>46111.52775804398</v>
@@ -7798,7 +7801,7 @@
         <v>46118.545570937495</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7825,13 +7828,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -7841,7 +7844,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B104" s="5">
         <v>46111.52780829861</v>
@@ -7851,7 +7854,7 @@
         <v>46118.545571608796</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7878,13 +7881,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7894,7 +7897,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B105" s="8">
         <v>46108.757191412034</v>
@@ -7904,7 +7907,7 @@
         <v>46114.636801493056</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -7931,13 +7934,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q105" s="8">
         <v>46276</v>
@@ -7957,7 +7960,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B106" s="5">
         <v>46111.527446493055</v>
@@ -7967,7 +7970,7 @@
         <v>46118.545569548616</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7994,13 +7997,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8010,7 +8013,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B107" s="8">
         <v>46111.52746010417</v>
@@ -8020,7 +8023,7 @@
         <v>46118.545570243055</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -8047,13 +8050,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -8063,7 +8066,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B108" s="5">
         <v>46108.757217025464</v>
@@ -8073,7 +8076,7 @@
         <v>46114.63686459491</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8100,13 +8103,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q108" s="5">
         <v>46280</v>
@@ -8126,7 +8129,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B109" s="8">
         <v>46111.528031932874</v>
@@ -8136,7 +8139,7 @@
         <v>46114.62850982639</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8161,13 +8164,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8177,7 +8180,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B110" s="5">
         <v>46111.52811128472</v>
@@ -8187,7 +8190,7 @@
         <v>46114.62851064815</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8212,13 +8215,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8228,7 +8231,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B111" s="8">
         <v>46108.75727585648</v>
@@ -8238,7 +8241,7 @@
         <v>46114.63695302083</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8263,13 +8266,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q111" s="8">
         <v>46286</v>
@@ -8289,7 +8292,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B112" s="5">
         <v>46111.5281812037</v>
@@ -8299,7 +8302,7 @@
         <v>46114.62864336805</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8324,13 +8327,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8340,7 +8343,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B113" s="8">
         <v>46111.528266423615</v>
@@ -8350,7 +8353,7 @@
         <v>46114.62864409722</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8375,13 +8378,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8391,7 +8394,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B114" s="5">
         <v>46108.757283217594</v>
@@ -8401,7 +8404,7 @@
         <v>46114.62962787037</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>25</v>
@@ -8425,7 +8428,7 @@
         <v>26</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>26</v>
@@ -8438,7 +8441,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B115" s="8">
         <v>46108.757287430555</v>
@@ -8448,16 +8451,16 @@
         <v>46114.63723893519</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I115" s="8">
         <v>46287</v>
@@ -8475,13 +8478,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q115" s="8">
         <v>46287</v>
@@ -8501,7 +8504,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B116" s="5">
         <v>46111.52846596065</v>
@@ -8511,16 +8514,16 @@
         <v>46114.62888387732</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8536,13 +8539,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8552,7 +8555,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B117" s="8">
         <v>46111.528518067134</v>
@@ -8562,16 +8565,16 @@
         <v>46114.62888469908</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="8">
@@ -8587,13 +8590,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8603,7 +8606,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B118" s="5">
         <v>46111.531216006944</v>
@@ -8619,10 +8622,10 @@
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I118" s="6"/>
       <c r="J118" s="5">
@@ -8638,13 +8641,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8654,7 +8657,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B119" s="8">
         <v>46111.53129275463</v>
@@ -8670,10 +8673,10 @@
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I119" s="9"/>
       <c r="J119" s="8">
@@ -8689,13 +8692,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O119" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8705,7 +8708,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B120" s="5">
         <v>46111.53134821759</v>
@@ -8715,16 +8718,16 @@
         <v>46114.628886921295</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
@@ -8740,13 +8743,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8756,7 +8759,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B121" s="8">
         <v>46111.53139942129</v>
@@ -8772,10 +8775,10 @@
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I121" s="9"/>
       <c r="J121" s="8">
@@ -8791,13 +8794,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O121" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8807,7 +8810,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B122" s="5">
         <v>46111.53343819444</v>
@@ -8817,16 +8820,16 @@
         <v>46114.628888437495</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I122" s="6"/>
       <c r="J122" s="5">
@@ -8842,13 +8845,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8858,7 +8861,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B123" s="8">
         <v>46108.75729289352</v>
@@ -8868,7 +8871,7 @@
         <v>46114.637374618054</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -8895,13 +8898,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q123" s="8">
         <v>46288</v>
@@ -8921,7 +8924,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B124" s="5">
         <v>46111.52857409722</v>
@@ -8931,7 +8934,7 @@
         <v>46114.629102280094</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8958,13 +8961,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8974,7 +8977,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B125" s="8">
         <v>46111.528674016205</v>
@@ -8984,7 +8987,7 @@
         <v>46114.62910302084</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -9011,13 +9014,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -9027,7 +9030,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B126" s="5">
         <v>46111.531552291664</v>
@@ -9064,13 +9067,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9080,7 +9083,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B127" s="8">
         <v>46111.531603344905</v>
@@ -9117,13 +9120,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O127" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9133,7 +9136,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B128" s="5">
         <v>46111.531648379634</v>
@@ -9143,7 +9146,7 @@
         <v>46114.62910528935</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9170,13 +9173,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9186,7 +9189,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B129" s="8">
         <v>46111.531705925925</v>
@@ -9223,13 +9226,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O129" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9239,7 +9242,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B130" s="5">
         <v>46111.533570127314</v>
@@ -9249,7 +9252,7 @@
         <v>46114.62910684028</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9276,13 +9279,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9292,7 +9295,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B131" s="8">
         <v>46108.75729930555</v>
@@ -9302,16 +9305,16 @@
         <v>46114.63748693287</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I131" s="8">
         <v>46293</v>
@@ -9329,13 +9332,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q131" s="8">
         <v>46293</v>
@@ -9355,7 +9358,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B132" s="5">
         <v>46111.528799872685</v>
@@ -9365,16 +9368,16 @@
         <v>46114.62931347222</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9390,13 +9393,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9406,7 +9409,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B133" s="8">
         <v>46111.52885179398</v>
@@ -9416,16 +9419,16 @@
         <v>46114.62931429398</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I133" s="9"/>
       <c r="J133" s="8">
@@ -9441,13 +9444,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9457,7 +9460,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B134" s="5">
         <v>46111.53215439815</v>
@@ -9473,10 +9476,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9492,13 +9495,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9508,7 +9511,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B135" s="8">
         <v>46111.53220642361</v>
@@ -9524,10 +9527,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I135" s="9"/>
       <c r="J135" s="8">
@@ -9543,13 +9546,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O135" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9559,7 +9562,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B136" s="5">
         <v>46111.532258287036</v>
@@ -9569,16 +9572,16 @@
         <v>46114.629316527775</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9594,13 +9597,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9610,7 +9613,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B137" s="8">
         <v>46111.53231001158</v>
@@ -9626,10 +9629,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I137" s="9"/>
       <c r="J137" s="8">
@@ -9645,13 +9648,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O137" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -9661,7 +9664,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B138" s="5">
         <v>46111.53368237268</v>
@@ -9671,16 +9674,16 @@
         <v>46114.62931805555</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
@@ -9696,13 +9699,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9712,7 +9715,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B139" s="8">
         <v>46108.757304583334</v>
@@ -9722,16 +9725,16 @@
         <v>46114.63755023148</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I139" s="8">
         <v>46294</v>
@@ -9749,13 +9752,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q139" s="8">
         <v>46294</v>
@@ -9775,7 +9778,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B140" s="5">
         <v>46111.528945011574</v>
@@ -9785,16 +9788,16 @@
         <v>46114.830281076385</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I140" s="5">
         <v>46294</v>
@@ -9812,13 +9815,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9828,7 +9831,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B141" s="8">
         <v>46111.52901092592</v>
@@ -9838,16 +9841,16 @@
         <v>46114.830302789356</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I141" s="8">
         <v>46294</v>
@@ -9865,13 +9868,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -9881,7 +9884,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B142" s="5">
         <v>46111.53247278935</v>
@@ -9897,10 +9900,10 @@
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I142" s="5">
         <v>46294</v>
@@ -9918,13 +9921,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9934,7 +9937,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B143" s="8">
         <v>46111.53253350694</v>
@@ -9950,10 +9953,10 @@
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I143" s="8">
         <v>46294</v>
@@ -9971,13 +9974,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O143" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -9987,7 +9990,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B144" s="5">
         <v>46111.532638414355</v>
@@ -10003,10 +10006,10 @@
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I144" s="5">
         <v>46294</v>
@@ -10024,13 +10027,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10040,7 +10043,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B145" s="8">
         <v>46111.53258112269</v>
@@ -10050,16 +10053,16 @@
         <v>46114.83037114583</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I145" s="8">
         <v>46294</v>
@@ -10077,13 +10080,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -10093,7 +10096,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B146" s="5">
         <v>46111.53385627315</v>
@@ -10103,16 +10106,16 @@
         <v>46114.83039427083</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I146" s="5">
         <v>46294</v>
@@ -10130,13 +10133,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10146,7 +10149,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B147" s="8">
         <v>46108.757310497684</v>
@@ -10156,7 +10159,7 @@
         <v>46114.62962797454</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>25</v>
@@ -10180,7 +10183,7 @@
         <v>26</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P147" s="9" t="s">
         <v>26</v>
@@ -10193,7 +10196,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B148" s="5">
         <v>46108.75731366898</v>
@@ -10203,16 +10206,16 @@
         <v>46114.63764361111</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="I148" s="5">
         <v>46295</v>
@@ -10230,13 +10233,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q148" s="5">
         <v>46295</v>
@@ -10256,7 +10259,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B149" s="8">
         <v>46108.75732001157</v>
@@ -10266,16 +10269,16 @@
         <v>46119.74841528935</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="I149" s="8">
         <v>46295</v>
@@ -10293,13 +10296,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q149" s="8">
         <v>46295</v>
@@ -10319,7 +10322,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B150" s="5">
         <v>46108.7573290625</v>
@@ -10329,7 +10332,7 @@
         <v>46114.62962836806</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>25</v>
@@ -10353,7 +10356,7 @@
         <v>26</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P150" s="6" t="s">
         <v>26</v>
@@ -10366,7 +10369,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B151" s="8">
         <v>46108.75733305556</v>
@@ -10376,7 +10379,7 @@
         <v>46119.748459016206</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
@@ -10403,13 +10406,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q151" s="8">
         <v>46295</v>
@@ -10429,7 +10432,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B152" s="5">
         <v>46108.757338703705</v>
@@ -10439,7 +10442,7 @@
         <v>46119.748502546296</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10466,13 +10469,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Q152" s="5">
         <v>46304</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="448">
   <si>
     <t>50001525- ZITRON PERU METRO DE LIMA  ESTACION 07</t>
   </si>
@@ -283,6 +283,9 @@
     <t>propuesta tableros,propuesta alabes,propuesta tableros,propuesta motor,propuesta alabes,propuesta rodete ot 4287 - 4288,Propuesta Sensores</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
     <t>1213833777465803</t>
   </si>
   <si>
@@ -311,9 +314,6 @@
   </si>
   <si>
     <t>Generación OC Rodete ot 4287 - 4288,Propuesta compras:</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1213833564668775</t>
@@ -1981,13 +1981,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46108.75671696759</v>
+        <v>46108.590050300925</v>
       </c>
       <c r="C4" s="5">
-        <v>46112.47493710648</v>
+        <v>46112.30827043981</v>
       </c>
       <c r="D4" s="5">
-        <v>46135.64529747685</v>
+        <v>46135.47863081019</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2030,13 +2030,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46108.75679971065</v>
+        <v>46108.59013304398</v>
       </c>
       <c r="C5" s="8">
-        <v>46112.47483056713</v>
+        <v>46112.30816390047</v>
       </c>
       <c r="D5" s="8">
-        <v>46112.47484888889</v>
+        <v>46112.30818222222</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2093,13 +2093,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46108.75680396991</v>
+        <v>46108.59013730324</v>
       </c>
       <c r="C6" s="5">
-        <v>46112.47487329861</v>
+        <v>46112.30820663195</v>
       </c>
       <c r="D6" s="5">
-        <v>46112.47488903935</v>
+        <v>46112.30822237268</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -2156,13 +2156,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8">
-        <v>46108.756807708334</v>
+        <v>46108.59014104167</v>
       </c>
       <c r="C7" s="8">
-        <v>46112.47488707176</v>
+        <v>46112.30822040509</v>
       </c>
       <c r="D7" s="8">
-        <v>46112.474903009264</v>
+        <v>46112.30823634259</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>36</v>
@@ -2219,13 +2219,13 @@
         <v>37</v>
       </c>
       <c r="B8" s="5">
-        <v>46108.75681655093</v>
+        <v>46108.59014988426</v>
       </c>
       <c r="C8" s="5">
-        <v>46112.47490608796</v>
+        <v>46112.3082394213</v>
       </c>
       <c r="D8" s="5">
-        <v>46112.47493739583</v>
+        <v>46112.30827072916</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>38</v>
@@ -2282,13 +2282,13 @@
         <v>40</v>
       </c>
       <c r="B9" s="8">
-        <v>46108.756821944444</v>
+        <v>46108.59015527778</v>
       </c>
       <c r="C9" s="8">
-        <v>46112.4749261574</v>
+        <v>46112.30825949074</v>
       </c>
       <c r="D9" s="8">
-        <v>46112.474944050926</v>
+        <v>46112.30827738426</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>41</v>
@@ -2345,11 +2345,11 @@
         <v>42</v>
       </c>
       <c r="B10" s="5">
-        <v>46108.75672240741</v>
+        <v>46108.590055740744</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46134.89424877315</v>
+        <v>46134.72758210648</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>43</v>
@@ -2392,13 +2392,13 @@
         <v>45</v>
       </c>
       <c r="B11" s="8">
-        <v>46108.75682599537</v>
+        <v>46108.590159328705</v>
       </c>
       <c r="C11" s="8">
-        <v>46134.89423844907</v>
+        <v>46134.72757178241</v>
       </c>
       <c r="D11" s="8">
-        <v>46134.89425622685</v>
+        <v>46134.727589560185</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>46</v>
@@ -2457,11 +2457,11 @@
         <v>50</v>
       </c>
       <c r="B12" s="5">
-        <v>46108.756832071755</v>
+        <v>46108.5901654051</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46111.57919192129</v>
+        <v>46111.41252525463</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -2520,11 +2520,11 @@
         <v>55</v>
       </c>
       <c r="B13" s="8">
-        <v>46111.52928783565</v>
+        <v>46111.362621168984</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46111.57933724537</v>
+        <v>46111.412670578706</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>56</v>
@@ -2573,11 +2573,11 @@
         <v>59</v>
       </c>
       <c r="B14" s="5">
-        <v>46111.529514953705</v>
+        <v>46111.36284828704</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46111.57933446759</v>
+        <v>46111.41266780093</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>60</v>
@@ -2626,11 +2626,11 @@
         <v>62</v>
       </c>
       <c r="B15" s="8">
-        <v>46111.52956931713</v>
+        <v>46111.362902650464</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="8">
-        <v>46111.579331643516</v>
+        <v>46111.41266497685</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>63</v>
@@ -2679,11 +2679,11 @@
         <v>65</v>
       </c>
       <c r="B16" s="5">
-        <v>46111.529618252316</v>
+        <v>46111.362951585645</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46111.579327326384</v>
+        <v>46111.41266065973</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>66</v>
@@ -2732,13 +2732,13 @@
         <v>68</v>
       </c>
       <c r="B17" s="8">
-        <v>46108.756727361106</v>
+        <v>46108.59006069445</v>
       </c>
       <c r="C17" s="8">
-        <v>46112.4753277662</v>
+        <v>46112.30866109954</v>
       </c>
       <c r="D17" s="8">
-        <v>46135.645324363424</v>
+        <v>46135.47865769676</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>69</v>
@@ -2781,13 +2781,13 @@
         <v>71</v>
       </c>
       <c r="B18" s="5">
-        <v>46108.75683751157</v>
+        <v>46108.59017084491</v>
       </c>
       <c r="C18" s="5">
-        <v>46112.47515777778</v>
+        <v>46112.30849111111</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.1503816551</v>
+        <v>46113.983714988426</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>72</v>
@@ -2846,13 +2846,13 @@
         <v>74</v>
       </c>
       <c r="B19" s="8">
-        <v>46108.75684753472</v>
+        <v>46108.59018086806</v>
       </c>
       <c r="C19" s="8">
-        <v>46112.47517543982</v>
+        <v>46112.308508773145</v>
       </c>
       <c r="D19" s="8">
-        <v>46121.17477054398</v>
+        <v>46121.00810387731</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>75</v>
@@ -2911,13 +2911,13 @@
         <v>77</v>
       </c>
       <c r="B20" s="5">
-        <v>46108.756853240746</v>
+        <v>46108.590186574074</v>
       </c>
       <c r="C20" s="5">
-        <v>46112.47523471065</v>
+        <v>46112.30856804398</v>
       </c>
       <c r="D20" s="5">
-        <v>46121.17477048611</v>
+        <v>46121.00810381945</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>78</v>
@@ -2976,13 +2976,13 @@
         <v>80</v>
       </c>
       <c r="B21" s="8">
-        <v>46108.7568596412</v>
+        <v>46108.59019297454</v>
       </c>
       <c r="C21" s="8">
-        <v>46112.47529054398</v>
+        <v>46112.30862387731</v>
       </c>
       <c r="D21" s="8">
-        <v>46121.174770729165</v>
+        <v>46121.0081040625</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>81</v>
@@ -3041,13 +3041,13 @@
         <v>84</v>
       </c>
       <c r="B22" s="5">
-        <v>46108.78930224537</v>
+        <v>46108.62263557871</v>
       </c>
       <c r="C22" s="5">
-        <v>46112.47531421296</v>
+        <v>46112.30864754629</v>
       </c>
       <c r="D22" s="5">
-        <v>46121.17477037037</v>
+        <v>46121.0081037037</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>85</v>
@@ -3106,11 +3106,11 @@
         <v>87</v>
       </c>
       <c r="B23" s="8">
-        <v>46108.756733738424</v>
+        <v>46108.59006707176</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="8">
-        <v>46135.546079583335</v>
+        <v>46205.3719346412</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>88</v>
@@ -3146,23 +3146,25 @@
       <c r="R23" s="9"/>
       <c r="S23" s="9"/>
       <c r="T23" s="9"/>
-      <c r="U23" s="9"/>
+      <c r="U23" s="12" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B24" s="5">
-        <v>46108.75686861111</v>
+        <v>46108.59020194445</v>
       </c>
       <c r="C24" s="5">
-        <v>46112.47551975695</v>
+        <v>46112.308853090275</v>
       </c>
       <c r="D24" s="5">
-        <v>46116.12918178241</v>
+        <v>46115.96251511574</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -3195,7 +3197,7 @@
         <v>72</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q24" s="5">
         <v>46114</v>
@@ -3215,19 +3217,19 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B25" s="8">
-        <v>46108.75687488426</v>
+        <v>46108.59020821759</v>
       </c>
       <c r="C25" s="8">
-        <v>46112.475488310185</v>
+        <v>46112.30882164351</v>
       </c>
       <c r="D25" s="8">
-        <v>46123.19348800926</v>
+        <v>46123.02682134259</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
@@ -3260,7 +3262,7 @@
         <v>75</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q25" s="8">
         <v>46121</v>
@@ -3280,26 +3282,28 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B26" s="5">
-        <v>46108.75688076389</v>
-      </c>
-      <c r="C26" s="6"/>
+        <v>46108.59021409722</v>
+      </c>
+      <c r="C26" s="5">
+        <v>46205.371915428244</v>
+      </c>
       <c r="D26" s="5">
-        <v>46198.619161863426</v>
+        <v>46205.371932118054</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I26" s="5">
         <v>46121</v>
@@ -3323,7 +3327,7 @@
         <v>75</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q26" s="5">
         <v>46121</v>
@@ -3332,13 +3336,13 @@
         <v>46122</v>
       </c>
       <c r="S26" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U26" s="12" t="s">
-        <v>100</v>
+      <c r="U26" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -3346,13 +3350,13 @@
         <v>101</v>
       </c>
       <c r="B27" s="8">
-        <v>46108.75688663195</v>
+        <v>46108.59021996528</v>
       </c>
       <c r="C27" s="8">
-        <v>46135.546072997684</v>
+        <v>46135.37940633102</v>
       </c>
       <c r="D27" s="8">
-        <v>46135.5462021412</v>
+        <v>46135.37953547454</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>102</v>
@@ -3411,11 +3415,11 @@
         <v>104</v>
       </c>
       <c r="B28" s="5">
-        <v>46108.756897349536</v>
+        <v>46108.59023068287</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46193.195807870376</v>
+        <v>46193.029141203704</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3466,7 +3470,7 @@
         <v>31</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3474,13 +3478,13 @@
         <v>110</v>
       </c>
       <c r="B29" s="8">
-        <v>46108.75690234954</v>
+        <v>46108.590235682874</v>
       </c>
       <c r="C29" s="8">
-        <v>46112.47581297454</v>
+        <v>46112.309146307874</v>
       </c>
       <c r="D29" s="8">
-        <v>46123.19348805556</v>
+        <v>46123.02682138889</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>111</v>
@@ -3539,11 +3543,11 @@
         <v>113</v>
       </c>
       <c r="B30" s="5">
-        <v>46108.75690841435</v>
+        <v>46108.59024174769</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46193.19580785879</v>
+        <v>46193.02914119213</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>114</v>
@@ -3594,7 +3598,7 @@
         <v>31</v>
       </c>
       <c r="U30" s="12" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3602,13 +3606,13 @@
         <v>116</v>
       </c>
       <c r="B31" s="8">
-        <v>46108.78647824074</v>
+        <v>46108.61981157407</v>
       </c>
       <c r="C31" s="8">
-        <v>46112.47576767361</v>
+        <v>46112.30910100695</v>
       </c>
       <c r="D31" s="8">
-        <v>46123.19348760416</v>
+        <v>46123.0268209375</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>86</v>
@@ -3667,11 +3671,11 @@
         <v>118</v>
       </c>
       <c r="B32" s="5">
-        <v>46108.756741087964</v>
+        <v>46108.5900744213</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46154.867849305556</v>
+        <v>46154.70118263889</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>119</v>
@@ -3714,11 +3718,11 @@
         <v>121</v>
       </c>
       <c r="B33" s="8">
-        <v>46108.75695274306</v>
+        <v>46108.59028607639</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="8">
-        <v>46182.6933722338</v>
+        <v>46182.52670556713</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>122</v>
@@ -3777,13 +3781,13 @@
         <v>126</v>
       </c>
       <c r="B34" s="5">
-        <v>46108.75695775463</v>
+        <v>46108.59029108797</v>
       </c>
       <c r="C34" s="5">
-        <v>46182.69336553241</v>
+        <v>46182.52669886574</v>
       </c>
       <c r="D34" s="5">
-        <v>46182.69336725694</v>
+        <v>46182.52670059028</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>127</v>
@@ -3816,7 +3820,7 @@
         <v>122</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>128</v>
@@ -3842,11 +3846,11 @@
         <v>129</v>
       </c>
       <c r="B35" s="8">
-        <v>46108.75696342593</v>
+        <v>46108.590296759256</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46182.69337332176</v>
+        <v>46182.52670665509</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>130</v>
@@ -3905,11 +3909,11 @@
         <v>132</v>
       </c>
       <c r="B36" s="5">
-        <v>46108.75697314815</v>
+        <v>46108.59030648148</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.854331932875</v>
+        <v>46169.6876652662</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>133</v>
@@ -3968,11 +3972,11 @@
         <v>135</v>
       </c>
       <c r="B37" s="8">
-        <v>46108.75697796296</v>
+        <v>46108.5903112963</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46135.54608165509</v>
+        <v>46135.37941498843</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>136</v>
@@ -4031,11 +4035,11 @@
         <v>138</v>
       </c>
       <c r="B38" s="5">
-        <v>46108.7569835301</v>
+        <v>46108.590316863425</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46111.58202451389</v>
+        <v>46111.41535784722</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>139</v>
@@ -4092,11 +4096,11 @@
         <v>141</v>
       </c>
       <c r="B39" s="8">
-        <v>46108.75698832176</v>
+        <v>46108.590321655094</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46183.16750024306</v>
+        <v>46183.000833576385</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>142</v>
@@ -4155,11 +4159,11 @@
         <v>144</v>
       </c>
       <c r="B40" s="5">
-        <v>46108.75699311343</v>
+        <v>46108.59032644676</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46169.85054255787</v>
+        <v>46205.3719227199</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>145</v>
@@ -4192,7 +4196,7 @@
         <v>142</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>146</v>
@@ -4218,11 +4222,11 @@
         <v>147</v>
       </c>
       <c r="B41" s="8">
-        <v>46108.75699847222</v>
+        <v>46108.59033180556</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46182.1679962037</v>
+        <v>46182.00132953704</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>148</v>
@@ -4281,11 +4285,11 @@
         <v>150</v>
       </c>
       <c r="B42" s="5">
-        <v>46108.75700357639</v>
+        <v>46108.59033690972</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46182.693445439814</v>
+        <v>46182.52677877314</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>151</v>
@@ -4344,13 +4348,13 @@
         <v>153</v>
       </c>
       <c r="B43" s="8">
-        <v>46108.75700856482</v>
+        <v>46108.59034189815</v>
       </c>
       <c r="C43" s="8">
-        <v>46182.69343829861</v>
+        <v>46182.52677163194</v>
       </c>
       <c r="D43" s="8">
-        <v>46182.69343975694</v>
+        <v>46182.52677309028</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>154</v>
@@ -4383,7 +4387,7 @@
         <v>151</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>155</v>
@@ -4409,11 +4413,11 @@
         <v>156</v>
       </c>
       <c r="B44" s="5">
-        <v>46108.757016435186</v>
+        <v>46108.59034976852</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46182.69344646991</v>
+        <v>46182.526779803244</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>157</v>
@@ -4472,11 +4476,11 @@
         <v>159</v>
       </c>
       <c r="B45" s="8">
-        <v>46108.7570218287</v>
+        <v>46108.590355162036</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46199.811805694444</v>
+        <v>46199.64513902778</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>160</v>
@@ -4535,11 +4539,11 @@
         <v>162</v>
       </c>
       <c r="B46" s="5">
-        <v>46108.75702719907</v>
+        <v>46108.590360532406</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46203.203189305554</v>
+        <v>46203.03652263889</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>163</v>
@@ -4598,11 +4602,11 @@
         <v>168</v>
       </c>
       <c r="B47" s="8">
-        <v>46108.75703201389</v>
+        <v>46108.59036534722</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46199.16861097222</v>
+        <v>46199.00194430556</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>109</v>
@@ -4661,11 +4665,11 @@
         <v>170</v>
       </c>
       <c r="B48" s="5">
-        <v>46108.75703761574</v>
+        <v>46108.590370949074</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46169.850767233795</v>
+        <v>46169.68410056713</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>171</v>
@@ -4724,13 +4728,13 @@
         <v>173</v>
       </c>
       <c r="B49" s="8">
-        <v>46108.75704306713</v>
+        <v>46108.59037640046</v>
       </c>
       <c r="C49" s="8">
-        <v>46154.86784248843</v>
+        <v>46154.701175821756</v>
       </c>
       <c r="D49" s="8">
-        <v>46154.86784422454</v>
+        <v>46154.70117755787</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>174</v>
@@ -4789,13 +4793,13 @@
         <v>176</v>
       </c>
       <c r="B50" s="5">
-        <v>46108.75705032407</v>
+        <v>46108.59038365741</v>
       </c>
       <c r="C50" s="5">
-        <v>46154.86746612268</v>
+        <v>46154.70079945602</v>
       </c>
       <c r="D50" s="5">
-        <v>46154.86746811343</v>
+        <v>46154.70080144676</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>177</v>
@@ -4844,13 +4848,13 @@
         <v>179</v>
       </c>
       <c r="B51" s="8">
-        <v>46108.75705728009</v>
+        <v>46108.590390613426</v>
       </c>
       <c r="C51" s="8">
-        <v>46154.86776271991</v>
+        <v>46154.70109605324</v>
       </c>
       <c r="D51" s="8">
-        <v>46154.8677641088</v>
+        <v>46154.70109744213</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>180</v>
@@ -4899,11 +4903,11 @@
         <v>182</v>
       </c>
       <c r="B52" s="5">
-        <v>46108.757061435186</v>
+        <v>46108.590394768515</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46169.85242414352</v>
+        <v>46169.68575747685</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>183</v>
@@ -4954,7 +4958,7 @@
         <v>53</v>
       </c>
       <c r="U52" s="12" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -4962,11 +4966,11 @@
         <v>187</v>
       </c>
       <c r="B53" s="8">
-        <v>46108.75710696759</v>
+        <v>46108.590440300926</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46199.168608900465</v>
+        <v>46199.001942233794</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>115</v>
@@ -5021,11 +5025,11 @@
         <v>189</v>
       </c>
       <c r="B54" s="5">
-        <v>46108.757112928244</v>
+        <v>46108.59044626157</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46169.85241099537</v>
+        <v>46169.6857443287</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -5074,13 +5078,13 @@
         <v>193</v>
       </c>
       <c r="B55" s="8">
-        <v>46111.50860645833</v>
+        <v>46111.341939791666</v>
       </c>
       <c r="C55" s="8">
-        <v>46182.69404997685</v>
+        <v>46182.52738331018</v>
       </c>
       <c r="D55" s="8">
-        <v>46182.69406362269</v>
+        <v>46182.52739695602</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>194</v>
@@ -5139,13 +5143,13 @@
         <v>196</v>
       </c>
       <c r="B56" s="5">
-        <v>46111.508755937495</v>
+        <v>46111.34208927084</v>
       </c>
       <c r="C56" s="5">
-        <v>46182.69350731482</v>
+        <v>46182.52684064815</v>
       </c>
       <c r="D56" s="5">
-        <v>46182.69350877315</v>
+        <v>46182.52684210648</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>197</v>
@@ -5194,13 +5198,13 @@
         <v>199</v>
       </c>
       <c r="B57" s="8">
-        <v>46111.508846770834</v>
+        <v>46111.34218010417</v>
       </c>
       <c r="C57" s="8">
-        <v>46182.69403621528</v>
+        <v>46182.52736954861</v>
       </c>
       <c r="D57" s="8">
-        <v>46182.69403748843</v>
+        <v>46182.52737082176</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>200</v>
@@ -5249,11 +5253,11 @@
         <v>202</v>
       </c>
       <c r="B58" s="5">
-        <v>46108.75711900463</v>
+        <v>46108.59045233796</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46141.52778395833</v>
+        <v>46141.36111729167</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>203</v>
@@ -5296,11 +5300,11 @@
         <v>205</v>
       </c>
       <c r="B59" s="8">
-        <v>46108.75712325232</v>
+        <v>46108.59045658565</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46141.52778434027</v>
+        <v>46141.361117673616</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>206</v>
@@ -5349,7 +5353,7 @@
         <v>31</v>
       </c>
       <c r="U59" s="12" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -5357,11 +5361,11 @@
         <v>211</v>
       </c>
       <c r="B60" s="5">
-        <v>46114.552579166666</v>
+        <v>46114.3859125</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46127.171562662035</v>
+        <v>46127.00489599537</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>212</v>
@@ -5410,11 +5414,11 @@
         <v>216</v>
       </c>
       <c r="B61" s="8">
-        <v>46114.552773240735</v>
+        <v>46114.38610657408</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46127.17156420139</v>
+        <v>46127.00489753472</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>217</v>
@@ -5463,11 +5467,11 @@
         <v>219</v>
       </c>
       <c r="B62" s="5">
-        <v>46108.75712855324</v>
+        <v>46108.590461886575</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46190.19261076389</v>
+        <v>46190.02594409722</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>220</v>
@@ -5526,11 +5530,11 @@
         <v>223</v>
       </c>
       <c r="B63" s="8">
-        <v>46114.55286452547</v>
+        <v>46114.386197858796</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46189.16802</v>
+        <v>46189.00135333333</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>212</v>
@@ -5579,11 +5583,11 @@
         <v>226</v>
       </c>
       <c r="B64" s="5">
-        <v>46114.552966620366</v>
+        <v>46114.38629995371</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46189.16802199074</v>
+        <v>46189.00135532407</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>217</v>
@@ -5632,11 +5636,11 @@
         <v>229</v>
       </c>
       <c r="B65" s="8">
-        <v>46108.75713383102</v>
+        <v>46108.59046716435</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46191.171331157406</v>
+        <v>46191.00466449074</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>108</v>
@@ -5695,11 +5699,11 @@
         <v>232</v>
       </c>
       <c r="B66" s="5">
-        <v>46114.55312298611</v>
+        <v>46114.386456319444</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46190.16810163195</v>
+        <v>46190.00143496528</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>212</v>
@@ -5746,11 +5750,11 @@
         <v>233</v>
       </c>
       <c r="B67" s="8">
-        <v>46114.553244675924</v>
+        <v>46114.38657800926</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46190.168103460644</v>
+        <v>46190.00143679398</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>234</v>
@@ -5797,11 +5801,11 @@
         <v>235</v>
       </c>
       <c r="B68" s="5">
-        <v>46108.757138761575</v>
+        <v>46108.590472094904</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46114.631384050925</v>
+        <v>46114.46471738426</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>236</v>
@@ -5860,11 +5864,11 @@
         <v>240</v>
       </c>
       <c r="B69" s="8">
-        <v>46111.55280189815</v>
+        <v>46111.386135231485</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46114.62851033565</v>
+        <v>46114.46184366898</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>212</v>
@@ -5911,11 +5915,11 @@
         <v>242</v>
       </c>
       <c r="B70" s="5">
-        <v>46111.55285245371</v>
+        <v>46111.386185787036</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46114.62851040509</v>
+        <v>46114.46184373843</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>243</v>
@@ -5962,11 +5966,11 @@
         <v>245</v>
       </c>
       <c r="B71" s="8">
-        <v>46108.75714166666</v>
+        <v>46108.590475000005</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46118.545566597226</v>
+        <v>46118.378899930554</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>246</v>
@@ -6009,11 +6013,11 @@
         <v>248</v>
       </c>
       <c r="B72" s="5">
-        <v>46108.75714454861</v>
+        <v>46108.590477881946</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46118.55132545139</v>
+        <v>46118.38465878472</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>247</v>
@@ -6070,11 +6074,11 @@
         <v>252</v>
       </c>
       <c r="B73" s="8">
-        <v>46111.50359008102</v>
+        <v>46111.33692341435</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46114.61935158564</v>
+        <v>46114.452684918986</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>253</v>
@@ -6117,11 +6121,11 @@
         <v>255</v>
       </c>
       <c r="B74" s="5">
-        <v>46111.50404616898</v>
+        <v>46111.337379502314</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46114.63328692129</v>
+        <v>46205.031393784724</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>256</v>
@@ -6168,8 +6172,8 @@
       <c r="S74" s="6">
         <v>0</v>
       </c>
-      <c r="T74" s="11" t="s">
-        <v>53</v>
+      <c r="T74" s="12" t="s">
+        <v>167</v>
       </c>
       <c r="U74" s="10" t="s">
         <v>54</v>
@@ -6180,11 +6184,11 @@
         <v>260</v>
       </c>
       <c r="B75" s="8">
-        <v>46111.50406170139</v>
+        <v>46111.33739503472</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46114.63343645833</v>
+        <v>46114.46676979167</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>261</v>
@@ -6243,11 +6247,11 @@
         <v>263</v>
       </c>
       <c r="B76" s="5">
-        <v>46111.50543856481</v>
+        <v>46111.33877189815</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46114.62176513889</v>
+        <v>46114.45509847222</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>264</v>
@@ -6290,11 +6294,11 @@
         <v>266</v>
       </c>
       <c r="B77" s="8">
-        <v>46111.505495046295</v>
+        <v>46111.33882837963</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46114.633869259254</v>
+        <v>46114.4672025926</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>267</v>
@@ -6353,11 +6357,11 @@
         <v>271</v>
       </c>
       <c r="B78" s="5">
-        <v>46111.50560314815</v>
+        <v>46111.33893648148</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46114.6339722338</v>
+        <v>46114.46730556713</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>272</v>
@@ -6416,11 +6420,11 @@
         <v>273</v>
       </c>
       <c r="B79" s="8">
-        <v>46111.52633317129</v>
+        <v>46111.35966650463</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46114.627016388884</v>
+        <v>46114.46034972223</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>212</v>
@@ -6469,11 +6473,11 @@
         <v>276</v>
       </c>
       <c r="B80" s="5">
-        <v>46111.526644375</v>
+        <v>46111.35997770833</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46114.627017175924</v>
+        <v>46114.46035050926</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>217</v>
@@ -6522,11 +6526,11 @@
         <v>278</v>
       </c>
       <c r="B81" s="8">
-        <v>46111.50563458333</v>
+        <v>46111.33896791667</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46114.63406568287</v>
+        <v>46114.467399016205</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>279</v>
@@ -6585,11 +6589,11 @@
         <v>280</v>
       </c>
       <c r="B82" s="5">
-        <v>46111.526916469906</v>
+        <v>46111.36024980324</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46114.62715587963</v>
+        <v>46114.460489212965</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>212</v>
@@ -6638,11 +6642,11 @@
         <v>283</v>
       </c>
       <c r="B83" s="8">
-        <v>46111.52699828704</v>
+        <v>46111.360331620366</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46114.62715672454</v>
+        <v>46114.46049005787</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>217</v>
@@ -6691,11 +6695,11 @@
         <v>286</v>
       </c>
       <c r="B84" s="5">
-        <v>46108.75714884259</v>
+        <v>46108.590482175925</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46118.54556668982</v>
+        <v>46118.37890002315</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>287</v>
@@ -6738,11 +6742,11 @@
         <v>289</v>
       </c>
       <c r="B85" s="8">
-        <v>46108.75715243055</v>
+        <v>46108.59048576389</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46185.184959907405</v>
+        <v>46185.01829324074</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>290</v>
@@ -6801,11 +6805,11 @@
         <v>292</v>
       </c>
       <c r="B86" s="5">
-        <v>46108.75715773148</v>
+        <v>46108.59049106481</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46118.55225699074</v>
+        <v>46118.38559032408</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>57</v>
@@ -6864,11 +6868,11 @@
         <v>294</v>
       </c>
       <c r="B87" s="8">
-        <v>46108.75716349537</v>
+        <v>46108.59049682871</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46111.59762381944</v>
+        <v>46111.43095715278</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>295</v>
@@ -6927,11 +6931,11 @@
         <v>297</v>
       </c>
       <c r="B88" s="5">
-        <v>46108.75716875</v>
+        <v>46108.59050208333</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46111.59782981481</v>
+        <v>46111.43116314815</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>298</v>
@@ -6990,11 +6994,11 @@
         <v>299</v>
       </c>
       <c r="B89" s="8">
-        <v>46108.75717430556</v>
+        <v>46108.59050763889</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46154.86778005787</v>
+        <v>46154.7011133912</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>300</v>
@@ -7045,7 +7049,7 @@
         <v>53</v>
       </c>
       <c r="U89" s="12" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
@@ -7053,11 +7057,11 @@
         <v>301</v>
       </c>
       <c r="B90" s="5">
-        <v>46108.75717877314</v>
+        <v>46108.590512106486</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46118.54556859954</v>
+        <v>46118.37890193287</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>302</v>
@@ -7114,11 +7118,11 @@
         <v>304</v>
       </c>
       <c r="B91" s="8">
-        <v>46108.822037094906</v>
+        <v>46108.65537042824</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46185.18495945602</v>
+        <v>46185.01829278935</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>305</v>
@@ -7169,7 +7173,7 @@
         <v>31</v>
       </c>
       <c r="U91" s="12" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -7177,11 +7181,11 @@
         <v>307</v>
       </c>
       <c r="B92" s="5">
-        <v>46108.757183124995</v>
+        <v>46108.59051645834</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46114.62594751157</v>
+        <v>46114.45928084491</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>308</v>
@@ -7224,11 +7228,11 @@
         <v>310</v>
       </c>
       <c r="B93" s="8">
-        <v>46108.757186296294</v>
+        <v>46108.59051962963</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46114.63518780093</v>
+        <v>46114.46852113426</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>311</v>
@@ -7237,10 +7241,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I93" s="8">
         <v>46248</v>
@@ -7287,11 +7291,11 @@
         <v>312</v>
       </c>
       <c r="B94" s="5">
-        <v>46111.52720202546</v>
+        <v>46111.36053535879</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46118.545567442125</v>
+        <v>46118.37890077547</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>212</v>
@@ -7300,10 +7304,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I94" s="5">
         <v>46248</v>
@@ -7340,11 +7344,11 @@
         <v>315</v>
       </c>
       <c r="B95" s="8">
-        <v>46111.52733795139</v>
+        <v>46111.360671284725</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46118.54556813657</v>
+        <v>46118.37890146991</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>217</v>
@@ -7353,10 +7357,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I95" s="8">
         <v>46248</v>
@@ -7393,11 +7397,11 @@
         <v>318</v>
       </c>
       <c r="B96" s="5">
-        <v>46108.75720997685</v>
+        <v>46108.59054331019</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46114.636429907405</v>
+        <v>46114.46976324074</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>319</v>
@@ -7406,10 +7410,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I96" s="5">
         <v>46268</v>
@@ -7456,11 +7460,11 @@
         <v>320</v>
       </c>
       <c r="B97" s="8">
-        <v>46111.52790079861</v>
+        <v>46111.361234131946</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46114.627765578705</v>
+        <v>46114.46109891204</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>212</v>
@@ -7469,10 +7473,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I97" s="8">
         <v>46268</v>
@@ -7509,11 +7513,11 @@
         <v>323</v>
       </c>
       <c r="B98" s="5">
-        <v>46111.52796104166</v>
+        <v>46111.361294375005</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46114.62776635417</v>
+        <v>46114.4610996875</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>217</v>
@@ -7522,10 +7526,10 @@
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I98" s="5">
         <v>46268</v>
@@ -7562,11 +7566,11 @@
         <v>326</v>
       </c>
       <c r="B99" s="8">
-        <v>46108.75719767361</v>
+        <v>46108.59053100694</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46114.63653665509</v>
+        <v>46114.469869988425</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>327</v>
@@ -7575,10 +7579,10 @@
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I99" s="8">
         <v>46272</v>
@@ -7625,11 +7629,11 @@
         <v>328</v>
       </c>
       <c r="B100" s="5">
-        <v>46111.52756633102</v>
+        <v>46111.36089966435</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46118.54557231482</v>
+        <v>46118.37890564815</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>212</v>
@@ -7638,10 +7642,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I100" s="5">
         <v>46272</v>
@@ -7678,11 +7682,11 @@
         <v>331</v>
       </c>
       <c r="B101" s="8">
-        <v>46111.527622395835</v>
+        <v>46111.360955729164</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46118.54556883102</v>
+        <v>46118.37890216435</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>217</v>
@@ -7691,10 +7695,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I101" s="8">
         <v>46272</v>
@@ -7731,11 +7735,11 @@
         <v>334</v>
       </c>
       <c r="B102" s="5">
-        <v>46108.75720341435</v>
+        <v>46108.59053674768</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46114.63667146991</v>
+        <v>46114.47000480324</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>335</v>
@@ -7744,10 +7748,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I102" s="5">
         <v>46274</v>
@@ -7794,11 +7798,11 @@
         <v>336</v>
       </c>
       <c r="B103" s="8">
-        <v>46111.52775804398</v>
+        <v>46111.361091377315</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46118.545570937495</v>
+        <v>46118.37890427084</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>212</v>
@@ -7807,10 +7811,10 @@
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I103" s="8">
         <v>46274</v>
@@ -7847,11 +7851,11 @@
         <v>338</v>
       </c>
       <c r="B104" s="5">
-        <v>46111.52780829861</v>
+        <v>46111.36114163195</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46118.545571608796</v>
+        <v>46118.37890494213</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>217</v>
@@ -7860,10 +7864,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I104" s="5">
         <v>46274</v>
@@ -7900,11 +7904,11 @@
         <v>340</v>
       </c>
       <c r="B105" s="8">
-        <v>46108.757191412034</v>
+        <v>46108.59052474537</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46114.636801493056</v>
+        <v>46114.47013482639</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>341</v>
@@ -7913,10 +7917,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I105" s="8">
         <v>46276</v>
@@ -7963,11 +7967,11 @@
         <v>342</v>
       </c>
       <c r="B106" s="5">
-        <v>46111.527446493055</v>
+        <v>46111.360779826384</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46118.545569548616</v>
+        <v>46118.378902881945</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>212</v>
@@ -7976,10 +7980,10 @@
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I106" s="5">
         <v>46276</v>
@@ -8016,11 +8020,11 @@
         <v>345</v>
       </c>
       <c r="B107" s="8">
-        <v>46111.52746010417</v>
+        <v>46111.3607934375</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46118.545570243055</v>
+        <v>46118.37890357639</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>217</v>
@@ -8029,10 +8033,10 @@
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I107" s="8">
         <v>46276</v>
@@ -8069,11 +8073,11 @@
         <v>348</v>
       </c>
       <c r="B108" s="5">
-        <v>46108.757217025464</v>
+        <v>46108.5905503588</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46114.63686459491</v>
+        <v>46114.47019792824</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>349</v>
@@ -8082,10 +8086,10 @@
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I108" s="5">
         <v>46280</v>
@@ -8132,11 +8136,11 @@
         <v>350</v>
       </c>
       <c r="B109" s="8">
-        <v>46111.528031932874</v>
+        <v>46111.3613652662</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46114.62850982639</v>
+        <v>46114.46184315972</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>212</v>
@@ -8145,10 +8149,10 @@
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I109" s="9"/>
       <c r="J109" s="8">
@@ -8183,11 +8187,11 @@
         <v>352</v>
       </c>
       <c r="B110" s="5">
-        <v>46111.52811128472</v>
+        <v>46111.36144461806</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46114.62851064815</v>
+        <v>46114.46184398148</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>217</v>
@@ -8196,10 +8200,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I110" s="6"/>
       <c r="J110" s="5">
@@ -8234,11 +8238,11 @@
         <v>354</v>
       </c>
       <c r="B111" s="8">
-        <v>46108.75727585648</v>
+        <v>46108.590609189814</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46114.63695302083</v>
+        <v>46114.47028635417</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>355</v>
@@ -8247,10 +8251,10 @@
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I111" s="9"/>
       <c r="J111" s="8">
@@ -8295,11 +8299,11 @@
         <v>357</v>
       </c>
       <c r="B112" s="5">
-        <v>46111.5281812037</v>
+        <v>46111.36151453704</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46114.62864336805</v>
+        <v>46114.461976701394</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>212</v>
@@ -8308,10 +8312,10 @@
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
@@ -8346,11 +8350,11 @@
         <v>359</v>
       </c>
       <c r="B113" s="8">
-        <v>46111.528266423615</v>
+        <v>46111.36159975694</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46114.62864409722</v>
+        <v>46114.461977430554</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>217</v>
@@ -8359,10 +8363,10 @@
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I113" s="9"/>
       <c r="J113" s="8">
@@ -8397,11 +8401,11 @@
         <v>361</v>
       </c>
       <c r="B114" s="5">
-        <v>46108.757283217594</v>
+        <v>46108.59061655092</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46114.62962787037</v>
+        <v>46114.4629612037</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>362</v>
@@ -8444,11 +8448,11 @@
         <v>364</v>
       </c>
       <c r="B115" s="8">
-        <v>46108.757287430555</v>
+        <v>46108.59062076389</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46114.63723893519</v>
+        <v>46114.47057226852</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>365</v>
@@ -8507,11 +8511,11 @@
         <v>369</v>
       </c>
       <c r="B116" s="5">
-        <v>46111.52846596065</v>
+        <v>46111.36179929398</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46114.62888387732</v>
+        <v>46114.46221721065</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>212</v>
@@ -8558,11 +8562,11 @@
         <v>371</v>
       </c>
       <c r="B117" s="8">
-        <v>46111.528518067134</v>
+        <v>46111.36185140046</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46114.62888469908</v>
+        <v>46114.46221803241</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>217</v>
@@ -8609,11 +8613,11 @@
         <v>373</v>
       </c>
       <c r="B118" s="5">
-        <v>46111.531216006944</v>
+        <v>46111.36454934027</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46114.62888542824</v>
+        <v>46114.462218761575</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>56</v>
@@ -8660,11 +8664,11 @@
         <v>375</v>
       </c>
       <c r="B119" s="8">
-        <v>46111.53129275463</v>
+        <v>46111.36462608796</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46114.62888615741</v>
+        <v>46114.46221949074</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>60</v>
@@ -8711,11 +8715,11 @@
         <v>377</v>
       </c>
       <c r="B120" s="5">
-        <v>46111.53134821759</v>
+        <v>46111.36468155093</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46114.628886921295</v>
+        <v>46114.46222025463</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>378</v>
@@ -8762,11 +8766,11 @@
         <v>380</v>
       </c>
       <c r="B121" s="8">
-        <v>46111.53139942129</v>
+        <v>46111.364732754635</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46114.62888767361</v>
+        <v>46114.46222100694</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>66</v>
@@ -8813,11 +8817,11 @@
         <v>382</v>
       </c>
       <c r="B122" s="5">
-        <v>46111.53343819444</v>
+        <v>46111.36677152778</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46114.628888437495</v>
+        <v>46114.46222177084</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>306</v>
@@ -8864,11 +8868,11 @@
         <v>384</v>
       </c>
       <c r="B123" s="8">
-        <v>46108.75729289352</v>
+        <v>46108.590626226855</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46114.637374618054</v>
+        <v>46114.47070795139</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>385</v>
@@ -8877,10 +8881,10 @@
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I123" s="8">
         <v>46288</v>
@@ -8927,11 +8931,11 @@
         <v>387</v>
       </c>
       <c r="B124" s="5">
-        <v>46111.52857409722</v>
+        <v>46111.36190743056</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46114.629102280094</v>
+        <v>46114.46243561343</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>212</v>
@@ -8940,10 +8944,10 @@
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I124" s="5">
         <v>46288</v>
@@ -8980,11 +8984,11 @@
         <v>389</v>
       </c>
       <c r="B125" s="8">
-        <v>46111.528674016205</v>
+        <v>46111.36200734954</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46114.62910302084</v>
+        <v>46114.462436354166</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>217</v>
@@ -8993,10 +8997,10 @@
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I125" s="8">
         <v>46288</v>
@@ -9033,11 +9037,11 @@
         <v>391</v>
       </c>
       <c r="B126" s="5">
-        <v>46111.531552291664</v>
+        <v>46111.364885625</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46114.629103784726</v>
+        <v>46114.462437118054</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>56</v>
@@ -9046,10 +9050,10 @@
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I126" s="5">
         <v>46288</v>
@@ -9086,11 +9090,11 @@
         <v>393</v>
       </c>
       <c r="B127" s="8">
-        <v>46111.531603344905</v>
+        <v>46111.36493667824</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46114.62910452546</v>
+        <v>46114.4624378588</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>60</v>
@@ -9099,10 +9103,10 @@
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I127" s="8">
         <v>46288</v>
@@ -9139,11 +9143,11 @@
         <v>395</v>
       </c>
       <c r="B128" s="5">
-        <v>46111.531648379634</v>
+        <v>46111.36498171296</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46114.62910528935</v>
+        <v>46114.462438622686</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>378</v>
@@ -9152,10 +9156,10 @@
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I128" s="5">
         <v>46288</v>
@@ -9192,11 +9196,11 @@
         <v>397</v>
       </c>
       <c r="B129" s="8">
-        <v>46111.531705925925</v>
+        <v>46111.36503925926</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46114.62910605324</v>
+        <v>46114.462439386574</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>66</v>
@@ -9205,10 +9209,10 @@
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I129" s="8">
         <v>46288</v>
@@ -9245,11 +9249,11 @@
         <v>399</v>
       </c>
       <c r="B130" s="5">
-        <v>46111.533570127314</v>
+        <v>46111.36690346064</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46114.62910684028</v>
+        <v>46114.46244017361</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>306</v>
@@ -9258,10 +9262,10 @@
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I130" s="5">
         <v>46288</v>
@@ -9298,11 +9302,11 @@
         <v>401</v>
       </c>
       <c r="B131" s="8">
-        <v>46108.75729930555</v>
+        <v>46108.590632638894</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46114.63748693287</v>
+        <v>46114.4708202662</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>402</v>
@@ -9361,11 +9365,11 @@
         <v>404</v>
       </c>
       <c r="B132" s="5">
-        <v>46111.528799872685</v>
+        <v>46111.362133206014</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46114.62931347222</v>
+        <v>46114.46264680555</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>212</v>
@@ -9412,11 +9416,11 @@
         <v>406</v>
       </c>
       <c r="B133" s="8">
-        <v>46111.52885179398</v>
+        <v>46111.36218512732</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46114.62931429398</v>
+        <v>46114.46264762731</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>217</v>
@@ -9463,11 +9467,11 @@
         <v>408</v>
       </c>
       <c r="B134" s="5">
-        <v>46111.53215439815</v>
+        <v>46111.365487731484</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46114.629315046295</v>
+        <v>46114.46264837963</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>56</v>
@@ -9514,11 +9518,11 @@
         <v>410</v>
       </c>
       <c r="B135" s="8">
-        <v>46111.53220642361</v>
+        <v>46111.365539756946</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46114.62931577546</v>
+        <v>46114.4626491088</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>60</v>
@@ -9565,11 +9569,11 @@
         <v>412</v>
       </c>
       <c r="B136" s="5">
-        <v>46111.532258287036</v>
+        <v>46111.36559162037</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46114.629316527775</v>
+        <v>46114.46264986111</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>378</v>
@@ -9616,11 +9620,11 @@
         <v>414</v>
       </c>
       <c r="B137" s="8">
-        <v>46111.53231001158</v>
+        <v>46111.36564334491</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46114.62931729166</v>
+        <v>46114.462650625</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>66</v>
@@ -9667,11 +9671,11 @@
         <v>416</v>
       </c>
       <c r="B138" s="5">
-        <v>46111.53368237268</v>
+        <v>46111.36701570602</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46114.62931805555</v>
+        <v>46114.462651388894</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>417</v>
@@ -9718,11 +9722,11 @@
         <v>419</v>
       </c>
       <c r="B139" s="8">
-        <v>46108.757304583334</v>
+        <v>46108.59063791667</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46114.63755023148</v>
+        <v>46114.47088356482</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>420</v>
@@ -9781,11 +9785,11 @@
         <v>422</v>
       </c>
       <c r="B140" s="5">
-        <v>46111.528945011574</v>
+        <v>46111.36227834491</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46114.830281076385</v>
+        <v>46114.66361440972</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>212</v>
@@ -9834,11 +9838,11 @@
         <v>424</v>
       </c>
       <c r="B141" s="8">
-        <v>46111.52901092592</v>
+        <v>46111.36234425926</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46114.830302789356</v>
+        <v>46114.663636122685</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>217</v>
@@ -9887,11 +9891,11 @@
         <v>425</v>
       </c>
       <c r="B142" s="5">
-        <v>46111.53247278935</v>
+        <v>46111.36580612269</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46114.830319201385</v>
+        <v>46114.66365253473</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>56</v>
@@ -9940,11 +9944,11 @@
         <v>426</v>
       </c>
       <c r="B143" s="8">
-        <v>46111.53253350694</v>
+        <v>46111.36586684028</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46114.83033574074</v>
+        <v>46114.66366907407</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>60</v>
@@ -9993,11 +9997,11 @@
         <v>427</v>
       </c>
       <c r="B144" s="5">
-        <v>46111.532638414355</v>
+        <v>46111.365971747684</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46114.83035239583</v>
+        <v>46114.66368572917</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>66</v>
@@ -10046,11 +10050,11 @@
         <v>428</v>
       </c>
       <c r="B145" s="8">
-        <v>46111.53258112269</v>
+        <v>46111.36591445602</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46114.83037114583</v>
+        <v>46114.66370447917</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>378</v>
@@ -10099,11 +10103,11 @@
         <v>429</v>
       </c>
       <c r="B146" s="5">
-        <v>46111.53385627315</v>
+        <v>46111.36718960648</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46114.83039427083</v>
+        <v>46114.663727604166</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>306</v>
@@ -10152,11 +10156,11 @@
         <v>430</v>
       </c>
       <c r="B147" s="8">
-        <v>46108.757310497684</v>
+        <v>46108.59064383102</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46114.62962797454</v>
+        <v>46114.46296130787</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>431</v>
@@ -10199,11 +10203,11 @@
         <v>433</v>
       </c>
       <c r="B148" s="5">
-        <v>46108.75731366898</v>
+        <v>46108.59064700232</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46114.63764361111</v>
+        <v>46114.470976944445</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>434</v>
@@ -10262,11 +10266,11 @@
         <v>437</v>
       </c>
       <c r="B149" s="8">
-        <v>46108.75732001157</v>
+        <v>46108.59065334491</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46119.74841528935</v>
+        <v>46119.58174862269</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>438</v>
@@ -10325,11 +10329,11 @@
         <v>440</v>
       </c>
       <c r="B150" s="5">
-        <v>46108.7573290625</v>
+        <v>46108.59066239583</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46114.62962836806</v>
+        <v>46114.462961701385</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>441</v>
@@ -10372,11 +10376,11 @@
         <v>443</v>
       </c>
       <c r="B151" s="8">
-        <v>46108.75733305556</v>
+        <v>46108.59066638889</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46119.748459016206</v>
+        <v>46119.581792349534</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>444</v>
@@ -10435,11 +10439,11 @@
         <v>446</v>
       </c>
       <c r="B152" s="5">
-        <v>46108.757338703705</v>
+        <v>46108.59067203704</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46119.748502546296</v>
+        <v>46119.58183587963</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>447</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -1981,13 +1981,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46108.590050300925</v>
+        <v>46108.75671696759</v>
       </c>
       <c r="C4" s="5">
-        <v>46112.30827043981</v>
+        <v>46112.47493710648</v>
       </c>
       <c r="D4" s="5">
-        <v>46135.47863081019</v>
+        <v>46135.64529747685</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2030,13 +2030,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46108.59013304398</v>
+        <v>46108.75679971065</v>
       </c>
       <c r="C5" s="8">
-        <v>46112.30816390047</v>
+        <v>46112.47483056713</v>
       </c>
       <c r="D5" s="8">
-        <v>46112.30818222222</v>
+        <v>46112.47484888889</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2093,13 +2093,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46108.59013730324</v>
+        <v>46108.75680396991</v>
       </c>
       <c r="C6" s="5">
-        <v>46112.30820663195</v>
+        <v>46112.47487329861</v>
       </c>
       <c r="D6" s="5">
-        <v>46112.30822237268</v>
+        <v>46112.47488903935</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -2156,13 +2156,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8">
-        <v>46108.59014104167</v>
+        <v>46108.756807708334</v>
       </c>
       <c r="C7" s="8">
-        <v>46112.30822040509</v>
+        <v>46112.47488707176</v>
       </c>
       <c r="D7" s="8">
-        <v>46112.30823634259</v>
+        <v>46112.474903009264</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>36</v>
@@ -2219,13 +2219,13 @@
         <v>37</v>
       </c>
       <c r="B8" s="5">
-        <v>46108.59014988426</v>
+        <v>46108.75681655093</v>
       </c>
       <c r="C8" s="5">
-        <v>46112.3082394213</v>
+        <v>46112.47490608796</v>
       </c>
       <c r="D8" s="5">
-        <v>46112.30827072916</v>
+        <v>46112.47493739583</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>38</v>
@@ -2282,13 +2282,13 @@
         <v>40</v>
       </c>
       <c r="B9" s="8">
-        <v>46108.59015527778</v>
+        <v>46108.756821944444</v>
       </c>
       <c r="C9" s="8">
-        <v>46112.30825949074</v>
+        <v>46112.4749261574</v>
       </c>
       <c r="D9" s="8">
-        <v>46112.30827738426</v>
+        <v>46112.474944050926</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>41</v>
@@ -2345,11 +2345,11 @@
         <v>42</v>
       </c>
       <c r="B10" s="5">
-        <v>46108.590055740744</v>
+        <v>46108.75672240741</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46134.72758210648</v>
+        <v>46134.89424877315</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>43</v>
@@ -2392,13 +2392,13 @@
         <v>45</v>
       </c>
       <c r="B11" s="8">
-        <v>46108.590159328705</v>
+        <v>46108.75682599537</v>
       </c>
       <c r="C11" s="8">
-        <v>46134.72757178241</v>
+        <v>46134.89423844907</v>
       </c>
       <c r="D11" s="8">
-        <v>46134.727589560185</v>
+        <v>46134.89425622685</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>46</v>
@@ -2457,11 +2457,11 @@
         <v>50</v>
       </c>
       <c r="B12" s="5">
-        <v>46108.5901654051</v>
+        <v>46108.756832071755</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46111.41252525463</v>
+        <v>46111.57919192129</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -2520,11 +2520,11 @@
         <v>55</v>
       </c>
       <c r="B13" s="8">
-        <v>46111.362621168984</v>
+        <v>46111.52928783565</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46111.412670578706</v>
+        <v>46111.57933724537</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>56</v>
@@ -2573,11 +2573,11 @@
         <v>59</v>
       </c>
       <c r="B14" s="5">
-        <v>46111.36284828704</v>
+        <v>46111.529514953705</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46111.41266780093</v>
+        <v>46111.57933446759</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>60</v>
@@ -2626,11 +2626,11 @@
         <v>62</v>
       </c>
       <c r="B15" s="8">
-        <v>46111.362902650464</v>
+        <v>46111.52956931713</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="8">
-        <v>46111.41266497685</v>
+        <v>46111.579331643516</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>63</v>
@@ -2679,11 +2679,11 @@
         <v>65</v>
       </c>
       <c r="B16" s="5">
-        <v>46111.362951585645</v>
+        <v>46111.529618252316</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46111.41266065973</v>
+        <v>46111.579327326384</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>66</v>
@@ -2732,13 +2732,13 @@
         <v>68</v>
       </c>
       <c r="B17" s="8">
-        <v>46108.59006069445</v>
+        <v>46108.756727361106</v>
       </c>
       <c r="C17" s="8">
-        <v>46112.30866109954</v>
+        <v>46112.4753277662</v>
       </c>
       <c r="D17" s="8">
-        <v>46135.47865769676</v>
+        <v>46135.645324363424</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>69</v>
@@ -2781,13 +2781,13 @@
         <v>71</v>
       </c>
       <c r="B18" s="5">
-        <v>46108.59017084491</v>
+        <v>46108.75683751157</v>
       </c>
       <c r="C18" s="5">
-        <v>46112.30849111111</v>
+        <v>46112.47515777778</v>
       </c>
       <c r="D18" s="5">
-        <v>46113.983714988426</v>
+        <v>46114.1503816551</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>72</v>
@@ -2846,13 +2846,13 @@
         <v>74</v>
       </c>
       <c r="B19" s="8">
-        <v>46108.59018086806</v>
+        <v>46108.75684753472</v>
       </c>
       <c r="C19" s="8">
-        <v>46112.308508773145</v>
+        <v>46112.47517543982</v>
       </c>
       <c r="D19" s="8">
-        <v>46121.00810387731</v>
+        <v>46121.17477054398</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>75</v>
@@ -2911,13 +2911,13 @@
         <v>77</v>
       </c>
       <c r="B20" s="5">
-        <v>46108.590186574074</v>
+        <v>46108.756853240746</v>
       </c>
       <c r="C20" s="5">
-        <v>46112.30856804398</v>
+        <v>46112.47523471065</v>
       </c>
       <c r="D20" s="5">
-        <v>46121.00810381945</v>
+        <v>46121.17477048611</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>78</v>
@@ -2976,13 +2976,13 @@
         <v>80</v>
       </c>
       <c r="B21" s="8">
-        <v>46108.59019297454</v>
+        <v>46108.7568596412</v>
       </c>
       <c r="C21" s="8">
-        <v>46112.30862387731</v>
+        <v>46112.47529054398</v>
       </c>
       <c r="D21" s="8">
-        <v>46121.0081040625</v>
+        <v>46121.174770729165</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>81</v>
@@ -3041,13 +3041,13 @@
         <v>84</v>
       </c>
       <c r="B22" s="5">
-        <v>46108.62263557871</v>
+        <v>46108.78930224537</v>
       </c>
       <c r="C22" s="5">
-        <v>46112.30864754629</v>
+        <v>46112.47531421296</v>
       </c>
       <c r="D22" s="5">
-        <v>46121.0081037037</v>
+        <v>46121.17477037037</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>85</v>
@@ -3106,11 +3106,11 @@
         <v>87</v>
       </c>
       <c r="B23" s="8">
-        <v>46108.59006707176</v>
+        <v>46108.756733738424</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="8">
-        <v>46205.3719346412</v>
+        <v>46205.53860130787</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>88</v>
@@ -3155,13 +3155,13 @@
         <v>91</v>
       </c>
       <c r="B24" s="5">
-        <v>46108.59020194445</v>
+        <v>46108.75686861111</v>
       </c>
       <c r="C24" s="5">
-        <v>46112.308853090275</v>
+        <v>46112.47551975695</v>
       </c>
       <c r="D24" s="5">
-        <v>46115.96251511574</v>
+        <v>46116.12918178241</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>92</v>
@@ -3220,13 +3220,13 @@
         <v>94</v>
       </c>
       <c r="B25" s="8">
-        <v>46108.59020821759</v>
+        <v>46108.75687488426</v>
       </c>
       <c r="C25" s="8">
-        <v>46112.30882164351</v>
+        <v>46112.475488310185</v>
       </c>
       <c r="D25" s="8">
-        <v>46123.02682134259</v>
+        <v>46123.19348800926</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>95</v>
@@ -3285,13 +3285,13 @@
         <v>97</v>
       </c>
       <c r="B26" s="5">
-        <v>46108.59021409722</v>
+        <v>46108.75688076389</v>
       </c>
       <c r="C26" s="5">
-        <v>46205.371915428244</v>
+        <v>46205.53858209491</v>
       </c>
       <c r="D26" s="5">
-        <v>46205.371932118054</v>
+        <v>46205.538598784726</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>98</v>
@@ -3350,13 +3350,13 @@
         <v>101</v>
       </c>
       <c r="B27" s="8">
-        <v>46108.59021996528</v>
+        <v>46108.75688663195</v>
       </c>
       <c r="C27" s="8">
-        <v>46135.37940633102</v>
+        <v>46135.546072997684</v>
       </c>
       <c r="D27" s="8">
-        <v>46135.37953547454</v>
+        <v>46135.5462021412</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>102</v>
@@ -3415,11 +3415,11 @@
         <v>104</v>
       </c>
       <c r="B28" s="5">
-        <v>46108.59023068287</v>
+        <v>46108.756897349536</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46193.029141203704</v>
+        <v>46193.195807870376</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3478,13 +3478,13 @@
         <v>110</v>
       </c>
       <c r="B29" s="8">
-        <v>46108.590235682874</v>
+        <v>46108.75690234954</v>
       </c>
       <c r="C29" s="8">
-        <v>46112.309146307874</v>
+        <v>46112.47581297454</v>
       </c>
       <c r="D29" s="8">
-        <v>46123.02682138889</v>
+        <v>46123.19348805556</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>111</v>
@@ -3543,11 +3543,11 @@
         <v>113</v>
       </c>
       <c r="B30" s="5">
-        <v>46108.59024174769</v>
+        <v>46108.75690841435</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46193.02914119213</v>
+        <v>46193.19580785879</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>114</v>
@@ -3606,13 +3606,13 @@
         <v>116</v>
       </c>
       <c r="B31" s="8">
-        <v>46108.61981157407</v>
+        <v>46108.78647824074</v>
       </c>
       <c r="C31" s="8">
-        <v>46112.30910100695</v>
+        <v>46112.47576767361</v>
       </c>
       <c r="D31" s="8">
-        <v>46123.0268209375</v>
+        <v>46123.19348760416</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>86</v>
@@ -3671,11 +3671,11 @@
         <v>118</v>
       </c>
       <c r="B32" s="5">
-        <v>46108.5900744213</v>
+        <v>46108.756741087964</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46154.70118263889</v>
+        <v>46154.867849305556</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>119</v>
@@ -3718,11 +3718,11 @@
         <v>121</v>
       </c>
       <c r="B33" s="8">
-        <v>46108.59028607639</v>
+        <v>46108.75695274306</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="8">
-        <v>46182.52670556713</v>
+        <v>46182.6933722338</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>122</v>
@@ -3781,13 +3781,13 @@
         <v>126</v>
       </c>
       <c r="B34" s="5">
-        <v>46108.59029108797</v>
+        <v>46108.75695775463</v>
       </c>
       <c r="C34" s="5">
-        <v>46182.52669886574</v>
+        <v>46182.69336553241</v>
       </c>
       <c r="D34" s="5">
-        <v>46182.52670059028</v>
+        <v>46182.69336725694</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>127</v>
@@ -3846,11 +3846,11 @@
         <v>129</v>
       </c>
       <c r="B35" s="8">
-        <v>46108.590296759256</v>
+        <v>46108.75696342593</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46182.52670665509</v>
+        <v>46182.69337332176</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>130</v>
@@ -3909,11 +3909,11 @@
         <v>132</v>
       </c>
       <c r="B36" s="5">
-        <v>46108.59030648148</v>
+        <v>46108.75697314815</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.6876652662</v>
+        <v>46169.854331932875</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>133</v>
@@ -3972,11 +3972,11 @@
         <v>135</v>
       </c>
       <c r="B37" s="8">
-        <v>46108.5903112963</v>
+        <v>46108.75697796296</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46135.37941498843</v>
+        <v>46135.54608165509</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>136</v>
@@ -4035,11 +4035,11 @@
         <v>138</v>
       </c>
       <c r="B38" s="5">
-        <v>46108.590316863425</v>
+        <v>46108.7569835301</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46111.41535784722</v>
+        <v>46111.58202451389</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>139</v>
@@ -4096,11 +4096,11 @@
         <v>141</v>
       </c>
       <c r="B39" s="8">
-        <v>46108.590321655094</v>
+        <v>46108.75698832176</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46183.000833576385</v>
+        <v>46183.16750024306</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>142</v>
@@ -4159,11 +4159,11 @@
         <v>144</v>
       </c>
       <c r="B40" s="5">
-        <v>46108.59032644676</v>
+        <v>46108.75699311343</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46205.3719227199</v>
+        <v>46205.538589386575</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>145</v>
@@ -4222,11 +4222,11 @@
         <v>147</v>
       </c>
       <c r="B41" s="8">
-        <v>46108.59033180556</v>
+        <v>46108.75699847222</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46182.00132953704</v>
+        <v>46182.1679962037</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>148</v>
@@ -4285,11 +4285,11 @@
         <v>150</v>
       </c>
       <c r="B42" s="5">
-        <v>46108.59033690972</v>
+        <v>46108.75700357639</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46182.52677877314</v>
+        <v>46182.693445439814</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>151</v>
@@ -4348,13 +4348,13 @@
         <v>153</v>
       </c>
       <c r="B43" s="8">
-        <v>46108.59034189815</v>
+        <v>46108.75700856482</v>
       </c>
       <c r="C43" s="8">
-        <v>46182.52677163194</v>
+        <v>46182.69343829861</v>
       </c>
       <c r="D43" s="8">
-        <v>46182.52677309028</v>
+        <v>46182.69343975694</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>154</v>
@@ -4413,11 +4413,11 @@
         <v>156</v>
       </c>
       <c r="B44" s="5">
-        <v>46108.59034976852</v>
+        <v>46108.757016435186</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46182.526779803244</v>
+        <v>46182.69344646991</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>157</v>
@@ -4476,11 +4476,11 @@
         <v>159</v>
       </c>
       <c r="B45" s="8">
-        <v>46108.590355162036</v>
+        <v>46108.7570218287</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46199.64513902778</v>
+        <v>46199.811805694444</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>160</v>
@@ -4539,11 +4539,11 @@
         <v>162</v>
       </c>
       <c r="B46" s="5">
-        <v>46108.590360532406</v>
+        <v>46108.75702719907</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46203.03652263889</v>
+        <v>46203.203189305554</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>163</v>
@@ -4602,11 +4602,11 @@
         <v>168</v>
       </c>
       <c r="B47" s="8">
-        <v>46108.59036534722</v>
+        <v>46108.75703201389</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46199.00194430556</v>
+        <v>46199.16861097222</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>109</v>
@@ -4665,11 +4665,11 @@
         <v>170</v>
       </c>
       <c r="B48" s="5">
-        <v>46108.590370949074</v>
+        <v>46108.75703761574</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46169.68410056713</v>
+        <v>46169.850767233795</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>171</v>
@@ -4728,13 +4728,13 @@
         <v>173</v>
       </c>
       <c r="B49" s="8">
-        <v>46108.59037640046</v>
+        <v>46108.75704306713</v>
       </c>
       <c r="C49" s="8">
-        <v>46154.701175821756</v>
+        <v>46154.86784248843</v>
       </c>
       <c r="D49" s="8">
-        <v>46154.70117755787</v>
+        <v>46154.86784422454</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>174</v>
@@ -4793,13 +4793,13 @@
         <v>176</v>
       </c>
       <c r="B50" s="5">
-        <v>46108.59038365741</v>
+        <v>46108.75705032407</v>
       </c>
       <c r="C50" s="5">
-        <v>46154.70079945602</v>
+        <v>46154.86746612268</v>
       </c>
       <c r="D50" s="5">
-        <v>46154.70080144676</v>
+        <v>46154.86746811343</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>177</v>
@@ -4848,13 +4848,13 @@
         <v>179</v>
       </c>
       <c r="B51" s="8">
-        <v>46108.590390613426</v>
+        <v>46108.75705728009</v>
       </c>
       <c r="C51" s="8">
-        <v>46154.70109605324</v>
+        <v>46154.86776271991</v>
       </c>
       <c r="D51" s="8">
-        <v>46154.70109744213</v>
+        <v>46154.8677641088</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>180</v>
@@ -4903,11 +4903,11 @@
         <v>182</v>
       </c>
       <c r="B52" s="5">
-        <v>46108.590394768515</v>
+        <v>46108.757061435186</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46169.68575747685</v>
+        <v>46169.85242414352</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>183</v>
@@ -4966,11 +4966,11 @@
         <v>187</v>
       </c>
       <c r="B53" s="8">
-        <v>46108.590440300926</v>
+        <v>46108.75710696759</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46199.001942233794</v>
+        <v>46199.168608900465</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>115</v>
@@ -5025,11 +5025,11 @@
         <v>189</v>
       </c>
       <c r="B54" s="5">
-        <v>46108.59044626157</v>
+        <v>46108.757112928244</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46169.6857443287</v>
+        <v>46169.85241099537</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -5078,13 +5078,13 @@
         <v>193</v>
       </c>
       <c r="B55" s="8">
-        <v>46111.341939791666</v>
+        <v>46111.50860645833</v>
       </c>
       <c r="C55" s="8">
-        <v>46182.52738331018</v>
+        <v>46182.69404997685</v>
       </c>
       <c r="D55" s="8">
-        <v>46182.52739695602</v>
+        <v>46182.69406362269</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>194</v>
@@ -5143,13 +5143,13 @@
         <v>196</v>
       </c>
       <c r="B56" s="5">
-        <v>46111.34208927084</v>
+        <v>46111.508755937495</v>
       </c>
       <c r="C56" s="5">
-        <v>46182.52684064815</v>
+        <v>46182.69350731482</v>
       </c>
       <c r="D56" s="5">
-        <v>46182.52684210648</v>
+        <v>46182.69350877315</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>197</v>
@@ -5198,13 +5198,13 @@
         <v>199</v>
       </c>
       <c r="B57" s="8">
-        <v>46111.34218010417</v>
+        <v>46111.508846770834</v>
       </c>
       <c r="C57" s="8">
-        <v>46182.52736954861</v>
+        <v>46182.69403621528</v>
       </c>
       <c r="D57" s="8">
-        <v>46182.52737082176</v>
+        <v>46182.69403748843</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>200</v>
@@ -5253,11 +5253,11 @@
         <v>202</v>
       </c>
       <c r="B58" s="5">
-        <v>46108.59045233796</v>
+        <v>46108.75711900463</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46141.36111729167</v>
+        <v>46141.52778395833</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>203</v>
@@ -5300,11 +5300,11 @@
         <v>205</v>
       </c>
       <c r="B59" s="8">
-        <v>46108.59045658565</v>
+        <v>46108.75712325232</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46141.361117673616</v>
+        <v>46141.52778434027</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>206</v>
@@ -5361,11 +5361,11 @@
         <v>211</v>
       </c>
       <c r="B60" s="5">
-        <v>46114.3859125</v>
+        <v>46114.552579166666</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46127.00489599537</v>
+        <v>46127.171562662035</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>212</v>
@@ -5414,11 +5414,11 @@
         <v>216</v>
       </c>
       <c r="B61" s="8">
-        <v>46114.38610657408</v>
+        <v>46114.552773240735</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46127.00489753472</v>
+        <v>46127.17156420139</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>217</v>
@@ -5467,11 +5467,11 @@
         <v>219</v>
       </c>
       <c r="B62" s="5">
-        <v>46108.590461886575</v>
+        <v>46108.75712855324</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46190.02594409722</v>
+        <v>46190.19261076389</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>220</v>
@@ -5530,11 +5530,11 @@
         <v>223</v>
       </c>
       <c r="B63" s="8">
-        <v>46114.386197858796</v>
+        <v>46114.55286452547</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46189.00135333333</v>
+        <v>46189.16802</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>212</v>
@@ -5583,11 +5583,11 @@
         <v>226</v>
       </c>
       <c r="B64" s="5">
-        <v>46114.38629995371</v>
+        <v>46114.552966620366</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46189.00135532407</v>
+        <v>46189.16802199074</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>217</v>
@@ -5636,11 +5636,11 @@
         <v>229</v>
       </c>
       <c r="B65" s="8">
-        <v>46108.59046716435</v>
+        <v>46108.75713383102</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46191.00466449074</v>
+        <v>46191.171331157406</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>108</v>
@@ -5699,11 +5699,11 @@
         <v>232</v>
       </c>
       <c r="B66" s="5">
-        <v>46114.386456319444</v>
+        <v>46114.55312298611</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46190.00143496528</v>
+        <v>46190.16810163195</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>212</v>
@@ -5750,11 +5750,11 @@
         <v>233</v>
       </c>
       <c r="B67" s="8">
-        <v>46114.38657800926</v>
+        <v>46114.553244675924</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46190.00143679398</v>
+        <v>46190.168103460644</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>234</v>
@@ -5801,11 +5801,11 @@
         <v>235</v>
       </c>
       <c r="B68" s="5">
-        <v>46108.590472094904</v>
+        <v>46108.757138761575</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46114.46471738426</v>
+        <v>46114.631384050925</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>236</v>
@@ -5864,11 +5864,11 @@
         <v>240</v>
       </c>
       <c r="B69" s="8">
-        <v>46111.386135231485</v>
+        <v>46111.55280189815</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46114.46184366898</v>
+        <v>46114.62851033565</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>212</v>
@@ -5915,11 +5915,11 @@
         <v>242</v>
       </c>
       <c r="B70" s="5">
-        <v>46111.386185787036</v>
+        <v>46111.55285245371</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46114.46184373843</v>
+        <v>46114.62851040509</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>243</v>
@@ -5966,11 +5966,11 @@
         <v>245</v>
       </c>
       <c r="B71" s="8">
-        <v>46108.590475000005</v>
+        <v>46108.75714166666</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46118.378899930554</v>
+        <v>46118.545566597226</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>246</v>
@@ -6013,11 +6013,11 @@
         <v>248</v>
       </c>
       <c r="B72" s="5">
-        <v>46108.590477881946</v>
+        <v>46108.75714454861</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46118.38465878472</v>
+        <v>46118.55132545139</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>247</v>
@@ -6074,11 +6074,11 @@
         <v>252</v>
       </c>
       <c r="B73" s="8">
-        <v>46111.33692341435</v>
+        <v>46111.50359008102</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46114.452684918986</v>
+        <v>46114.61935158564</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>253</v>
@@ -6121,11 +6121,11 @@
         <v>255</v>
       </c>
       <c r="B74" s="5">
-        <v>46111.337379502314</v>
+        <v>46111.50404616898</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46205.031393784724</v>
+        <v>46205.19806045139</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>256</v>
@@ -6184,11 +6184,11 @@
         <v>260</v>
       </c>
       <c r="B75" s="8">
-        <v>46111.33739503472</v>
+        <v>46111.50406170139</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46114.46676979167</v>
+        <v>46114.63343645833</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>261</v>
@@ -6247,11 +6247,11 @@
         <v>263</v>
       </c>
       <c r="B76" s="5">
-        <v>46111.33877189815</v>
+        <v>46111.50543856481</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46114.45509847222</v>
+        <v>46114.62176513889</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>264</v>
@@ -6294,11 +6294,11 @@
         <v>266</v>
       </c>
       <c r="B77" s="8">
-        <v>46111.33882837963</v>
+        <v>46111.505495046295</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46114.4672025926</v>
+        <v>46114.633869259254</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>267</v>
@@ -6357,11 +6357,11 @@
         <v>271</v>
       </c>
       <c r="B78" s="5">
-        <v>46111.33893648148</v>
+        <v>46111.50560314815</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46114.46730556713</v>
+        <v>46114.6339722338</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>272</v>
@@ -6420,11 +6420,11 @@
         <v>273</v>
       </c>
       <c r="B79" s="8">
-        <v>46111.35966650463</v>
+        <v>46111.52633317129</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46114.46034972223</v>
+        <v>46114.627016388884</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>212</v>
@@ -6473,11 +6473,11 @@
         <v>276</v>
       </c>
       <c r="B80" s="5">
-        <v>46111.35997770833</v>
+        <v>46111.526644375</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46114.46035050926</v>
+        <v>46114.627017175924</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>217</v>
@@ -6526,11 +6526,11 @@
         <v>278</v>
       </c>
       <c r="B81" s="8">
-        <v>46111.33896791667</v>
+        <v>46111.50563458333</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46114.467399016205</v>
+        <v>46114.63406568287</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>279</v>
@@ -6589,11 +6589,11 @@
         <v>280</v>
       </c>
       <c r="B82" s="5">
-        <v>46111.36024980324</v>
+        <v>46111.526916469906</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46114.460489212965</v>
+        <v>46114.62715587963</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>212</v>
@@ -6642,11 +6642,11 @@
         <v>283</v>
       </c>
       <c r="B83" s="8">
-        <v>46111.360331620366</v>
+        <v>46111.52699828704</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46114.46049005787</v>
+        <v>46114.62715672454</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>217</v>
@@ -6695,11 +6695,11 @@
         <v>286</v>
       </c>
       <c r="B84" s="5">
-        <v>46108.590482175925</v>
+        <v>46108.75714884259</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46118.37890002315</v>
+        <v>46118.54556668982</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>287</v>
@@ -6742,11 +6742,11 @@
         <v>289</v>
       </c>
       <c r="B85" s="8">
-        <v>46108.59048576389</v>
+        <v>46108.75715243055</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46185.01829324074</v>
+        <v>46185.184959907405</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>290</v>
@@ -6805,11 +6805,11 @@
         <v>292</v>
       </c>
       <c r="B86" s="5">
-        <v>46108.59049106481</v>
+        <v>46108.75715773148</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46118.38559032408</v>
+        <v>46118.55225699074</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>57</v>
@@ -6868,11 +6868,11 @@
         <v>294</v>
       </c>
       <c r="B87" s="8">
-        <v>46108.59049682871</v>
+        <v>46108.75716349537</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46111.43095715278</v>
+        <v>46111.59762381944</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>295</v>
@@ -6931,11 +6931,11 @@
         <v>297</v>
       </c>
       <c r="B88" s="5">
-        <v>46108.59050208333</v>
+        <v>46108.75716875</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46111.43116314815</v>
+        <v>46111.59782981481</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>298</v>
@@ -6994,11 +6994,11 @@
         <v>299</v>
       </c>
       <c r="B89" s="8">
-        <v>46108.59050763889</v>
+        <v>46108.75717430556</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46154.7011133912</v>
+        <v>46154.86778005787</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>300</v>
@@ -7057,11 +7057,11 @@
         <v>301</v>
       </c>
       <c r="B90" s="5">
-        <v>46108.590512106486</v>
+        <v>46108.75717877314</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46118.37890193287</v>
+        <v>46118.54556859954</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>302</v>
@@ -7118,11 +7118,11 @@
         <v>304</v>
       </c>
       <c r="B91" s="8">
-        <v>46108.65537042824</v>
+        <v>46108.822037094906</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46185.01829278935</v>
+        <v>46185.18495945602</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>305</v>
@@ -7181,11 +7181,11 @@
         <v>307</v>
       </c>
       <c r="B92" s="5">
-        <v>46108.59051645834</v>
+        <v>46108.757183124995</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46114.45928084491</v>
+        <v>46114.62594751157</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>308</v>
@@ -7228,11 +7228,11 @@
         <v>310</v>
       </c>
       <c r="B93" s="8">
-        <v>46108.59051962963</v>
+        <v>46108.757186296294</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46114.46852113426</v>
+        <v>46114.63518780093</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>311</v>
@@ -7291,11 +7291,11 @@
         <v>312</v>
       </c>
       <c r="B94" s="5">
-        <v>46111.36053535879</v>
+        <v>46111.52720202546</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46118.37890077547</v>
+        <v>46118.545567442125</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>212</v>
@@ -7344,11 +7344,11 @@
         <v>315</v>
       </c>
       <c r="B95" s="8">
-        <v>46111.360671284725</v>
+        <v>46111.52733795139</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46118.37890146991</v>
+        <v>46118.54556813657</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>217</v>
@@ -7397,11 +7397,11 @@
         <v>318</v>
       </c>
       <c r="B96" s="5">
-        <v>46108.59054331019</v>
+        <v>46108.75720997685</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46114.46976324074</v>
+        <v>46114.636429907405</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>319</v>
@@ -7460,11 +7460,11 @@
         <v>320</v>
       </c>
       <c r="B97" s="8">
-        <v>46111.361234131946</v>
+        <v>46111.52790079861</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46114.46109891204</v>
+        <v>46114.627765578705</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>212</v>
@@ -7513,11 +7513,11 @@
         <v>323</v>
       </c>
       <c r="B98" s="5">
-        <v>46111.361294375005</v>
+        <v>46111.52796104166</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46114.4610996875</v>
+        <v>46114.62776635417</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>217</v>
@@ -7566,11 +7566,11 @@
         <v>326</v>
       </c>
       <c r="B99" s="8">
-        <v>46108.59053100694</v>
+        <v>46108.75719767361</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46114.469869988425</v>
+        <v>46114.63653665509</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>327</v>
@@ -7629,11 +7629,11 @@
         <v>328</v>
       </c>
       <c r="B100" s="5">
-        <v>46111.36089966435</v>
+        <v>46111.52756633102</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46118.37890564815</v>
+        <v>46118.54557231482</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>212</v>
@@ -7682,11 +7682,11 @@
         <v>331</v>
       </c>
       <c r="B101" s="8">
-        <v>46111.360955729164</v>
+        <v>46111.527622395835</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46118.37890216435</v>
+        <v>46118.54556883102</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>217</v>
@@ -7735,11 +7735,11 @@
         <v>334</v>
       </c>
       <c r="B102" s="5">
-        <v>46108.59053674768</v>
+        <v>46108.75720341435</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46114.47000480324</v>
+        <v>46114.63667146991</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>335</v>
@@ -7798,11 +7798,11 @@
         <v>336</v>
       </c>
       <c r="B103" s="8">
-        <v>46111.361091377315</v>
+        <v>46111.52775804398</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46118.37890427084</v>
+        <v>46118.545570937495</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>212</v>
@@ -7851,11 +7851,11 @@
         <v>338</v>
       </c>
       <c r="B104" s="5">
-        <v>46111.36114163195</v>
+        <v>46111.52780829861</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46118.37890494213</v>
+        <v>46118.545571608796</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>217</v>
@@ -7904,11 +7904,11 @@
         <v>340</v>
       </c>
       <c r="B105" s="8">
-        <v>46108.59052474537</v>
+        <v>46108.757191412034</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46114.47013482639</v>
+        <v>46114.636801493056</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>341</v>
@@ -7967,11 +7967,11 @@
         <v>342</v>
       </c>
       <c r="B106" s="5">
-        <v>46111.360779826384</v>
+        <v>46111.527446493055</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46118.378902881945</v>
+        <v>46118.545569548616</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>212</v>
@@ -8020,11 +8020,11 @@
         <v>345</v>
       </c>
       <c r="B107" s="8">
-        <v>46111.3607934375</v>
+        <v>46111.52746010417</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46118.37890357639</v>
+        <v>46118.545570243055</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>217</v>
@@ -8073,11 +8073,11 @@
         <v>348</v>
       </c>
       <c r="B108" s="5">
-        <v>46108.5905503588</v>
+        <v>46108.757217025464</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46114.47019792824</v>
+        <v>46114.63686459491</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>349</v>
@@ -8136,11 +8136,11 @@
         <v>350</v>
       </c>
       <c r="B109" s="8">
-        <v>46111.3613652662</v>
+        <v>46111.528031932874</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46114.46184315972</v>
+        <v>46114.62850982639</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>212</v>
@@ -8187,11 +8187,11 @@
         <v>352</v>
       </c>
       <c r="B110" s="5">
-        <v>46111.36144461806</v>
+        <v>46111.52811128472</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46114.46184398148</v>
+        <v>46114.62851064815</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>217</v>
@@ -8238,11 +8238,11 @@
         <v>354</v>
       </c>
       <c r="B111" s="8">
-        <v>46108.590609189814</v>
+        <v>46108.75727585648</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46114.47028635417</v>
+        <v>46114.63695302083</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>355</v>
@@ -8299,11 +8299,11 @@
         <v>357</v>
       </c>
       <c r="B112" s="5">
-        <v>46111.36151453704</v>
+        <v>46111.5281812037</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46114.461976701394</v>
+        <v>46114.62864336805</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>212</v>
@@ -8350,11 +8350,11 @@
         <v>359</v>
       </c>
       <c r="B113" s="8">
-        <v>46111.36159975694</v>
+        <v>46111.528266423615</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46114.461977430554</v>
+        <v>46114.62864409722</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>217</v>
@@ -8401,11 +8401,11 @@
         <v>361</v>
       </c>
       <c r="B114" s="5">
-        <v>46108.59061655092</v>
+        <v>46108.757283217594</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46114.4629612037</v>
+        <v>46114.62962787037</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>362</v>
@@ -8448,11 +8448,11 @@
         <v>364</v>
       </c>
       <c r="B115" s="8">
-        <v>46108.59062076389</v>
+        <v>46108.757287430555</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46114.47057226852</v>
+        <v>46114.63723893519</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>365</v>
@@ -8511,11 +8511,11 @@
         <v>369</v>
       </c>
       <c r="B116" s="5">
-        <v>46111.36179929398</v>
+        <v>46111.52846596065</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46114.46221721065</v>
+        <v>46114.62888387732</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>212</v>
@@ -8562,11 +8562,11 @@
         <v>371</v>
       </c>
       <c r="B117" s="8">
-        <v>46111.36185140046</v>
+        <v>46111.528518067134</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46114.46221803241</v>
+        <v>46114.62888469908</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>217</v>
@@ -8613,11 +8613,11 @@
         <v>373</v>
       </c>
       <c r="B118" s="5">
-        <v>46111.36454934027</v>
+        <v>46111.531216006944</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46114.462218761575</v>
+        <v>46114.62888542824</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>56</v>
@@ -8664,11 +8664,11 @@
         <v>375</v>
       </c>
       <c r="B119" s="8">
-        <v>46111.36462608796</v>
+        <v>46111.53129275463</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46114.46221949074</v>
+        <v>46114.62888615741</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>60</v>
@@ -8715,11 +8715,11 @@
         <v>377</v>
       </c>
       <c r="B120" s="5">
-        <v>46111.36468155093</v>
+        <v>46111.53134821759</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46114.46222025463</v>
+        <v>46114.628886921295</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>378</v>
@@ -8766,11 +8766,11 @@
         <v>380</v>
       </c>
       <c r="B121" s="8">
-        <v>46111.364732754635</v>
+        <v>46111.53139942129</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46114.46222100694</v>
+        <v>46114.62888767361</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>66</v>
@@ -8817,11 +8817,11 @@
         <v>382</v>
       </c>
       <c r="B122" s="5">
-        <v>46111.36677152778</v>
+        <v>46111.53343819444</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46114.46222177084</v>
+        <v>46114.628888437495</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>306</v>
@@ -8868,11 +8868,11 @@
         <v>384</v>
       </c>
       <c r="B123" s="8">
-        <v>46108.590626226855</v>
+        <v>46108.75729289352</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46114.47070795139</v>
+        <v>46114.637374618054</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>385</v>
@@ -8931,11 +8931,11 @@
         <v>387</v>
       </c>
       <c r="B124" s="5">
-        <v>46111.36190743056</v>
+        <v>46111.52857409722</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46114.46243561343</v>
+        <v>46114.629102280094</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>212</v>
@@ -8984,11 +8984,11 @@
         <v>389</v>
       </c>
       <c r="B125" s="8">
-        <v>46111.36200734954</v>
+        <v>46111.528674016205</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46114.462436354166</v>
+        <v>46114.62910302084</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>217</v>
@@ -9037,11 +9037,11 @@
         <v>391</v>
       </c>
       <c r="B126" s="5">
-        <v>46111.364885625</v>
+        <v>46111.531552291664</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46114.462437118054</v>
+        <v>46114.629103784726</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>56</v>
@@ -9090,11 +9090,11 @@
         <v>393</v>
       </c>
       <c r="B127" s="8">
-        <v>46111.36493667824</v>
+        <v>46111.531603344905</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46114.4624378588</v>
+        <v>46114.62910452546</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>60</v>
@@ -9143,11 +9143,11 @@
         <v>395</v>
       </c>
       <c r="B128" s="5">
-        <v>46111.36498171296</v>
+        <v>46111.531648379634</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46114.462438622686</v>
+        <v>46114.62910528935</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>378</v>
@@ -9196,11 +9196,11 @@
         <v>397</v>
       </c>
       <c r="B129" s="8">
-        <v>46111.36503925926</v>
+        <v>46111.531705925925</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46114.462439386574</v>
+        <v>46114.62910605324</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>66</v>
@@ -9249,11 +9249,11 @@
         <v>399</v>
       </c>
       <c r="B130" s="5">
-        <v>46111.36690346064</v>
+        <v>46111.533570127314</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46114.46244017361</v>
+        <v>46114.62910684028</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>306</v>
@@ -9302,11 +9302,11 @@
         <v>401</v>
       </c>
       <c r="B131" s="8">
-        <v>46108.590632638894</v>
+        <v>46108.75729930555</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46114.4708202662</v>
+        <v>46114.63748693287</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>402</v>
@@ -9365,11 +9365,11 @@
         <v>404</v>
       </c>
       <c r="B132" s="5">
-        <v>46111.362133206014</v>
+        <v>46111.528799872685</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46114.46264680555</v>
+        <v>46114.62931347222</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>212</v>
@@ -9416,11 +9416,11 @@
         <v>406</v>
       </c>
       <c r="B133" s="8">
-        <v>46111.36218512732</v>
+        <v>46111.52885179398</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46114.46264762731</v>
+        <v>46114.62931429398</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>217</v>
@@ -9467,11 +9467,11 @@
         <v>408</v>
       </c>
       <c r="B134" s="5">
-        <v>46111.365487731484</v>
+        <v>46111.53215439815</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46114.46264837963</v>
+        <v>46114.629315046295</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>56</v>
@@ -9518,11 +9518,11 @@
         <v>410</v>
       </c>
       <c r="B135" s="8">
-        <v>46111.365539756946</v>
+        <v>46111.53220642361</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46114.4626491088</v>
+        <v>46114.62931577546</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>60</v>
@@ -9569,11 +9569,11 @@
         <v>412</v>
       </c>
       <c r="B136" s="5">
-        <v>46111.36559162037</v>
+        <v>46111.532258287036</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46114.46264986111</v>
+        <v>46114.629316527775</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>378</v>
@@ -9620,11 +9620,11 @@
         <v>414</v>
       </c>
       <c r="B137" s="8">
-        <v>46111.36564334491</v>
+        <v>46111.53231001158</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46114.462650625</v>
+        <v>46114.62931729166</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>66</v>
@@ -9671,11 +9671,11 @@
         <v>416</v>
       </c>
       <c r="B138" s="5">
-        <v>46111.36701570602</v>
+        <v>46111.53368237268</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46114.462651388894</v>
+        <v>46114.62931805555</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>417</v>
@@ -9722,11 +9722,11 @@
         <v>419</v>
       </c>
       <c r="B139" s="8">
-        <v>46108.59063791667</v>
+        <v>46108.757304583334</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46114.47088356482</v>
+        <v>46114.63755023148</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>420</v>
@@ -9785,11 +9785,11 @@
         <v>422</v>
       </c>
       <c r="B140" s="5">
-        <v>46111.36227834491</v>
+        <v>46111.528945011574</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46114.66361440972</v>
+        <v>46114.830281076385</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>212</v>
@@ -9838,11 +9838,11 @@
         <v>424</v>
       </c>
       <c r="B141" s="8">
-        <v>46111.36234425926</v>
+        <v>46111.52901092592</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46114.663636122685</v>
+        <v>46114.830302789356</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>217</v>
@@ -9891,11 +9891,11 @@
         <v>425</v>
       </c>
       <c r="B142" s="5">
-        <v>46111.36580612269</v>
+        <v>46111.53247278935</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46114.66365253473</v>
+        <v>46114.830319201385</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>56</v>
@@ -9944,11 +9944,11 @@
         <v>426</v>
       </c>
       <c r="B143" s="8">
-        <v>46111.36586684028</v>
+        <v>46111.53253350694</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46114.66366907407</v>
+        <v>46114.83033574074</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>60</v>
@@ -9997,11 +9997,11 @@
         <v>427</v>
       </c>
       <c r="B144" s="5">
-        <v>46111.365971747684</v>
+        <v>46111.532638414355</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46114.66368572917</v>
+        <v>46114.83035239583</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>66</v>
@@ -10050,11 +10050,11 @@
         <v>428</v>
       </c>
       <c r="B145" s="8">
-        <v>46111.36591445602</v>
+        <v>46111.53258112269</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46114.66370447917</v>
+        <v>46114.83037114583</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>378</v>
@@ -10103,11 +10103,11 @@
         <v>429</v>
       </c>
       <c r="B146" s="5">
-        <v>46111.36718960648</v>
+        <v>46111.53385627315</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46114.663727604166</v>
+        <v>46114.83039427083</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>306</v>
@@ -10156,11 +10156,11 @@
         <v>430</v>
       </c>
       <c r="B147" s="8">
-        <v>46108.59064383102</v>
+        <v>46108.757310497684</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46114.46296130787</v>
+        <v>46114.62962797454</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>431</v>
@@ -10203,11 +10203,11 @@
         <v>433</v>
       </c>
       <c r="B148" s="5">
-        <v>46108.59064700232</v>
+        <v>46108.75731366898</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46114.470976944445</v>
+        <v>46114.63764361111</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>434</v>
@@ -10266,11 +10266,11 @@
         <v>437</v>
       </c>
       <c r="B149" s="8">
-        <v>46108.59065334491</v>
+        <v>46108.75732001157</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46119.58174862269</v>
+        <v>46119.74841528935</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>438</v>
@@ -10329,11 +10329,11 @@
         <v>440</v>
       </c>
       <c r="B150" s="5">
-        <v>46108.59066239583</v>
+        <v>46108.7573290625</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46114.462961701385</v>
+        <v>46114.62962836806</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>441</v>
@@ -10376,11 +10376,11 @@
         <v>443</v>
       </c>
       <c r="B151" s="8">
-        <v>46108.59066638889</v>
+        <v>46108.75733305556</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46119.581792349534</v>
+        <v>46119.748459016206</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>444</v>
@@ -10439,11 +10439,11 @@
         <v>446</v>
       </c>
       <c r="B152" s="5">
-        <v>46108.59067203704</v>
+        <v>46108.757338703705</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46119.58183587963</v>
+        <v>46119.748502546296</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>447</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -3417,7 +3417,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46193.195807870376</v>
+        <v>46206.57726722222</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46193.19580785879</v>
+        <v>46206.577005486106</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>114</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -6186,7 +6186,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46114.63343645833</v>
+        <v>46209.20762703704</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>261</v>
@@ -6233,8 +6233,8 @@
       <c r="S75" s="9">
         <v>0</v>
       </c>
-      <c r="T75" s="11" t="s">
-        <v>53</v>
+      <c r="T75" s="12" t="s">
+        <v>167</v>
       </c>
       <c r="U75" s="10" t="s">
         <v>54</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -3110,7 +3110,7 @@
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="8">
-        <v>46205.72132123842</v>
+        <v>46209.59541466435</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>88</v>
@@ -3287,9 +3287,11 @@
       <c r="B26" s="5">
         <v>46108.75688076389</v>
       </c>
-      <c r="C26" s="6"/>
+      <c r="C26" s="5">
+        <v>46209.595404629625</v>
+      </c>
       <c r="D26" s="5">
-        <v>46205.72131620371</v>
+        <v>46209.59540697916</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>98</v>
@@ -3417,7 +3419,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46206.57726722222</v>
+        <v>46209.59805664352</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3462,13 +3464,13 @@
         <v>46192</v>
       </c>
       <c r="S28" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U28" s="12" t="s">
-        <v>90</v>
+      <c r="U28" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -4161,7 +4163,7 @@
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46205.7213208912</v>
+        <v>46209.595412939816</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>145</v>
@@ -4604,7 +4606,7 @@
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46199.16861097222</v>
+        <v>46209.598061192126</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>109</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -634,10 +634,10 @@
     <t>Planos preliminar</t>
   </si>
   <si>
-    <t>Gabriel Venegas</t>
-  </si>
-  <si>
-    <t>gabriel.venegas@zitron.com</t>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
   </si>
   <si>
     <t>Ingenieria Detalle,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4</t>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46203.203189305554</v>
+        <v>46210.168692928244</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>163</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46169.850767233795</v>
+        <v>46210.16869111111</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>171</v>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46141.52778434027</v>
+        <v>46210.49827609953</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>206</v>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46190.19261076389</v>
+        <v>46210.49819702546</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>220</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -514,283 +514,283 @@
     <t>Generación OC materiales ot 4287 - 4288,Fabricacion a codigo y compras locales ot 4287 - 4288</t>
   </si>
   <si>
+    <t>1213833777483168</t>
+  </si>
+  <si>
+    <t>Materiales a codigo // compras locales aprovisionamientomiento: ot 4287 - 4288,Fabricacion a codigo y compras locales ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>1213833564688412</t>
+  </si>
+  <si>
+    <t>Fabricacion a codigo y compras locales ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>Materiales a codigo // compras locales aprovisionamientomiento: ot 4287 - 4288,Recepcion materiales a codigos // compras locales aprovisionamiento,Fabricacion estructura proveedor externo ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>1213833763284961</t>
+  </si>
+  <si>
+    <t>Sensores</t>
+  </si>
+  <si>
+    <t>Generacion OC Sensor,Fabricacion Sensores</t>
+  </si>
+  <si>
+    <t>1213833763284977</t>
+  </si>
+  <si>
+    <t>Generacion OC Sensor</t>
+  </si>
+  <si>
+    <t>Sensores,Fabricacion Sensores</t>
+  </si>
+  <si>
+    <t>1213833777489751</t>
+  </si>
+  <si>
+    <t>Fabricacion Sensores</t>
+  </si>
+  <si>
+    <t>Recepción Sensores,Sensores</t>
+  </si>
+  <si>
+    <t>1213833777489767</t>
+  </si>
+  <si>
+    <t>Fabricacion Externa ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Generacion OC Fabricacion Externa ot 4287 - 4288,Fabricacion estructura proveedor externo ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>1213833564667630</t>
+  </si>
+  <si>
+    <t>Fabricacion Externa ot 4287 - 4288,Fabricacion estructura proveedor externo ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>1213833763295351</t>
+  </si>
+  <si>
+    <t>Fabricacion estructura proveedor externo ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>Check Planos,Fabricacion a codigo y compras locales ot 4287 - 4288, Generacion OC Fabricacion Externa ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>Control de calidad Fabricación externa,Fabricacion Externa ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>1213869987281796</t>
+  </si>
+  <si>
+    <t>Atenuador ot 4289</t>
+  </si>
+  <si>
+    <t>Propuesta Atenuadores ,Generacion oc Atenuador  ot 4289,Fabricacion atenuador ot 4289</t>
+  </si>
+  <si>
+    <t>1213869987281797</t>
+  </si>
+  <si>
+    <t>Generacion oc Atenuador  ot 4289</t>
+  </si>
+  <si>
+    <t>Fabricacion atenuador ot 4289,Atenuador ot 4289</t>
+  </si>
+  <si>
+    <t>1213869987281798</t>
+  </si>
+  <si>
+    <t>Fabricacion atenuador ot 4289</t>
+  </si>
+  <si>
+    <t>Atenuadores,Atenuador ot 4289</t>
+  </si>
+  <si>
+    <t>1213833564706217</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1213833564706230</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:,Check Planos</t>
+  </si>
+  <si>
+    <t>1213899500210867</t>
+  </si>
+  <si>
+    <t>OT 4287 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Planos preliminar,OT 4287 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213899500210869</t>
+  </si>
+  <si>
+    <t>OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>Planos preliminar,OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>1213833763300853</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>Check Planos,Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t>1213899500210870</t>
+  </si>
+  <si>
+    <t>OT 4287 ZVR 1-14-42/4,Planos motor proveedor ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>Planos definitivos,OT 4287 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213899500210871</t>
+  </si>
+  <si>
+    <t>OT 4288 ZVR1-14-30/4,Planos motor proveedor ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>Planos definitivos,OT4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>1213833763300879</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Planos preliminar</t>
+  </si>
+  <si>
+    <t>OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,propuesta compras a codigo // aprovisionamiento ot 4287 - 4288,Propuesta Fabricacion Externa ot 4287 - 4288,Fabricacion estructura proveedor externo ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>1213899500210872</t>
+  </si>
+  <si>
+    <t>1213899500210873</t>
+  </si>
+  <si>
+    <t>OT4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>1213833622855505</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4287 ZVR 1-14-42/4,OT  4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>1213869987281952</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT,OT 4287 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213869987281953</t>
+  </si>
+  <si>
+    <t>OT  4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT,OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>1213833622855516</t>
+  </si>
+  <si>
+    <t>Control de calidad</t>
+  </si>
+  <si>
+    <t>Control de calidad Fabricación externa</t>
+  </si>
+  <si>
+    <t>1213833622855625</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>Control de calidad,Recepcion Fabricacion externa</t>
+  </si>
+  <si>
+    <t>1213840446207872</t>
+  </si>
+  <si>
+    <t>Bodega</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
+  </si>
+  <si>
+    <t>1213840446207876</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamient,Bodega</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213833777483168</t>
-  </si>
-  <si>
-    <t>Materiales a codigo // compras locales aprovisionamientomiento: ot 4287 - 4288,Fabricacion a codigo y compras locales ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>1213833564688412</t>
-  </si>
-  <si>
-    <t>Fabricacion a codigo y compras locales ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>Materiales a codigo // compras locales aprovisionamientomiento: ot 4287 - 4288,Recepcion materiales a codigos // compras locales aprovisionamiento,Fabricacion estructura proveedor externo ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>1213833763284961</t>
-  </si>
-  <si>
-    <t>Sensores</t>
-  </si>
-  <si>
-    <t>Generacion OC Sensor,Fabricacion Sensores</t>
-  </si>
-  <si>
-    <t>1213833763284977</t>
-  </si>
-  <si>
-    <t>Generacion OC Sensor</t>
-  </si>
-  <si>
-    <t>Sensores,Fabricacion Sensores</t>
-  </si>
-  <si>
-    <t>1213833777489751</t>
-  </si>
-  <si>
-    <t>Fabricacion Sensores</t>
-  </si>
-  <si>
-    <t>Recepción Sensores,Sensores</t>
-  </si>
-  <si>
-    <t>1213833777489767</t>
-  </si>
-  <si>
-    <t>Fabricacion Externa ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Generacion OC Fabricacion Externa ot 4287 - 4288,Fabricacion estructura proveedor externo ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>1213833564667630</t>
-  </si>
-  <si>
-    <t>Fabricacion Externa ot 4287 - 4288,Fabricacion estructura proveedor externo ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>1213833763295351</t>
-  </si>
-  <si>
-    <t>Fabricacion estructura proveedor externo ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>Check Planos,Fabricacion a codigo y compras locales ot 4287 - 4288, Generacion OC Fabricacion Externa ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>Control de calidad Fabricación externa,Fabricacion Externa ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>1213869987281796</t>
-  </si>
-  <si>
-    <t>Atenuador ot 4289</t>
-  </si>
-  <si>
-    <t>Propuesta Atenuadores ,Generacion oc Atenuador  ot 4289,Fabricacion atenuador ot 4289</t>
-  </si>
-  <si>
-    <t>1213869987281797</t>
-  </si>
-  <si>
-    <t>Generacion oc Atenuador  ot 4289</t>
-  </si>
-  <si>
-    <t>Fabricacion atenuador ot 4289,Atenuador ot 4289</t>
-  </si>
-  <si>
-    <t>1213869987281798</t>
-  </si>
-  <si>
-    <t>Fabricacion atenuador ot 4289</t>
-  </si>
-  <si>
-    <t>Atenuadores,Atenuador ot 4289</t>
-  </si>
-  <si>
-    <t>1213833564706217</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1213833564706230</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:,Check Planos</t>
-  </si>
-  <si>
-    <t>1213899500210867</t>
-  </si>
-  <si>
-    <t>OT 4287 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Planos preliminar,OT 4287 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213899500210869</t>
-  </si>
-  <si>
-    <t>OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>Planos preliminar,OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>1213833763300853</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>Check Planos,Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t>1213899500210870</t>
-  </si>
-  <si>
-    <t>OT 4287 ZVR 1-14-42/4,Planos motor proveedor ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>Planos definitivos,OT 4287 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213899500210871</t>
-  </si>
-  <si>
-    <t>OT 4288 ZVR1-14-30/4,Planos motor proveedor ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>Planos definitivos,OT4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>1213833763300879</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Planos preliminar</t>
-  </si>
-  <si>
-    <t>OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,propuesta compras a codigo // aprovisionamiento ot 4287 - 4288,Propuesta Fabricacion Externa ot 4287 - 4288,Fabricacion estructura proveedor externo ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>1213899500210872</t>
-  </si>
-  <si>
-    <t>1213899500210873</t>
-  </si>
-  <si>
-    <t>OT4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>1213833622855505</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4287 ZVR 1-14-42/4,OT  4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>1213869987281952</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT,OT 4287 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213869987281953</t>
-  </si>
-  <si>
-    <t>OT  4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT,OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>1213833622855516</t>
-  </si>
-  <si>
-    <t>Control de calidad</t>
-  </si>
-  <si>
-    <t>Control de calidad Fabricación externa</t>
-  </si>
-  <si>
-    <t>1213833622855625</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>Control de calidad,Recepcion Fabricacion externa</t>
-  </si>
-  <si>
-    <t>1213840446207872</t>
-  </si>
-  <si>
-    <t>Bodega</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
-  </si>
-  <si>
-    <t>1213840446207876</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamient,Bodega</t>
   </si>
   <si>
     <t>1213840446207878</t>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46210.168692928244</v>
+        <v>46211.173315312495</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>163</v>
@@ -4590,8 +4590,8 @@
       <c r="S46" s="6">
         <v>0</v>
       </c>
-      <c r="T46" s="12" t="s">
-        <v>167</v>
+      <c r="T46" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U46" s="10" t="s">
         <v>54</v>
@@ -4599,7 +4599,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B47" s="8">
         <v>46108.75703201389</v>
@@ -4642,7 +4642,7 @@
         <v>105</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q47" s="8">
         <v>45985</v>
@@ -4662,7 +4662,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B48" s="5">
         <v>46108.75703761574</v>
@@ -4672,7 +4672,7 @@
         <v>46210.16869111111</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
@@ -4705,7 +4705,7 @@
         <v>109</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q48" s="5">
         <v>46007</v>
@@ -4725,7 +4725,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B49" s="8">
         <v>46108.75704306713</v>
@@ -4737,7 +4737,7 @@
         <v>46154.86784422454</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
@@ -4767,7 +4767,7 @@
         <v>119</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>119</v>
@@ -4790,7 +4790,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B50" s="5">
         <v>46108.75705032407</v>
@@ -4802,7 +4802,7 @@
         <v>46154.86746811343</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
@@ -4829,13 +4829,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>111</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4845,7 +4845,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B51" s="8">
         <v>46108.75705728009</v>
@@ -4857,7 +4857,7 @@
         <v>46154.8677641088</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
@@ -4884,13 +4884,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4900,7 +4900,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B52" s="5">
         <v>46108.757061435186</v>
@@ -4910,16 +4910,16 @@
         <v>46169.85242414352</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
+      <c r="H52" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I52" s="5">
         <v>46195</v>
@@ -4940,7 +4940,7 @@
         <v>119</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>119</v>
@@ -4963,7 +4963,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B53" s="8">
         <v>46108.75710696759</v>
@@ -4979,10 +4979,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="H53" s="9" t="s">
         <v>184</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>185</v>
       </c>
       <c r="I53" s="8">
         <v>46195</v>
@@ -5000,13 +5000,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>114</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5022,7 +5022,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B54" s="5">
         <v>46108.757112928244</v>
@@ -5032,16 +5032,16 @@
         <v>46169.85241099537</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I54" s="5">
         <v>46210</v>
@@ -5059,13 +5059,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O54" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="P54" s="6" t="s">
         <v>191</v>
-      </c>
-      <c r="P54" s="6" t="s">
-        <v>192</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5075,7 +5075,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B55" s="8">
         <v>46111.50860645833</v>
@@ -5087,7 +5087,7 @@
         <v>46182.69406362269</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
@@ -5117,7 +5117,7 @@
         <v>119</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5140,7 +5140,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B56" s="5">
         <v>46111.508755937495</v>
@@ -5152,7 +5152,7 @@
         <v>46182.69350877315</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -5179,13 +5179,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>86</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5195,7 +5195,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B57" s="8">
         <v>46111.508846770834</v>
@@ -5207,7 +5207,7 @@
         <v>46182.69403748843</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
@@ -5234,13 +5234,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5250,7 +5250,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B58" s="5">
         <v>46108.75711900463</v>
@@ -5260,7 +5260,7 @@
         <v>46141.52778395833</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -5284,7 +5284,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5297,7 +5297,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B59" s="8">
         <v>46108.75712325232</v>
@@ -5307,16 +5307,16 @@
         <v>46210.49827609953</v>
       </c>
       <c r="E59" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="F59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="9" t="s">
+      <c r="H59" s="9" t="s">
         <v>207</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>208</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="8">
@@ -5332,13 +5332,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O59" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="P59" s="9" t="s">
         <v>209</v>
-      </c>
-      <c r="P59" s="9" t="s">
-        <v>210</v>
       </c>
       <c r="Q59" s="8">
         <v>46121</v>
@@ -5358,7 +5358,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B60" s="5">
         <v>46114.552579166666</v>
@@ -5368,16 +5368,16 @@
         <v>46127.171562662035</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
+      <c r="H60" s="6" t="s">
         <v>213</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>214</v>
       </c>
       <c r="I60" s="5">
         <v>46121</v>
@@ -5395,13 +5395,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5411,7 +5411,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B61" s="8">
         <v>46114.552773240735</v>
@@ -5421,16 +5421,16 @@
         <v>46127.17156420139</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>213</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>214</v>
       </c>
       <c r="I61" s="8">
         <v>46121</v>
@@ -5448,13 +5448,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>78</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5464,7 +5464,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B62" s="5">
         <v>46108.75712855324</v>
@@ -5474,16 +5474,16 @@
         <v>46210.49819702546</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>207</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>208</v>
       </c>
       <c r="I62" s="5">
         <v>46183</v>
@@ -5501,13 +5501,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O62" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="P62" s="6" t="s">
         <v>221</v>
-      </c>
-      <c r="P62" s="6" t="s">
-        <v>222</v>
       </c>
       <c r="Q62" s="5">
         <v>46183</v>
@@ -5527,7 +5527,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B63" s="8">
         <v>46114.55286452547</v>
@@ -5537,16 +5537,16 @@
         <v>46189.16802</v>
       </c>
       <c r="E63" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="F63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="9" t="s">
+      <c r="H63" s="9" t="s">
         <v>213</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>214</v>
       </c>
       <c r="I63" s="8">
         <v>46183</v>
@@ -5564,13 +5564,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O63" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="P63" s="9" t="s">
         <v>224</v>
-      </c>
-      <c r="P63" s="9" t="s">
-        <v>225</v>
       </c>
       <c r="Q63" s="9"/>
       <c r="R63" s="9"/>
@@ -5580,7 +5580,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B64" s="5">
         <v>46114.552966620366</v>
@@ -5590,16 +5590,16 @@
         <v>46189.16802199074</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>213</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>214</v>
       </c>
       <c r="I64" s="5">
         <v>46183</v>
@@ -5617,13 +5617,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O64" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>227</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>228</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5633,7 +5633,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B65" s="8">
         <v>46108.75713383102</v>
@@ -5649,10 +5649,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>213</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>214</v>
       </c>
       <c r="I65" s="8">
         <v>46190</v>
@@ -5670,13 +5670,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O65" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="P65" s="9" t="s">
         <v>230</v>
-      </c>
-      <c r="P65" s="9" t="s">
-        <v>231</v>
       </c>
       <c r="Q65" s="8">
         <v>46190</v>
@@ -5696,7 +5696,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B66" s="5">
         <v>46114.55312298611</v>
@@ -5706,16 +5706,16 @@
         <v>46190.16810163195</v>
       </c>
       <c r="E66" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G66" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="F66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G66" s="6" t="s">
+      <c r="H66" s="6" t="s">
         <v>213</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>214</v>
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="5">
@@ -5734,7 +5734,7 @@
         <v>108</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5747,7 +5747,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B67" s="8">
         <v>46114.553244675924</v>
@@ -5757,16 +5757,16 @@
         <v>46190.168103460644</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>213</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>214</v>
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="8">
@@ -5785,7 +5785,7 @@
         <v>108</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>26</v>
@@ -5798,7 +5798,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B68" s="5">
         <v>46108.757138761575</v>
@@ -5808,16 +5808,16 @@
         <v>46114.631384050925</v>
       </c>
       <c r="E68" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G68" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="F68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G68" s="6" t="s">
+      <c r="H68" s="6" t="s">
         <v>237</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>238</v>
       </c>
       <c r="I68" s="5">
         <v>46281</v>
@@ -5835,10 +5835,10 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5861,7 +5861,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B69" s="8">
         <v>46111.55280189815</v>
@@ -5871,16 +5871,16 @@
         <v>46114.62851033565</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -5896,13 +5896,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5912,7 +5912,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B70" s="5">
         <v>46111.55285245371</v>
@@ -5922,16 +5922,16 @@
         <v>46114.62851040509</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>237</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>238</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -5947,13 +5947,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5963,7 +5963,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B71" s="8">
         <v>46108.75714166666</v>
@@ -5973,7 +5973,7 @@
         <v>46118.545566597226</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -5997,7 +5997,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -6010,7 +6010,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B72" s="5">
         <v>46108.75714454861</v>
@@ -6020,16 +6020,16 @@
         <v>46118.55132545139</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -6045,13 +6045,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Q72" s="5">
         <v>46231</v>
@@ -6071,7 +6071,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B73" s="8">
         <v>46111.50359008102</v>
@@ -6081,7 +6081,7 @@
         <v>46114.61935158564</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -6105,7 +6105,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -6118,7 +6118,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B74" s="5">
         <v>46111.50404616898</v>
@@ -6128,16 +6128,16 @@
         <v>46205.19806045139</v>
       </c>
       <c r="E74" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G74" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="F74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G74" s="6" t="s">
+      <c r="H74" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I74" s="5">
         <v>46211</v>
@@ -6155,13 +6155,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q74" s="5">
         <v>46211</v>
@@ -6173,7 +6173,7 @@
         <v>0</v>
       </c>
       <c r="T74" s="12" t="s">
-        <v>167</v>
+        <v>259</v>
       </c>
       <c r="U74" s="10" t="s">
         <v>54</v>
@@ -6197,10 +6197,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="H75" s="9" t="s">
         <v>249</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>250</v>
       </c>
       <c r="I75" s="8">
         <v>46213</v>
@@ -6218,10 +6218,10 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P75" s="9" t="s">
         <v>262</v>
@@ -6236,7 +6236,7 @@
         <v>0</v>
       </c>
       <c r="T75" s="12" t="s">
-        <v>167</v>
+        <v>259</v>
       </c>
       <c r="U75" s="10" t="s">
         <v>54</v>
@@ -6394,7 +6394,7 @@
         <v>264</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>264</v>
@@ -6427,7 +6427,7 @@
         <v>46114.627016388884</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -6480,7 +6480,7 @@
         <v>46114.627017175924</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6539,10 +6539,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="H81" s="9" t="s">
         <v>249</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>250</v>
       </c>
       <c r="I81" s="8">
         <v>46246</v>
@@ -6563,7 +6563,7 @@
         <v>264</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P81" s="9" t="s">
         <v>264</v>
@@ -6596,16 +6596,16 @@
         <v>46114.62715587963</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I82" s="5">
         <v>46246</v>
@@ -6649,16 +6649,16 @@
         <v>46114.62715672454</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="H83" s="9" t="s">
         <v>249</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>250</v>
       </c>
       <c r="I83" s="8">
         <v>46246</v>
@@ -6755,10 +6755,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="H85" s="9" t="s">
         <v>257</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>258</v>
       </c>
       <c r="I85" s="8">
         <v>46183</v>
@@ -6818,10 +6818,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I86" s="5">
         <v>46239</v>
@@ -6881,10 +6881,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="H87" s="9" t="s">
         <v>257</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>258</v>
       </c>
       <c r="I87" s="8">
         <v>46246</v>
@@ -6944,10 +6944,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I88" s="5">
         <v>46273</v>
@@ -7007,10 +7007,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="H89" s="9" t="s">
         <v>257</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>258</v>
       </c>
       <c r="I89" s="8">
         <v>46220</v>
@@ -7031,10 +7031,10 @@
         <v>287</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q89" s="8">
         <v>46220</v>
@@ -7070,10 +7070,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
@@ -7092,7 +7092,7 @@
         <v>287</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>303</v>
@@ -7131,10 +7131,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="H91" s="9" t="s">
         <v>257</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>258</v>
       </c>
       <c r="I91" s="8">
         <v>46181</v>
@@ -7155,7 +7155,7 @@
         <v>287</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P91" s="9" t="s">
         <v>306</v>
@@ -7265,7 +7265,7 @@
         <v>308</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P93" s="9" t="s">
         <v>308</v>
@@ -7298,7 +7298,7 @@
         <v>46118.545567442125</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7351,7 +7351,7 @@
         <v>46118.54556813657</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7434,7 +7434,7 @@
         <v>308</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>308</v>
@@ -7467,7 +7467,7 @@
         <v>46114.627765578705</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7520,7 +7520,7 @@
         <v>46114.62776635417</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7603,7 +7603,7 @@
         <v>308</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P99" s="9" t="s">
         <v>308</v>
@@ -7636,7 +7636,7 @@
         <v>46118.54557231482</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7689,7 +7689,7 @@
         <v>46118.54556883102</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7772,7 +7772,7 @@
         <v>308</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>308</v>
@@ -7805,7 +7805,7 @@
         <v>46118.545570937495</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7858,7 +7858,7 @@
         <v>46118.545571608796</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7941,7 +7941,7 @@
         <v>308</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P105" s="9" t="s">
         <v>308</v>
@@ -7974,7 +7974,7 @@
         <v>46118.545569548616</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -8027,7 +8027,7 @@
         <v>46118.545570243055</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -8110,7 +8110,7 @@
         <v>308</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>308</v>
@@ -8143,7 +8143,7 @@
         <v>46114.62850982639</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8171,7 +8171,7 @@
         <v>349</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P109" s="9" t="s">
         <v>351</v>
@@ -8194,7 +8194,7 @@
         <v>46114.62851064815</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8222,7 +8222,7 @@
         <v>349</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>353</v>
@@ -8306,7 +8306,7 @@
         <v>46114.62864336805</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8334,7 +8334,7 @@
         <v>355</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>358</v>
@@ -8357,7 +8357,7 @@
         <v>46114.62864409722</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8385,7 +8385,7 @@
         <v>355</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P113" s="9" t="s">
         <v>360</v>
@@ -8518,7 +8518,7 @@
         <v>46114.62888387732</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8546,7 +8546,7 @@
         <v>365</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>370</v>
@@ -8569,7 +8569,7 @@
         <v>46114.62888469908</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8597,7 +8597,7 @@
         <v>365</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P117" s="9" t="s">
         <v>372</v>
@@ -8938,7 +8938,7 @@
         <v>46114.629102280094</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8968,7 +8968,7 @@
         <v>385</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>388</v>
@@ -8991,7 +8991,7 @@
         <v>46114.62910302084</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -9021,7 +9021,7 @@
         <v>385</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P125" s="9" t="s">
         <v>390</v>
@@ -9372,7 +9372,7 @@
         <v>46114.62931347222</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9400,7 +9400,7 @@
         <v>402</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>405</v>
@@ -9423,7 +9423,7 @@
         <v>46114.62931429398</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
@@ -9451,7 +9451,7 @@
         <v>402</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P133" s="9" t="s">
         <v>407</v>
@@ -9792,7 +9792,7 @@
         <v>46114.830281076385</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9822,7 +9822,7 @@
         <v>420</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>423</v>
@@ -9845,7 +9845,7 @@
         <v>46114.830302789356</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
@@ -9875,7 +9875,7 @@
         <v>420</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P141" s="9" t="s">
         <v>420</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -4289,7 +4289,7 @@
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46182.693445439814</v>
+        <v>46211.84653167824</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>151</v>
@@ -4478,9 +4478,11 @@
       <c r="B45" s="8">
         <v>46108.7570218287</v>
       </c>
-      <c r="C45" s="9"/>
+      <c r="C45" s="8">
+        <v>46211.84652571759</v>
+      </c>
       <c r="D45" s="8">
-        <v>46199.811805694444</v>
+        <v>46211.84652803241</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>160</v>
@@ -5257,7 +5259,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46141.52778395833</v>
+        <v>46211.84618952546</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>202</v>
@@ -5302,9 +5304,11 @@
       <c r="B59" s="8">
         <v>46108.75712325232</v>
       </c>
-      <c r="C59" s="9"/>
+      <c r="C59" s="8">
+        <v>46211.846184131944</v>
+      </c>
       <c r="D59" s="8">
-        <v>46210.49827609953</v>
+        <v>46211.84618561342</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>205</v>
@@ -5347,13 +5351,13 @@
         <v>46127</v>
       </c>
       <c r="S59" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T59" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U59" s="12" t="s">
-        <v>90</v>
+      <c r="U59" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -5363,9 +5367,11 @@
       <c r="B60" s="5">
         <v>46114.552579166666</v>
       </c>
-      <c r="C60" s="6"/>
+      <c r="C60" s="5">
+        <v>46211.84604746528</v>
+      </c>
       <c r="D60" s="5">
-        <v>46127.171562662035</v>
+        <v>46211.84604957176</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>211</v>
@@ -5416,9 +5422,11 @@
       <c r="B61" s="8">
         <v>46114.552773240735</v>
       </c>
-      <c r="C61" s="9"/>
+      <c r="C61" s="8">
+        <v>46211.84605395833</v>
+      </c>
       <c r="D61" s="8">
-        <v>46127.17156420139</v>
+        <v>46211.846055462964</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>216</v>
@@ -5534,7 +5542,7 @@
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46189.16802</v>
+        <v>46211.846533206015</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>211</v>
@@ -5587,7 +5595,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46189.16802199074</v>
+        <v>46211.84653444444</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>216</v>
@@ -5640,7 +5648,7 @@
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46191.171331157406</v>
+        <v>46211.84618984954</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>108</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -538,6 +538,9 @@
     <t>Generacion OC Sensor,Fabricacion Sensores</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1213833763284977</t>
   </si>
   <si>
@@ -788,9 +791,6 @@
   </si>
   <si>
     <t>Control de calidad compras materiales a codigo // compras locale aprovisionamient,Bodega</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213840446207878</t>
@@ -4736,7 +4736,7 @@
         <v>46154.86784248843</v>
       </c>
       <c r="D49" s="8">
-        <v>46154.86784422454</v>
+        <v>46212.17359799768</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>173</v>
@@ -4783,8 +4783,8 @@
       <c r="S49" s="9">
         <v>1</v>
       </c>
-      <c r="T49" s="11" t="s">
-        <v>53</v>
+      <c r="T49" s="12" t="s">
+        <v>175</v>
       </c>
       <c r="U49" s="11" t="s">
         <v>32</v>
@@ -4792,7 +4792,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B50" s="5">
         <v>46108.75705032407</v>
@@ -4804,7 +4804,7 @@
         <v>46154.86746811343</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
@@ -4837,7 +4837,7 @@
         <v>111</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4847,7 +4847,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B51" s="8">
         <v>46108.75705728009</v>
@@ -4859,7 +4859,7 @@
         <v>46154.8677641088</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
@@ -4889,10 +4889,10 @@
         <v>173</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4902,7 +4902,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B52" s="5">
         <v>46108.757061435186</v>
@@ -4912,16 +4912,16 @@
         <v>46169.85242414352</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I52" s="5">
         <v>46195</v>
@@ -4942,7 +4942,7 @@
         <v>119</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>119</v>
@@ -4965,7 +4965,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B53" s="8">
         <v>46108.75710696759</v>
@@ -4981,10 +4981,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I53" s="8">
         <v>46195</v>
@@ -5002,13 +5002,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>114</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5024,7 +5024,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B54" s="5">
         <v>46108.757112928244</v>
@@ -5034,16 +5034,16 @@
         <v>46169.85241099537</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I54" s="5">
         <v>46210</v>
@@ -5061,13 +5061,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5077,7 +5077,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B55" s="8">
         <v>46111.50860645833</v>
@@ -5089,7 +5089,7 @@
         <v>46182.69406362269</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
@@ -5119,7 +5119,7 @@
         <v>119</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5142,7 +5142,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B56" s="5">
         <v>46111.508755937495</v>
@@ -5154,7 +5154,7 @@
         <v>46182.69350877315</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -5181,13 +5181,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>86</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5197,7 +5197,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B57" s="8">
         <v>46111.508846770834</v>
@@ -5209,7 +5209,7 @@
         <v>46182.69403748843</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
@@ -5236,13 +5236,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5252,7 +5252,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B58" s="5">
         <v>46108.75711900463</v>
@@ -5262,7 +5262,7 @@
         <v>46211.84618952546</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -5286,7 +5286,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5299,7 +5299,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B59" s="8">
         <v>46108.75712325232</v>
@@ -5311,16 +5311,16 @@
         <v>46211.84618561342</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="8">
@@ -5336,13 +5336,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q59" s="8">
         <v>46121</v>
@@ -5362,7 +5362,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B60" s="5">
         <v>46114.552579166666</v>
@@ -5374,16 +5374,16 @@
         <v>46211.84604957176</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I60" s="5">
         <v>46121</v>
@@ -5401,13 +5401,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5417,7 +5417,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B61" s="8">
         <v>46114.552773240735</v>
@@ -5429,16 +5429,16 @@
         <v>46211.846055462964</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I61" s="8">
         <v>46121</v>
@@ -5456,13 +5456,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>78</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5472,7 +5472,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B62" s="5">
         <v>46108.75712855324</v>
@@ -5482,16 +5482,16 @@
         <v>46210.49819702546</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I62" s="5">
         <v>46183</v>
@@ -5509,13 +5509,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q62" s="5">
         <v>46183</v>
@@ -5535,7 +5535,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B63" s="8">
         <v>46114.55286452547</v>
@@ -5545,16 +5545,16 @@
         <v>46211.846533206015</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I63" s="8">
         <v>46183</v>
@@ -5572,13 +5572,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q63" s="9"/>
       <c r="R63" s="9"/>
@@ -5588,7 +5588,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B64" s="5">
         <v>46114.552966620366</v>
@@ -5598,16 +5598,16 @@
         <v>46211.84653444444</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I64" s="5">
         <v>46183</v>
@@ -5625,13 +5625,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5641,7 +5641,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B65" s="8">
         <v>46108.75713383102</v>
@@ -5657,10 +5657,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I65" s="8">
         <v>46190</v>
@@ -5678,13 +5678,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q65" s="8">
         <v>46190</v>
@@ -5704,7 +5704,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B66" s="5">
         <v>46114.55312298611</v>
@@ -5714,16 +5714,16 @@
         <v>46190.16810163195</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="5">
@@ -5742,7 +5742,7 @@
         <v>108</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5755,7 +5755,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B67" s="8">
         <v>46114.553244675924</v>
@@ -5765,16 +5765,16 @@
         <v>46190.168103460644</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="8">
@@ -5793,7 +5793,7 @@
         <v>108</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>26</v>
@@ -5806,7 +5806,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B68" s="5">
         <v>46108.757138761575</v>
@@ -5816,16 +5816,16 @@
         <v>46114.631384050925</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I68" s="5">
         <v>46281</v>
@@ -5843,10 +5843,10 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5869,7 +5869,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B69" s="8">
         <v>46111.55280189815</v>
@@ -5879,16 +5879,16 @@
         <v>46114.62851033565</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -5904,13 +5904,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5920,7 +5920,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B70" s="5">
         <v>46111.55285245371</v>
@@ -5930,16 +5930,16 @@
         <v>46114.62851040509</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -5955,13 +5955,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5971,7 +5971,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B71" s="8">
         <v>46108.75714166666</v>
@@ -5981,7 +5981,7 @@
         <v>46118.545566597226</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -6005,7 +6005,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -6018,7 +6018,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B72" s="5">
         <v>46108.75714454861</v>
@@ -6028,16 +6028,16 @@
         <v>46118.55132545139</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -6053,13 +6053,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q72" s="5">
         <v>46231</v>
@@ -6079,7 +6079,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B73" s="8">
         <v>46111.50359008102</v>
@@ -6089,7 +6089,7 @@
         <v>46114.61935158564</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -6113,7 +6113,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -6126,26 +6126,26 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B74" s="5">
         <v>46111.50404616898</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46205.19806045139</v>
+        <v>46212.167788067134</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I74" s="5">
         <v>46211</v>
@@ -6163,13 +6163,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>170</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q74" s="5">
         <v>46211</v>
@@ -6181,7 +6181,7 @@
         <v>0</v>
       </c>
       <c r="T74" s="12" t="s">
-        <v>259</v>
+        <v>175</v>
       </c>
       <c r="U74" s="10" t="s">
         <v>54</v>
@@ -6205,10 +6205,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I75" s="8">
         <v>46213</v>
@@ -6226,10 +6226,10 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P75" s="9" t="s">
         <v>262</v>
@@ -6244,7 +6244,7 @@
         <v>0</v>
       </c>
       <c r="T75" s="12" t="s">
-        <v>259</v>
+        <v>175</v>
       </c>
       <c r="U75" s="10" t="s">
         <v>54</v>
@@ -6402,7 +6402,7 @@
         <v>264</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>264</v>
@@ -6435,7 +6435,7 @@
         <v>46114.627016388884</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -6488,7 +6488,7 @@
         <v>46114.627017175924</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6547,10 +6547,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I81" s="8">
         <v>46246</v>
@@ -6571,7 +6571,7 @@
         <v>264</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P81" s="9" t="s">
         <v>264</v>
@@ -6604,16 +6604,16 @@
         <v>46114.62715587963</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I82" s="5">
         <v>46246</v>
@@ -6657,16 +6657,16 @@
         <v>46114.62715672454</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I83" s="8">
         <v>46246</v>
@@ -6763,10 +6763,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I85" s="8">
         <v>46183</v>
@@ -6826,10 +6826,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I86" s="5">
         <v>46239</v>
@@ -6889,10 +6889,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I87" s="8">
         <v>46246</v>
@@ -6952,10 +6952,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I88" s="5">
         <v>46273</v>
@@ -7015,10 +7015,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I89" s="8">
         <v>46220</v>
@@ -7039,10 +7039,10 @@
         <v>287</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q89" s="8">
         <v>46220</v>
@@ -7078,10 +7078,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
@@ -7100,7 +7100,7 @@
         <v>287</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>303</v>
@@ -7139,10 +7139,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I91" s="8">
         <v>46181</v>
@@ -7163,7 +7163,7 @@
         <v>287</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P91" s="9" t="s">
         <v>306</v>
@@ -7273,7 +7273,7 @@
         <v>308</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P93" s="9" t="s">
         <v>308</v>
@@ -7306,7 +7306,7 @@
         <v>46118.545567442125</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7359,7 +7359,7 @@
         <v>46118.54556813657</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7442,7 +7442,7 @@
         <v>308</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>308</v>
@@ -7475,7 +7475,7 @@
         <v>46114.627765578705</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7528,7 +7528,7 @@
         <v>46114.62776635417</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7611,7 +7611,7 @@
         <v>308</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P99" s="9" t="s">
         <v>308</v>
@@ -7644,7 +7644,7 @@
         <v>46118.54557231482</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7697,7 +7697,7 @@
         <v>46118.54556883102</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7780,7 +7780,7 @@
         <v>308</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>308</v>
@@ -7813,7 +7813,7 @@
         <v>46118.545570937495</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7866,7 +7866,7 @@
         <v>46118.545571608796</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7949,7 +7949,7 @@
         <v>308</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P105" s="9" t="s">
         <v>308</v>
@@ -7982,7 +7982,7 @@
         <v>46118.545569548616</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -8035,7 +8035,7 @@
         <v>46118.545570243055</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -8118,7 +8118,7 @@
         <v>308</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>308</v>
@@ -8151,7 +8151,7 @@
         <v>46114.62850982639</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8179,7 +8179,7 @@
         <v>349</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P109" s="9" t="s">
         <v>351</v>
@@ -8202,7 +8202,7 @@
         <v>46114.62851064815</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8230,7 +8230,7 @@
         <v>349</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>353</v>
@@ -8314,7 +8314,7 @@
         <v>46114.62864336805</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8342,7 +8342,7 @@
         <v>355</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>358</v>
@@ -8365,7 +8365,7 @@
         <v>46114.62864409722</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8393,7 +8393,7 @@
         <v>355</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P113" s="9" t="s">
         <v>360</v>
@@ -8526,7 +8526,7 @@
         <v>46114.62888387732</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8554,7 +8554,7 @@
         <v>365</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>370</v>
@@ -8577,7 +8577,7 @@
         <v>46114.62888469908</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8605,7 +8605,7 @@
         <v>365</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P117" s="9" t="s">
         <v>372</v>
@@ -8946,7 +8946,7 @@
         <v>46114.629102280094</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8976,7 +8976,7 @@
         <v>385</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>388</v>
@@ -8999,7 +8999,7 @@
         <v>46114.62910302084</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -9029,7 +9029,7 @@
         <v>385</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P125" s="9" t="s">
         <v>390</v>
@@ -9380,7 +9380,7 @@
         <v>46114.62931347222</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9408,7 +9408,7 @@
         <v>402</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>405</v>
@@ -9431,7 +9431,7 @@
         <v>46114.62931429398</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
@@ -9459,7 +9459,7 @@
         <v>402</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P133" s="9" t="s">
         <v>407</v>
@@ -9800,7 +9800,7 @@
         <v>46114.830281076385</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9830,7 +9830,7 @@
         <v>420</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>423</v>
@@ -9853,7 +9853,7 @@
         <v>46114.830302789356</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
@@ -9883,7 +9883,7 @@
         <v>420</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P141" s="9" t="s">
         <v>420</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -6133,7 +6133,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46212.167788067134</v>
+        <v>46213.19769318287</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>256</v>
@@ -6180,8 +6180,8 @@
       <c r="S74" s="6">
         <v>0</v>
       </c>
-      <c r="T74" s="12" t="s">
-        <v>175</v>
+      <c r="T74" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U74" s="10" t="s">
         <v>54</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -6196,7 +6196,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46209.20762703704</v>
+        <v>46216.168086481484</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>261</v>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46154.86778005787</v>
+        <v>46216.198306990744</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>300</v>
@@ -7053,8 +7053,8 @@
       <c r="S89" s="9">
         <v>0</v>
       </c>
-      <c r="T89" s="11" t="s">
-        <v>53</v>
+      <c r="T89" s="12" t="s">
+        <v>175</v>
       </c>
       <c r="U89" s="12" t="s">
         <v>90</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -6196,7 +6196,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46216.168086481484</v>
+        <v>46217.17519608796</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>261</v>
@@ -6243,8 +6243,8 @@
       <c r="S75" s="9">
         <v>0</v>
       </c>
-      <c r="T75" s="12" t="s">
-        <v>175</v>
+      <c r="T75" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U75" s="10" t="s">
         <v>54</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="448">
   <si>
     <t>50001525- ZITRON PERU METRO DE LIMA  ESTACION 07</t>
   </si>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46211.84618952546</v>
+        <v>46217.85709320602</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>203</v>
@@ -5295,7 +5295,9 @@
       <c r="R58" s="6"/>
       <c r="S58" s="6"/>
       <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
+      <c r="U58" s="12" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
@@ -5477,9 +5479,11 @@
       <c r="B62" s="5">
         <v>46108.75712855324</v>
       </c>
-      <c r="C62" s="6"/>
+      <c r="C62" s="5">
+        <v>46217.857069363425</v>
+      </c>
       <c r="D62" s="5">
-        <v>46210.49819702546</v>
+        <v>46217.857082789356</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>220</v>
@@ -5524,13 +5528,13 @@
         <v>46189</v>
       </c>
       <c r="S62" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T62" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U62" s="10" t="s">
-        <v>54</v>
+      <c r="U62" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5540,9 +5544,11 @@
       <c r="B63" s="8">
         <v>46114.55286452547</v>
       </c>
-      <c r="C63" s="9"/>
+      <c r="C63" s="8">
+        <v>46217.85704474537</v>
+      </c>
       <c r="D63" s="8">
-        <v>46211.846533206015</v>
+        <v>46217.85704695602</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>212</v>
@@ -5593,9 +5599,11 @@
       <c r="B64" s="5">
         <v>46114.552966620366</v>
       </c>
-      <c r="C64" s="6"/>
+      <c r="C64" s="5">
+        <v>46217.85705295139</v>
+      </c>
       <c r="D64" s="5">
-        <v>46211.84653444444</v>
+        <v>46217.85705476852</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>217</v>
@@ -5648,7 +5656,7 @@
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46211.84618984954</v>
+        <v>46217.857092986116</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>108</v>
@@ -5698,8 +5706,8 @@
       <c r="T65" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U65" s="10" t="s">
-        <v>54</v>
+      <c r="U65" s="12" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5711,7 +5719,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46190.16810163195</v>
+        <v>46217.85705168982</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>212</v>
@@ -5762,7 +5770,7 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46190.168103460644</v>
+        <v>46217.85706487269</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>234</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46114.633869259254</v>
+        <v>46218.20417449074</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>267</v>
@@ -6361,8 +6361,8 @@
       <c r="S77" s="9">
         <v>0</v>
       </c>
-      <c r="T77" s="11" t="s">
-        <v>53</v>
+      <c r="T77" s="12" t="s">
+        <v>175</v>
       </c>
       <c r="U77" s="10" t="s">
         <v>54</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="445">
   <si>
     <t>50001525- ZITRON PERU METRO DE LIMA  ESTACION 07</t>
   </si>
@@ -310,9 +310,6 @@
     <t>propuesta rodete ot 4287 - 4288</t>
   </si>
   <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
     <t>Generación OC Rodete ot 4287 - 4288,Propuesta compras:</t>
   </si>
   <si>
@@ -329,12 +326,6 @@
   </si>
   <si>
     <t>propuesta compras a codigo // aprovisionamiento ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
   </si>
   <si>
     <t>Check Planos</t>
@@ -3300,11 +3291,9 @@
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H26" s="6"/>
       <c r="I26" s="5">
         <v>46121</v>
       </c>
@@ -3327,7 +3316,7 @@
         <v>75</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q26" s="5">
         <v>46121</v>
@@ -3347,7 +3336,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B27" s="8">
         <v>46108.75688663195</v>
@@ -3359,7 +3348,7 @@
         <v>46135.5462021412</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
@@ -3392,7 +3381,7 @@
         <v>46</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Q27" s="8">
         <v>46121</v>
@@ -3412,7 +3401,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B28" s="5">
         <v>46108.756897349536</v>
@@ -3422,17 +3411,15 @@
         <v>46209.59805664352</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>107</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H28" s="6"/>
       <c r="I28" s="5">
         <v>46191</v>
       </c>
@@ -3452,10 +3439,10 @@
         <v>88</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="Q28" s="5">
         <v>46191</v>
@@ -3475,7 +3462,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B29" s="8">
         <v>46108.75690234954</v>
@@ -3487,7 +3474,7 @@
         <v>46123.19348805556</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3520,7 +3507,7 @@
         <v>78</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="Q29" s="8">
         <v>46121</v>
@@ -3540,7 +3527,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B30" s="5">
         <v>46108.75690841435</v>
@@ -3550,17 +3537,15 @@
         <v>46206.577005486106</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>107</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H30" s="6"/>
       <c r="I30" s="5">
         <v>46191</v>
       </c>
@@ -3580,10 +3565,10 @@
         <v>88</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="Q30" s="5">
         <v>46191</v>
@@ -3603,7 +3588,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B31" s="8">
         <v>46108.78647824074</v>
@@ -3648,7 +3633,7 @@
         <v>85</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="Q31" s="8">
         <v>46121</v>
@@ -3668,7 +3653,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B32" s="5">
         <v>46108.756741087964</v>
@@ -3678,7 +3663,7 @@
         <v>46154.867849305556</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>25</v>
@@ -3702,7 +3687,7 @@
         <v>26</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3715,7 +3700,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B33" s="8">
         <v>46108.75695274306</v>
@@ -3725,16 +3710,16 @@
         <v>46182.6933722338</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I33" s="8">
         <v>46125</v>
@@ -3752,13 +3737,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q33" s="8">
         <v>46125</v>
@@ -3778,7 +3763,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B34" s="5">
         <v>46108.75695775463</v>
@@ -3790,16 +3775,16 @@
         <v>46182.69336725694</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I34" s="5">
         <v>46125</v>
@@ -3817,13 +3802,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>95</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="Q34" s="5">
         <v>45985</v>
@@ -3843,7 +3828,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B35" s="8">
         <v>46108.75696342593</v>
@@ -3853,16 +3838,16 @@
         <v>46182.69337332176</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I35" s="8">
         <v>46127</v>
@@ -3880,13 +3865,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Q35" s="8">
         <v>45987</v>
@@ -3906,7 +3891,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B36" s="5">
         <v>46108.75697314815</v>
@@ -3916,16 +3901,16 @@
         <v>46169.854331932875</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I36" s="5">
         <v>46125</v>
@@ -3943,13 +3928,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q36" s="5">
         <v>46125</v>
@@ -3969,7 +3954,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B37" s="8">
         <v>46108.75697796296</v>
@@ -3979,16 +3964,16 @@
         <v>46135.54608165509</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I37" s="8">
         <v>46125</v>
@@ -4006,13 +3991,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="Q37" s="8">
         <v>45979</v>
@@ -4032,7 +4017,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B38" s="5">
         <v>46108.7569835301</v>
@@ -4042,16 +4027,16 @@
         <v>46111.58202451389</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I38" s="5">
         <v>46134</v>
@@ -4069,13 +4054,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="O38" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="O38" s="6" t="s">
-        <v>136</v>
-      </c>
       <c r="P38" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="Q38" s="5">
         <v>45988</v>
@@ -4093,7 +4078,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B39" s="8">
         <v>46108.75698832176</v>
@@ -4103,16 +4088,16 @@
         <v>46183.16750024306</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I39" s="8">
         <v>46125</v>
@@ -4130,13 +4115,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q39" s="8">
         <v>46125</v>
@@ -4156,7 +4141,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B40" s="5">
         <v>46108.75699311343</v>
@@ -4166,16 +4151,16 @@
         <v>46209.595412939816</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I40" s="5">
         <v>46125</v>
@@ -4193,13 +4178,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>98</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="Q40" s="5">
         <v>45985</v>
@@ -4219,7 +4204,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B41" s="8">
         <v>46108.75699847222</v>
@@ -4229,16 +4214,16 @@
         <v>46182.1679962037</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I41" s="8">
         <v>46127</v>
@@ -4256,13 +4241,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="O41" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="O41" s="9" t="s">
-        <v>145</v>
-      </c>
       <c r="P41" s="9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="Q41" s="8">
         <v>45987</v>
@@ -4282,7 +4267,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B42" s="5">
         <v>46108.75700357639</v>
@@ -4292,16 +4277,16 @@
         <v>46211.84653167824</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I42" s="5">
         <v>46118</v>
@@ -4319,13 +4304,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q42" s="5">
         <v>46118</v>
@@ -4345,7 +4330,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B43" s="8">
         <v>46108.75700856482</v>
@@ -4357,16 +4342,16 @@
         <v>46182.69343975694</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I43" s="8">
         <v>46118</v>
@@ -4384,13 +4369,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>92</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="Q43" s="8">
         <v>45978</v>
@@ -4410,7 +4395,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B44" s="5">
         <v>46108.757016435186</v>
@@ -4420,16 +4405,16 @@
         <v>46182.69344646991</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I44" s="5">
         <v>46139</v>
@@ -4447,13 +4432,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="O44" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="O44" s="6" t="s">
-        <v>154</v>
-      </c>
       <c r="P44" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="Q44" s="5">
         <v>45999</v>
@@ -4473,7 +4458,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B45" s="8">
         <v>46108.7570218287</v>
@@ -4485,16 +4470,16 @@
         <v>46211.84652803241</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I45" s="8">
         <v>46139</v>
@@ -4512,13 +4497,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="O45" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="O45" s="9" t="s">
-        <v>154</v>
-      </c>
       <c r="P45" s="9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q45" s="8">
         <v>45999</v>
@@ -4538,7 +4523,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B46" s="5">
         <v>46108.75702719907</v>
@@ -4548,16 +4533,16 @@
         <v>46211.173315312495</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I46" s="5">
         <v>46195</v>
@@ -4575,13 +4560,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q46" s="5">
         <v>46195</v>
@@ -4601,7 +4586,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B47" s="8">
         <v>46108.75703201389</v>
@@ -4611,16 +4596,16 @@
         <v>46209.598061192126</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I47" s="8">
         <v>46195</v>
@@ -4638,13 +4623,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="Q47" s="8">
         <v>45985</v>
@@ -4664,7 +4649,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B48" s="5">
         <v>46108.75703761574</v>
@@ -4674,16 +4659,16 @@
         <v>46210.16869111111</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I48" s="5">
         <v>46202</v>
@@ -4701,13 +4686,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="Q48" s="5">
         <v>46007</v>
@@ -4727,7 +4712,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B49" s="8">
         <v>46108.75704306713</v>
@@ -4739,16 +4724,16 @@
         <v>46212.17359799768</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I49" s="8">
         <v>46125</v>
@@ -4766,13 +4751,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q49" s="8">
         <v>46125</v>
@@ -4784,7 +4769,7 @@
         <v>1</v>
       </c>
       <c r="T49" s="12" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="U49" s="11" t="s">
         <v>32</v>
@@ -4792,7 +4777,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B50" s="5">
         <v>46108.75705032407</v>
@@ -4804,16 +4789,16 @@
         <v>46154.86746811343</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I50" s="5">
         <v>46125</v>
@@ -4831,13 +4816,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4847,7 +4832,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B51" s="8">
         <v>46108.75705728009</v>
@@ -4859,16 +4844,16 @@
         <v>46154.8677641088</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I51" s="8">
         <v>46135</v>
@@ -4886,13 +4871,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4902,7 +4887,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B52" s="5">
         <v>46108.757061435186</v>
@@ -4912,16 +4897,16 @@
         <v>46169.85242414352</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I52" s="5">
         <v>46195</v>
@@ -4939,13 +4924,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q52" s="5">
         <v>46195</v>
@@ -4965,7 +4950,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B53" s="8">
         <v>46108.75710696759</v>
@@ -4975,16 +4960,16 @@
         <v>46199.168608900465</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I53" s="8">
         <v>46195</v>
@@ -5002,13 +4987,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5024,7 +5009,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B54" s="5">
         <v>46108.757112928244</v>
@@ -5034,16 +5019,16 @@
         <v>46169.85241099537</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I54" s="5">
         <v>46210</v>
@@ -5061,13 +5046,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5077,7 +5062,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B55" s="8">
         <v>46111.50860645833</v>
@@ -5089,16 +5074,16 @@
         <v>46182.69406362269</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I55" s="8">
         <v>46125</v>
@@ -5116,10 +5101,10 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5142,7 +5127,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B56" s="5">
         <v>46111.508755937495</v>
@@ -5154,16 +5139,16 @@
         <v>46182.69350877315</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I56" s="5">
         <v>46125</v>
@@ -5181,13 +5166,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>86</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5197,7 +5182,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B57" s="8">
         <v>46111.508846770834</v>
@@ -5209,16 +5194,16 @@
         <v>46182.69403748843</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I57" s="8">
         <v>46132</v>
@@ -5236,13 +5221,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="O57" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="O57" s="9" t="s">
-        <v>197</v>
-      </c>
       <c r="P57" s="9" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5252,7 +5237,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B58" s="5">
         <v>46108.75711900463</v>
@@ -5262,7 +5247,7 @@
         <v>46217.85709320602</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -5286,7 +5271,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5301,7 +5286,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B59" s="8">
         <v>46108.75712325232</v>
@@ -5313,16 +5298,16 @@
         <v>46211.84618561342</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="8">
@@ -5338,13 +5323,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="Q59" s="8">
         <v>46121</v>
@@ -5364,7 +5349,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B60" s="5">
         <v>46114.552579166666</v>
@@ -5376,16 +5361,16 @@
         <v>46211.84604957176</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I60" s="5">
         <v>46121</v>
@@ -5403,13 +5388,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5419,7 +5404,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B61" s="8">
         <v>46114.552773240735</v>
@@ -5431,16 +5416,16 @@
         <v>46211.846055462964</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I61" s="8">
         <v>46121</v>
@@ -5458,13 +5443,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>78</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5474,7 +5459,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B62" s="5">
         <v>46108.75712855324</v>
@@ -5486,16 +5471,16 @@
         <v>46217.857082789356</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="I62" s="5">
         <v>46183</v>
@@ -5513,13 +5498,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="Q62" s="5">
         <v>46183</v>
@@ -5539,7 +5524,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B63" s="8">
         <v>46114.55286452547</v>
@@ -5551,16 +5536,16 @@
         <v>46217.85704695602</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I63" s="8">
         <v>46183</v>
@@ -5578,13 +5563,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="Q63" s="9"/>
       <c r="R63" s="9"/>
@@ -5594,7 +5579,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B64" s="5">
         <v>46114.552966620366</v>
@@ -5606,16 +5591,16 @@
         <v>46217.85705476852</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I64" s="5">
         <v>46183</v>
@@ -5633,13 +5618,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5649,7 +5634,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B65" s="8">
         <v>46108.75713383102</v>
@@ -5659,16 +5644,16 @@
         <v>46217.857092986116</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I65" s="8">
         <v>46190</v>
@@ -5686,13 +5671,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="Q65" s="8">
         <v>46190</v>
@@ -5712,7 +5697,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B66" s="5">
         <v>46114.55312298611</v>
@@ -5722,16 +5707,16 @@
         <v>46217.85705168982</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="5">
@@ -5747,10 +5732,10 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5763,7 +5748,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B67" s="8">
         <v>46114.553244675924</v>
@@ -5773,16 +5758,16 @@
         <v>46217.85706487269</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="8">
@@ -5798,10 +5783,10 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>26</v>
@@ -5814,7 +5799,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B68" s="5">
         <v>46108.757138761575</v>
@@ -5824,16 +5809,16 @@
         <v>46114.631384050925</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I68" s="5">
         <v>46281</v>
@@ -5851,10 +5836,10 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5877,7 +5862,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B69" s="8">
         <v>46111.55280189815</v>
@@ -5887,16 +5872,16 @@
         <v>46114.62851033565</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -5912,13 +5897,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5928,7 +5913,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B70" s="5">
         <v>46111.55285245371</v>
@@ -5938,16 +5923,16 @@
         <v>46114.62851040509</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -5963,13 +5948,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5979,7 +5964,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B71" s="8">
         <v>46108.75714166666</v>
@@ -5989,7 +5974,7 @@
         <v>46118.545566597226</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -6013,7 +5998,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -6026,7 +6011,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B72" s="5">
         <v>46108.75714454861</v>
@@ -6036,16 +6021,16 @@
         <v>46118.55132545139</v>
       </c>
       <c r="E72" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>247</v>
-      </c>
-      <c r="F72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G72" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -6061,13 +6046,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="Q72" s="5">
         <v>46231</v>
@@ -6087,7 +6072,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B73" s="8">
         <v>46111.50359008102</v>
@@ -6097,7 +6082,7 @@
         <v>46114.61935158564</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -6121,7 +6106,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -6134,7 +6119,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B74" s="5">
         <v>46111.50404616898</v>
@@ -6144,16 +6129,16 @@
         <v>46213.19769318287</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I74" s="5">
         <v>46211</v>
@@ -6171,13 +6156,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="Q74" s="5">
         <v>46211</v>
@@ -6197,7 +6182,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B75" s="8">
         <v>46111.50406170139</v>
@@ -6207,16 +6192,16 @@
         <v>46217.17519608796</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="I75" s="8">
         <v>46213</v>
@@ -6234,13 +6219,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="O75" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="O75" s="9" t="s">
-        <v>256</v>
-      </c>
       <c r="P75" s="9" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="Q75" s="8">
         <v>46213</v>
@@ -6260,7 +6245,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B76" s="5">
         <v>46111.50543856481</v>
@@ -6270,7 +6255,7 @@
         <v>46114.62176513889</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -6294,7 +6279,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -6307,7 +6292,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B77" s="8">
         <v>46111.505495046295</v>
@@ -6317,16 +6302,16 @@
         <v>46218.20417449074</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I77" s="8">
         <v>46217</v>
@@ -6344,13 +6329,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="Q77" s="8">
         <v>46217</v>
@@ -6362,7 +6347,7 @@
         <v>0</v>
       </c>
       <c r="T77" s="12" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="U77" s="10" t="s">
         <v>54</v>
@@ -6370,7 +6355,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B78" s="5">
         <v>46111.50560314815</v>
@@ -6380,16 +6365,16 @@
         <v>46114.6339722338</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I78" s="5">
         <v>46226</v>
@@ -6407,13 +6392,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="Q78" s="5">
         <v>46226</v>
@@ -6433,7 +6418,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B79" s="8">
         <v>46111.52633317129</v>
@@ -6443,16 +6428,16 @@
         <v>46114.627016388884</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I79" s="8">
         <v>46226</v>
@@ -6470,13 +6455,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="O79" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="P79" s="9" t="s">
         <v>272</v>
-      </c>
-      <c r="O79" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="P79" s="9" t="s">
-        <v>275</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6486,7 +6471,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B80" s="5">
         <v>46111.526644375</v>
@@ -6496,16 +6481,16 @@
         <v>46114.627017175924</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I80" s="5">
         <v>46226</v>
@@ -6523,13 +6508,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="O80" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="P80" s="6" t="s">
         <v>274</v>
-      </c>
-      <c r="P80" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6539,7 +6524,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B81" s="8">
         <v>46111.50563458333</v>
@@ -6549,16 +6534,16 @@
         <v>46114.63406568287</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="I81" s="8">
         <v>46246</v>
@@ -6576,13 +6561,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="Q81" s="8">
         <v>46246</v>
@@ -6602,7 +6587,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B82" s="5">
         <v>46111.526916469906</v>
@@ -6612,16 +6597,16 @@
         <v>46114.62715587963</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="I82" s="5">
         <v>46246</v>
@@ -6639,13 +6624,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="O82" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="P82" s="6" t="s">
         <v>279</v>
-      </c>
-      <c r="O82" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>282</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6655,7 +6640,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B83" s="8">
         <v>46111.52699828704</v>
@@ -6665,16 +6650,16 @@
         <v>46114.62715672454</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="I83" s="8">
         <v>46246</v>
@@ -6692,13 +6677,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6708,7 +6693,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B84" s="5">
         <v>46108.75714884259</v>
@@ -6718,7 +6703,7 @@
         <v>46118.54556668982</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -6742,7 +6727,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6755,7 +6740,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B85" s="8">
         <v>46108.75715243055</v>
@@ -6765,16 +6750,16 @@
         <v>46185.184959907405</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I85" s="8">
         <v>46183</v>
@@ -6792,13 +6777,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="Q85" s="8">
         <v>46183</v>
@@ -6818,7 +6803,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B86" s="5">
         <v>46108.75715773148</v>
@@ -6834,10 +6819,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I86" s="5">
         <v>46239</v>
@@ -6855,13 +6840,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="Q86" s="5">
         <v>46239</v>
@@ -6881,7 +6866,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B87" s="8">
         <v>46108.75716349537</v>
@@ -6891,16 +6876,16 @@
         <v>46111.59762381944</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I87" s="8">
         <v>46246</v>
@@ -6918,13 +6903,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="Q87" s="8">
         <v>46246</v>
@@ -6944,7 +6929,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B88" s="5">
         <v>46108.75716875</v>
@@ -6954,16 +6939,16 @@
         <v>46111.59782981481</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I88" s="5">
         <v>46273</v>
@@ -6981,13 +6966,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="Q88" s="5">
         <v>46273</v>
@@ -7007,7 +6992,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B89" s="8">
         <v>46108.75717430556</v>
@@ -7017,16 +7002,16 @@
         <v>46216.198306990744</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I89" s="8">
         <v>46220</v>
@@ -7044,13 +7029,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="Q89" s="8">
         <v>46220</v>
@@ -7062,7 +7047,7 @@
         <v>0</v>
       </c>
       <c r="T89" s="12" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="U89" s="12" t="s">
         <v>90</v>
@@ -7070,7 +7055,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B90" s="5">
         <v>46108.75717877314</v>
@@ -7080,16 +7065,16 @@
         <v>46118.54556859954</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
@@ -7105,13 +7090,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="Q90" s="5">
         <v>46231</v>
@@ -7131,7 +7116,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B91" s="8">
         <v>46108.822037094906</v>
@@ -7141,16 +7126,16 @@
         <v>46185.18495945602</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I91" s="8">
         <v>46181</v>
@@ -7168,13 +7153,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="Q91" s="8">
         <v>46183</v>
@@ -7194,7 +7179,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B92" s="5">
         <v>46108.757183124995</v>
@@ -7204,7 +7189,7 @@
         <v>46114.62594751157</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>25</v>
@@ -7228,7 +7213,7 @@
         <v>26</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>26</v>
@@ -7241,7 +7226,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B93" s="8">
         <v>46108.757186296294</v>
@@ -7251,17 +7236,15 @@
         <v>46114.63518780093</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H93" s="9"/>
       <c r="I93" s="8">
         <v>46248</v>
       </c>
@@ -7278,13 +7261,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="Q93" s="8">
         <v>46248</v>
@@ -7304,7 +7287,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B94" s="5">
         <v>46111.52720202546</v>
@@ -7314,17 +7297,15 @@
         <v>46118.545567442125</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H94" s="6"/>
       <c r="I94" s="5">
         <v>46248</v>
       </c>
@@ -7341,13 +7322,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="O94" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="P94" s="6" t="s">
         <v>311</v>
-      </c>
-      <c r="O94" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="P94" s="6" t="s">
-        <v>314</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7357,7 +7338,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B95" s="8">
         <v>46111.52733795139</v>
@@ -7367,17 +7348,15 @@
         <v>46118.54556813657</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H95" s="9"/>
       <c r="I95" s="8">
         <v>46248</v>
       </c>
@@ -7394,13 +7373,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7410,7 +7389,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B96" s="5">
         <v>46108.75720997685</v>
@@ -7420,17 +7399,15 @@
         <v>46114.636429907405</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H96" s="6"/>
       <c r="I96" s="5">
         <v>46268</v>
       </c>
@@ -7447,13 +7424,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="Q96" s="5">
         <v>46268</v>
@@ -7473,7 +7450,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B97" s="8">
         <v>46111.52790079861</v>
@@ -7483,17 +7460,15 @@
         <v>46114.627765578705</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H97" s="9"/>
       <c r="I97" s="8">
         <v>46268</v>
       </c>
@@ -7510,13 +7485,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="O97" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="P97" s="9" t="s">
         <v>319</v>
-      </c>
-      <c r="O97" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="P97" s="9" t="s">
-        <v>322</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7526,7 +7501,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B98" s="5">
         <v>46111.52796104166</v>
@@ -7536,17 +7511,15 @@
         <v>46114.62776635417</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H98" s="6"/>
       <c r="I98" s="5">
         <v>46268</v>
       </c>
@@ -7563,13 +7536,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7579,7 +7552,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B99" s="8">
         <v>46108.75719767361</v>
@@ -7589,17 +7562,15 @@
         <v>46114.63653665509</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="H99" s="9" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H99" s="9"/>
       <c r="I99" s="8">
         <v>46272</v>
       </c>
@@ -7616,13 +7587,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="Q99" s="8">
         <v>46272</v>
@@ -7642,7 +7613,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B100" s="5">
         <v>46111.52756633102</v>
@@ -7652,17 +7623,15 @@
         <v>46118.54557231482</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H100" s="6"/>
       <c r="I100" s="5">
         <v>46272</v>
       </c>
@@ -7679,13 +7648,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="O100" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="P100" s="6" t="s">
         <v>327</v>
-      </c>
-      <c r="O100" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="P100" s="6" t="s">
-        <v>330</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7695,7 +7664,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B101" s="8">
         <v>46111.527622395835</v>
@@ -7705,17 +7674,15 @@
         <v>46118.54556883102</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="H101" s="9" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H101" s="9"/>
       <c r="I101" s="8">
         <v>46272</v>
       </c>
@@ -7732,13 +7699,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7748,7 +7715,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B102" s="5">
         <v>46108.75720341435</v>
@@ -7758,17 +7725,15 @@
         <v>46114.63667146991</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H102" s="6"/>
       <c r="I102" s="5">
         <v>46274</v>
       </c>
@@ -7785,13 +7750,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="Q102" s="5">
         <v>46274</v>
@@ -7811,7 +7776,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B103" s="8">
         <v>46111.52775804398</v>
@@ -7821,17 +7786,15 @@
         <v>46118.545570937495</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="H103" s="9" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H103" s="9"/>
       <c r="I103" s="8">
         <v>46274</v>
       </c>
@@ -7848,13 +7811,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -7864,7 +7827,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B104" s="5">
         <v>46111.52780829861</v>
@@ -7874,17 +7837,15 @@
         <v>46118.545571608796</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H104" s="6"/>
       <c r="I104" s="5">
         <v>46274</v>
       </c>
@@ -7901,13 +7862,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7917,7 +7878,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B105" s="8">
         <v>46108.757191412034</v>
@@ -7927,17 +7888,15 @@
         <v>46114.636801493056</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="H105" s="9" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H105" s="9"/>
       <c r="I105" s="8">
         <v>46276</v>
       </c>
@@ -7954,13 +7913,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="Q105" s="8">
         <v>46276</v>
@@ -7980,7 +7939,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B106" s="5">
         <v>46111.527446493055</v>
@@ -7990,17 +7949,15 @@
         <v>46118.545569548616</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H106" s="6"/>
       <c r="I106" s="5">
         <v>46276</v>
       </c>
@@ -8017,13 +7974,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="O106" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="P106" s="6" t="s">
         <v>341</v>
-      </c>
-      <c r="O106" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="P106" s="6" t="s">
-        <v>344</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8033,7 +7990,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B107" s="8">
         <v>46111.52746010417</v>
@@ -8043,17 +8000,15 @@
         <v>46118.545570243055</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="H107" s="9" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H107" s="9"/>
       <c r="I107" s="8">
         <v>46276</v>
       </c>
@@ -8070,13 +8025,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -8086,7 +8041,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B108" s="5">
         <v>46108.757217025464</v>
@@ -8096,17 +8051,15 @@
         <v>46114.63686459491</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H108" s="6"/>
       <c r="I108" s="5">
         <v>46280</v>
       </c>
@@ -8123,13 +8076,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="Q108" s="5">
         <v>46280</v>
@@ -8149,7 +8102,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B109" s="8">
         <v>46111.528031932874</v>
@@ -8159,17 +8112,15 @@
         <v>46114.62850982639</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="H109" s="9" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H109" s="9"/>
       <c r="I109" s="9"/>
       <c r="J109" s="8">
         <v>46280</v>
@@ -8184,13 +8135,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8200,7 +8151,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B110" s="5">
         <v>46111.52811128472</v>
@@ -8210,17 +8161,15 @@
         <v>46114.62851064815</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H110" s="6"/>
       <c r="I110" s="6"/>
       <c r="J110" s="5">
         <v>46280</v>
@@ -8235,13 +8184,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8251,7 +8200,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B111" s="8">
         <v>46108.75727585648</v>
@@ -8261,17 +8210,15 @@
         <v>46114.63695302083</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="H111" s="9" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H111" s="9"/>
       <c r="I111" s="9"/>
       <c r="J111" s="8">
         <v>46286</v>
@@ -8286,13 +8233,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="Q111" s="8">
         <v>46286</v>
@@ -8312,7 +8259,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B112" s="5">
         <v>46111.5281812037</v>
@@ -8322,17 +8269,15 @@
         <v>46114.62864336805</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H112" s="6"/>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
         <v>46286</v>
@@ -8347,13 +8292,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="O112" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="P112" s="6" t="s">
         <v>355</v>
-      </c>
-      <c r="O112" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="P112" s="6" t="s">
-        <v>358</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8363,7 +8308,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B113" s="8">
         <v>46111.528266423615</v>
@@ -8373,17 +8318,15 @@
         <v>46114.62864409722</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="H113" s="9" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H113" s="9"/>
       <c r="I113" s="9"/>
       <c r="J113" s="8">
         <v>46286</v>
@@ -8398,13 +8341,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8414,7 +8357,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B114" s="5">
         <v>46108.757283217594</v>
@@ -8424,7 +8367,7 @@
         <v>46114.62962787037</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>25</v>
@@ -8448,7 +8391,7 @@
         <v>26</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>26</v>
@@ -8461,7 +8404,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B115" s="8">
         <v>46108.757287430555</v>
@@ -8471,16 +8414,16 @@
         <v>46114.63723893519</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="I115" s="8">
         <v>46287</v>
@@ -8498,13 +8441,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="Q115" s="8">
         <v>46287</v>
@@ -8524,7 +8467,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B116" s="5">
         <v>46111.52846596065</v>
@@ -8534,16 +8477,16 @@
         <v>46114.62888387732</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8559,13 +8502,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8575,7 +8518,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B117" s="8">
         <v>46111.528518067134</v>
@@ -8585,16 +8528,16 @@
         <v>46114.62888469908</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="8">
@@ -8610,13 +8553,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8626,7 +8569,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B118" s="5">
         <v>46111.531216006944</v>
@@ -8642,10 +8585,10 @@
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="I118" s="6"/>
       <c r="J118" s="5">
@@ -8661,13 +8604,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8677,7 +8620,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B119" s="8">
         <v>46111.53129275463</v>
@@ -8693,10 +8636,10 @@
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="I119" s="9"/>
       <c r="J119" s="8">
@@ -8712,13 +8655,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="O119" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8728,7 +8671,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B120" s="5">
         <v>46111.53134821759</v>
@@ -8738,16 +8681,16 @@
         <v>46114.628886921295</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
@@ -8763,13 +8706,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8779,7 +8722,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B121" s="8">
         <v>46111.53139942129</v>
@@ -8795,10 +8738,10 @@
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="I121" s="9"/>
       <c r="J121" s="8">
@@ -8814,13 +8757,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="O121" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8830,7 +8773,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B122" s="5">
         <v>46111.53343819444</v>
@@ -8840,16 +8783,16 @@
         <v>46114.628888437495</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="I122" s="6"/>
       <c r="J122" s="5">
@@ -8865,13 +8808,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8881,7 +8824,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B123" s="8">
         <v>46108.75729289352</v>
@@ -8891,17 +8834,15 @@
         <v>46114.637374618054</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="H123" s="9" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H123" s="9"/>
       <c r="I123" s="8">
         <v>46288</v>
       </c>
@@ -8918,13 +8859,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="Q123" s="8">
         <v>46288</v>
@@ -8944,7 +8885,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B124" s="5">
         <v>46111.52857409722</v>
@@ -8954,17 +8895,15 @@
         <v>46114.629102280094</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H124" s="6"/>
       <c r="I124" s="5">
         <v>46288</v>
       </c>
@@ -8981,13 +8920,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="O124" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="P124" s="6" t="s">
         <v>385</v>
-      </c>
-      <c r="O124" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="P124" s="6" t="s">
-        <v>388</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8997,7 +8936,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B125" s="8">
         <v>46111.528674016205</v>
@@ -9007,17 +8946,15 @@
         <v>46114.62910302084</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="H125" s="9" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H125" s="9"/>
       <c r="I125" s="8">
         <v>46288</v>
       </c>
@@ -9034,13 +8971,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -9050,7 +8987,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B126" s="5">
         <v>46111.531552291664</v>
@@ -9066,11 +9003,9 @@
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H126" s="6"/>
       <c r="I126" s="5">
         <v>46288</v>
       </c>
@@ -9087,13 +9022,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9103,7 +9038,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B127" s="8">
         <v>46111.531603344905</v>
@@ -9119,11 +9054,9 @@
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="H127" s="9" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H127" s="9"/>
       <c r="I127" s="8">
         <v>46288</v>
       </c>
@@ -9140,13 +9073,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="O127" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9156,7 +9089,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B128" s="5">
         <v>46111.531648379634</v>
@@ -9166,17 +9099,15 @@
         <v>46114.62910528935</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H128" s="6"/>
       <c r="I128" s="5">
         <v>46288</v>
       </c>
@@ -9193,13 +9124,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9209,7 +9140,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B129" s="8">
         <v>46111.531705925925</v>
@@ -9225,11 +9156,9 @@
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="H129" s="9" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H129" s="9"/>
       <c r="I129" s="8">
         <v>46288</v>
       </c>
@@ -9246,13 +9175,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="O129" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9262,7 +9191,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B130" s="5">
         <v>46111.533570127314</v>
@@ -9272,17 +9201,15 @@
         <v>46114.62910684028</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H130" s="6" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H130" s="6"/>
       <c r="I130" s="5">
         <v>46288</v>
       </c>
@@ -9299,13 +9226,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9315,7 +9242,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B131" s="8">
         <v>46108.75729930555</v>
@@ -9325,16 +9252,16 @@
         <v>46114.63748693287</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I131" s="8">
         <v>46293</v>
@@ -9352,13 +9279,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="Q131" s="8">
         <v>46293</v>
@@ -9378,7 +9305,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B132" s="5">
         <v>46111.528799872685</v>
@@ -9388,16 +9315,16 @@
         <v>46114.62931347222</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9413,13 +9340,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="O132" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="P132" s="6" t="s">
         <v>402</v>
-      </c>
-      <c r="O132" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="P132" s="6" t="s">
-        <v>405</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9429,7 +9356,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B133" s="8">
         <v>46111.52885179398</v>
@@ -9439,16 +9366,16 @@
         <v>46114.62931429398</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I133" s="9"/>
       <c r="J133" s="8">
@@ -9464,13 +9391,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9480,7 +9407,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B134" s="5">
         <v>46111.53215439815</v>
@@ -9496,10 +9423,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9515,13 +9442,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9531,7 +9458,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B135" s="8">
         <v>46111.53220642361</v>
@@ -9547,10 +9474,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I135" s="9"/>
       <c r="J135" s="8">
@@ -9566,13 +9493,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="O135" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9582,7 +9509,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B136" s="5">
         <v>46111.532258287036</v>
@@ -9592,16 +9519,16 @@
         <v>46114.629316527775</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9617,13 +9544,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9633,7 +9560,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B137" s="8">
         <v>46111.53231001158</v>
@@ -9649,10 +9576,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I137" s="9"/>
       <c r="J137" s="8">
@@ -9668,13 +9595,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="O137" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -9684,7 +9611,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B138" s="5">
         <v>46111.53368237268</v>
@@ -9694,16 +9621,16 @@
         <v>46114.62931805555</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
@@ -9719,13 +9646,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9735,7 +9662,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B139" s="8">
         <v>46108.757304583334</v>
@@ -9745,16 +9672,16 @@
         <v>46114.63755023148</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I139" s="8">
         <v>46294</v>
@@ -9772,13 +9699,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="Q139" s="8">
         <v>46294</v>
@@ -9798,7 +9725,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B140" s="5">
         <v>46111.528945011574</v>
@@ -9808,16 +9735,16 @@
         <v>46114.830281076385</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I140" s="5">
         <v>46294</v>
@@ -9835,13 +9762,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="O140" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="P140" s="6" t="s">
         <v>420</v>
-      </c>
-      <c r="O140" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="P140" s="6" t="s">
-        <v>423</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9851,7 +9778,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B141" s="8">
         <v>46111.52901092592</v>
@@ -9861,16 +9788,16 @@
         <v>46114.830302789356</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I141" s="8">
         <v>46294</v>
@@ -9888,13 +9815,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -9904,7 +9831,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B142" s="5">
         <v>46111.53247278935</v>
@@ -9920,10 +9847,10 @@
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I142" s="5">
         <v>46294</v>
@@ -9941,13 +9868,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9957,7 +9884,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B143" s="8">
         <v>46111.53253350694</v>
@@ -9973,10 +9900,10 @@
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I143" s="8">
         <v>46294</v>
@@ -9994,13 +9921,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="O143" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -10010,7 +9937,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B144" s="5">
         <v>46111.532638414355</v>
@@ -10026,10 +9953,10 @@
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I144" s="5">
         <v>46294</v>
@@ -10047,13 +9974,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10063,7 +9990,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B145" s="8">
         <v>46111.53258112269</v>
@@ -10073,16 +10000,16 @@
         <v>46114.83037114583</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I145" s="8">
         <v>46294</v>
@@ -10100,13 +10027,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -10116,7 +10043,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B146" s="5">
         <v>46111.53385627315</v>
@@ -10126,16 +10053,16 @@
         <v>46114.83039427083</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I146" s="5">
         <v>46294</v>
@@ -10153,13 +10080,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="O146" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="P146" s="6" t="s">
         <v>417</v>
-      </c>
-      <c r="P146" s="6" t="s">
-        <v>420</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10169,7 +10096,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B147" s="8">
         <v>46108.757310497684</v>
@@ -10179,7 +10106,7 @@
         <v>46114.62962797454</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>25</v>
@@ -10203,7 +10130,7 @@
         <v>26</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="P147" s="9" t="s">
         <v>26</v>
@@ -10216,7 +10143,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B148" s="5">
         <v>46108.75731366898</v>
@@ -10226,16 +10153,16 @@
         <v>46114.63764361111</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I148" s="5">
         <v>46295</v>
@@ -10253,13 +10180,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="Q148" s="5">
         <v>46295</v>
@@ -10279,7 +10206,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B149" s="8">
         <v>46108.75732001157</v>
@@ -10289,16 +10216,16 @@
         <v>46119.74841528935</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I149" s="8">
         <v>46295</v>
@@ -10316,13 +10243,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="Q149" s="8">
         <v>46295</v>
@@ -10342,7 +10269,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B150" s="5">
         <v>46108.7573290625</v>
@@ -10352,7 +10279,7 @@
         <v>46114.62962836806</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>25</v>
@@ -10376,7 +10303,7 @@
         <v>26</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="P150" s="6" t="s">
         <v>26</v>
@@ -10389,7 +10316,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B151" s="8">
         <v>46108.75733305556</v>
@@ -10399,7 +10326,7 @@
         <v>46119.748459016206</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
@@ -10426,13 +10353,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="Q151" s="8">
         <v>46295</v>
@@ -10452,7 +10379,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B152" s="5">
         <v>46108.757338703705</v>
@@ -10462,7 +10389,7 @@
         <v>46119.748502546296</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10489,13 +10416,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="O152" s="6" t="s">
         <v>441</v>
       </c>
-      <c r="O152" s="6" t="s">
-        <v>444</v>
-      </c>
       <c r="P152" s="6" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="Q152" s="5">
         <v>46304</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -529,292 +529,292 @@
     <t>Generacion OC Sensor,Fabricacion Sensores</t>
   </si>
   <si>
+    <t>1213833763284977</t>
+  </si>
+  <si>
+    <t>Generacion OC Sensor</t>
+  </si>
+  <si>
+    <t>Sensores,Fabricacion Sensores</t>
+  </si>
+  <si>
+    <t>1213833777489751</t>
+  </si>
+  <si>
+    <t>Fabricacion Sensores</t>
+  </si>
+  <si>
+    <t>Recepción Sensores,Sensores</t>
+  </si>
+  <si>
+    <t>1213833777489767</t>
+  </si>
+  <si>
+    <t>Fabricacion Externa ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Generacion OC Fabricacion Externa ot 4287 - 4288,Fabricacion estructura proveedor externo ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>1213833564667630</t>
+  </si>
+  <si>
+    <t>Fabricacion Externa ot 4287 - 4288,Fabricacion estructura proveedor externo ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>1213833763295351</t>
+  </si>
+  <si>
+    <t>Fabricacion estructura proveedor externo ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>Check Planos,Fabricacion a codigo y compras locales ot 4287 - 4288, Generacion OC Fabricacion Externa ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>Control de calidad Fabricación externa,Fabricacion Externa ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>1213869987281796</t>
+  </si>
+  <si>
+    <t>Atenuador ot 4289</t>
+  </si>
+  <si>
+    <t>Propuesta Atenuadores ,Generacion oc Atenuador  ot 4289,Fabricacion atenuador ot 4289</t>
+  </si>
+  <si>
+    <t>1213869987281797</t>
+  </si>
+  <si>
+    <t>Generacion oc Atenuador  ot 4289</t>
+  </si>
+  <si>
+    <t>Fabricacion atenuador ot 4289,Atenuador ot 4289</t>
+  </si>
+  <si>
+    <t>1213869987281798</t>
+  </si>
+  <si>
+    <t>Fabricacion atenuador ot 4289</t>
+  </si>
+  <si>
+    <t>Atenuadores,Atenuador ot 4289</t>
+  </si>
+  <si>
+    <t>1213833564706217</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1213833564706230</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:,Check Planos</t>
+  </si>
+  <si>
+    <t>1213899500210867</t>
+  </si>
+  <si>
+    <t>OT 4287 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Planos preliminar,OT 4287 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213899500210869</t>
+  </si>
+  <si>
+    <t>OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>Planos preliminar,OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>1213833763300853</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>Check Planos,Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t>1213899500210870</t>
+  </si>
+  <si>
+    <t>OT 4287 ZVR 1-14-42/4,Planos motor proveedor ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>Planos definitivos,OT 4287 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213899500210871</t>
+  </si>
+  <si>
+    <t>OT 4288 ZVR1-14-30/4,Planos motor proveedor ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>Planos definitivos,OT4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>1213833763300879</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Planos preliminar</t>
+  </si>
+  <si>
+    <t>OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,propuesta compras a codigo // aprovisionamiento ot 4287 - 4288,Propuesta Fabricacion Externa ot 4287 - 4288,Fabricacion estructura proveedor externo ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>1213899500210872</t>
+  </si>
+  <si>
+    <t>1213899500210873</t>
+  </si>
+  <si>
+    <t>OT4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>1213833622855505</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4287 ZVR 1-14-42/4,OT  4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>1213869987281952</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT,OT 4287 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213869987281953</t>
+  </si>
+  <si>
+    <t>OT  4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT,OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>1213833622855516</t>
+  </si>
+  <si>
+    <t>Control de calidad</t>
+  </si>
+  <si>
+    <t>Control de calidad Fabricación externa</t>
+  </si>
+  <si>
+    <t>1213833622855625</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>Control de calidad,Recepcion Fabricacion externa</t>
+  </si>
+  <si>
+    <t>1213840446207872</t>
+  </si>
+  <si>
+    <t>Bodega</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
+  </si>
+  <si>
+    <t>1213840446207876</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamient,Bodega</t>
+  </si>
+  <si>
+    <t>1213840446207878</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
+  </si>
+  <si>
+    <t>Bodega,Preparacion materiales</t>
+  </si>
+  <si>
+    <t>1213869987281780</t>
+  </si>
+  <si>
+    <t>Caldereria</t>
+  </si>
+  <si>
+    <t>Preparacion materiales,Armado,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1213869987281782</t>
+  </si>
+  <si>
+    <t>Preparacion materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>Caldereria,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213833763284977</t>
-  </si>
-  <si>
-    <t>Generacion OC Sensor</t>
-  </si>
-  <si>
-    <t>Sensores,Fabricacion Sensores</t>
-  </si>
-  <si>
-    <t>1213833777489751</t>
-  </si>
-  <si>
-    <t>Fabricacion Sensores</t>
-  </si>
-  <si>
-    <t>Recepción Sensores,Sensores</t>
-  </si>
-  <si>
-    <t>1213833777489767</t>
-  </si>
-  <si>
-    <t>Fabricacion Externa ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Generacion OC Fabricacion Externa ot 4287 - 4288,Fabricacion estructura proveedor externo ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>1213833564667630</t>
-  </si>
-  <si>
-    <t>Fabricacion Externa ot 4287 - 4288,Fabricacion estructura proveedor externo ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>1213833763295351</t>
-  </si>
-  <si>
-    <t>Fabricacion estructura proveedor externo ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>Check Planos,Fabricacion a codigo y compras locales ot 4287 - 4288, Generacion OC Fabricacion Externa ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>Control de calidad Fabricación externa,Fabricacion Externa ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>1213869987281796</t>
-  </si>
-  <si>
-    <t>Atenuador ot 4289</t>
-  </si>
-  <si>
-    <t>Propuesta Atenuadores ,Generacion oc Atenuador  ot 4289,Fabricacion atenuador ot 4289</t>
-  </si>
-  <si>
-    <t>1213869987281797</t>
-  </si>
-  <si>
-    <t>Generacion oc Atenuador  ot 4289</t>
-  </si>
-  <si>
-    <t>Fabricacion atenuador ot 4289,Atenuador ot 4289</t>
-  </si>
-  <si>
-    <t>1213869987281798</t>
-  </si>
-  <si>
-    <t>Fabricacion atenuador ot 4289</t>
-  </si>
-  <si>
-    <t>Atenuadores,Atenuador ot 4289</t>
-  </si>
-  <si>
-    <t>1213833564706217</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1213833564706230</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:,Check Planos</t>
-  </si>
-  <si>
-    <t>1213899500210867</t>
-  </si>
-  <si>
-    <t>OT 4287 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Planos preliminar,OT 4287 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213899500210869</t>
-  </si>
-  <si>
-    <t>OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>Planos preliminar,OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>1213833763300853</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>Check Planos,Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t>1213899500210870</t>
-  </si>
-  <si>
-    <t>OT 4287 ZVR 1-14-42/4,Planos motor proveedor ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>Planos definitivos,OT 4287 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213899500210871</t>
-  </si>
-  <si>
-    <t>OT 4288 ZVR1-14-30/4,Planos motor proveedor ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>Planos definitivos,OT4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>1213833763300879</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Planos preliminar</t>
-  </si>
-  <si>
-    <t>OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,propuesta compras a codigo // aprovisionamiento ot 4287 - 4288,Propuesta Fabricacion Externa ot 4287 - 4288,Fabricacion estructura proveedor externo ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>1213899500210872</t>
-  </si>
-  <si>
-    <t>1213899500210873</t>
-  </si>
-  <si>
-    <t>OT4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>1213833622855505</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4287 ZVR 1-14-42/4,OT  4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>1213869987281952</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT,OT 4287 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213869987281953</t>
-  </si>
-  <si>
-    <t>OT  4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT,OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>1213833622855516</t>
-  </si>
-  <si>
-    <t>Control de calidad</t>
-  </si>
-  <si>
-    <t>Control de calidad Fabricación externa</t>
-  </si>
-  <si>
-    <t>1213833622855625</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>Control de calidad,Recepcion Fabricacion externa</t>
-  </si>
-  <si>
-    <t>1213840446207872</t>
-  </si>
-  <si>
-    <t>Bodega</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
-  </si>
-  <si>
-    <t>1213840446207876</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamient,Bodega</t>
-  </si>
-  <si>
-    <t>1213840446207878</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
-  </si>
-  <si>
-    <t>Bodega,Preparacion materiales</t>
-  </si>
-  <si>
-    <t>1213869987281780</t>
-  </si>
-  <si>
-    <t>Caldereria</t>
-  </si>
-  <si>
-    <t>Preparacion materiales,Armado,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1213869987281782</t>
-  </si>
-  <si>
-    <t>Preparacion materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>Caldereria,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4</t>
   </si>
   <si>
     <t>1213869987281784</t>
@@ -4721,7 +4721,7 @@
         <v>46154.86784248843</v>
       </c>
       <c r="D49" s="8">
-        <v>46212.17359799768</v>
+        <v>46220.16760561343</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>170</v>
@@ -4768,8 +4768,8 @@
       <c r="S49" s="9">
         <v>1</v>
       </c>
-      <c r="T49" s="12" t="s">
-        <v>172</v>
+      <c r="T49" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U49" s="11" t="s">
         <v>32</v>
@@ -4777,7 +4777,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B50" s="5">
         <v>46108.75705032407</v>
@@ -4789,7 +4789,7 @@
         <v>46154.86746811343</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
@@ -4822,7 +4822,7 @@
         <v>108</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4832,7 +4832,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B51" s="8">
         <v>46108.75705728009</v>
@@ -4844,7 +4844,7 @@
         <v>46154.8677641088</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
@@ -4874,10 +4874,10 @@
         <v>170</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B52" s="5">
         <v>46108.757061435186</v>
@@ -4897,16 +4897,16 @@
         <v>46169.85242414352</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
+      <c r="H52" s="6" t="s">
         <v>181</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>182</v>
       </c>
       <c r="I52" s="5">
         <v>46195</v>
@@ -4927,7 +4927,7 @@
         <v>116</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>116</v>
@@ -4950,7 +4950,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B53" s="8">
         <v>46108.75710696759</v>
@@ -4966,10 +4966,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="H53" s="9" t="s">
         <v>181</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>182</v>
       </c>
       <c r="I53" s="8">
         <v>46195</v>
@@ -4987,13 +4987,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>111</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5009,7 +5009,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B54" s="5">
         <v>46108.757112928244</v>
@@ -5019,16 +5019,16 @@
         <v>46169.85241099537</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>181</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>182</v>
       </c>
       <c r="I54" s="5">
         <v>46210</v>
@@ -5046,13 +5046,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O54" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="P54" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="P54" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5062,7 +5062,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B55" s="8">
         <v>46111.50860645833</v>
@@ -5074,7 +5074,7 @@
         <v>46182.69406362269</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
@@ -5104,7 +5104,7 @@
         <v>116</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5127,7 +5127,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B56" s="5">
         <v>46111.508755937495</v>
@@ -5139,7 +5139,7 @@
         <v>46182.69350877315</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -5166,13 +5166,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>86</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5182,7 +5182,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B57" s="8">
         <v>46111.508846770834</v>
@@ -5194,7 +5194,7 @@
         <v>46182.69403748843</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
@@ -5221,13 +5221,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5237,7 +5237,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B58" s="5">
         <v>46108.75711900463</v>
@@ -5247,7 +5247,7 @@
         <v>46217.85709320602</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -5271,7 +5271,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5286,7 +5286,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B59" s="8">
         <v>46108.75712325232</v>
@@ -5298,16 +5298,16 @@
         <v>46211.84618561342</v>
       </c>
       <c r="E59" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="F59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="9" t="s">
+      <c r="H59" s="9" t="s">
         <v>204</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>205</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="8">
@@ -5323,13 +5323,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O59" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="P59" s="9" t="s">
         <v>206</v>
-      </c>
-      <c r="P59" s="9" t="s">
-        <v>207</v>
       </c>
       <c r="Q59" s="8">
         <v>46121</v>
@@ -5349,7 +5349,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B60" s="5">
         <v>46114.552579166666</v>
@@ -5361,16 +5361,16 @@
         <v>46211.84604957176</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
+      <c r="H60" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I60" s="5">
         <v>46121</v>
@@ -5388,13 +5388,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5404,7 +5404,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B61" s="8">
         <v>46114.552773240735</v>
@@ -5416,16 +5416,16 @@
         <v>46211.846055462964</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>210</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>211</v>
       </c>
       <c r="I61" s="8">
         <v>46121</v>
@@ -5443,13 +5443,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>78</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5459,7 +5459,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B62" s="5">
         <v>46108.75712855324</v>
@@ -5471,16 +5471,16 @@
         <v>46217.857082789356</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="I62" s="5">
         <v>46183</v>
@@ -5498,13 +5498,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O62" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="P62" s="6" t="s">
         <v>218</v>
-      </c>
-      <c r="P62" s="6" t="s">
-        <v>219</v>
       </c>
       <c r="Q62" s="5">
         <v>46183</v>
@@ -5524,7 +5524,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B63" s="8">
         <v>46114.55286452547</v>
@@ -5536,16 +5536,16 @@
         <v>46217.85704695602</v>
       </c>
       <c r="E63" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="F63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="9" t="s">
+      <c r="H63" s="9" t="s">
         <v>210</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>211</v>
       </c>
       <c r="I63" s="8">
         <v>46183</v>
@@ -5563,13 +5563,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O63" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="P63" s="9" t="s">
         <v>221</v>
-      </c>
-      <c r="P63" s="9" t="s">
-        <v>222</v>
       </c>
       <c r="Q63" s="9"/>
       <c r="R63" s="9"/>
@@ -5579,7 +5579,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B64" s="5">
         <v>46114.552966620366</v>
@@ -5591,16 +5591,16 @@
         <v>46217.85705476852</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I64" s="5">
         <v>46183</v>
@@ -5618,13 +5618,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O64" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>225</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5634,7 +5634,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B65" s="8">
         <v>46108.75713383102</v>
@@ -5650,10 +5650,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>210</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>211</v>
       </c>
       <c r="I65" s="8">
         <v>46190</v>
@@ -5671,13 +5671,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O65" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="P65" s="9" t="s">
         <v>227</v>
-      </c>
-      <c r="P65" s="9" t="s">
-        <v>228</v>
       </c>
       <c r="Q65" s="8">
         <v>46190</v>
@@ -5697,7 +5697,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B66" s="5">
         <v>46114.55312298611</v>
@@ -5707,16 +5707,16 @@
         <v>46217.85705168982</v>
       </c>
       <c r="E66" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G66" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="F66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G66" s="6" t="s">
+      <c r="H66" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="5">
@@ -5735,7 +5735,7 @@
         <v>105</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5748,7 +5748,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B67" s="8">
         <v>46114.553244675924</v>
@@ -5758,16 +5758,16 @@
         <v>46217.85706487269</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>210</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>211</v>
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="8">
@@ -5786,7 +5786,7 @@
         <v>105</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>26</v>
@@ -5799,7 +5799,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B68" s="5">
         <v>46108.757138761575</v>
@@ -5809,16 +5809,16 @@
         <v>46114.631384050925</v>
       </c>
       <c r="E68" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G68" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="F68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G68" s="6" t="s">
+      <c r="H68" s="6" t="s">
         <v>234</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>235</v>
       </c>
       <c r="I68" s="5">
         <v>46281</v>
@@ -5836,10 +5836,10 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5862,7 +5862,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B69" s="8">
         <v>46111.55280189815</v>
@@ -5872,16 +5872,16 @@
         <v>46114.62851033565</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>234</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>235</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -5897,13 +5897,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5913,7 +5913,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B70" s="5">
         <v>46111.55285245371</v>
@@ -5923,16 +5923,16 @@
         <v>46114.62851040509</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>234</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>235</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -5948,13 +5948,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5964,7 +5964,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B71" s="8">
         <v>46108.75714166666</v>
@@ -5974,7 +5974,7 @@
         <v>46118.545566597226</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -5998,7 +5998,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -6011,7 +6011,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B72" s="5">
         <v>46108.75714454861</v>
@@ -6021,16 +6021,16 @@
         <v>46118.55132545139</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>246</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>247</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -6046,13 +6046,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q72" s="5">
         <v>46231</v>
@@ -6072,7 +6072,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B73" s="8">
         <v>46111.50359008102</v>
@@ -6082,7 +6082,7 @@
         <v>46114.61935158564</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -6106,7 +6106,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -6119,7 +6119,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B74" s="5">
         <v>46111.50404616898</v>
@@ -6129,16 +6129,16 @@
         <v>46213.19769318287</v>
       </c>
       <c r="E74" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G74" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="F74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G74" s="6" t="s">
+      <c r="H74" s="6" t="s">
         <v>254</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>255</v>
       </c>
       <c r="I74" s="5">
         <v>46211</v>
@@ -6156,13 +6156,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>167</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q74" s="5">
         <v>46211</v>
@@ -6182,7 +6182,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B75" s="8">
         <v>46111.50406170139</v>
@@ -6192,16 +6192,16 @@
         <v>46217.17519608796</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="H75" s="9" t="s">
         <v>246</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>247</v>
       </c>
       <c r="I75" s="8">
         <v>46213</v>
@@ -6219,13 +6219,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q75" s="8">
         <v>46213</v>
@@ -6245,7 +6245,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B76" s="5">
         <v>46111.50543856481</v>
@@ -6255,7 +6255,7 @@
         <v>46114.62176513889</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -6279,7 +6279,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -6292,7 +6292,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B77" s="8">
         <v>46111.505495046295</v>
@@ -6302,16 +6302,16 @@
         <v>46218.20417449074</v>
       </c>
       <c r="E77" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G77" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="F77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G77" s="9" t="s">
+      <c r="H77" s="9" t="s">
         <v>265</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>266</v>
       </c>
       <c r="I77" s="8">
         <v>46217</v>
@@ -6329,13 +6329,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q77" s="8">
         <v>46217</v>
@@ -6347,7 +6347,7 @@
         <v>0</v>
       </c>
       <c r="T77" s="12" t="s">
-        <v>172</v>
+        <v>267</v>
       </c>
       <c r="U77" s="10" t="s">
         <v>54</v>
@@ -6371,10 +6371,10 @@
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>266</v>
       </c>
       <c r="I78" s="5">
         <v>46226</v>
@@ -6392,13 +6392,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q78" s="5">
         <v>46226</v>
@@ -6428,16 +6428,16 @@
         <v>46114.627016388884</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="H79" s="9" t="s">
         <v>265</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>266</v>
       </c>
       <c r="I79" s="8">
         <v>46226</v>
@@ -6481,16 +6481,16 @@
         <v>46114.627017175924</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>266</v>
       </c>
       <c r="I80" s="5">
         <v>46226</v>
@@ -6540,10 +6540,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="H81" s="9" t="s">
         <v>246</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>247</v>
       </c>
       <c r="I81" s="8">
         <v>46246</v>
@@ -6561,13 +6561,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q81" s="8">
         <v>46246</v>
@@ -6597,16 +6597,16 @@
         <v>46114.62715587963</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>246</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>247</v>
       </c>
       <c r="I82" s="5">
         <v>46246</v>
@@ -6650,16 +6650,16 @@
         <v>46114.62715672454</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="H83" s="9" t="s">
         <v>246</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>247</v>
       </c>
       <c r="I83" s="8">
         <v>46246</v>
@@ -6756,10 +6756,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="H85" s="9" t="s">
         <v>254</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>255</v>
       </c>
       <c r="I85" s="8">
         <v>46183</v>
@@ -6819,10 +6819,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>254</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>255</v>
       </c>
       <c r="I86" s="5">
         <v>46239</v>
@@ -6882,10 +6882,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="H87" s="9" t="s">
         <v>254</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>255</v>
       </c>
       <c r="I87" s="8">
         <v>46246</v>
@@ -6945,10 +6945,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>254</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>255</v>
       </c>
       <c r="I88" s="5">
         <v>46273</v>
@@ -7008,10 +7008,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="H89" s="9" t="s">
         <v>254</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>255</v>
       </c>
       <c r="I89" s="8">
         <v>46220</v>
@@ -7032,10 +7032,10 @@
         <v>284</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q89" s="8">
         <v>46220</v>
@@ -7047,7 +7047,7 @@
         <v>0</v>
       </c>
       <c r="T89" s="12" t="s">
-        <v>172</v>
+        <v>267</v>
       </c>
       <c r="U89" s="12" t="s">
         <v>90</v>
@@ -7071,10 +7071,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>254</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>255</v>
       </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
@@ -7093,7 +7093,7 @@
         <v>284</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>300</v>
@@ -7132,10 +7132,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="H91" s="9" t="s">
         <v>254</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>255</v>
       </c>
       <c r="I91" s="8">
         <v>46181</v>
@@ -7156,7 +7156,7 @@
         <v>284</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P91" s="9" t="s">
         <v>303</v>
@@ -7264,7 +7264,7 @@
         <v>305</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P93" s="9" t="s">
         <v>305</v>
@@ -7297,7 +7297,7 @@
         <v>46118.545567442125</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7348,7 +7348,7 @@
         <v>46118.54556813657</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7427,7 +7427,7 @@
         <v>305</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>305</v>
@@ -7460,7 +7460,7 @@
         <v>46114.627765578705</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7511,7 +7511,7 @@
         <v>46114.62776635417</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7590,7 +7590,7 @@
         <v>305</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P99" s="9" t="s">
         <v>305</v>
@@ -7623,7 +7623,7 @@
         <v>46118.54557231482</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7674,7 +7674,7 @@
         <v>46118.54556883102</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7753,7 +7753,7 @@
         <v>305</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>305</v>
@@ -7786,7 +7786,7 @@
         <v>46118.545570937495</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7837,7 +7837,7 @@
         <v>46118.545571608796</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7916,7 +7916,7 @@
         <v>305</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P105" s="9" t="s">
         <v>305</v>
@@ -7949,7 +7949,7 @@
         <v>46118.545569548616</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -8000,7 +8000,7 @@
         <v>46118.545570243055</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -8079,7 +8079,7 @@
         <v>305</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>305</v>
@@ -8112,7 +8112,7 @@
         <v>46114.62850982639</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8138,7 +8138,7 @@
         <v>346</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P109" s="9" t="s">
         <v>348</v>
@@ -8161,7 +8161,7 @@
         <v>46114.62851064815</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8187,7 +8187,7 @@
         <v>346</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>350</v>
@@ -8269,7 +8269,7 @@
         <v>46114.62864336805</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8295,7 +8295,7 @@
         <v>352</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>355</v>
@@ -8318,7 +8318,7 @@
         <v>46114.62864409722</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8344,7 +8344,7 @@
         <v>352</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P113" s="9" t="s">
         <v>357</v>
@@ -8477,7 +8477,7 @@
         <v>46114.62888387732</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8505,7 +8505,7 @@
         <v>362</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>367</v>
@@ -8528,7 +8528,7 @@
         <v>46114.62888469908</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8556,7 +8556,7 @@
         <v>362</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P117" s="9" t="s">
         <v>369</v>
@@ -8895,7 +8895,7 @@
         <v>46114.629102280094</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8923,7 +8923,7 @@
         <v>382</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>385</v>
@@ -8946,7 +8946,7 @@
         <v>46114.62910302084</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -8974,7 +8974,7 @@
         <v>382</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P125" s="9" t="s">
         <v>387</v>
@@ -9258,10 +9258,10 @@
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="H131" s="9" t="s">
         <v>265</v>
-      </c>
-      <c r="H131" s="9" t="s">
-        <v>266</v>
       </c>
       <c r="I131" s="8">
         <v>46293</v>
@@ -9315,16 +9315,16 @@
         <v>46114.62931347222</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="H132" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>266</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9343,7 +9343,7 @@
         <v>399</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>402</v>
@@ -9366,16 +9366,16 @@
         <v>46114.62931429398</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="H133" s="9" t="s">
         <v>265</v>
-      </c>
-      <c r="H133" s="9" t="s">
-        <v>266</v>
       </c>
       <c r="I133" s="9"/>
       <c r="J133" s="8">
@@ -9394,7 +9394,7 @@
         <v>399</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P133" s="9" t="s">
         <v>404</v>
@@ -9423,10 +9423,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="H134" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>266</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9474,10 +9474,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="H135" s="9" t="s">
         <v>265</v>
-      </c>
-      <c r="H135" s="9" t="s">
-        <v>266</v>
       </c>
       <c r="I135" s="9"/>
       <c r="J135" s="8">
@@ -9525,10 +9525,10 @@
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="H136" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="H136" s="6" t="s">
-        <v>266</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9576,10 +9576,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="H137" s="9" t="s">
         <v>265</v>
-      </c>
-      <c r="H137" s="9" t="s">
-        <v>266</v>
       </c>
       <c r="I137" s="9"/>
       <c r="J137" s="8">
@@ -9627,10 +9627,10 @@
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="H138" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="H138" s="6" t="s">
-        <v>266</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
@@ -9678,10 +9678,10 @@
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="H139" s="9" t="s">
         <v>265</v>
-      </c>
-      <c r="H139" s="9" t="s">
-        <v>266</v>
       </c>
       <c r="I139" s="8">
         <v>46294</v>
@@ -9735,16 +9735,16 @@
         <v>46114.830281076385</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="H140" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>266</v>
       </c>
       <c r="I140" s="5">
         <v>46294</v>
@@ -9765,7 +9765,7 @@
         <v>417</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>420</v>
@@ -9788,16 +9788,16 @@
         <v>46114.830302789356</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="H141" s="9" t="s">
         <v>265</v>
-      </c>
-      <c r="H141" s="9" t="s">
-        <v>266</v>
       </c>
       <c r="I141" s="8">
         <v>46294</v>
@@ -9818,7 +9818,7 @@
         <v>417</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P141" s="9" t="s">
         <v>417</v>
@@ -9847,10 +9847,10 @@
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="H142" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="H142" s="6" t="s">
-        <v>266</v>
       </c>
       <c r="I142" s="5">
         <v>46294</v>
@@ -9900,10 +9900,10 @@
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="H143" s="9" t="s">
         <v>265</v>
-      </c>
-      <c r="H143" s="9" t="s">
-        <v>266</v>
       </c>
       <c r="I143" s="8">
         <v>46294</v>
@@ -9953,10 +9953,10 @@
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="H144" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="H144" s="6" t="s">
-        <v>266</v>
       </c>
       <c r="I144" s="5">
         <v>46294</v>
@@ -10006,10 +10006,10 @@
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="H145" s="9" t="s">
         <v>265</v>
-      </c>
-      <c r="H145" s="9" t="s">
-        <v>266</v>
       </c>
       <c r="I145" s="8">
         <v>46294</v>
@@ -10059,10 +10059,10 @@
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="H146" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="H146" s="6" t="s">
-        <v>266</v>
       </c>
       <c r="I146" s="5">
         <v>46294</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -2729,7 +2729,7 @@
         <v>46112.4753277662</v>
       </c>
       <c r="D17" s="8">
-        <v>46135.645324363424</v>
+        <v>46221.35628416667</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>69</v>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="8">
-        <v>46209.59541466435</v>
+        <v>46221.31477258102</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>88</v>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46154.867849305556</v>
+        <v>46221.115510891206</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>116</v>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46114.62176513889</v>
+        <v>46221.31555423611</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>260</v>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46114.6339722338</v>
+        <v>46221.31797234954</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>269</v>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46118.54556668982</v>
+        <v>46221.1155655787</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>284</v>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46114.62594751157</v>
+        <v>46221.36615074074</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>305</v>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46114.63686459491</v>
+        <v>46221.32620268519</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>346</v>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46114.62962787037</v>
+        <v>46221.10727317129</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>359</v>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46114.63748693287</v>
+        <v>46221.36200443287</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>399</v>
@@ -9669,7 +9669,7 @@
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46114.63755023148</v>
+        <v>46221.31842321759</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>417</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -5295,7 +5295,7 @@
         <v>46211.846184131944</v>
       </c>
       <c r="D59" s="8">
-        <v>46211.84618561342</v>
+        <v>46222.09270599537</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>202</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="446">
   <si>
     <t>50001525- ZITRON PERU METRO DE LIMA  ESTACION 07</t>
   </si>
@@ -310,6 +310,9 @@
     <t>propuesta rodete ot 4287 - 4288</t>
   </si>
   <si>
+    <t>nespinoza@zitron.com</t>
+  </si>
+  <si>
     <t>Generación OC Rodete ot 4287 - 4288,Propuesta compras:</t>
   </si>
   <si>
@@ -562,6 +565,9 @@
     <t xml:space="preserve"> Generacion OC Fabricacion Externa ot 4287 - 4288,Fabricacion estructura proveedor externo ot 4287 - 4288</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1213833564667630</t>
   </si>
   <si>
@@ -812,9 +818,6 @@
   </si>
   <si>
     <t>Caldereria,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213869987281784</t>
@@ -3282,7 +3285,7 @@
         <v>46209.595404629625</v>
       </c>
       <c r="D26" s="5">
-        <v>46209.59540697916</v>
+        <v>46223.59446482639</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>98</v>
@@ -3291,9 +3294,11 @@
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H26" s="6"/>
+        <v>99</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="I26" s="5">
         <v>46121</v>
       </c>
@@ -3316,7 +3321,7 @@
         <v>75</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q26" s="5">
         <v>46121</v>
@@ -3336,7 +3341,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B27" s="8">
         <v>46108.75688663195</v>
@@ -3348,7 +3353,7 @@
         <v>46135.5462021412</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
@@ -3381,7 +3386,7 @@
         <v>46</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q27" s="8">
         <v>46121</v>
@@ -3401,25 +3406,27 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B28" s="5">
         <v>46108.756897349536</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46209.59805664352</v>
+        <v>46223.594457824074</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H28" s="6"/>
+        <v>99</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="I28" s="5">
         <v>46191</v>
       </c>
@@ -3439,10 +3446,10 @@
         <v>88</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q28" s="5">
         <v>46191</v>
@@ -3462,7 +3469,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B29" s="8">
         <v>46108.75690234954</v>
@@ -3474,7 +3481,7 @@
         <v>46123.19348805556</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3507,7 +3514,7 @@
         <v>78</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q29" s="8">
         <v>46121</v>
@@ -3527,25 +3534,27 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B30" s="5">
         <v>46108.75690841435</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46206.577005486106</v>
+        <v>46223.594457175925</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H30" s="6"/>
+        <v>99</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="I30" s="5">
         <v>46191</v>
       </c>
@@ -3565,10 +3574,10 @@
         <v>88</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q30" s="5">
         <v>46191</v>
@@ -3588,7 +3597,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B31" s="8">
         <v>46108.78647824074</v>
@@ -3633,7 +3642,7 @@
         <v>85</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q31" s="8">
         <v>46121</v>
@@ -3653,7 +3662,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B32" s="5">
         <v>46108.756741087964</v>
@@ -3663,7 +3672,7 @@
         <v>46221.115510891206</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>25</v>
@@ -3687,7 +3696,7 @@
         <v>26</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3700,7 +3709,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B33" s="8">
         <v>46108.75695274306</v>
@@ -3710,16 +3719,16 @@
         <v>46182.6933722338</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I33" s="8">
         <v>46125</v>
@@ -3737,13 +3746,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q33" s="8">
         <v>46125</v>
@@ -3763,7 +3772,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B34" s="5">
         <v>46108.75695775463</v>
@@ -3775,16 +3784,16 @@
         <v>46182.69336725694</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I34" s="5">
         <v>46125</v>
@@ -3802,13 +3811,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>95</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q34" s="5">
         <v>45985</v>
@@ -3828,7 +3837,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B35" s="8">
         <v>46108.75696342593</v>
@@ -3838,16 +3847,16 @@
         <v>46182.69337332176</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I35" s="8">
         <v>46127</v>
@@ -3865,13 +3874,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q35" s="8">
         <v>45987</v>
@@ -3891,7 +3900,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B36" s="5">
         <v>46108.75697314815</v>
@@ -3901,16 +3910,16 @@
         <v>46169.854331932875</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I36" s="5">
         <v>46125</v>
@@ -3928,13 +3937,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q36" s="5">
         <v>46125</v>
@@ -3954,7 +3963,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B37" s="8">
         <v>46108.75697796296</v>
@@ -3964,16 +3973,16 @@
         <v>46135.54608165509</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I37" s="8">
         <v>46125</v>
@@ -3991,13 +4000,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q37" s="8">
         <v>45979</v>
@@ -4017,7 +4026,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B38" s="5">
         <v>46108.7569835301</v>
@@ -4027,16 +4036,16 @@
         <v>46111.58202451389</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I38" s="5">
         <v>46134</v>
@@ -4054,13 +4063,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q38" s="5">
         <v>45988</v>
@@ -4078,7 +4087,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B39" s="8">
         <v>46108.75698832176</v>
@@ -4088,16 +4097,16 @@
         <v>46183.16750024306</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I39" s="8">
         <v>46125</v>
@@ -4115,13 +4124,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q39" s="8">
         <v>46125</v>
@@ -4141,7 +4150,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B40" s="5">
         <v>46108.75699311343</v>
@@ -4151,16 +4160,16 @@
         <v>46209.595412939816</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I40" s="5">
         <v>46125</v>
@@ -4178,13 +4187,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>98</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q40" s="5">
         <v>45985</v>
@@ -4204,7 +4213,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B41" s="8">
         <v>46108.75699847222</v>
@@ -4214,16 +4223,16 @@
         <v>46182.1679962037</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I41" s="8">
         <v>46127</v>
@@ -4241,13 +4250,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q41" s="8">
         <v>45987</v>
@@ -4267,7 +4276,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B42" s="5">
         <v>46108.75700357639</v>
@@ -4277,16 +4286,16 @@
         <v>46211.84653167824</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I42" s="5">
         <v>46118</v>
@@ -4304,13 +4313,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q42" s="5">
         <v>46118</v>
@@ -4330,7 +4339,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B43" s="8">
         <v>46108.75700856482</v>
@@ -4342,16 +4351,16 @@
         <v>46182.69343975694</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I43" s="8">
         <v>46118</v>
@@ -4369,13 +4378,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>92</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q43" s="8">
         <v>45978</v>
@@ -4395,7 +4404,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B44" s="5">
         <v>46108.757016435186</v>
@@ -4405,16 +4414,16 @@
         <v>46182.69344646991</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I44" s="5">
         <v>46139</v>
@@ -4432,13 +4441,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q44" s="5">
         <v>45999</v>
@@ -4458,7 +4467,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B45" s="8">
         <v>46108.7570218287</v>
@@ -4470,16 +4479,16 @@
         <v>46211.84652803241</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I45" s="8">
         <v>46139</v>
@@ -4497,13 +4506,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q45" s="8">
         <v>45999</v>
@@ -4523,7 +4532,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B46" s="5">
         <v>46108.75702719907</v>
@@ -4533,16 +4542,16 @@
         <v>46211.173315312495</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I46" s="5">
         <v>46195</v>
@@ -4560,13 +4569,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q46" s="5">
         <v>46195</v>
@@ -4586,7 +4595,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B47" s="8">
         <v>46108.75703201389</v>
@@ -4596,16 +4605,16 @@
         <v>46209.598061192126</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I47" s="8">
         <v>46195</v>
@@ -4623,13 +4632,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q47" s="8">
         <v>45985</v>
@@ -4649,7 +4658,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B48" s="5">
         <v>46108.75703761574</v>
@@ -4659,16 +4668,16 @@
         <v>46210.16869111111</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I48" s="5">
         <v>46202</v>
@@ -4686,13 +4695,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q48" s="5">
         <v>46007</v>
@@ -4712,7 +4721,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B49" s="8">
         <v>46108.75704306713</v>
@@ -4724,16 +4733,16 @@
         <v>46220.16760561343</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I49" s="8">
         <v>46125</v>
@@ -4751,13 +4760,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q49" s="8">
         <v>46125</v>
@@ -4777,7 +4786,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B50" s="5">
         <v>46108.75705032407</v>
@@ -4789,16 +4798,16 @@
         <v>46154.86746811343</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I50" s="5">
         <v>46125</v>
@@ -4816,13 +4825,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4832,7 +4841,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B51" s="8">
         <v>46108.75705728009</v>
@@ -4844,16 +4853,16 @@
         <v>46154.8677641088</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I51" s="8">
         <v>46135</v>
@@ -4871,13 +4880,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4887,26 +4896,26 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B52" s="5">
         <v>46108.757061435186</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46169.85242414352</v>
+        <v>46223.1904159375</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I52" s="5">
         <v>46195</v>
@@ -4924,13 +4933,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q52" s="5">
         <v>46195</v>
@@ -4941,8 +4950,8 @@
       <c r="S52" s="6">
         <v>0</v>
       </c>
-      <c r="T52" s="11" t="s">
-        <v>53</v>
+      <c r="T52" s="12" t="s">
+        <v>184</v>
       </c>
       <c r="U52" s="12" t="s">
         <v>90</v>
@@ -4950,7 +4959,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B53" s="8">
         <v>46108.75710696759</v>
@@ -4960,16 +4969,16 @@
         <v>46199.168608900465</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I53" s="8">
         <v>46195</v>
@@ -4987,13 +4996,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5009,7 +5018,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B54" s="5">
         <v>46108.757112928244</v>
@@ -5019,16 +5028,16 @@
         <v>46169.85241099537</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I54" s="5">
         <v>46210</v>
@@ -5046,13 +5055,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5062,7 +5071,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B55" s="8">
         <v>46111.50860645833</v>
@@ -5074,16 +5083,16 @@
         <v>46182.69406362269</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I55" s="8">
         <v>46125</v>
@@ -5101,10 +5110,10 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5127,7 +5136,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B56" s="5">
         <v>46111.508755937495</v>
@@ -5139,16 +5148,16 @@
         <v>46182.69350877315</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I56" s="5">
         <v>46125</v>
@@ -5166,13 +5175,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>86</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5182,7 +5191,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B57" s="8">
         <v>46111.508846770834</v>
@@ -5194,16 +5203,16 @@
         <v>46182.69403748843</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I57" s="8">
         <v>46132</v>
@@ -5221,13 +5230,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5237,7 +5246,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B58" s="5">
         <v>46108.75711900463</v>
@@ -5247,7 +5256,7 @@
         <v>46217.85709320602</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -5271,7 +5280,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5286,7 +5295,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B59" s="8">
         <v>46108.75712325232</v>
@@ -5298,16 +5307,16 @@
         <v>46222.09270599537</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="8">
@@ -5323,13 +5332,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q59" s="8">
         <v>46121</v>
@@ -5349,7 +5358,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B60" s="5">
         <v>46114.552579166666</v>
@@ -5361,16 +5370,16 @@
         <v>46211.84604957176</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I60" s="5">
         <v>46121</v>
@@ -5388,13 +5397,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5404,7 +5413,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B61" s="8">
         <v>46114.552773240735</v>
@@ -5416,16 +5425,16 @@
         <v>46211.846055462964</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I61" s="8">
         <v>46121</v>
@@ -5443,13 +5452,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>78</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5459,7 +5468,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B62" s="5">
         <v>46108.75712855324</v>
@@ -5471,16 +5480,16 @@
         <v>46217.857082789356</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="I62" s="5">
         <v>46183</v>
@@ -5498,13 +5507,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q62" s="5">
         <v>46183</v>
@@ -5524,7 +5533,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B63" s="8">
         <v>46114.55286452547</v>
@@ -5536,16 +5545,16 @@
         <v>46217.85704695602</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I63" s="8">
         <v>46183</v>
@@ -5563,13 +5572,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q63" s="9"/>
       <c r="R63" s="9"/>
@@ -5579,7 +5588,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B64" s="5">
         <v>46114.552966620366</v>
@@ -5591,16 +5600,16 @@
         <v>46217.85705476852</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I64" s="5">
         <v>46183</v>
@@ -5618,13 +5627,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5634,7 +5643,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B65" s="8">
         <v>46108.75713383102</v>
@@ -5644,16 +5653,16 @@
         <v>46217.857092986116</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I65" s="8">
         <v>46190</v>
@@ -5671,13 +5680,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q65" s="8">
         <v>46190</v>
@@ -5697,7 +5706,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B66" s="5">
         <v>46114.55312298611</v>
@@ -5707,16 +5716,16 @@
         <v>46217.85705168982</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="5">
@@ -5732,10 +5741,10 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5748,7 +5757,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B67" s="8">
         <v>46114.553244675924</v>
@@ -5758,16 +5767,16 @@
         <v>46217.85706487269</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="8">
@@ -5783,10 +5792,10 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>26</v>
@@ -5799,7 +5808,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B68" s="5">
         <v>46108.757138761575</v>
@@ -5809,16 +5818,16 @@
         <v>46114.631384050925</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I68" s="5">
         <v>46281</v>
@@ -5836,10 +5845,10 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5862,7 +5871,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B69" s="8">
         <v>46111.55280189815</v>
@@ -5872,16 +5881,16 @@
         <v>46114.62851033565</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -5897,13 +5906,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5913,7 +5922,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B70" s="5">
         <v>46111.55285245371</v>
@@ -5923,16 +5932,16 @@
         <v>46114.62851040509</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -5948,13 +5957,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5964,7 +5973,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B71" s="8">
         <v>46108.75714166666</v>
@@ -5974,7 +5983,7 @@
         <v>46118.545566597226</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -5998,7 +6007,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -6011,7 +6020,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B72" s="5">
         <v>46108.75714454861</v>
@@ -6021,16 +6030,16 @@
         <v>46118.55132545139</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -6046,13 +6055,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q72" s="5">
         <v>46231</v>
@@ -6072,7 +6081,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B73" s="8">
         <v>46111.50359008102</v>
@@ -6082,7 +6091,7 @@
         <v>46114.61935158564</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -6106,7 +6115,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -6119,7 +6128,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B74" s="5">
         <v>46111.50404616898</v>
@@ -6129,16 +6138,16 @@
         <v>46213.19769318287</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I74" s="5">
         <v>46211</v>
@@ -6156,13 +6165,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q74" s="5">
         <v>46211</v>
@@ -6182,7 +6191,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B75" s="8">
         <v>46111.50406170139</v>
@@ -6192,16 +6201,16 @@
         <v>46217.17519608796</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I75" s="8">
         <v>46213</v>
@@ -6219,13 +6228,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q75" s="8">
         <v>46213</v>
@@ -6245,7 +6254,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B76" s="5">
         <v>46111.50543856481</v>
@@ -6255,7 +6264,7 @@
         <v>46221.31555423611</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -6279,7 +6288,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -6292,7 +6301,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B77" s="8">
         <v>46111.505495046295</v>
@@ -6302,16 +6311,16 @@
         <v>46218.20417449074</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I77" s="8">
         <v>46217</v>
@@ -6329,13 +6338,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q77" s="8">
         <v>46217</v>
@@ -6347,7 +6356,7 @@
         <v>0</v>
       </c>
       <c r="T77" s="12" t="s">
-        <v>267</v>
+        <v>184</v>
       </c>
       <c r="U77" s="10" t="s">
         <v>54</v>
@@ -6355,7 +6364,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B78" s="5">
         <v>46111.50560314815</v>
@@ -6365,16 +6374,16 @@
         <v>46221.31797234954</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I78" s="5">
         <v>46226</v>
@@ -6392,13 +6401,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q78" s="5">
         <v>46226</v>
@@ -6418,7 +6427,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B79" s="8">
         <v>46111.52633317129</v>
@@ -6428,16 +6437,16 @@
         <v>46114.627016388884</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I79" s="8">
         <v>46226</v>
@@ -6455,13 +6464,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6471,7 +6480,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B80" s="5">
         <v>46111.526644375</v>
@@ -6481,16 +6490,16 @@
         <v>46114.627017175924</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I80" s="5">
         <v>46226</v>
@@ -6508,13 +6517,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6524,7 +6533,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B81" s="8">
         <v>46111.50563458333</v>
@@ -6534,16 +6543,16 @@
         <v>46114.63406568287</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I81" s="8">
         <v>46246</v>
@@ -6561,13 +6570,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q81" s="8">
         <v>46246</v>
@@ -6587,7 +6596,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B82" s="5">
         <v>46111.526916469906</v>
@@ -6597,16 +6606,16 @@
         <v>46114.62715587963</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I82" s="5">
         <v>46246</v>
@@ -6624,13 +6633,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6640,7 +6649,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B83" s="8">
         <v>46111.52699828704</v>
@@ -6650,16 +6659,16 @@
         <v>46114.62715672454</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I83" s="8">
         <v>46246</v>
@@ -6677,13 +6686,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6693,7 +6702,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B84" s="5">
         <v>46108.75714884259</v>
@@ -6703,7 +6712,7 @@
         <v>46221.1155655787</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -6727,7 +6736,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6740,7 +6749,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B85" s="8">
         <v>46108.75715243055</v>
@@ -6750,16 +6759,16 @@
         <v>46185.184959907405</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I85" s="8">
         <v>46183</v>
@@ -6777,13 +6786,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q85" s="8">
         <v>46183</v>
@@ -6803,7 +6812,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B86" s="5">
         <v>46108.75715773148</v>
@@ -6819,10 +6828,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I86" s="5">
         <v>46239</v>
@@ -6840,13 +6849,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q86" s="5">
         <v>46239</v>
@@ -6866,7 +6875,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B87" s="8">
         <v>46108.75716349537</v>
@@ -6876,16 +6885,16 @@
         <v>46111.59762381944</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I87" s="8">
         <v>46246</v>
@@ -6903,13 +6912,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q87" s="8">
         <v>46246</v>
@@ -6929,7 +6938,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B88" s="5">
         <v>46108.75716875</v>
@@ -6939,16 +6948,16 @@
         <v>46111.59782981481</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I88" s="5">
         <v>46273</v>
@@ -6966,13 +6975,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q88" s="5">
         <v>46273</v>
@@ -6992,26 +7001,26 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B89" s="8">
         <v>46108.75717430556</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46216.198306990744</v>
+        <v>46223.1679734375</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I89" s="8">
         <v>46220</v>
@@ -7029,13 +7038,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q89" s="8">
         <v>46220</v>
@@ -7047,7 +7056,7 @@
         <v>0</v>
       </c>
       <c r="T89" s="12" t="s">
-        <v>267</v>
+        <v>184</v>
       </c>
       <c r="U89" s="12" t="s">
         <v>90</v>
@@ -7055,7 +7064,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B90" s="5">
         <v>46108.75717877314</v>
@@ -7065,16 +7074,16 @@
         <v>46118.54556859954</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
@@ -7090,13 +7099,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q90" s="5">
         <v>46231</v>
@@ -7116,7 +7125,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B91" s="8">
         <v>46108.822037094906</v>
@@ -7126,16 +7135,16 @@
         <v>46185.18495945602</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I91" s="8">
         <v>46181</v>
@@ -7153,13 +7162,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q91" s="8">
         <v>46183</v>
@@ -7179,7 +7188,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B92" s="5">
         <v>46108.757183124995</v>
@@ -7189,7 +7198,7 @@
         <v>46221.36615074074</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>25</v>
@@ -7213,7 +7222,7 @@
         <v>26</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>26</v>
@@ -7226,25 +7235,27 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B93" s="8">
         <v>46108.757186296294</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46114.63518780093</v>
+        <v>46223.59523664352</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H93" s="9"/>
+        <v>99</v>
+      </c>
+      <c r="H93" s="9" t="s">
+        <v>99</v>
+      </c>
       <c r="I93" s="8">
         <v>46248</v>
       </c>
@@ -7261,13 +7272,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q93" s="8">
         <v>46248</v>
@@ -7287,25 +7298,27 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B94" s="5">
         <v>46111.52720202546</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46118.545567442125</v>
+        <v>46223.59457288195</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H94" s="6"/>
+        <v>99</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="I94" s="5">
         <v>46248</v>
       </c>
@@ -7322,13 +7335,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7338,25 +7351,27 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B95" s="8">
         <v>46111.52733795139</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46118.54556813657</v>
+        <v>46223.594572268514</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H95" s="9"/>
+        <v>99</v>
+      </c>
+      <c r="H95" s="9" t="s">
+        <v>99</v>
+      </c>
       <c r="I95" s="8">
         <v>46248</v>
       </c>
@@ -7373,13 +7388,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7389,25 +7404,27 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B96" s="5">
         <v>46108.75720997685</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46114.636429907405</v>
+        <v>46223.595235995366</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H96" s="6"/>
+        <v>99</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="I96" s="5">
         <v>46268</v>
       </c>
@@ -7424,13 +7441,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q96" s="5">
         <v>46268</v>
@@ -7450,25 +7467,27 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B97" s="8">
         <v>46111.52790079861</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46114.627765578705</v>
+        <v>46223.5946628588</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H97" s="9"/>
+        <v>99</v>
+      </c>
+      <c r="H97" s="9" t="s">
+        <v>99</v>
+      </c>
       <c r="I97" s="8">
         <v>46268</v>
       </c>
@@ -7485,13 +7504,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7501,25 +7520,27 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B98" s="5">
         <v>46111.52796104166</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46114.62776635417</v>
+        <v>46223.59466224537</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H98" s="6"/>
+        <v>99</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="I98" s="5">
         <v>46268</v>
       </c>
@@ -7536,13 +7557,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7552,25 +7573,27 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B99" s="8">
         <v>46108.75719767361</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46114.63653665509</v>
+        <v>46223.5952353125</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H99" s="9"/>
+        <v>99</v>
+      </c>
+      <c r="H99" s="9" t="s">
+        <v>99</v>
+      </c>
       <c r="I99" s="8">
         <v>46272</v>
       </c>
@@ -7587,13 +7610,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q99" s="8">
         <v>46272</v>
@@ -7613,25 +7636,27 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B100" s="5">
         <v>46111.52756633102</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46118.54557231482</v>
+        <v>46223.59474541667</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H100" s="6"/>
+        <v>99</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="I100" s="5">
         <v>46272</v>
       </c>
@@ -7648,13 +7673,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7664,25 +7689,27 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B101" s="8">
         <v>46111.527622395835</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46118.54556883102</v>
+        <v>46223.594744710645</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H101" s="9"/>
+        <v>99</v>
+      </c>
+      <c r="H101" s="9" t="s">
+        <v>99</v>
+      </c>
       <c r="I101" s="8">
         <v>46272</v>
       </c>
@@ -7699,13 +7726,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7715,25 +7742,27 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B102" s="5">
         <v>46108.75720341435</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46114.63667146991</v>
+        <v>46223.595234629625</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H102" s="6"/>
+        <v>99</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="I102" s="5">
         <v>46274</v>
       </c>
@@ -7750,13 +7779,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q102" s="5">
         <v>46274</v>
@@ -7776,25 +7805,27 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B103" s="8">
         <v>46111.52775804398</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46118.545570937495</v>
+        <v>46223.594845011576</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H103" s="9"/>
+        <v>99</v>
+      </c>
+      <c r="H103" s="9" t="s">
+        <v>99</v>
+      </c>
       <c r="I103" s="8">
         <v>46274</v>
       </c>
@@ -7811,13 +7842,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -7827,25 +7858,27 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B104" s="5">
         <v>46111.52780829861</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46118.545571608796</v>
+        <v>46223.59484435185</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H104" s="6"/>
+        <v>99</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="I104" s="5">
         <v>46274</v>
       </c>
@@ -7862,13 +7895,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7878,25 +7911,27 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B105" s="8">
         <v>46108.757191412034</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46114.636801493056</v>
+        <v>46223.59523400463</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H105" s="9"/>
+        <v>99</v>
+      </c>
+      <c r="H105" s="9" t="s">
+        <v>99</v>
+      </c>
       <c r="I105" s="8">
         <v>46276</v>
       </c>
@@ -7913,13 +7948,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q105" s="8">
         <v>46276</v>
@@ -7939,25 +7974,27 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B106" s="5">
         <v>46111.527446493055</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46118.545569548616</v>
+        <v>46223.594939675924</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H106" s="6"/>
+        <v>99</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="I106" s="5">
         <v>46276</v>
       </c>
@@ -7974,13 +8011,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7990,25 +8027,27 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B107" s="8">
         <v>46111.52746010417</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46118.545570243055</v>
+        <v>46223.59493908565</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H107" s="9"/>
+        <v>99</v>
+      </c>
+      <c r="H107" s="9" t="s">
+        <v>99</v>
+      </c>
       <c r="I107" s="8">
         <v>46276</v>
       </c>
@@ -8025,13 +8064,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -8041,25 +8080,27 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B108" s="5">
         <v>46108.757217025464</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46221.32620268519</v>
+        <v>46223.59523337963</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H108" s="6"/>
+        <v>99</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="I108" s="5">
         <v>46280</v>
       </c>
@@ -8076,13 +8117,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q108" s="5">
         <v>46280</v>
@@ -8102,25 +8143,27 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B109" s="8">
         <v>46111.528031932874</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46114.62850982639</v>
+        <v>46223.59502533565</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H109" s="9"/>
+        <v>99</v>
+      </c>
+      <c r="H109" s="9" t="s">
+        <v>99</v>
+      </c>
       <c r="I109" s="9"/>
       <c r="J109" s="8">
         <v>46280</v>
@@ -8135,13 +8178,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8151,25 +8194,27 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B110" s="5">
         <v>46111.52811128472</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46114.62851064815</v>
+        <v>46223.59502458334</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H110" s="6"/>
+        <v>99</v>
+      </c>
+      <c r="H110" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="I110" s="6"/>
       <c r="J110" s="5">
         <v>46280</v>
@@ -8184,13 +8229,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8200,25 +8245,27 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B111" s="8">
         <v>46108.75727585648</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46114.63695302083</v>
+        <v>46223.595232754626</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H111" s="9"/>
+        <v>99</v>
+      </c>
+      <c r="H111" s="9" t="s">
+        <v>99</v>
+      </c>
       <c r="I111" s="9"/>
       <c r="J111" s="8">
         <v>46286</v>
@@ -8233,13 +8280,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q111" s="8">
         <v>46286</v>
@@ -8259,25 +8306,27 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B112" s="5">
         <v>46111.5281812037</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46114.62864336805</v>
+        <v>46223.595106875</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H112" s="6"/>
+        <v>99</v>
+      </c>
+      <c r="H112" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
         <v>46286</v>
@@ -8292,13 +8341,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8308,25 +8357,27 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B113" s="8">
         <v>46111.528266423615</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46114.62864409722</v>
+        <v>46223.59510622685</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H113" s="9"/>
+        <v>99</v>
+      </c>
+      <c r="H113" s="9" t="s">
+        <v>99</v>
+      </c>
       <c r="I113" s="9"/>
       <c r="J113" s="8">
         <v>46286</v>
@@ -8341,13 +8392,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8357,7 +8408,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B114" s="5">
         <v>46108.757283217594</v>
@@ -8367,7 +8418,7 @@
         <v>46221.10727317129</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>25</v>
@@ -8391,7 +8442,7 @@
         <v>26</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>26</v>
@@ -8404,7 +8455,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B115" s="8">
         <v>46108.757287430555</v>
@@ -8414,16 +8465,16 @@
         <v>46114.63723893519</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I115" s="8">
         <v>46287</v>
@@ -8441,13 +8492,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q115" s="8">
         <v>46287</v>
@@ -8467,7 +8518,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B116" s="5">
         <v>46111.52846596065</v>
@@ -8477,16 +8528,16 @@
         <v>46114.62888387732</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8502,13 +8553,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8518,7 +8569,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B117" s="8">
         <v>46111.528518067134</v>
@@ -8528,16 +8579,16 @@
         <v>46114.62888469908</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="8">
@@ -8553,13 +8604,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8569,7 +8620,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B118" s="5">
         <v>46111.531216006944</v>
@@ -8585,10 +8636,10 @@
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I118" s="6"/>
       <c r="J118" s="5">
@@ -8604,13 +8655,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8620,7 +8671,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B119" s="8">
         <v>46111.53129275463</v>
@@ -8636,10 +8687,10 @@
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I119" s="9"/>
       <c r="J119" s="8">
@@ -8655,13 +8706,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O119" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8671,7 +8722,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B120" s="5">
         <v>46111.53134821759</v>
@@ -8681,16 +8732,16 @@
         <v>46114.628886921295</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
@@ -8706,13 +8757,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8722,7 +8773,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B121" s="8">
         <v>46111.53139942129</v>
@@ -8738,10 +8789,10 @@
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I121" s="9"/>
       <c r="J121" s="8">
@@ -8757,13 +8808,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O121" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8773,7 +8824,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B122" s="5">
         <v>46111.53343819444</v>
@@ -8783,16 +8834,16 @@
         <v>46114.628888437495</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I122" s="6"/>
       <c r="J122" s="5">
@@ -8808,13 +8859,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8824,25 +8875,27 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B123" s="8">
         <v>46108.75729289352</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46114.637374618054</v>
+        <v>46223.59539700231</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H123" s="9"/>
+        <v>99</v>
+      </c>
+      <c r="H123" s="9" t="s">
+        <v>99</v>
+      </c>
       <c r="I123" s="8">
         <v>46288</v>
       </c>
@@ -8859,13 +8912,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q123" s="8">
         <v>46288</v>
@@ -8885,25 +8938,27 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B124" s="5">
         <v>46111.52857409722</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46114.629102280094</v>
+        <v>46223.595359328705</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H124" s="6"/>
+        <v>99</v>
+      </c>
+      <c r="H124" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="I124" s="5">
         <v>46288</v>
       </c>
@@ -8920,13 +8975,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8936,25 +8991,27 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B125" s="8">
         <v>46111.528674016205</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46114.62910302084</v>
+        <v>46223.59535869213</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H125" s="9"/>
+        <v>99</v>
+      </c>
+      <c r="H125" s="9" t="s">
+        <v>99</v>
+      </c>
       <c r="I125" s="8">
         <v>46288</v>
       </c>
@@ -8971,13 +9028,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -8987,14 +9044,14 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B126" s="5">
         <v>46111.531552291664</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46114.629103784726</v>
+        <v>46223.59535802083</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>56</v>
@@ -9003,9 +9060,11 @@
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H126" s="6"/>
+        <v>99</v>
+      </c>
+      <c r="H126" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="I126" s="5">
         <v>46288</v>
       </c>
@@ -9022,13 +9081,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9038,14 +9097,14 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B127" s="8">
         <v>46111.531603344905</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46114.62910452546</v>
+        <v>46223.595357349535</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>60</v>
@@ -9054,9 +9113,11 @@
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H127" s="9"/>
+        <v>99</v>
+      </c>
+      <c r="H127" s="9" t="s">
+        <v>99</v>
+      </c>
       <c r="I127" s="8">
         <v>46288</v>
       </c>
@@ -9073,13 +9134,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O127" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9089,25 +9150,27 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B128" s="5">
         <v>46111.531648379634</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46114.62910528935</v>
+        <v>46223.59535668981</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H128" s="6"/>
+        <v>99</v>
+      </c>
+      <c r="H128" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="I128" s="5">
         <v>46288</v>
       </c>
@@ -9124,13 +9187,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9140,14 +9203,14 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B129" s="8">
         <v>46111.531705925925</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46114.62910605324</v>
+        <v>46223.595356018515</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>66</v>
@@ -9156,9 +9219,11 @@
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H129" s="9"/>
+        <v>99</v>
+      </c>
+      <c r="H129" s="9" t="s">
+        <v>99</v>
+      </c>
       <c r="I129" s="8">
         <v>46288</v>
       </c>
@@ -9175,13 +9240,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O129" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9191,25 +9256,27 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B130" s="5">
         <v>46111.533570127314</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46114.62910684028</v>
+        <v>46223.59535532407</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H130" s="6"/>
+        <v>99</v>
+      </c>
+      <c r="H130" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="I130" s="5">
         <v>46288</v>
       </c>
@@ -9226,13 +9293,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9242,7 +9309,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B131" s="8">
         <v>46108.75729930555</v>
@@ -9252,16 +9319,16 @@
         <v>46221.36200443287</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I131" s="8">
         <v>46293</v>
@@ -9279,13 +9346,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q131" s="8">
         <v>46293</v>
@@ -9305,7 +9372,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B132" s="5">
         <v>46111.528799872685</v>
@@ -9315,16 +9382,16 @@
         <v>46114.62931347222</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9340,13 +9407,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9356,7 +9423,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B133" s="8">
         <v>46111.52885179398</v>
@@ -9366,16 +9433,16 @@
         <v>46114.62931429398</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I133" s="9"/>
       <c r="J133" s="8">
@@ -9391,13 +9458,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9407,7 +9474,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B134" s="5">
         <v>46111.53215439815</v>
@@ -9423,10 +9490,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9442,13 +9509,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9458,7 +9525,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B135" s="8">
         <v>46111.53220642361</v>
@@ -9474,10 +9541,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I135" s="9"/>
       <c r="J135" s="8">
@@ -9493,13 +9560,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O135" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9509,7 +9576,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B136" s="5">
         <v>46111.532258287036</v>
@@ -9519,16 +9586,16 @@
         <v>46114.629316527775</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9544,13 +9611,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9560,7 +9627,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B137" s="8">
         <v>46111.53231001158</v>
@@ -9576,10 +9643,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I137" s="9"/>
       <c r="J137" s="8">
@@ -9595,13 +9662,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O137" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -9611,7 +9678,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B138" s="5">
         <v>46111.53368237268</v>
@@ -9621,16 +9688,16 @@
         <v>46114.62931805555</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
@@ -9646,13 +9713,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9662,7 +9729,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B139" s="8">
         <v>46108.757304583334</v>
@@ -9672,16 +9739,16 @@
         <v>46221.31842321759</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I139" s="8">
         <v>46294</v>
@@ -9699,13 +9766,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q139" s="8">
         <v>46294</v>
@@ -9725,7 +9792,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B140" s="5">
         <v>46111.528945011574</v>
@@ -9735,16 +9802,16 @@
         <v>46114.830281076385</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I140" s="5">
         <v>46294</v>
@@ -9762,13 +9829,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9778,7 +9845,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B141" s="8">
         <v>46111.52901092592</v>
@@ -9788,16 +9855,16 @@
         <v>46114.830302789356</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I141" s="8">
         <v>46294</v>
@@ -9815,13 +9882,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -9831,7 +9898,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B142" s="5">
         <v>46111.53247278935</v>
@@ -9847,10 +9914,10 @@
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I142" s="5">
         <v>46294</v>
@@ -9868,13 +9935,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9884,7 +9951,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B143" s="8">
         <v>46111.53253350694</v>
@@ -9900,10 +9967,10 @@
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I143" s="8">
         <v>46294</v>
@@ -9921,13 +9988,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O143" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -9937,7 +10004,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B144" s="5">
         <v>46111.532638414355</v>
@@ -9953,10 +10020,10 @@
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I144" s="5">
         <v>46294</v>
@@ -9974,13 +10041,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9990,7 +10057,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B145" s="8">
         <v>46111.53258112269</v>
@@ -10000,16 +10067,16 @@
         <v>46114.83037114583</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I145" s="8">
         <v>46294</v>
@@ -10027,13 +10094,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -10043,7 +10110,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B146" s="5">
         <v>46111.53385627315</v>
@@ -10053,16 +10120,16 @@
         <v>46114.83039427083</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I146" s="5">
         <v>46294</v>
@@ -10080,13 +10147,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10096,7 +10163,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B147" s="8">
         <v>46108.757310497684</v>
@@ -10106,7 +10173,7 @@
         <v>46114.62962797454</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>25</v>
@@ -10130,7 +10197,7 @@
         <v>26</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P147" s="9" t="s">
         <v>26</v>
@@ -10143,7 +10210,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B148" s="5">
         <v>46108.75731366898</v>
@@ -10153,16 +10220,16 @@
         <v>46114.63764361111</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="I148" s="5">
         <v>46295</v>
@@ -10180,13 +10247,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q148" s="5">
         <v>46295</v>
@@ -10206,7 +10273,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B149" s="8">
         <v>46108.75732001157</v>
@@ -10216,16 +10283,16 @@
         <v>46119.74841528935</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="I149" s="8">
         <v>46295</v>
@@ -10243,13 +10310,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q149" s="8">
         <v>46295</v>
@@ -10269,7 +10336,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B150" s="5">
         <v>46108.7573290625</v>
@@ -10279,7 +10346,7 @@
         <v>46114.62962836806</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>25</v>
@@ -10303,7 +10370,7 @@
         <v>26</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P150" s="6" t="s">
         <v>26</v>
@@ -10316,7 +10383,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B151" s="8">
         <v>46108.75733305556</v>
@@ -10326,7 +10393,7 @@
         <v>46119.748459016206</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
@@ -10353,13 +10420,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Q151" s="8">
         <v>46295</v>
@@ -10379,7 +10446,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B152" s="5">
         <v>46108.757338703705</v>
@@ -10389,7 +10456,7 @@
         <v>46119.748502546296</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10416,13 +10483,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q152" s="5">
         <v>46304</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -6027,7 +6027,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46118.55132545139</v>
+        <v>46224.175318078705</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>245</v>
@@ -6072,8 +6072,8 @@
       <c r="S72" s="6">
         <v>0</v>
       </c>
-      <c r="T72" s="11" t="s">
-        <v>53</v>
+      <c r="T72" s="12" t="s">
+        <v>184</v>
       </c>
       <c r="U72" s="11" t="s">
         <v>32</v>
@@ -7008,7 +7008,7 @@
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46223.1679734375</v>
+        <v>46224.18129432871</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>298</v>
@@ -7055,8 +7055,8 @@
       <c r="S89" s="9">
         <v>0</v>
       </c>
-      <c r="T89" s="12" t="s">
-        <v>184</v>
+      <c r="T89" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U89" s="12" t="s">
         <v>90</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46118.54556859954</v>
+        <v>46224.17531539351</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>300</v>
@@ -7116,8 +7116,8 @@
       <c r="S90" s="6">
         <v>0</v>
       </c>
-      <c r="T90" s="11" t="s">
-        <v>53</v>
+      <c r="T90" s="12" t="s">
+        <v>184</v>
       </c>
       <c r="U90" s="10" t="s">
         <v>54</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -6308,7 +6308,7 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46218.20417449074</v>
+        <v>46225.16765394676</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>265</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="447">
   <si>
     <t>50001525- ZITRON PERU METRO DE LIMA  ESTACION 07</t>
   </si>
@@ -308,6 +308,9 @@
   </si>
   <si>
     <t>propuesta rodete ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
   </si>
   <si>
     <t>nespinoza@zitron.com</t>
@@ -3297,7 +3300,7 @@
         <v>99</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I26" s="5">
         <v>46121</v>
@@ -3321,7 +3324,7 @@
         <v>75</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q26" s="5">
         <v>46121</v>
@@ -3341,7 +3344,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B27" s="8">
         <v>46108.75688663195</v>
@@ -3353,7 +3356,7 @@
         <v>46135.5462021412</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
@@ -3386,7 +3389,7 @@
         <v>46</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q27" s="8">
         <v>46121</v>
@@ -3406,7 +3409,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B28" s="5">
         <v>46108.756897349536</v>
@@ -3416,7 +3419,7 @@
         <v>46223.594457824074</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3425,7 +3428,7 @@
         <v>99</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I28" s="5">
         <v>46191</v>
@@ -3446,10 +3449,10 @@
         <v>88</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q28" s="5">
         <v>46191</v>
@@ -3469,7 +3472,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B29" s="8">
         <v>46108.75690234954</v>
@@ -3481,7 +3484,7 @@
         <v>46123.19348805556</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3514,7 +3517,7 @@
         <v>78</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q29" s="8">
         <v>46121</v>
@@ -3534,7 +3537,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B30" s="5">
         <v>46108.75690841435</v>
@@ -3544,7 +3547,7 @@
         <v>46223.594457175925</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3553,7 +3556,7 @@
         <v>99</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I30" s="5">
         <v>46191</v>
@@ -3574,10 +3577,10 @@
         <v>88</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q30" s="5">
         <v>46191</v>
@@ -3597,7 +3600,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B31" s="8">
         <v>46108.78647824074</v>
@@ -3642,7 +3645,7 @@
         <v>85</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q31" s="8">
         <v>46121</v>
@@ -3662,7 +3665,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B32" s="5">
         <v>46108.756741087964</v>
@@ -3672,7 +3675,7 @@
         <v>46221.115510891206</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>25</v>
@@ -3696,7 +3699,7 @@
         <v>26</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3709,7 +3712,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B33" s="8">
         <v>46108.75695274306</v>
@@ -3719,16 +3722,16 @@
         <v>46182.6933722338</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I33" s="8">
         <v>46125</v>
@@ -3746,13 +3749,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q33" s="8">
         <v>46125</v>
@@ -3772,7 +3775,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B34" s="5">
         <v>46108.75695775463</v>
@@ -3784,16 +3787,16 @@
         <v>46182.69336725694</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I34" s="5">
         <v>46125</v>
@@ -3811,13 +3814,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>95</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q34" s="5">
         <v>45985</v>
@@ -3837,7 +3840,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B35" s="8">
         <v>46108.75696342593</v>
@@ -3847,16 +3850,16 @@
         <v>46182.69337332176</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I35" s="8">
         <v>46127</v>
@@ -3874,13 +3877,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q35" s="8">
         <v>45987</v>
@@ -3900,7 +3903,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B36" s="5">
         <v>46108.75697314815</v>
@@ -3910,16 +3913,16 @@
         <v>46169.854331932875</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I36" s="5">
         <v>46125</v>
@@ -3937,13 +3940,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q36" s="5">
         <v>46125</v>
@@ -3963,7 +3966,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B37" s="8">
         <v>46108.75697796296</v>
@@ -3973,16 +3976,16 @@
         <v>46135.54608165509</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I37" s="8">
         <v>46125</v>
@@ -4000,13 +4003,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q37" s="8">
         <v>45979</v>
@@ -4026,7 +4029,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B38" s="5">
         <v>46108.7569835301</v>
@@ -4036,16 +4039,16 @@
         <v>46111.58202451389</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I38" s="5">
         <v>46134</v>
@@ -4063,13 +4066,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q38" s="5">
         <v>45988</v>
@@ -4087,7 +4090,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B39" s="8">
         <v>46108.75698832176</v>
@@ -4097,16 +4100,16 @@
         <v>46183.16750024306</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I39" s="8">
         <v>46125</v>
@@ -4124,13 +4127,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q39" s="8">
         <v>46125</v>
@@ -4150,7 +4153,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B40" s="5">
         <v>46108.75699311343</v>
@@ -4160,16 +4163,16 @@
         <v>46209.595412939816</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I40" s="5">
         <v>46125</v>
@@ -4187,13 +4190,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>98</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q40" s="5">
         <v>45985</v>
@@ -4213,7 +4216,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B41" s="8">
         <v>46108.75699847222</v>
@@ -4223,16 +4226,16 @@
         <v>46182.1679962037</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I41" s="8">
         <v>46127</v>
@@ -4250,13 +4253,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q41" s="8">
         <v>45987</v>
@@ -4276,7 +4279,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B42" s="5">
         <v>46108.75700357639</v>
@@ -4286,16 +4289,16 @@
         <v>46211.84653167824</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I42" s="5">
         <v>46118</v>
@@ -4313,13 +4316,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q42" s="5">
         <v>46118</v>
@@ -4339,7 +4342,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B43" s="8">
         <v>46108.75700856482</v>
@@ -4351,16 +4354,16 @@
         <v>46182.69343975694</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I43" s="8">
         <v>46118</v>
@@ -4378,13 +4381,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>92</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q43" s="8">
         <v>45978</v>
@@ -4404,7 +4407,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B44" s="5">
         <v>46108.757016435186</v>
@@ -4414,16 +4417,16 @@
         <v>46182.69344646991</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I44" s="5">
         <v>46139</v>
@@ -4441,13 +4444,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q44" s="5">
         <v>45999</v>
@@ -4467,7 +4470,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B45" s="8">
         <v>46108.7570218287</v>
@@ -4479,16 +4482,16 @@
         <v>46211.84652803241</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I45" s="8">
         <v>46139</v>
@@ -4506,13 +4509,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q45" s="8">
         <v>45999</v>
@@ -4532,7 +4535,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B46" s="5">
         <v>46108.75702719907</v>
@@ -4542,16 +4545,16 @@
         <v>46211.173315312495</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I46" s="5">
         <v>46195</v>
@@ -4569,13 +4572,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q46" s="5">
         <v>46195</v>
@@ -4595,7 +4598,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B47" s="8">
         <v>46108.75703201389</v>
@@ -4605,16 +4608,16 @@
         <v>46209.598061192126</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I47" s="8">
         <v>46195</v>
@@ -4632,13 +4635,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q47" s="8">
         <v>45985</v>
@@ -4658,7 +4661,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B48" s="5">
         <v>46108.75703761574</v>
@@ -4668,16 +4671,16 @@
         <v>46210.16869111111</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I48" s="5">
         <v>46202</v>
@@ -4695,13 +4698,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q48" s="5">
         <v>46007</v>
@@ -4721,7 +4724,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B49" s="8">
         <v>46108.75704306713</v>
@@ -4733,16 +4736,16 @@
         <v>46220.16760561343</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I49" s="8">
         <v>46125</v>
@@ -4760,13 +4763,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q49" s="8">
         <v>46125</v>
@@ -4786,7 +4789,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B50" s="5">
         <v>46108.75705032407</v>
@@ -4798,16 +4801,16 @@
         <v>46154.86746811343</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I50" s="5">
         <v>46125</v>
@@ -4825,13 +4828,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4841,7 +4844,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B51" s="8">
         <v>46108.75705728009</v>
@@ -4853,16 +4856,16 @@
         <v>46154.8677641088</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I51" s="8">
         <v>46135</v>
@@ -4880,13 +4883,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4896,7 +4899,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B52" s="5">
         <v>46108.757061435186</v>
@@ -4906,16 +4909,16 @@
         <v>46223.1904159375</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I52" s="5">
         <v>46195</v>
@@ -4933,13 +4936,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q52" s="5">
         <v>46195</v>
@@ -4951,7 +4954,7 @@
         <v>0</v>
       </c>
       <c r="T52" s="12" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="U52" s="12" t="s">
         <v>90</v>
@@ -4959,7 +4962,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B53" s="8">
         <v>46108.75710696759</v>
@@ -4969,16 +4972,16 @@
         <v>46199.168608900465</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I53" s="8">
         <v>46195</v>
@@ -4996,13 +4999,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5018,7 +5021,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B54" s="5">
         <v>46108.757112928244</v>
@@ -5028,16 +5031,16 @@
         <v>46169.85241099537</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I54" s="5">
         <v>46210</v>
@@ -5055,13 +5058,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5071,7 +5074,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B55" s="8">
         <v>46111.50860645833</v>
@@ -5083,16 +5086,16 @@
         <v>46182.69406362269</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I55" s="8">
         <v>46125</v>
@@ -5110,10 +5113,10 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5136,7 +5139,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B56" s="5">
         <v>46111.508755937495</v>
@@ -5148,16 +5151,16 @@
         <v>46182.69350877315</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I56" s="5">
         <v>46125</v>
@@ -5175,13 +5178,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>86</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5191,7 +5194,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B57" s="8">
         <v>46111.508846770834</v>
@@ -5203,16 +5206,16 @@
         <v>46182.69403748843</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I57" s="8">
         <v>46132</v>
@@ -5230,13 +5233,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5246,7 +5249,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B58" s="5">
         <v>46108.75711900463</v>
@@ -5256,7 +5259,7 @@
         <v>46217.85709320602</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -5280,7 +5283,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5295,7 +5298,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B59" s="8">
         <v>46108.75712325232</v>
@@ -5307,16 +5310,16 @@
         <v>46222.09270599537</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="8">
@@ -5332,13 +5335,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q59" s="8">
         <v>46121</v>
@@ -5358,7 +5361,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B60" s="5">
         <v>46114.552579166666</v>
@@ -5370,16 +5373,16 @@
         <v>46211.84604957176</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I60" s="5">
         <v>46121</v>
@@ -5397,13 +5400,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5413,7 +5416,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B61" s="8">
         <v>46114.552773240735</v>
@@ -5425,16 +5428,16 @@
         <v>46211.846055462964</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I61" s="8">
         <v>46121</v>
@@ -5452,13 +5455,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>78</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5468,7 +5471,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B62" s="5">
         <v>46108.75712855324</v>
@@ -5480,16 +5483,16 @@
         <v>46217.857082789356</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I62" s="5">
         <v>46183</v>
@@ -5507,13 +5510,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q62" s="5">
         <v>46183</v>
@@ -5533,7 +5536,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B63" s="8">
         <v>46114.55286452547</v>
@@ -5545,16 +5548,16 @@
         <v>46217.85704695602</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I63" s="8">
         <v>46183</v>
@@ -5572,13 +5575,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q63" s="9"/>
       <c r="R63" s="9"/>
@@ -5588,7 +5591,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B64" s="5">
         <v>46114.552966620366</v>
@@ -5600,16 +5603,16 @@
         <v>46217.85705476852</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I64" s="5">
         <v>46183</v>
@@ -5627,13 +5630,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5643,7 +5646,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B65" s="8">
         <v>46108.75713383102</v>
@@ -5653,16 +5656,16 @@
         <v>46217.857092986116</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I65" s="8">
         <v>46190</v>
@@ -5680,13 +5683,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q65" s="8">
         <v>46190</v>
@@ -5706,7 +5709,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B66" s="5">
         <v>46114.55312298611</v>
@@ -5716,16 +5719,16 @@
         <v>46217.85705168982</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="5">
@@ -5741,10 +5744,10 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5757,7 +5760,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B67" s="8">
         <v>46114.553244675924</v>
@@ -5767,16 +5770,16 @@
         <v>46217.85706487269</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="8">
@@ -5792,10 +5795,10 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>26</v>
@@ -5808,7 +5811,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B68" s="5">
         <v>46108.757138761575</v>
@@ -5818,16 +5821,16 @@
         <v>46114.631384050925</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I68" s="5">
         <v>46281</v>
@@ -5845,10 +5848,10 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5871,7 +5874,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B69" s="8">
         <v>46111.55280189815</v>
@@ -5881,16 +5884,16 @@
         <v>46114.62851033565</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -5906,13 +5909,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5922,7 +5925,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B70" s="5">
         <v>46111.55285245371</v>
@@ -5932,16 +5935,16 @@
         <v>46114.62851040509</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -5957,13 +5960,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5973,7 +5976,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B71" s="8">
         <v>46108.75714166666</v>
@@ -5983,7 +5986,7 @@
         <v>46118.545566597226</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -6007,7 +6010,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -6020,7 +6023,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B72" s="5">
         <v>46108.75714454861</v>
@@ -6030,16 +6033,16 @@
         <v>46224.175318078705</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -6055,13 +6058,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q72" s="5">
         <v>46231</v>
@@ -6073,7 +6076,7 @@
         <v>0</v>
       </c>
       <c r="T72" s="12" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="U72" s="11" t="s">
         <v>32</v>
@@ -6081,7 +6084,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B73" s="8">
         <v>46111.50359008102</v>
@@ -6091,7 +6094,7 @@
         <v>46114.61935158564</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -6115,7 +6118,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -6128,7 +6131,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B74" s="5">
         <v>46111.50404616898</v>
@@ -6138,16 +6141,16 @@
         <v>46213.19769318287</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I74" s="5">
         <v>46211</v>
@@ -6165,13 +6168,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q74" s="5">
         <v>46211</v>
@@ -6191,7 +6194,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B75" s="8">
         <v>46111.50406170139</v>
@@ -6201,16 +6204,16 @@
         <v>46217.17519608796</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I75" s="8">
         <v>46213</v>
@@ -6228,13 +6231,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q75" s="8">
         <v>46213</v>
@@ -6254,7 +6257,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B76" s="5">
         <v>46111.50543856481</v>
@@ -6264,7 +6267,7 @@
         <v>46221.31555423611</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -6288,7 +6291,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -6301,7 +6304,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B77" s="8">
         <v>46111.505495046295</v>
@@ -6311,16 +6314,16 @@
         <v>46225.16765394676</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I77" s="8">
         <v>46217</v>
@@ -6338,13 +6341,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q77" s="8">
         <v>46217</v>
@@ -6356,7 +6359,7 @@
         <v>0</v>
       </c>
       <c r="T77" s="12" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="U77" s="10" t="s">
         <v>54</v>
@@ -6364,7 +6367,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B78" s="5">
         <v>46111.50560314815</v>
@@ -6374,16 +6377,16 @@
         <v>46221.31797234954</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I78" s="5">
         <v>46226</v>
@@ -6401,13 +6404,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q78" s="5">
         <v>46226</v>
@@ -6427,7 +6430,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B79" s="8">
         <v>46111.52633317129</v>
@@ -6437,16 +6440,16 @@
         <v>46114.627016388884</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I79" s="8">
         <v>46226</v>
@@ -6464,13 +6467,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6480,7 +6483,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B80" s="5">
         <v>46111.526644375</v>
@@ -6490,16 +6493,16 @@
         <v>46114.627017175924</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I80" s="5">
         <v>46226</v>
@@ -6517,13 +6520,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6533,7 +6536,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B81" s="8">
         <v>46111.50563458333</v>
@@ -6543,16 +6546,16 @@
         <v>46114.63406568287</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I81" s="8">
         <v>46246</v>
@@ -6570,13 +6573,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q81" s="8">
         <v>46246</v>
@@ -6596,7 +6599,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B82" s="5">
         <v>46111.526916469906</v>
@@ -6606,16 +6609,16 @@
         <v>46114.62715587963</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I82" s="5">
         <v>46246</v>
@@ -6633,13 +6636,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6649,7 +6652,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B83" s="8">
         <v>46111.52699828704</v>
@@ -6659,16 +6662,16 @@
         <v>46114.62715672454</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I83" s="8">
         <v>46246</v>
@@ -6686,13 +6689,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6702,7 +6705,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B84" s="5">
         <v>46108.75714884259</v>
@@ -6712,7 +6715,7 @@
         <v>46221.1155655787</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -6736,7 +6739,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6749,7 +6752,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B85" s="8">
         <v>46108.75715243055</v>
@@ -6759,16 +6762,16 @@
         <v>46185.184959907405</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I85" s="8">
         <v>46183</v>
@@ -6786,13 +6789,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q85" s="8">
         <v>46183</v>
@@ -6812,7 +6815,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B86" s="5">
         <v>46108.75715773148</v>
@@ -6828,10 +6831,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I86" s="5">
         <v>46239</v>
@@ -6849,13 +6852,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q86" s="5">
         <v>46239</v>
@@ -6875,7 +6878,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B87" s="8">
         <v>46108.75716349537</v>
@@ -6885,16 +6888,16 @@
         <v>46111.59762381944</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I87" s="8">
         <v>46246</v>
@@ -6912,13 +6915,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q87" s="8">
         <v>46246</v>
@@ -6938,7 +6941,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B88" s="5">
         <v>46108.75716875</v>
@@ -6948,16 +6951,16 @@
         <v>46111.59782981481</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I88" s="5">
         <v>46273</v>
@@ -6975,13 +6978,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q88" s="5">
         <v>46273</v>
@@ -7001,7 +7004,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B89" s="8">
         <v>46108.75717430556</v>
@@ -7011,16 +7014,16 @@
         <v>46224.18129432871</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I89" s="8">
         <v>46220</v>
@@ -7038,13 +7041,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q89" s="8">
         <v>46220</v>
@@ -7064,7 +7067,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B90" s="5">
         <v>46108.75717877314</v>
@@ -7074,16 +7077,16 @@
         <v>46224.17531539351</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
@@ -7099,13 +7102,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q90" s="5">
         <v>46231</v>
@@ -7117,7 +7120,7 @@
         <v>0</v>
       </c>
       <c r="T90" s="12" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="U90" s="10" t="s">
         <v>54</v>
@@ -7125,7 +7128,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B91" s="8">
         <v>46108.822037094906</v>
@@ -7135,16 +7138,16 @@
         <v>46185.18495945602</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I91" s="8">
         <v>46181</v>
@@ -7162,13 +7165,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q91" s="8">
         <v>46183</v>
@@ -7188,7 +7191,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B92" s="5">
         <v>46108.757183124995</v>
@@ -7198,7 +7201,7 @@
         <v>46221.36615074074</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>25</v>
@@ -7222,7 +7225,7 @@
         <v>26</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>26</v>
@@ -7235,7 +7238,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B93" s="8">
         <v>46108.757186296294</v>
@@ -7245,7 +7248,7 @@
         <v>46223.59523664352</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7254,7 +7257,7 @@
         <v>99</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I93" s="8">
         <v>46248</v>
@@ -7272,13 +7275,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q93" s="8">
         <v>46248</v>
@@ -7298,7 +7301,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B94" s="5">
         <v>46111.52720202546</v>
@@ -7308,7 +7311,7 @@
         <v>46223.59457288195</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7317,7 +7320,7 @@
         <v>99</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I94" s="5">
         <v>46248</v>
@@ -7335,13 +7338,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7351,7 +7354,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B95" s="8">
         <v>46111.52733795139</v>
@@ -7361,7 +7364,7 @@
         <v>46223.594572268514</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7370,7 +7373,7 @@
         <v>99</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I95" s="8">
         <v>46248</v>
@@ -7388,13 +7391,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7404,7 +7407,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B96" s="5">
         <v>46108.75720997685</v>
@@ -7414,7 +7417,7 @@
         <v>46223.595235995366</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7423,7 +7426,7 @@
         <v>99</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I96" s="5">
         <v>46268</v>
@@ -7441,13 +7444,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q96" s="5">
         <v>46268</v>
@@ -7467,7 +7470,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B97" s="8">
         <v>46111.52790079861</v>
@@ -7477,7 +7480,7 @@
         <v>46223.5946628588</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7486,7 +7489,7 @@
         <v>99</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I97" s="8">
         <v>46268</v>
@@ -7504,13 +7507,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7520,7 +7523,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B98" s="5">
         <v>46111.52796104166</v>
@@ -7530,7 +7533,7 @@
         <v>46223.59466224537</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7539,7 +7542,7 @@
         <v>99</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I98" s="5">
         <v>46268</v>
@@ -7557,13 +7560,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7573,7 +7576,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B99" s="8">
         <v>46108.75719767361</v>
@@ -7583,7 +7586,7 @@
         <v>46223.5952353125</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7592,7 +7595,7 @@
         <v>99</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I99" s="8">
         <v>46272</v>
@@ -7610,13 +7613,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q99" s="8">
         <v>46272</v>
@@ -7636,7 +7639,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B100" s="5">
         <v>46111.52756633102</v>
@@ -7646,7 +7649,7 @@
         <v>46223.59474541667</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7655,7 +7658,7 @@
         <v>99</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I100" s="5">
         <v>46272</v>
@@ -7673,13 +7676,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7689,7 +7692,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B101" s="8">
         <v>46111.527622395835</v>
@@ -7699,7 +7702,7 @@
         <v>46223.594744710645</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7708,7 +7711,7 @@
         <v>99</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I101" s="8">
         <v>46272</v>
@@ -7726,13 +7729,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7742,7 +7745,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B102" s="5">
         <v>46108.75720341435</v>
@@ -7752,7 +7755,7 @@
         <v>46223.595234629625</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7761,7 +7764,7 @@
         <v>99</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I102" s="5">
         <v>46274</v>
@@ -7779,13 +7782,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q102" s="5">
         <v>46274</v>
@@ -7805,7 +7808,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B103" s="8">
         <v>46111.52775804398</v>
@@ -7815,7 +7818,7 @@
         <v>46223.594845011576</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7824,7 +7827,7 @@
         <v>99</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I103" s="8">
         <v>46274</v>
@@ -7842,13 +7845,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -7858,7 +7861,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B104" s="5">
         <v>46111.52780829861</v>
@@ -7868,7 +7871,7 @@
         <v>46223.59484435185</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7877,7 +7880,7 @@
         <v>99</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I104" s="5">
         <v>46274</v>
@@ -7895,13 +7898,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7911,7 +7914,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B105" s="8">
         <v>46108.757191412034</v>
@@ -7921,7 +7924,7 @@
         <v>46223.59523400463</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -7930,7 +7933,7 @@
         <v>99</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I105" s="8">
         <v>46276</v>
@@ -7948,13 +7951,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q105" s="8">
         <v>46276</v>
@@ -7974,7 +7977,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B106" s="5">
         <v>46111.527446493055</v>
@@ -7984,7 +7987,7 @@
         <v>46223.594939675924</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7993,7 +7996,7 @@
         <v>99</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I106" s="5">
         <v>46276</v>
@@ -8011,13 +8014,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8027,7 +8030,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B107" s="8">
         <v>46111.52746010417</v>
@@ -8037,7 +8040,7 @@
         <v>46223.59493908565</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -8046,7 +8049,7 @@
         <v>99</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I107" s="8">
         <v>46276</v>
@@ -8064,13 +8067,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -8080,7 +8083,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B108" s="5">
         <v>46108.757217025464</v>
@@ -8090,7 +8093,7 @@
         <v>46223.59523337963</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8099,7 +8102,7 @@
         <v>99</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I108" s="5">
         <v>46280</v>
@@ -8117,13 +8120,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q108" s="5">
         <v>46280</v>
@@ -8143,7 +8146,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B109" s="8">
         <v>46111.528031932874</v>
@@ -8153,7 +8156,7 @@
         <v>46223.59502533565</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8162,7 +8165,7 @@
         <v>99</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I109" s="9"/>
       <c r="J109" s="8">
@@ -8178,13 +8181,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8194,7 +8197,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B110" s="5">
         <v>46111.52811128472</v>
@@ -8204,7 +8207,7 @@
         <v>46223.59502458334</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8213,7 +8216,7 @@
         <v>99</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I110" s="6"/>
       <c r="J110" s="5">
@@ -8229,13 +8232,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8245,7 +8248,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B111" s="8">
         <v>46108.75727585648</v>
@@ -8255,7 +8258,7 @@
         <v>46223.595232754626</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8264,7 +8267,7 @@
         <v>99</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I111" s="9"/>
       <c r="J111" s="8">
@@ -8280,13 +8283,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q111" s="8">
         <v>46286</v>
@@ -8306,7 +8309,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B112" s="5">
         <v>46111.5281812037</v>
@@ -8316,7 +8319,7 @@
         <v>46223.595106875</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8325,7 +8328,7 @@
         <v>99</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
@@ -8341,13 +8344,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8357,7 +8360,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B113" s="8">
         <v>46111.528266423615</v>
@@ -8367,7 +8370,7 @@
         <v>46223.59510622685</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8376,7 +8379,7 @@
         <v>99</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I113" s="9"/>
       <c r="J113" s="8">
@@ -8392,13 +8395,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8408,7 +8411,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B114" s="5">
         <v>46108.757283217594</v>
@@ -8418,7 +8421,7 @@
         <v>46221.10727317129</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>25</v>
@@ -8442,7 +8445,7 @@
         <v>26</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>26</v>
@@ -8455,7 +8458,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B115" s="8">
         <v>46108.757287430555</v>
@@ -8465,16 +8468,16 @@
         <v>46114.63723893519</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I115" s="8">
         <v>46287</v>
@@ -8492,13 +8495,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q115" s="8">
         <v>46287</v>
@@ -8518,7 +8521,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B116" s="5">
         <v>46111.52846596065</v>
@@ -8528,16 +8531,16 @@
         <v>46114.62888387732</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8553,13 +8556,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8569,7 +8572,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B117" s="8">
         <v>46111.528518067134</v>
@@ -8579,16 +8582,16 @@
         <v>46114.62888469908</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="8">
@@ -8604,13 +8607,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8620,7 +8623,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B118" s="5">
         <v>46111.531216006944</v>
@@ -8636,10 +8639,10 @@
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I118" s="6"/>
       <c r="J118" s="5">
@@ -8655,13 +8658,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8671,7 +8674,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B119" s="8">
         <v>46111.53129275463</v>
@@ -8687,10 +8690,10 @@
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I119" s="9"/>
       <c r="J119" s="8">
@@ -8706,13 +8709,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O119" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8722,7 +8725,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B120" s="5">
         <v>46111.53134821759</v>
@@ -8732,16 +8735,16 @@
         <v>46114.628886921295</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
@@ -8757,13 +8760,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8773,7 +8776,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B121" s="8">
         <v>46111.53139942129</v>
@@ -8789,10 +8792,10 @@
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I121" s="9"/>
       <c r="J121" s="8">
@@ -8808,13 +8811,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O121" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8824,7 +8827,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B122" s="5">
         <v>46111.53343819444</v>
@@ -8834,16 +8837,16 @@
         <v>46114.628888437495</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I122" s="6"/>
       <c r="J122" s="5">
@@ -8859,13 +8862,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8875,7 +8878,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B123" s="8">
         <v>46108.75729289352</v>
@@ -8885,7 +8888,7 @@
         <v>46223.59539700231</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -8894,7 +8897,7 @@
         <v>99</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I123" s="8">
         <v>46288</v>
@@ -8912,13 +8915,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q123" s="8">
         <v>46288</v>
@@ -8938,7 +8941,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B124" s="5">
         <v>46111.52857409722</v>
@@ -8948,7 +8951,7 @@
         <v>46223.595359328705</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8957,7 +8960,7 @@
         <v>99</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I124" s="5">
         <v>46288</v>
@@ -8975,13 +8978,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8991,7 +8994,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B125" s="8">
         <v>46111.528674016205</v>
@@ -9001,7 +9004,7 @@
         <v>46223.59535869213</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -9010,7 +9013,7 @@
         <v>99</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I125" s="8">
         <v>46288</v>
@@ -9028,13 +9031,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -9044,7 +9047,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B126" s="5">
         <v>46111.531552291664</v>
@@ -9063,7 +9066,7 @@
         <v>99</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I126" s="5">
         <v>46288</v>
@@ -9081,13 +9084,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9097,7 +9100,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B127" s="8">
         <v>46111.531603344905</v>
@@ -9116,7 +9119,7 @@
         <v>99</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I127" s="8">
         <v>46288</v>
@@ -9134,13 +9137,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O127" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9150,7 +9153,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B128" s="5">
         <v>46111.531648379634</v>
@@ -9160,7 +9163,7 @@
         <v>46223.59535668981</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9169,7 +9172,7 @@
         <v>99</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I128" s="5">
         <v>46288</v>
@@ -9187,13 +9190,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9203,7 +9206,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B129" s="8">
         <v>46111.531705925925</v>
@@ -9222,7 +9225,7 @@
         <v>99</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I129" s="8">
         <v>46288</v>
@@ -9240,13 +9243,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O129" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9256,7 +9259,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B130" s="5">
         <v>46111.533570127314</v>
@@ -9266,7 +9269,7 @@
         <v>46223.59535532407</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9275,7 +9278,7 @@
         <v>99</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I130" s="5">
         <v>46288</v>
@@ -9293,13 +9296,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9309,7 +9312,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B131" s="8">
         <v>46108.75729930555</v>
@@ -9319,16 +9322,16 @@
         <v>46221.36200443287</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I131" s="8">
         <v>46293</v>
@@ -9346,13 +9349,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q131" s="8">
         <v>46293</v>
@@ -9372,7 +9375,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B132" s="5">
         <v>46111.528799872685</v>
@@ -9382,16 +9385,16 @@
         <v>46114.62931347222</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9407,13 +9410,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9423,7 +9426,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B133" s="8">
         <v>46111.52885179398</v>
@@ -9433,16 +9436,16 @@
         <v>46114.62931429398</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I133" s="9"/>
       <c r="J133" s="8">
@@ -9458,13 +9461,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9474,7 +9477,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B134" s="5">
         <v>46111.53215439815</v>
@@ -9490,10 +9493,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9509,13 +9512,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9525,7 +9528,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B135" s="8">
         <v>46111.53220642361</v>
@@ -9541,10 +9544,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I135" s="9"/>
       <c r="J135" s="8">
@@ -9560,13 +9563,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O135" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9576,7 +9579,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B136" s="5">
         <v>46111.532258287036</v>
@@ -9586,16 +9589,16 @@
         <v>46114.629316527775</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9611,13 +9614,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9627,7 +9630,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B137" s="8">
         <v>46111.53231001158</v>
@@ -9643,10 +9646,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I137" s="9"/>
       <c r="J137" s="8">
@@ -9662,13 +9665,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O137" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -9678,7 +9681,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B138" s="5">
         <v>46111.53368237268</v>
@@ -9688,16 +9691,16 @@
         <v>46114.62931805555</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
@@ -9713,13 +9716,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9729,7 +9732,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B139" s="8">
         <v>46108.757304583334</v>
@@ -9739,16 +9742,16 @@
         <v>46221.31842321759</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I139" s="8">
         <v>46294</v>
@@ -9766,13 +9769,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q139" s="8">
         <v>46294</v>
@@ -9792,7 +9795,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B140" s="5">
         <v>46111.528945011574</v>
@@ -9802,16 +9805,16 @@
         <v>46114.830281076385</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I140" s="5">
         <v>46294</v>
@@ -9829,13 +9832,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9845,7 +9848,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B141" s="8">
         <v>46111.52901092592</v>
@@ -9855,16 +9858,16 @@
         <v>46114.830302789356</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I141" s="8">
         <v>46294</v>
@@ -9882,13 +9885,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -9898,7 +9901,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B142" s="5">
         <v>46111.53247278935</v>
@@ -9914,10 +9917,10 @@
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I142" s="5">
         <v>46294</v>
@@ -9935,13 +9938,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9951,7 +9954,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B143" s="8">
         <v>46111.53253350694</v>
@@ -9967,10 +9970,10 @@
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I143" s="8">
         <v>46294</v>
@@ -9988,13 +9991,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O143" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -10004,7 +10007,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B144" s="5">
         <v>46111.532638414355</v>
@@ -10020,10 +10023,10 @@
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I144" s="5">
         <v>46294</v>
@@ -10041,13 +10044,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10057,7 +10060,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B145" s="8">
         <v>46111.53258112269</v>
@@ -10067,16 +10070,16 @@
         <v>46114.83037114583</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I145" s="8">
         <v>46294</v>
@@ -10094,13 +10097,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -10110,7 +10113,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B146" s="5">
         <v>46111.53385627315</v>
@@ -10120,16 +10123,16 @@
         <v>46114.83039427083</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I146" s="5">
         <v>46294</v>
@@ -10147,13 +10150,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10163,7 +10166,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B147" s="8">
         <v>46108.757310497684</v>
@@ -10173,7 +10176,7 @@
         <v>46114.62962797454</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>25</v>
@@ -10197,7 +10200,7 @@
         <v>26</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="P147" s="9" t="s">
         <v>26</v>
@@ -10210,7 +10213,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B148" s="5">
         <v>46108.75731366898</v>
@@ -10220,16 +10223,16 @@
         <v>46114.63764361111</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="I148" s="5">
         <v>46295</v>
@@ -10247,13 +10250,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q148" s="5">
         <v>46295</v>
@@ -10273,7 +10276,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B149" s="8">
         <v>46108.75732001157</v>
@@ -10283,16 +10286,16 @@
         <v>46119.74841528935</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="I149" s="8">
         <v>46295</v>
@@ -10310,13 +10313,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q149" s="8">
         <v>46295</v>
@@ -10336,7 +10339,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B150" s="5">
         <v>46108.7573290625</v>
@@ -10346,7 +10349,7 @@
         <v>46114.62962836806</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>25</v>
@@ -10370,7 +10373,7 @@
         <v>26</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="P150" s="6" t="s">
         <v>26</v>
@@ -10383,7 +10386,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B151" s="8">
         <v>46108.75733305556</v>
@@ -10393,7 +10396,7 @@
         <v>46119.748459016206</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
@@ -10420,13 +10423,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q151" s="8">
         <v>46295</v>
@@ -10446,7 +10449,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B152" s="5">
         <v>46108.757338703705</v>
@@ -10456,7 +10459,7 @@
         <v>46119.748502546296</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10483,13 +10486,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Q152" s="5">
         <v>46304</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -6311,7 +6311,7 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46225.16765394676</v>
+        <v>46226.19708370371</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>266</v>
@@ -6358,8 +6358,8 @@
       <c r="S77" s="9">
         <v>0</v>
       </c>
-      <c r="T77" s="12" t="s">
-        <v>185</v>
+      <c r="T77" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U77" s="10" t="s">
         <v>54</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -3416,7 +3416,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46223.594457824074</v>
+        <v>46227.72252761574</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>106</v>
@@ -3466,8 +3466,8 @@
       <c r="T28" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U28" s="11" t="s">
-        <v>32</v>
+      <c r="U28" s="12" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46223.594457175925</v>
+        <v>46227.722518124996</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>113</v>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46223.1904159375</v>
+        <v>46230.167913576384</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>181</v>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46169.85241099537</v>
+        <v>46227.72251912037</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>189</v>
@@ -5651,9 +5651,11 @@
       <c r="B65" s="8">
         <v>46108.75713383102</v>
       </c>
-      <c r="C65" s="9"/>
+      <c r="C65" s="8">
+        <v>46227.72250047454</v>
+      </c>
       <c r="D65" s="8">
-        <v>46217.857092986116</v>
+        <v>46227.722518622686</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>107</v>
@@ -5698,13 +5700,13 @@
         <v>46190</v>
       </c>
       <c r="S65" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T65" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U65" s="12" t="s">
-        <v>90</v>
+      <c r="U65" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -6437,7 +6439,7 @@
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46114.627016388884</v>
+        <v>46227.72250855324</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>211</v>
@@ -6490,7 +6492,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46114.627017175924</v>
+        <v>46227.72250912037</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>216</v>
@@ -6606,7 +6608,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46114.62715587963</v>
+        <v>46227.7225096412</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>211</v>
@@ -6659,7 +6661,7 @@
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46114.62715672454</v>
+        <v>46227.722510057865</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>216</v>
@@ -7477,7 +7479,7 @@
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46223.5946628588</v>
+        <v>46227.72251041667</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>211</v>
@@ -7530,7 +7532,7 @@
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46223.59466224537</v>
+        <v>46227.72251091435</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>216</v>
@@ -7646,7 +7648,7 @@
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46223.59474541667</v>
+        <v>46227.72251393519</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>211</v>
@@ -7699,7 +7701,7 @@
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46223.594744710645</v>
+        <v>46227.72251137732</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>216</v>
@@ -7815,7 +7817,7 @@
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46223.594845011576</v>
+        <v>46227.722512928245</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>211</v>
@@ -7868,7 +7870,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46223.59484435185</v>
+        <v>46227.72251365741</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>216</v>
@@ -7984,7 +7986,7 @@
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46223.594939675924</v>
+        <v>46227.722511921296</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>211</v>
@@ -8037,7 +8039,7 @@
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46223.59493908565</v>
+        <v>46227.72251247685</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>216</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -415,6 +415,9 @@
     <t>Generación OC Tableros,Fabricación Tablero</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1213833763273348</t>
   </si>
   <si>
@@ -566,9 +569,6 @@
   </si>
   <si>
     <t xml:space="preserve"> Generacion OC Fabricacion Externa ot 4287 - 4288,Fabricacion estructura proveedor externo ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213833564667630</t>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.854331932875</v>
+        <v>46231.2083012963</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>132</v>
@@ -3957,8 +3957,8 @@
       <c r="S36" s="6">
         <v>0</v>
       </c>
-      <c r="T36" s="11" t="s">
-        <v>53</v>
+      <c r="T36" s="12" t="s">
+        <v>134</v>
       </c>
       <c r="U36" s="10" t="s">
         <v>54</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B37" s="8">
         <v>46108.75697796296</v>
@@ -3976,7 +3976,7 @@
         <v>46135.54608165509</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
@@ -4009,7 +4009,7 @@
         <v>103</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q37" s="8">
         <v>45979</v>
@@ -4029,7 +4029,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B38" s="5">
         <v>46108.7569835301</v>
@@ -4039,7 +4039,7 @@
         <v>46111.58202451389</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -4069,10 +4069,10 @@
         <v>132</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q38" s="5">
         <v>45988</v>
@@ -4090,7 +4090,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B39" s="8">
         <v>46108.75698832176</v>
@@ -4100,7 +4100,7 @@
         <v>46183.16750024306</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
@@ -4130,7 +4130,7 @@
         <v>118</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>118</v>
@@ -4153,7 +4153,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B40" s="5">
         <v>46108.75699311343</v>
@@ -4163,7 +4163,7 @@
         <v>46209.595412939816</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
@@ -4190,13 +4190,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>98</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q40" s="5">
         <v>45985</v>
@@ -4216,7 +4216,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B41" s="8">
         <v>46108.75699847222</v>
@@ -4226,7 +4226,7 @@
         <v>46182.1679962037</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
@@ -4253,13 +4253,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q41" s="8">
         <v>45987</v>
@@ -4279,7 +4279,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B42" s="5">
         <v>46108.75700357639</v>
@@ -4289,7 +4289,7 @@
         <v>46211.84653167824</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
@@ -4319,7 +4319,7 @@
         <v>118</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>118</v>
@@ -4342,7 +4342,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B43" s="8">
         <v>46108.75700856482</v>
@@ -4354,7 +4354,7 @@
         <v>46182.69343975694</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
@@ -4381,13 +4381,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>92</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q43" s="8">
         <v>45978</v>
@@ -4407,7 +4407,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B44" s="5">
         <v>46108.757016435186</v>
@@ -4417,7 +4417,7 @@
         <v>46182.69344646991</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
@@ -4444,13 +4444,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q44" s="5">
         <v>45999</v>
@@ -4470,7 +4470,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B45" s="8">
         <v>46108.7570218287</v>
@@ -4482,7 +4482,7 @@
         <v>46211.84652803241</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
@@ -4509,13 +4509,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q45" s="8">
         <v>45999</v>
@@ -4535,7 +4535,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B46" s="5">
         <v>46108.75702719907</v>
@@ -4545,16 +4545,16 @@
         <v>46211.173315312495</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I46" s="5">
         <v>46195</v>
@@ -4575,7 +4575,7 @@
         <v>118</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>118</v>
@@ -4598,7 +4598,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B47" s="8">
         <v>46108.75703201389</v>
@@ -4614,10 +4614,10 @@
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I47" s="8">
         <v>46195</v>
@@ -4635,13 +4635,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>106</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q47" s="8">
         <v>45985</v>
@@ -4661,7 +4661,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B48" s="5">
         <v>46108.75703761574</v>
@@ -4671,16 +4671,16 @@
         <v>46210.16869111111</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I48" s="5">
         <v>46202</v>
@@ -4698,13 +4698,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>108</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q48" s="5">
         <v>46007</v>
@@ -4724,7 +4724,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B49" s="8">
         <v>46108.75704306713</v>
@@ -4736,16 +4736,16 @@
         <v>46220.16760561343</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I49" s="8">
         <v>46125</v>
@@ -4766,7 +4766,7 @@
         <v>118</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>118</v>
@@ -4789,7 +4789,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B50" s="5">
         <v>46108.75705032407</v>
@@ -4801,16 +4801,16 @@
         <v>46154.86746811343</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I50" s="5">
         <v>46125</v>
@@ -4828,13 +4828,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>110</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4844,7 +4844,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B51" s="8">
         <v>46108.75705728009</v>
@@ -4856,16 +4856,16 @@
         <v>46154.8677641088</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I51" s="8">
         <v>46135</v>
@@ -4883,13 +4883,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4899,26 +4899,26 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B52" s="5">
         <v>46108.757061435186</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46230.167913576384</v>
+        <v>46231.17690494213</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I52" s="5">
         <v>46195</v>
@@ -4939,7 +4939,7 @@
         <v>118</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>118</v>
@@ -4953,8 +4953,8 @@
       <c r="S52" s="6">
         <v>0</v>
       </c>
-      <c r="T52" s="12" t="s">
-        <v>185</v>
+      <c r="T52" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U52" s="12" t="s">
         <v>90</v>
@@ -4978,10 +4978,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I53" s="8">
         <v>46195</v>
@@ -4999,7 +4999,7 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>113</v>
@@ -5037,10 +5037,10 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I54" s="5">
         <v>46210</v>
@@ -5058,7 +5058,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>190</v>
@@ -6078,7 +6078,7 @@
         <v>0</v>
       </c>
       <c r="T72" s="12" t="s">
-        <v>185</v>
+        <v>134</v>
       </c>
       <c r="U72" s="11" t="s">
         <v>32</v>
@@ -6173,7 +6173,7 @@
         <v>252</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>258</v>
@@ -6794,7 +6794,7 @@
         <v>286</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>290</v>
@@ -6857,7 +6857,7 @@
         <v>286</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>292</v>
@@ -6983,7 +6983,7 @@
         <v>286</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>290</v>
@@ -7046,7 +7046,7 @@
         <v>286</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P89" s="9" t="s">
         <v>220</v>
@@ -7122,7 +7122,7 @@
         <v>0</v>
       </c>
       <c r="T90" s="12" t="s">
-        <v>185</v>
+        <v>134</v>
       </c>
       <c r="U90" s="10" t="s">
         <v>54</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -6032,7 +6032,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46224.175318078705</v>
+        <v>46232.19038798611</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>246</v>
@@ -6077,8 +6077,8 @@
       <c r="S72" s="6">
         <v>0</v>
       </c>
-      <c r="T72" s="12" t="s">
-        <v>134</v>
+      <c r="T72" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U72" s="11" t="s">
         <v>32</v>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46224.17531539351</v>
+        <v>46232.1903880787</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>301</v>
@@ -7121,8 +7121,8 @@
       <c r="S90" s="6">
         <v>0</v>
       </c>
-      <c r="T90" s="12" t="s">
-        <v>134</v>
+      <c r="T90" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U90" s="10" t="s">
         <v>54</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -6824,7 +6824,7 @@
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46118.55225699074</v>
+        <v>46233.20378162037</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>57</v>
@@ -6871,8 +6871,8 @@
       <c r="S86" s="6">
         <v>0</v>
       </c>
-      <c r="T86" s="11" t="s">
-        <v>53</v>
+      <c r="T86" s="12" t="s">
+        <v>134</v>
       </c>
       <c r="U86" s="10" t="s">
         <v>54</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -5480,7 +5480,7 @@
         <v>46217.857069363425</v>
       </c>
       <c r="D62" s="5">
-        <v>46217.857082789356</v>
+        <v>46236.273657928235</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>219</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -3416,7 +3416,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46227.72252761574</v>
+        <v>46237.53668097222</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>106</v>
@@ -3466,8 +3466,8 @@
       <c r="T28" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U28" s="12" t="s">
-        <v>90</v>
+      <c r="U28" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46227.722518124996</v>
+        <v>46237.536746666665</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>113</v>
@@ -3594,8 +3594,8 @@
       <c r="T30" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U30" s="12" t="s">
-        <v>90</v>
+      <c r="U30" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -388,6 +388,9 @@
     <t>Generación OC Alabe ot 4287 - 4288,Fabricación Alabe ot 4287 - 4288</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1213833777465555</t>
   </si>
   <si>
@@ -413,9 +416,6 @@
   </si>
   <si>
     <t>Generación OC Tableros,Fabricación Tablero</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213833763273348</t>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="8">
-        <v>46182.6933722338</v>
+        <v>46238.20722586806</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>121</v>
@@ -3766,8 +3766,8 @@
       <c r="S33" s="9">
         <v>0</v>
       </c>
-      <c r="T33" s="11" t="s">
-        <v>53</v>
+      <c r="T33" s="12" t="s">
+        <v>125</v>
       </c>
       <c r="U33" s="10" t="s">
         <v>54</v>
@@ -3775,7 +3775,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B34" s="5">
         <v>46108.75695775463</v>
@@ -3787,7 +3787,7 @@
         <v>46182.69336725694</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3820,7 +3820,7 @@
         <v>95</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q34" s="5">
         <v>45985</v>
@@ -3840,7 +3840,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B35" s="8">
         <v>46108.75696342593</v>
@@ -3850,7 +3850,7 @@
         <v>46182.69337332176</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
@@ -3880,10 +3880,10 @@
         <v>121</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q35" s="8">
         <v>45987</v>
@@ -3903,17 +3903,17 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B36" s="5">
         <v>46108.75697314815</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46231.2083012963</v>
+        <v>46238.16767181713</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3943,7 +3943,7 @@
         <v>118</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>118</v>
@@ -3958,7 +3958,7 @@
         <v>0</v>
       </c>
       <c r="T36" s="12" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="U36" s="10" t="s">
         <v>54</v>
@@ -4003,7 +4003,7 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>103</v>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46111.58202451389</v>
+        <v>46238.16766954861</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>139</v>
@@ -4066,7 +4066,7 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>136</v>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46227.72251912037</v>
+        <v>46238.167673738426</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>189</v>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46221.31797234954</v>
+        <v>46238.207226134255</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>271</v>
@@ -6423,8 +6423,8 @@
       <c r="S78" s="6">
         <v>0</v>
       </c>
-      <c r="T78" s="11" t="s">
-        <v>53</v>
+      <c r="T78" s="12" t="s">
+        <v>125</v>
       </c>
       <c r="U78" s="10" t="s">
         <v>54</v>
@@ -6872,7 +6872,7 @@
         <v>0</v>
       </c>
       <c r="T86" s="12" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="U86" s="10" t="s">
         <v>54</v>
@@ -6920,7 +6920,7 @@
         <v>286</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>295</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -3910,7 +3910,7 @@
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46238.16767181713</v>
+        <v>46239.19366604167</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>133</v>
@@ -3957,8 +3957,8 @@
       <c r="S36" s="6">
         <v>0</v>
       </c>
-      <c r="T36" s="12" t="s">
-        <v>125</v>
+      <c r="T36" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U36" s="10" t="s">
         <v>54</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -172,232 +172,232 @@
     <t>OT 4290 - TABLERO VDF ABB ACS880-17,OT 4291- TABLERO PLC,OT 4292- TABLERO BOTONERA ,OT 4293-COMPONENTES TABLERO COMPUERTAS</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1213869987281845</t>
+  </si>
+  <si>
+    <t>OT 4290 - TABLERO VDF ABB ACS880-17</t>
+  </si>
+  <si>
+    <t>Recepcion Tableros y componentes electricos</t>
+  </si>
+  <si>
+    <t>Revisión tableros pruebas,OT 4290 - TABLERO VDF ABB ACS880-17</t>
+  </si>
+  <si>
+    <t>1213869987281846</t>
+  </si>
+  <si>
+    <t>OT 4291- TABLERO PLC</t>
+  </si>
+  <si>
+    <t>Revisión tableros pruebas,OT 4291- TABLERO PLC</t>
+  </si>
+  <si>
+    <t>1213869987281847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4292- TABLERO BOTONERA </t>
+  </si>
+  <si>
+    <t>Revisión tableros pruebas,OT 4292- TABLERO BOTONERA</t>
+  </si>
+  <si>
+    <t>1213869987281848</t>
+  </si>
+  <si>
+    <t>OT 4293-COMPONENTES TABLERO COMPUERTAS</t>
+  </si>
+  <si>
+    <t>Revisión tableros pruebas,OT 4293-COMPONENTES TABLERO COMPUERTAS</t>
+  </si>
+  <si>
+    <t>1213832650589320</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:</t>
+  </si>
+  <si>
+    <t>Ingenieria Basica Motor,Ingenieria basica nucleo Rodete,Ingenieria Detalle,Analisis de costeo</t>
+  </si>
+  <si>
+    <t>1213833564662500</t>
+  </si>
+  <si>
+    <t>Ingenieria Basica Motor</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,Analisis de costeo,propuesta motor</t>
+  </si>
+  <si>
+    <t>1213833564662798</t>
+  </si>
+  <si>
+    <t>Ingenieria basica nucleo Rodete</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,Analisis de costeo,propuesta rodete ot 4287 - 4288,propuesta alabes</t>
+  </si>
+  <si>
+    <t>1213833763251389</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Ingenieria Jefe de proyecto:,Analisis de costeo,Propuesta Sensores,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>1213833763253606</t>
+  </si>
+  <si>
+    <t>Analisis de costeo</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica nucleo Rodete</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,Costos</t>
+  </si>
+  <si>
+    <t>1213832650589385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingenieria Atenuador </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta Atenuadores </t>
+  </si>
+  <si>
+    <t>1213832650589322</t>
+  </si>
+  <si>
+    <t>Propuesta compras:</t>
+  </si>
+  <si>
+    <t>propuesta tableros,propuesta alabes,propuesta tableros,propuesta motor,propuesta alabes,propuesta rodete ot 4287 - 4288,Propuesta Sensores</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1213833777465803</t>
+  </si>
+  <si>
+    <t>propuesta motor</t>
+  </si>
+  <si>
+    <t>Generación OC motor ot 4287 - 4288,Propuesta compras:</t>
+  </si>
+  <si>
+    <t>1213833777465824</t>
+  </si>
+  <si>
+    <t>propuesta alabes</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Alabe ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>1213833777466969</t>
+  </si>
+  <si>
+    <t>propuesta rodete ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete ot 4287 - 4288,Propuesta compras:</t>
+  </si>
+  <si>
+    <t>1213833564668775</t>
+  </si>
+  <si>
+    <t>propuesta tableros</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Tableros</t>
+  </si>
+  <si>
+    <t>1213833564668796</t>
+  </si>
+  <si>
+    <t>propuesta compras a codigo // aprovisionamiento ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>Check Planos</t>
+  </si>
+  <si>
+    <t>Generación OC materiales ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>1213833777470493</t>
+  </si>
+  <si>
+    <t>Propuesta Sensores</t>
+  </si>
+  <si>
+    <t>Generacion OC Sensor,Propuesta compras:</t>
+  </si>
+  <si>
+    <t>1213833777472673</t>
+  </si>
+  <si>
+    <t>Propuesta Fabricacion Externa ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Generacion OC Fabricacion Externa ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>1213832650589382</t>
+  </si>
+  <si>
+    <t>Generacion oc Atenuador  ot 4289,Atenuador ot 4289</t>
+  </si>
+  <si>
+    <t>1213832650589324</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Motor ot 4287 - 4288,Rodete ot 4287 - 4288,Tablero y componentes electricos  ot 4290 - 4291 -4292 ,Sensores,Alabe ot 4287 - 4288,Materiales a codigo // compras locales aprovisionamientomiento: ot 4287 - 4288,Fabricacion Externa ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>1213833777465539</t>
+  </si>
+  <si>
+    <t>Alabe ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe ot 4287 - 4288,Fabricación Alabe ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>1213833777465555</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>Alabe ot 4287 - 4288,Fabricación Alabe ot 4287 - 4288</t>
+  </si>
+  <si>
     <t>Baja</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1213869987281845</t>
-  </si>
-  <si>
-    <t>OT 4290 - TABLERO VDF ABB ACS880-17</t>
-  </si>
-  <si>
-    <t>Recepcion Tableros y componentes electricos</t>
-  </si>
-  <si>
-    <t>Revisión tableros pruebas,OT 4290 - TABLERO VDF ABB ACS880-17</t>
-  </si>
-  <si>
-    <t>1213869987281846</t>
-  </si>
-  <si>
-    <t>OT 4291- TABLERO PLC</t>
-  </si>
-  <si>
-    <t>Revisión tableros pruebas,OT 4291- TABLERO PLC</t>
-  </si>
-  <si>
-    <t>1213869987281847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4292- TABLERO BOTONERA </t>
-  </si>
-  <si>
-    <t>Revisión tableros pruebas,OT 4292- TABLERO BOTONERA</t>
-  </si>
-  <si>
-    <t>1213869987281848</t>
-  </si>
-  <si>
-    <t>OT 4293-COMPONENTES TABLERO COMPUERTAS</t>
-  </si>
-  <si>
-    <t>Revisión tableros pruebas,OT 4293-COMPONENTES TABLERO COMPUERTAS</t>
-  </si>
-  <si>
-    <t>1213832650589320</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:</t>
-  </si>
-  <si>
-    <t>Ingenieria Basica Motor,Ingenieria basica nucleo Rodete,Ingenieria Detalle,Analisis de costeo</t>
-  </si>
-  <si>
-    <t>1213833564662500</t>
-  </si>
-  <si>
-    <t>Ingenieria Basica Motor</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Analisis de costeo,propuesta motor</t>
-  </si>
-  <si>
-    <t>1213833564662798</t>
-  </si>
-  <si>
-    <t>Ingenieria basica nucleo Rodete</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Analisis de costeo,propuesta rodete ot 4287 - 4288,propuesta alabes</t>
-  </si>
-  <si>
-    <t>1213833763251389</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Ingenieria Jefe de proyecto:,Analisis de costeo,Propuesta Sensores,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>1213833763253606</t>
-  </si>
-  <si>
-    <t>Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica nucleo Rodete</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Costos</t>
-  </si>
-  <si>
-    <t>1213832650589385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingenieria Atenuador </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta Atenuadores </t>
-  </si>
-  <si>
-    <t>1213832650589322</t>
-  </si>
-  <si>
-    <t>Propuesta compras:</t>
-  </si>
-  <si>
-    <t>propuesta tableros,propuesta alabes,propuesta tableros,propuesta motor,propuesta alabes,propuesta rodete ot 4287 - 4288,Propuesta Sensores</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1213833777465803</t>
-  </si>
-  <si>
-    <t>propuesta motor</t>
-  </si>
-  <si>
-    <t>Generación OC motor ot 4287 - 4288,Propuesta compras:</t>
-  </si>
-  <si>
-    <t>1213833777465824</t>
-  </si>
-  <si>
-    <t>propuesta alabes</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Alabe ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>1213833777466969</t>
-  </si>
-  <si>
-    <t>propuesta rodete ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>NATALYA ESPINOZA</t>
-  </si>
-  <si>
-    <t>nespinoza@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete ot 4287 - 4288,Propuesta compras:</t>
-  </si>
-  <si>
-    <t>1213833564668775</t>
-  </si>
-  <si>
-    <t>propuesta tableros</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Tableros</t>
-  </si>
-  <si>
-    <t>1213833564668796</t>
-  </si>
-  <si>
-    <t>propuesta compras a codigo // aprovisionamiento ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>Check Planos</t>
-  </si>
-  <si>
-    <t>Generación OC materiales ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>1213833777470493</t>
-  </si>
-  <si>
-    <t>Propuesta Sensores</t>
-  </si>
-  <si>
-    <t>Generacion OC Sensor,Propuesta compras:</t>
-  </si>
-  <si>
-    <t>1213833777472673</t>
-  </si>
-  <si>
-    <t>Propuesta Fabricacion Externa ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Generacion OC Fabricacion Externa ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>1213832650589382</t>
-  </si>
-  <si>
-    <t>Generacion oc Atenuador  ot 4289,Atenuador ot 4289</t>
-  </si>
-  <si>
-    <t>1213832650589324</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Motor ot 4287 - 4288,Rodete ot 4287 - 4288,Tablero y componentes electricos  ot 4290 - 4291 -4292 ,Sensores,Alabe ot 4287 - 4288,Materiales a codigo // compras locales aprovisionamientomiento: ot 4287 - 4288,Fabricacion Externa ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>1213833777465539</t>
-  </si>
-  <si>
-    <t>Alabe ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe ot 4287 - 4288,Fabricación Alabe ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>Media</t>
-  </si>
-  <si>
-    <t>1213833777465555</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>Alabe ot 4287 - 4288,Fabricación Alabe ot 4287 - 4288</t>
   </si>
   <si>
     <t>1213833806756992</t>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46111.57919192129</v>
+        <v>46240.18483663195</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -2505,7 +2505,7 @@
       <c r="S12" s="6">
         <v>0</v>
       </c>
-      <c r="T12" s="11" t="s">
+      <c r="T12" s="12" t="s">
         <v>53</v>
       </c>
       <c r="U12" s="10" t="s">
@@ -3767,7 +3767,7 @@
         <v>0</v>
       </c>
       <c r="T33" s="12" t="s">
-        <v>125</v>
+        <v>53</v>
       </c>
       <c r="U33" s="10" t="s">
         <v>54</v>
@@ -3775,7 +3775,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B34" s="5">
         <v>46108.75695775463</v>
@@ -3787,7 +3787,7 @@
         <v>46182.69336725694</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3820,7 +3820,7 @@
         <v>95</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q34" s="5">
         <v>45985</v>
@@ -3832,7 +3832,7 @@
         <v>0</v>
       </c>
       <c r="T34" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U34" s="10" t="s">
         <v>54</v>
@@ -3880,7 +3880,7 @@
         <v>121</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="P35" s="9" t="s">
         <v>131</v>
@@ -3895,7 +3895,7 @@
         <v>0</v>
       </c>
       <c r="T35" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U35" s="10" t="s">
         <v>54</v>
@@ -4021,7 +4021,7 @@
         <v>0</v>
       </c>
       <c r="T37" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U37" s="10" t="s">
         <v>54</v>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="S38" s="6"/>
       <c r="T38" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U38" s="10" t="s">
         <v>54</v>
@@ -4208,7 +4208,7 @@
         <v>0</v>
       </c>
       <c r="T40" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U40" s="10" t="s">
         <v>54</v>
@@ -4271,7 +4271,7 @@
         <v>0</v>
       </c>
       <c r="T41" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U41" s="10" t="s">
         <v>54</v>
@@ -4334,7 +4334,7 @@
         <v>0</v>
       </c>
       <c r="T42" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U42" s="10" t="s">
         <v>54</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="T43" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U43" s="10" t="s">
         <v>54</v>
@@ -4462,7 +4462,7 @@
         <v>0</v>
       </c>
       <c r="T44" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U44" s="10" t="s">
         <v>54</v>
@@ -4527,7 +4527,7 @@
         <v>0</v>
       </c>
       <c r="T45" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U45" s="10" t="s">
         <v>54</v>
@@ -4653,7 +4653,7 @@
         <v>0</v>
       </c>
       <c r="T47" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U47" s="10" t="s">
         <v>54</v>
@@ -4716,7 +4716,7 @@
         <v>0</v>
       </c>
       <c r="T48" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U48" s="10" t="s">
         <v>54</v>
@@ -5013,7 +5013,7 @@
         <v>0</v>
       </c>
       <c r="T53" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U53" s="10" t="s">
         <v>54</v>
@@ -5868,7 +5868,7 @@
         <v>0</v>
       </c>
       <c r="T68" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U68" s="10" t="s">
         <v>54</v>
@@ -6032,7 +6032,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46232.19038798611</v>
+        <v>46240.16751462963</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>246</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="T78" s="12" t="s">
-        <v>125</v>
+        <v>53</v>
       </c>
       <c r="U78" s="10" t="s">
         <v>54</v>
@@ -6545,7 +6545,7 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46114.63406568287</v>
+        <v>46240.18483673611</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>278</v>
@@ -6592,7 +6592,7 @@
       <c r="S81" s="9">
         <v>0</v>
       </c>
-      <c r="T81" s="11" t="s">
+      <c r="T81" s="12" t="s">
         <v>53</v>
       </c>
       <c r="U81" s="10" t="s">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46233.20378162037</v>
+        <v>46240.16751622685</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>57</v>
@@ -6872,7 +6872,7 @@
         <v>0</v>
       </c>
       <c r="T86" s="12" t="s">
-        <v>125</v>
+        <v>53</v>
       </c>
       <c r="U86" s="10" t="s">
         <v>54</v>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46111.59762381944</v>
+        <v>46240.18483702546</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>294</v>
@@ -6934,7 +6934,7 @@
       <c r="S87" s="9">
         <v>0</v>
       </c>
-      <c r="T87" s="11" t="s">
+      <c r="T87" s="12" t="s">
         <v>53</v>
       </c>
       <c r="U87" s="10" t="s">
@@ -6998,7 +6998,7 @@
         <v>0</v>
       </c>
       <c r="T88" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U88" s="10" t="s">
         <v>54</v>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46232.1903880787</v>
+        <v>46240.16751195602</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>301</v>
@@ -7295,7 +7295,7 @@
         <v>0</v>
       </c>
       <c r="T93" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U93" s="10" t="s">
         <v>54</v>
@@ -7464,7 +7464,7 @@
         <v>0</v>
       </c>
       <c r="T96" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U96" s="10" t="s">
         <v>54</v>
@@ -7633,7 +7633,7 @@
         <v>0</v>
       </c>
       <c r="T99" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U99" s="10" t="s">
         <v>54</v>
@@ -7802,7 +7802,7 @@
         <v>0</v>
       </c>
       <c r="T102" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U102" s="10" t="s">
         <v>54</v>
@@ -7971,7 +7971,7 @@
         <v>0</v>
       </c>
       <c r="T105" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U105" s="10" t="s">
         <v>54</v>
@@ -8140,7 +8140,7 @@
         <v>0</v>
       </c>
       <c r="T108" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U108" s="10" t="s">
         <v>54</v>
@@ -8303,7 +8303,7 @@
         <v>0</v>
       </c>
       <c r="T111" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U111" s="10" t="s">
         <v>54</v>
@@ -8515,7 +8515,7 @@
         <v>0</v>
       </c>
       <c r="T115" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U115" s="10" t="s">
         <v>54</v>
@@ -8935,7 +8935,7 @@
         <v>0</v>
       </c>
       <c r="T123" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U123" s="10" t="s">
         <v>54</v>
@@ -9369,7 +9369,7 @@
         <v>0</v>
       </c>
       <c r="T131" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U131" s="10" t="s">
         <v>54</v>
@@ -9789,7 +9789,7 @@
         <v>0</v>
       </c>
       <c r="T139" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U139" s="10" t="s">
         <v>54</v>
@@ -10270,7 +10270,7 @@
         <v>0</v>
       </c>
       <c r="T148" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U148" s="10" t="s">
         <v>54</v>
@@ -10333,7 +10333,7 @@
         <v>0</v>
       </c>
       <c r="T149" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U149" s="10" t="s">
         <v>54</v>
@@ -10443,7 +10443,7 @@
         <v>0</v>
       </c>
       <c r="T151" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U151" s="10" t="s">
         <v>54</v>
@@ -10506,7 +10506,7 @@
         <v>0</v>
       </c>
       <c r="T152" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U152" s="10" t="s">
         <v>54</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="439">
   <si>
     <t>50001525- ZITRON PERU METRO DE LIMA  ESTACION 07</t>
   </si>
@@ -1273,7 +1273,7 @@
     <t>Despacho</t>
   </si>
   <si>
-    <t>Logistica:,Costos,Instalación Componentes,Gestion</t>
+    <t>Logistica:,Costos,Gestion</t>
   </si>
   <si>
     <t>1213869987281842</t>
@@ -1328,30 +1328,6 @@
   </si>
   <si>
     <t>Despacho,Analisis de costeo</t>
-  </si>
-  <si>
-    <t>1213833777528838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puesta en marcha </t>
-  </si>
-  <si>
-    <t>Pruebas instalacion componentes,Instalación Componentes</t>
-  </si>
-  <si>
-    <t>1213833777529979</t>
-  </si>
-  <si>
-    <t>Instalación Componentes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pruebas instalacion componentes,Puesta en marcha </t>
-  </si>
-  <si>
-    <t>1213833622894183</t>
-  </si>
-  <si>
-    <t>Pruebas instalacion componentes</t>
   </si>
 </sst>
 </file>
@@ -1875,7 +1851,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U152"/>
+  <dimension ref="A1:U149"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -9741,7 +9717,7 @@
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46221.31842321759</v>
+        <v>46240.71896241898</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>419</v>
@@ -10336,179 +10312,6 @@
         <v>128</v>
       </c>
       <c r="U149" s="10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="150" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A150" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="B150" s="5">
-        <v>46108.7573290625</v>
-      </c>
-      <c r="C150" s="6"/>
-      <c r="D150" s="5">
-        <v>46114.62962836806</v>
-      </c>
-      <c r="E150" s="6" t="s">
-        <v>440</v>
-      </c>
-      <c r="F150" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G150" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H150" s="6"/>
-      <c r="I150" s="6"/>
-      <c r="J150" s="6"/>
-      <c r="K150" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L150" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M150" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="N150" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O150" s="6" t="s">
-        <v>441</v>
-      </c>
-      <c r="P150" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q150" s="6"/>
-      <c r="R150" s="6"/>
-      <c r="S150" s="6"/>
-      <c r="T150" s="6"/>
-      <c r="U150" s="6"/>
-    </row>
-    <row r="151" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A151" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="B151" s="8">
-        <v>46108.75733305556</v>
-      </c>
-      <c r="C151" s="9"/>
-      <c r="D151" s="8">
-        <v>46119.748459016206</v>
-      </c>
-      <c r="E151" s="9" t="s">
-        <v>443</v>
-      </c>
-      <c r="F151" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G151" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H151" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="I151" s="8">
-        <v>46295</v>
-      </c>
-      <c r="J151" s="8">
-        <v>46303</v>
-      </c>
-      <c r="K151" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L151" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M151" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N151" s="9" t="s">
-        <v>440</v>
-      </c>
-      <c r="O151" s="9" t="s">
-        <v>419</v>
-      </c>
-      <c r="P151" s="9" t="s">
-        <v>444</v>
-      </c>
-      <c r="Q151" s="8">
-        <v>46295</v>
-      </c>
-      <c r="R151" s="8">
-        <v>46303</v>
-      </c>
-      <c r="S151" s="9">
-        <v>0</v>
-      </c>
-      <c r="T151" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="U151" s="10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="152" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A152" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="B152" s="5">
-        <v>46108.757338703705</v>
-      </c>
-      <c r="C152" s="6"/>
-      <c r="D152" s="5">
-        <v>46119.748502546296</v>
-      </c>
-      <c r="E152" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="F152" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G152" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="H152" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="I152" s="5">
-        <v>46304</v>
-      </c>
-      <c r="J152" s="5">
-        <v>46314</v>
-      </c>
-      <c r="K152" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L152" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M152" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N152" s="6" t="s">
-        <v>440</v>
-      </c>
-      <c r="O152" s="6" t="s">
-        <v>443</v>
-      </c>
-      <c r="P152" s="6" t="s">
-        <v>440</v>
-      </c>
-      <c r="Q152" s="5">
-        <v>46304</v>
-      </c>
-      <c r="R152" s="5">
-        <v>46314</v>
-      </c>
-      <c r="S152" s="6">
-        <v>0</v>
-      </c>
-      <c r="T152" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="U152" s="10" t="s">
         <v>54</v>
       </c>
     </row>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -6800,7 +6800,7 @@
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46240.16751622685</v>
+        <v>46241.20565452546</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>57</v>
@@ -6847,8 +6847,8 @@
       <c r="S86" s="6">
         <v>0</v>
       </c>
-      <c r="T86" s="12" t="s">
-        <v>53</v>
+      <c r="T86" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U86" s="10" t="s">
         <v>54</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -8068,7 +8068,7 @@
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46223.59523337963</v>
+        <v>46244.72987326389</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>348</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -3695,7 +3695,7 @@
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="8">
-        <v>46238.20722586806</v>
+        <v>46245.16740877315</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>121</v>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46182.69337332176</v>
+        <v>46245.167410787035</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>130</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46238.207226134255</v>
+        <v>46245.16741194444</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>271</v>
@@ -6415,7 +6415,7 @@
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46227.72250855324</v>
+        <v>46245.167413460644</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>211</v>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46227.72250912037</v>
+        <v>46245.167414490745</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>216</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -8068,7 +8068,7 @@
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46244.72987326389</v>
+        <v>46245.73985467592</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>348</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -3695,7 +3695,7 @@
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="8">
-        <v>46245.16740877315</v>
+        <v>46246.195240925925</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>121</v>
@@ -3742,8 +3742,8 @@
       <c r="S33" s="9">
         <v>0</v>
       </c>
-      <c r="T33" s="12" t="s">
-        <v>53</v>
+      <c r="T33" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U33" s="10" t="s">
         <v>54</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46245.16741194444</v>
+        <v>46246.19524059028</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>271</v>
@@ -6399,8 +6399,8 @@
       <c r="S78" s="6">
         <v>0</v>
       </c>
-      <c r="T78" s="12" t="s">
-        <v>53</v>
+      <c r="T78" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U78" s="10" t="s">
         <v>54</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -2434,7 +2434,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46240.18483663195</v>
+        <v>46247.16736709491</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46111.57933724537</v>
+        <v>46247.16738287037</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>56</v>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46111.57933446759</v>
+        <v>46247.16738408565</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>60</v>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="8">
-        <v>46111.579331643516</v>
+        <v>46247.1673853588</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>63</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46111.579327326384</v>
+        <v>46247.167386597226</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>66</v>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46221.31555423611</v>
+        <v>46246.95004469907</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>263</v>
@@ -6287,9 +6287,11 @@
       <c r="B77" s="8">
         <v>46111.505495046295</v>
       </c>
-      <c r="C77" s="9"/>
+      <c r="C77" s="8">
+        <v>46246.950038807874</v>
+      </c>
       <c r="D77" s="8">
-        <v>46226.19708370371</v>
+        <v>46246.95005820601</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>266</v>
@@ -6334,13 +6336,13 @@
         <v>46225</v>
       </c>
       <c r="S77" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T77" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U77" s="10" t="s">
-        <v>54</v>
+      <c r="U77" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -6352,7 +6354,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46246.19524059028</v>
+        <v>46246.95045744213</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>271</v>
@@ -6402,8 +6404,8 @@
       <c r="T78" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U78" s="10" t="s">
-        <v>54</v>
+      <c r="U78" s="12" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6415,7 +6417,7 @@
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46245.167413460644</v>
+        <v>46246.95004574074</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>211</v>
@@ -6468,7 +6470,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46245.167414490745</v>
+        <v>46246.95004674769</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>216</v>
@@ -6521,7 +6523,7 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46240.18483673611</v>
+        <v>46247.1673787037</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>278</v>
@@ -6584,7 +6586,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46227.7225096412</v>
+        <v>46247.16738049769</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>211</v>
@@ -6637,7 +6639,7 @@
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46227.722510057865</v>
+        <v>46247.167381701394</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>216</v>
@@ -6863,7 +6865,7 @@
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46240.18483702546</v>
+        <v>46247.1673696875</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>294</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="438">
   <si>
     <t>50001525- ZITRON PERU METRO DE LIMA  ESTACION 07</t>
   </si>
@@ -170,9 +170,6 @@
   </si>
   <si>
     <t>OT 4290 - TABLERO VDF ABB ACS880-17,OT 4291- TABLERO PLC,OT 4292- TABLERO BOTONERA ,OT 4293-COMPONENTES TABLERO COMPUERTAS</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>Tarea sin iniciar</t>
@@ -2434,7 +2431,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46247.16736709491</v>
+        <v>46248.16971180556</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -2481,16 +2478,16 @@
       <c r="S12" s="6">
         <v>0</v>
       </c>
-      <c r="T12" s="12" t="s">
+      <c r="T12" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="U12" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="U12" s="10" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="8">
         <v>46111.52928783565</v>
@@ -2500,7 +2497,7 @@
         <v>46247.16738287037</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>26</v>
@@ -2530,10 +2527,10 @@
         <v>51</v>
       </c>
       <c r="O13" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="P13" s="9" t="s">
         <v>57</v>
-      </c>
-      <c r="P13" s="9" t="s">
-        <v>58</v>
       </c>
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
@@ -2543,7 +2540,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B14" s="5">
         <v>46111.529514953705</v>
@@ -2553,7 +2550,7 @@
         <v>46247.16738408565</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -2583,10 +2580,10 @@
         <v>51</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
@@ -2596,7 +2593,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B15" s="8">
         <v>46111.52956931713</v>
@@ -2606,7 +2603,7 @@
         <v>46247.1673853588</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
@@ -2636,10 +2633,10 @@
         <v>51</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
@@ -2649,7 +2646,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B16" s="5">
         <v>46111.529618252316</v>
@@ -2659,7 +2656,7 @@
         <v>46247.167386597226</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2689,10 +2686,10 @@
         <v>51</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q16" s="6"/>
       <c r="R16" s="6"/>
@@ -2702,7 +2699,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B17" s="8">
         <v>46108.756727361106</v>
@@ -2714,7 +2711,7 @@
         <v>46221.35628416667</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>25</v>
@@ -2738,7 +2735,7 @@
         <v>26</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P17" s="9" t="s">
         <v>26</v>
@@ -2751,7 +2748,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B18" s="5">
         <v>46108.75683751157</v>
@@ -2763,7 +2760,7 @@
         <v>46114.1503816551</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2790,13 +2787,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>38</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q18" s="5">
         <v>46112</v>
@@ -2816,7 +2813,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B19" s="8">
         <v>46108.75684753472</v>
@@ -2828,7 +2825,7 @@
         <v>46121.17477054398</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
@@ -2855,13 +2852,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O19" s="9" t="s">
         <v>38</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q19" s="8">
         <v>46112</v>
@@ -2881,7 +2878,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B20" s="5">
         <v>46108.756853240746</v>
@@ -2893,7 +2890,7 @@
         <v>46121.17477048611</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2920,13 +2917,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>38</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q20" s="5">
         <v>46112</v>
@@ -2946,7 +2943,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B21" s="8">
         <v>46108.7568596412</v>
@@ -2958,7 +2955,7 @@
         <v>46121.174770729165</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
@@ -2985,13 +2982,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O21" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="P21" s="9" t="s">
         <v>82</v>
-      </c>
-      <c r="P21" s="9" t="s">
-        <v>83</v>
       </c>
       <c r="Q21" s="8">
         <v>46112</v>
@@ -3011,7 +3008,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B22" s="5">
         <v>46108.78930224537</v>
@@ -3023,7 +3020,7 @@
         <v>46121.17477037037</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -3050,13 +3047,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>38</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q22" s="5">
         <v>46112</v>
@@ -3076,7 +3073,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B23" s="8">
         <v>46108.756733738424</v>
@@ -3086,7 +3083,7 @@
         <v>46221.31477258102</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>25</v>
@@ -3110,7 +3107,7 @@
         <v>26</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P23" s="9" t="s">
         <v>26</v>
@@ -3120,12 +3117,12 @@
       <c r="S23" s="9"/>
       <c r="T23" s="9"/>
       <c r="U23" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B24" s="5">
         <v>46108.75686861111</v>
@@ -3137,7 +3134,7 @@
         <v>46116.12918178241</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -3164,13 +3161,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q24" s="5">
         <v>46114</v>
@@ -3190,7 +3187,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B25" s="8">
         <v>46108.75687488426</v>
@@ -3202,7 +3199,7 @@
         <v>46123.19348800926</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
@@ -3229,13 +3226,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q25" s="8">
         <v>46121</v>
@@ -3255,7 +3252,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B26" s="5">
         <v>46108.75688076389</v>
@@ -3267,16 +3264,16 @@
         <v>46223.59446482639</v>
       </c>
       <c r="E26" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="6" t="s">
+      <c r="H26" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="I26" s="5">
         <v>46121</v>
@@ -3294,13 +3291,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Q26" s="5">
         <v>46121</v>
@@ -3320,7 +3317,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B27" s="8">
         <v>46108.75688663195</v>
@@ -3332,7 +3329,7 @@
         <v>46135.5462021412</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
@@ -3359,13 +3356,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>46</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Q27" s="8">
         <v>46121</v>
@@ -3385,7 +3382,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B28" s="5">
         <v>46108.756897349536</v>
@@ -3395,16 +3392,16 @@
         <v>46237.53668097222</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="I28" s="5">
         <v>46191</v>
@@ -3422,13 +3419,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O28" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="P28" s="6" t="s">
         <v>107</v>
-      </c>
-      <c r="P28" s="6" t="s">
-        <v>108</v>
       </c>
       <c r="Q28" s="5">
         <v>46191</v>
@@ -3448,7 +3445,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B29" s="8">
         <v>46108.75690234954</v>
@@ -3460,7 +3457,7 @@
         <v>46123.19348805556</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3487,13 +3484,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q29" s="8">
         <v>46121</v>
@@ -3513,7 +3510,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B30" s="5">
         <v>46108.75690841435</v>
@@ -3523,16 +3520,16 @@
         <v>46237.536746666665</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="I30" s="5">
         <v>46191</v>
@@ -3550,13 +3547,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q30" s="5">
         <v>46191</v>
@@ -3576,7 +3573,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B31" s="8">
         <v>46108.78647824074</v>
@@ -3588,7 +3585,7 @@
         <v>46123.19348760416</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
@@ -3615,13 +3612,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q31" s="8">
         <v>46121</v>
@@ -3641,7 +3638,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B32" s="5">
         <v>46108.756741087964</v>
@@ -3651,7 +3648,7 @@
         <v>46221.115510891206</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>25</v>
@@ -3675,7 +3672,7 @@
         <v>26</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3688,7 +3685,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B33" s="8">
         <v>46108.75695274306</v>
@@ -3698,16 +3695,16 @@
         <v>46246.195240925925</v>
       </c>
       <c r="E33" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="F33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="9" t="s">
+      <c r="H33" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="I33" s="8">
         <v>46125</v>
@@ -3725,13 +3722,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q33" s="8">
         <v>46125</v>
@@ -3746,12 +3743,12 @@
         <v>31</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B34" s="5">
         <v>46108.75695775463</v>
@@ -3763,16 +3760,16 @@
         <v>46182.69336725694</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>123</v>
       </c>
       <c r="I34" s="5">
         <v>46125</v>
@@ -3790,13 +3787,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q34" s="5">
         <v>45985</v>
@@ -3808,15 +3805,15 @@
         <v>0</v>
       </c>
       <c r="T34" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B35" s="8">
         <v>46108.75696342593</v>
@@ -3826,16 +3823,16 @@
         <v>46245.167410787035</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H35" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="I35" s="8">
         <v>46127</v>
@@ -3853,13 +3850,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q35" s="8">
         <v>45987</v>
@@ -3871,15 +3868,15 @@
         <v>0</v>
       </c>
       <c r="T35" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U35" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B36" s="5">
         <v>46108.75697314815</v>
@@ -3889,16 +3886,16 @@
         <v>46239.19366604167</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>123</v>
       </c>
       <c r="I36" s="5">
         <v>46125</v>
@@ -3916,13 +3913,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q36" s="5">
         <v>46125</v>
@@ -3937,12 +3934,12 @@
         <v>31</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B37" s="8">
         <v>46108.75697796296</v>
@@ -3952,16 +3949,16 @@
         <v>46135.54608165509</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H37" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="I37" s="8">
         <v>46125</v>
@@ -3979,13 +3976,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q37" s="8">
         <v>45979</v>
@@ -3997,15 +3994,15 @@
         <v>0</v>
       </c>
       <c r="T37" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U37" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B38" s="5">
         <v>46108.7569835301</v>
@@ -4015,16 +4012,16 @@
         <v>46238.16766954861</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>123</v>
       </c>
       <c r="I38" s="5">
         <v>46134</v>
@@ -4042,13 +4039,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Q38" s="5">
         <v>45988</v>
@@ -4058,15 +4055,15 @@
       </c>
       <c r="S38" s="6"/>
       <c r="T38" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U38" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B39" s="8">
         <v>46108.75698832176</v>
@@ -4076,16 +4073,16 @@
         <v>46183.16750024306</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H39" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="I39" s="8">
         <v>46125</v>
@@ -4103,13 +4100,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q39" s="8">
         <v>46125</v>
@@ -4124,12 +4121,12 @@
         <v>31</v>
       </c>
       <c r="U39" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B40" s="5">
         <v>46108.75699311343</v>
@@ -4139,16 +4136,16 @@
         <v>46209.595412939816</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>123</v>
       </c>
       <c r="I40" s="5">
         <v>46125</v>
@@ -4166,13 +4163,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Q40" s="5">
         <v>45985</v>
@@ -4184,15 +4181,15 @@
         <v>0</v>
       </c>
       <c r="T40" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U40" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B41" s="8">
         <v>46108.75699847222</v>
@@ -4202,16 +4199,16 @@
         <v>46182.1679962037</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="I41" s="8">
         <v>46127</v>
@@ -4229,13 +4226,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Q41" s="8">
         <v>45987</v>
@@ -4247,15 +4244,15 @@
         <v>0</v>
       </c>
       <c r="T41" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U41" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B42" s="5">
         <v>46108.75700357639</v>
@@ -4265,16 +4262,16 @@
         <v>46211.84653167824</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>123</v>
       </c>
       <c r="I42" s="5">
         <v>46118</v>
@@ -4292,13 +4289,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q42" s="5">
         <v>46118</v>
@@ -4310,15 +4307,15 @@
         <v>0</v>
       </c>
       <c r="T42" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U42" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B43" s="8">
         <v>46108.75700856482</v>
@@ -4330,16 +4327,16 @@
         <v>46182.69343975694</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H43" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="I43" s="8">
         <v>46118</v>
@@ -4357,13 +4354,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q43" s="8">
         <v>45978</v>
@@ -4375,15 +4372,15 @@
         <v>0</v>
       </c>
       <c r="T43" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U43" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B44" s="5">
         <v>46108.757016435186</v>
@@ -4393,16 +4390,16 @@
         <v>46182.69344646991</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>123</v>
       </c>
       <c r="I44" s="5">
         <v>46139</v>
@@ -4420,13 +4417,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q44" s="5">
         <v>45999</v>
@@ -4438,15 +4435,15 @@
         <v>0</v>
       </c>
       <c r="T44" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U44" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B45" s="8">
         <v>46108.7570218287</v>
@@ -4458,16 +4455,16 @@
         <v>46211.84652803241</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H45" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="I45" s="8">
         <v>46139</v>
@@ -4485,13 +4482,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q45" s="8">
         <v>45999</v>
@@ -4503,15 +4500,15 @@
         <v>0</v>
       </c>
       <c r="T45" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U45" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B46" s="5">
         <v>46108.75702719907</v>
@@ -4521,16 +4518,16 @@
         <v>46211.173315312495</v>
       </c>
       <c r="E46" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="6" t="s">
+      <c r="H46" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="I46" s="5">
         <v>46195</v>
@@ -4548,13 +4545,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q46" s="5">
         <v>46195</v>
@@ -4569,12 +4566,12 @@
         <v>31</v>
       </c>
       <c r="U46" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B47" s="8">
         <v>46108.75703201389</v>
@@ -4584,16 +4581,16 @@
         <v>46209.598061192126</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="H47" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="I47" s="8">
         <v>46195</v>
@@ -4611,13 +4608,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q47" s="8">
         <v>45985</v>
@@ -4629,15 +4626,15 @@
         <v>0</v>
       </c>
       <c r="T47" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U47" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B48" s="5">
         <v>46108.75703761574</v>
@@ -4647,16 +4644,16 @@
         <v>46210.16869111111</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="I48" s="5">
         <v>46202</v>
@@ -4674,13 +4671,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q48" s="5">
         <v>46007</v>
@@ -4692,15 +4689,15 @@
         <v>0</v>
       </c>
       <c r="T48" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U48" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B49" s="8">
         <v>46108.75704306713</v>
@@ -4712,16 +4709,16 @@
         <v>46220.16760561343</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="H49" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="I49" s="8">
         <v>46125</v>
@@ -4739,13 +4736,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q49" s="8">
         <v>46125</v>
@@ -4765,7 +4762,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B50" s="5">
         <v>46108.75705032407</v>
@@ -4777,16 +4774,16 @@
         <v>46154.86746811343</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="I50" s="5">
         <v>46125</v>
@@ -4804,13 +4801,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4820,7 +4817,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B51" s="8">
         <v>46108.75705728009</v>
@@ -4832,16 +4829,16 @@
         <v>46154.8677641088</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="I51" s="8">
         <v>46135</v>
@@ -4859,13 +4856,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4875,7 +4872,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B52" s="5">
         <v>46108.757061435186</v>
@@ -4885,16 +4882,16 @@
         <v>46231.17690494213</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
+      <c r="H52" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="I52" s="5">
         <v>46195</v>
@@ -4912,13 +4909,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q52" s="5">
         <v>46195</v>
@@ -4933,12 +4930,12 @@
         <v>31</v>
       </c>
       <c r="U52" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B53" s="8">
         <v>46108.75710696759</v>
@@ -4948,16 +4945,16 @@
         <v>46199.168608900465</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="H53" s="9" t="s">
         <v>183</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>184</v>
       </c>
       <c r="I53" s="8">
         <v>46195</v>
@@ -4975,13 +4972,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4989,15 +4986,15 @@
         <v>0</v>
       </c>
       <c r="T53" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U53" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B54" s="5">
         <v>46108.757112928244</v>
@@ -5007,16 +5004,16 @@
         <v>46238.167673738426</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="I54" s="5">
         <v>46210</v>
@@ -5034,13 +5031,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O54" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="P54" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="P54" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5050,7 +5047,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B55" s="8">
         <v>46111.50860645833</v>
@@ -5062,16 +5059,16 @@
         <v>46182.69406362269</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H55" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="I55" s="8">
         <v>46125</v>
@@ -5089,10 +5086,10 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5115,7 +5112,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B56" s="5">
         <v>46111.508755937495</v>
@@ -5127,16 +5124,16 @@
         <v>46182.69350877315</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>123</v>
       </c>
       <c r="I56" s="5">
         <v>46125</v>
@@ -5154,13 +5151,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5170,7 +5167,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B57" s="8">
         <v>46111.508846770834</v>
@@ -5182,16 +5179,16 @@
         <v>46182.69403748843</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="I57" s="8">
         <v>46132</v>
@@ -5209,13 +5206,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5225,7 +5222,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B58" s="5">
         <v>46108.75711900463</v>
@@ -5235,7 +5232,7 @@
         <v>46217.85709320602</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -5259,7 +5256,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5269,12 +5266,12 @@
       <c r="S58" s="6"/>
       <c r="T58" s="6"/>
       <c r="U58" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B59" s="8">
         <v>46108.75712325232</v>
@@ -5286,16 +5283,16 @@
         <v>46222.09270599537</v>
       </c>
       <c r="E59" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="F59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="9" t="s">
+      <c r="H59" s="9" t="s">
         <v>206</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>207</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="8">
@@ -5311,13 +5308,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O59" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="P59" s="9" t="s">
         <v>208</v>
-      </c>
-      <c r="P59" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="Q59" s="8">
         <v>46121</v>
@@ -5337,7 +5334,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B60" s="5">
         <v>46114.552579166666</v>
@@ -5349,16 +5346,16 @@
         <v>46211.84604957176</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
+      <c r="H60" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="I60" s="5">
         <v>46121</v>
@@ -5376,13 +5373,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5392,7 +5389,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B61" s="8">
         <v>46114.552773240735</v>
@@ -5404,16 +5401,16 @@
         <v>46211.846055462964</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>213</v>
       </c>
       <c r="I61" s="8">
         <v>46121</v>
@@ -5431,13 +5428,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5447,7 +5444,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B62" s="5">
         <v>46108.75712855324</v>
@@ -5459,16 +5456,16 @@
         <v>46236.273657928235</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>206</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>207</v>
       </c>
       <c r="I62" s="5">
         <v>46183</v>
@@ -5486,13 +5483,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O62" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="P62" s="6" t="s">
         <v>220</v>
-      </c>
-      <c r="P62" s="6" t="s">
-        <v>221</v>
       </c>
       <c r="Q62" s="5">
         <v>46183</v>
@@ -5512,7 +5509,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B63" s="8">
         <v>46114.55286452547</v>
@@ -5524,16 +5521,16 @@
         <v>46217.85704695602</v>
       </c>
       <c r="E63" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="F63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="9" t="s">
+      <c r="H63" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>213</v>
       </c>
       <c r="I63" s="8">
         <v>46183</v>
@@ -5551,13 +5548,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O63" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="P63" s="9" t="s">
         <v>223</v>
-      </c>
-      <c r="P63" s="9" t="s">
-        <v>224</v>
       </c>
       <c r="Q63" s="9"/>
       <c r="R63" s="9"/>
@@ -5567,7 +5564,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B64" s="5">
         <v>46114.552966620366</v>
@@ -5579,16 +5576,16 @@
         <v>46217.85705476852</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="I64" s="5">
         <v>46183</v>
@@ -5606,13 +5603,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O64" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5622,7 +5619,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B65" s="8">
         <v>46108.75713383102</v>
@@ -5634,16 +5631,16 @@
         <v>46227.722518622686</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>213</v>
       </c>
       <c r="I65" s="8">
         <v>46190</v>
@@ -5661,13 +5658,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O65" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="P65" s="9" t="s">
         <v>229</v>
-      </c>
-      <c r="P65" s="9" t="s">
-        <v>230</v>
       </c>
       <c r="Q65" s="8">
         <v>46190</v>
@@ -5687,7 +5684,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B66" s="5">
         <v>46114.55312298611</v>
@@ -5697,16 +5694,16 @@
         <v>46217.85705168982</v>
       </c>
       <c r="E66" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G66" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="F66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G66" s="6" t="s">
+      <c r="H66" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="5">
@@ -5722,10 +5719,10 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5738,7 +5735,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B67" s="8">
         <v>46114.553244675924</v>
@@ -5748,16 +5745,16 @@
         <v>46217.85706487269</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>213</v>
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="8">
@@ -5773,10 +5770,10 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>26</v>
@@ -5789,7 +5786,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B68" s="5">
         <v>46108.757138761575</v>
@@ -5799,16 +5796,16 @@
         <v>46114.631384050925</v>
       </c>
       <c r="E68" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G68" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="F68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G68" s="6" t="s">
+      <c r="H68" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="I68" s="5">
         <v>46281</v>
@@ -5826,10 +5823,10 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5844,15 +5841,15 @@
         <v>0</v>
       </c>
       <c r="T68" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U68" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B69" s="8">
         <v>46111.55280189815</v>
@@ -5862,16 +5859,16 @@
         <v>46114.62851033565</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -5887,13 +5884,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5903,7 +5900,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B70" s="5">
         <v>46111.55285245371</v>
@@ -5913,16 +5910,16 @@
         <v>46114.62851040509</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -5938,13 +5935,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5954,7 +5951,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B71" s="8">
         <v>46108.75714166666</v>
@@ -5964,7 +5961,7 @@
         <v>46118.545566597226</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -5988,7 +5985,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -6001,7 +5998,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B72" s="5">
         <v>46108.75714454861</v>
@@ -6011,16 +6008,16 @@
         <v>46240.16751462963</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>248</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>249</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -6036,13 +6033,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q72" s="5">
         <v>46231</v>
@@ -6062,7 +6059,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B73" s="8">
         <v>46111.50359008102</v>
@@ -6072,7 +6069,7 @@
         <v>46114.61935158564</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -6096,7 +6093,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -6109,7 +6106,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B74" s="5">
         <v>46111.50404616898</v>
@@ -6119,16 +6116,16 @@
         <v>46213.19769318287</v>
       </c>
       <c r="E74" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G74" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="F74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G74" s="6" t="s">
+      <c r="H74" s="6" t="s">
         <v>256</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>257</v>
       </c>
       <c r="I74" s="5">
         <v>46211</v>
@@ -6146,13 +6143,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q74" s="5">
         <v>46211</v>
@@ -6167,12 +6164,12 @@
         <v>31</v>
       </c>
       <c r="U74" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B75" s="8">
         <v>46111.50406170139</v>
@@ -6182,16 +6179,16 @@
         <v>46217.17519608796</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="H75" s="9" t="s">
         <v>248</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>249</v>
       </c>
       <c r="I75" s="8">
         <v>46213</v>
@@ -6209,13 +6206,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q75" s="8">
         <v>46213</v>
@@ -6230,12 +6227,12 @@
         <v>31</v>
       </c>
       <c r="U75" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B76" s="5">
         <v>46111.50543856481</v>
@@ -6245,7 +6242,7 @@
         <v>46246.95004469907</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -6269,7 +6266,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -6282,7 +6279,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B77" s="8">
         <v>46111.505495046295</v>
@@ -6294,16 +6291,16 @@
         <v>46246.95005820601</v>
       </c>
       <c r="E77" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G77" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="F77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G77" s="9" t="s">
+      <c r="H77" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="I77" s="8">
         <v>46217</v>
@@ -6321,13 +6318,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q77" s="8">
         <v>46217</v>
@@ -6347,26 +6344,26 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B78" s="5">
         <v>46111.50560314815</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46246.95045744213</v>
+        <v>46247.95303712963</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="I78" s="5">
         <v>46226</v>
@@ -6384,13 +6381,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q78" s="5">
         <v>46226</v>
@@ -6405,12 +6402,12 @@
         <v>31</v>
       </c>
       <c r="U78" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B79" s="8">
         <v>46111.52633317129</v>
@@ -6420,16 +6417,16 @@
         <v>46246.95004574074</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H79" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="I79" s="8">
         <v>46226</v>
@@ -6447,13 +6444,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O79" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="P79" s="9" t="s">
         <v>273</v>
-      </c>
-      <c r="P79" s="9" t="s">
-        <v>274</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6463,7 +6460,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B80" s="5">
         <v>46111.526644375</v>
@@ -6473,16 +6470,16 @@
         <v>46246.95004674769</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="I80" s="5">
         <v>46226</v>
@@ -6500,13 +6497,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6516,26 +6513,26 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B81" s="8">
         <v>46111.50563458333</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46247.1673787037</v>
+        <v>46248.169711875</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="H81" s="9" t="s">
         <v>248</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>249</v>
       </c>
       <c r="I81" s="8">
         <v>46246</v>
@@ -6553,13 +6550,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q81" s="8">
         <v>46246</v>
@@ -6570,16 +6567,16 @@
       <c r="S81" s="9">
         <v>0</v>
       </c>
-      <c r="T81" s="12" t="s">
+      <c r="T81" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="U81" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="U81" s="10" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B82" s="5">
         <v>46111.526916469906</v>
@@ -6589,16 +6586,16 @@
         <v>46247.16738049769</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>248</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>249</v>
       </c>
       <c r="I82" s="5">
         <v>46246</v>
@@ -6616,13 +6613,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="O82" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="P82" s="6" t="s">
         <v>280</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>281</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6632,7 +6629,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B83" s="8">
         <v>46111.52699828704</v>
@@ -6642,16 +6639,16 @@
         <v>46247.167381701394</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="H83" s="9" t="s">
         <v>248</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>249</v>
       </c>
       <c r="I83" s="8">
         <v>46246</v>
@@ -6669,13 +6666,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="O83" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="P83" s="9" t="s">
         <v>283</v>
-      </c>
-      <c r="P83" s="9" t="s">
-        <v>284</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6685,7 +6682,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B84" s="5">
         <v>46108.75714884259</v>
@@ -6695,7 +6692,7 @@
         <v>46221.1155655787</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -6719,7 +6716,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6732,7 +6729,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B85" s="8">
         <v>46108.75715243055</v>
@@ -6742,16 +6739,16 @@
         <v>46185.184959907405</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="H85" s="9" t="s">
         <v>256</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>257</v>
       </c>
       <c r="I85" s="8">
         <v>46183</v>
@@ -6769,13 +6766,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q85" s="8">
         <v>46183</v>
@@ -6790,12 +6787,12 @@
         <v>31</v>
       </c>
       <c r="U85" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B86" s="5">
         <v>46108.75715773148</v>
@@ -6805,16 +6802,16 @@
         <v>46241.20565452546</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>256</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>257</v>
       </c>
       <c r="I86" s="5">
         <v>46239</v>
@@ -6832,13 +6829,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Q86" s="5">
         <v>46239</v>
@@ -6853,31 +6850,31 @@
         <v>31</v>
       </c>
       <c r="U86" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B87" s="8">
         <v>46108.75716349537</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46247.1673696875</v>
+        <v>46248.16971915509</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="H87" s="9" t="s">
         <v>256</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>257</v>
       </c>
       <c r="I87" s="8">
         <v>46246</v>
@@ -6895,13 +6892,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q87" s="8">
         <v>46246</v>
@@ -6912,16 +6909,16 @@
       <c r="S87" s="9">
         <v>0</v>
       </c>
-      <c r="T87" s="12" t="s">
+      <c r="T87" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="U87" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="U87" s="10" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B88" s="5">
         <v>46108.75716875</v>
@@ -6931,16 +6928,16 @@
         <v>46111.59782981481</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>256</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>257</v>
       </c>
       <c r="I88" s="5">
         <v>46273</v>
@@ -6958,13 +6955,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q88" s="5">
         <v>46273</v>
@@ -6976,15 +6973,15 @@
         <v>0</v>
       </c>
       <c r="T88" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U88" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B89" s="8">
         <v>46108.75717430556</v>
@@ -6994,16 +6991,16 @@
         <v>46224.18129432871</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="H89" s="9" t="s">
         <v>256</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>257</v>
       </c>
       <c r="I89" s="8">
         <v>46220</v>
@@ -7021,13 +7018,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q89" s="8">
         <v>46220</v>
@@ -7042,12 +7039,12 @@
         <v>31</v>
       </c>
       <c r="U89" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B90" s="5">
         <v>46108.75717877314</v>
@@ -7057,16 +7054,16 @@
         <v>46240.16751195602</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>256</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>257</v>
       </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
@@ -7082,13 +7079,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q90" s="5">
         <v>46231</v>
@@ -7103,12 +7100,12 @@
         <v>31</v>
       </c>
       <c r="U90" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B91" s="8">
         <v>46108.822037094906</v>
@@ -7118,16 +7115,16 @@
         <v>46185.18495945602</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="H91" s="9" t="s">
         <v>256</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>257</v>
       </c>
       <c r="I91" s="8">
         <v>46181</v>
@@ -7145,13 +7142,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q91" s="8">
         <v>46183</v>
@@ -7166,12 +7163,12 @@
         <v>31</v>
       </c>
       <c r="U91" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B92" s="5">
         <v>46108.757183124995</v>
@@ -7181,7 +7178,7 @@
         <v>46221.36615074074</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>25</v>
@@ -7205,7 +7202,7 @@
         <v>26</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>26</v>
@@ -7218,7 +7215,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B93" s="8">
         <v>46108.757186296294</v>
@@ -7228,16 +7225,16 @@
         <v>46223.59523664352</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H93" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="I93" s="8">
         <v>46248</v>
@@ -7255,13 +7252,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q93" s="8">
         <v>46248</v>
@@ -7273,15 +7270,15 @@
         <v>0</v>
       </c>
       <c r="T93" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U93" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B94" s="5">
         <v>46111.52720202546</v>
@@ -7291,16 +7288,16 @@
         <v>46223.59457288195</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="I94" s="5">
         <v>46248</v>
@@ -7318,13 +7315,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O94" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="P94" s="6" t="s">
         <v>312</v>
-      </c>
-      <c r="P94" s="6" t="s">
-        <v>313</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7334,7 +7331,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B95" s="8">
         <v>46111.52733795139</v>
@@ -7344,16 +7341,16 @@
         <v>46223.594572268514</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H95" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="I95" s="8">
         <v>46248</v>
@@ -7371,13 +7368,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O95" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="P95" s="9" t="s">
         <v>315</v>
-      </c>
-      <c r="P95" s="9" t="s">
-        <v>316</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7387,7 +7384,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B96" s="5">
         <v>46108.75720997685</v>
@@ -7397,16 +7394,16 @@
         <v>46223.595235995366</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="I96" s="5">
         <v>46268</v>
@@ -7424,13 +7421,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q96" s="5">
         <v>46268</v>
@@ -7442,15 +7439,15 @@
         <v>0</v>
       </c>
       <c r="T96" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U96" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B97" s="8">
         <v>46111.52790079861</v>
@@ -7460,16 +7457,16 @@
         <v>46227.72251041667</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H97" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="I97" s="8">
         <v>46268</v>
@@ -7487,13 +7484,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="O97" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="P97" s="9" t="s">
         <v>320</v>
-      </c>
-      <c r="P97" s="9" t="s">
-        <v>321</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7503,7 +7500,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B98" s="5">
         <v>46111.52796104166</v>
@@ -7513,16 +7510,16 @@
         <v>46227.72251091435</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="I98" s="5">
         <v>46268</v>
@@ -7540,13 +7537,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="O98" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="P98" s="6" t="s">
         <v>323</v>
-      </c>
-      <c r="P98" s="6" t="s">
-        <v>324</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7556,7 +7553,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B99" s="8">
         <v>46108.75719767361</v>
@@ -7566,16 +7563,16 @@
         <v>46223.5952353125</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H99" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="H99" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="I99" s="8">
         <v>46272</v>
@@ -7593,13 +7590,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q99" s="8">
         <v>46272</v>
@@ -7611,15 +7608,15 @@
         <v>0</v>
       </c>
       <c r="T99" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U99" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B100" s="5">
         <v>46111.52756633102</v>
@@ -7629,16 +7626,16 @@
         <v>46227.72251393519</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="I100" s="5">
         <v>46272</v>
@@ -7656,13 +7653,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O100" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="P100" s="6" t="s">
         <v>328</v>
-      </c>
-      <c r="P100" s="6" t="s">
-        <v>329</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7672,7 +7669,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B101" s="8">
         <v>46111.527622395835</v>
@@ -7682,16 +7679,16 @@
         <v>46227.72251137732</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H101" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="H101" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="I101" s="8">
         <v>46272</v>
@@ -7709,13 +7706,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O101" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="P101" s="9" t="s">
         <v>331</v>
-      </c>
-      <c r="P101" s="9" t="s">
-        <v>332</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7725,7 +7722,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B102" s="5">
         <v>46108.75720341435</v>
@@ -7735,16 +7732,16 @@
         <v>46223.595234629625</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="I102" s="5">
         <v>46274</v>
@@ -7762,13 +7759,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q102" s="5">
         <v>46274</v>
@@ -7780,15 +7777,15 @@
         <v>0</v>
       </c>
       <c r="T102" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U102" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B103" s="8">
         <v>46111.52775804398</v>
@@ -7798,16 +7795,16 @@
         <v>46227.722512928245</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H103" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="H103" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="I103" s="8">
         <v>46274</v>
@@ -7825,13 +7822,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -7841,7 +7838,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B104" s="5">
         <v>46111.52780829861</v>
@@ -7851,16 +7848,16 @@
         <v>46227.72251365741</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="I104" s="5">
         <v>46274</v>
@@ -7878,13 +7875,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7894,7 +7891,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B105" s="8">
         <v>46108.757191412034</v>
@@ -7904,16 +7901,16 @@
         <v>46223.59523400463</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H105" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="H105" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="I105" s="8">
         <v>46276</v>
@@ -7931,13 +7928,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q105" s="8">
         <v>46276</v>
@@ -7949,15 +7946,15 @@
         <v>0</v>
       </c>
       <c r="T105" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U105" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B106" s="5">
         <v>46111.527446493055</v>
@@ -7967,16 +7964,16 @@
         <v>46227.722511921296</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H106" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="I106" s="5">
         <v>46276</v>
@@ -7994,13 +7991,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O106" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="P106" s="6" t="s">
         <v>342</v>
-      </c>
-      <c r="P106" s="6" t="s">
-        <v>343</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8010,7 +8007,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B107" s="8">
         <v>46111.52746010417</v>
@@ -8020,16 +8017,16 @@
         <v>46227.72251247685</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H107" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="H107" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="I107" s="8">
         <v>46276</v>
@@ -8047,13 +8044,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O107" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="P107" s="9" t="s">
         <v>345</v>
-      </c>
-      <c r="P107" s="9" t="s">
-        <v>346</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -8063,7 +8060,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B108" s="5">
         <v>46108.757217025464</v>
@@ -8073,16 +8070,16 @@
         <v>46245.73985467592</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H108" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="I108" s="5">
         <v>46280</v>
@@ -8100,13 +8097,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q108" s="5">
         <v>46280</v>
@@ -8118,15 +8115,15 @@
         <v>0</v>
       </c>
       <c r="T108" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U108" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B109" s="8">
         <v>46111.528031932874</v>
@@ -8136,16 +8133,16 @@
         <v>46223.59502533565</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H109" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="H109" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="I109" s="9"/>
       <c r="J109" s="8">
@@ -8161,13 +8158,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8177,7 +8174,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B110" s="5">
         <v>46111.52811128472</v>
@@ -8187,16 +8184,16 @@
         <v>46223.59502458334</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H110" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="I110" s="6"/>
       <c r="J110" s="5">
@@ -8212,13 +8209,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8228,7 +8225,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B111" s="8">
         <v>46108.75727585648</v>
@@ -8238,16 +8235,16 @@
         <v>46223.595232754626</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H111" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="H111" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="I111" s="9"/>
       <c r="J111" s="8">
@@ -8263,13 +8260,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q111" s="8">
         <v>46286</v>
@@ -8281,15 +8278,15 @@
         <v>0</v>
       </c>
       <c r="T111" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U111" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B112" s="5">
         <v>46111.5281812037</v>
@@ -8299,16 +8296,16 @@
         <v>46223.595106875</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H112" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
@@ -8324,13 +8321,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8340,7 +8337,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B113" s="8">
         <v>46111.528266423615</v>
@@ -8350,16 +8347,16 @@
         <v>46223.59510622685</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H113" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="H113" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="I113" s="9"/>
       <c r="J113" s="8">
@@ -8375,13 +8372,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8391,7 +8388,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B114" s="5">
         <v>46108.757283217594</v>
@@ -8401,7 +8398,7 @@
         <v>46221.10727317129</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>25</v>
@@ -8425,7 +8422,7 @@
         <v>26</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>26</v>
@@ -8438,7 +8435,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B115" s="8">
         <v>46108.757287430555</v>
@@ -8448,16 +8445,16 @@
         <v>46114.63723893519</v>
       </c>
       <c r="E115" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="F115" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G115" s="9" t="s">
         <v>364</v>
       </c>
-      <c r="F115" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G115" s="9" t="s">
+      <c r="H115" s="9" t="s">
         <v>365</v>
-      </c>
-      <c r="H115" s="9" t="s">
-        <v>366</v>
       </c>
       <c r="I115" s="8">
         <v>46287</v>
@@ -8475,13 +8472,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Q115" s="8">
         <v>46287</v>
@@ -8493,15 +8490,15 @@
         <v>0</v>
       </c>
       <c r="T115" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U115" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B116" s="5">
         <v>46111.52846596065</v>
@@ -8511,16 +8508,16 @@
         <v>46114.62888387732</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="H116" s="6" t="s">
         <v>365</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>366</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8536,13 +8533,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8552,7 +8549,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B117" s="8">
         <v>46111.528518067134</v>
@@ -8562,16 +8559,16 @@
         <v>46114.62888469908</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="H117" s="9" t="s">
         <v>365</v>
-      </c>
-      <c r="H117" s="9" t="s">
-        <v>366</v>
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="8">
@@ -8587,13 +8584,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8603,7 +8600,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B118" s="5">
         <v>46111.531216006944</v>
@@ -8613,16 +8610,16 @@
         <v>46114.62888542824</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="H118" s="6" t="s">
         <v>365</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>366</v>
       </c>
       <c r="I118" s="6"/>
       <c r="J118" s="5">
@@ -8638,13 +8635,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8654,7 +8651,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B119" s="8">
         <v>46111.53129275463</v>
@@ -8664,16 +8661,16 @@
         <v>46114.62888615741</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="H119" s="9" t="s">
         <v>365</v>
-      </c>
-      <c r="H119" s="9" t="s">
-        <v>366</v>
       </c>
       <c r="I119" s="9"/>
       <c r="J119" s="8">
@@ -8689,13 +8686,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8705,7 +8702,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B120" s="5">
         <v>46111.53134821759</v>
@@ -8715,16 +8712,16 @@
         <v>46114.628886921295</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="H120" s="6" t="s">
         <v>365</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>366</v>
       </c>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
@@ -8740,13 +8737,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8756,7 +8753,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B121" s="8">
         <v>46111.53139942129</v>
@@ -8766,16 +8763,16 @@
         <v>46114.62888767361</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="H121" s="9" t="s">
         <v>365</v>
-      </c>
-      <c r="H121" s="9" t="s">
-        <v>366</v>
       </c>
       <c r="I121" s="9"/>
       <c r="J121" s="8">
@@ -8791,13 +8788,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8807,7 +8804,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B122" s="5">
         <v>46111.53343819444</v>
@@ -8817,16 +8814,16 @@
         <v>46114.628888437495</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="H122" s="6" t="s">
         <v>365</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>366</v>
       </c>
       <c r="I122" s="6"/>
       <c r="J122" s="5">
@@ -8842,13 +8839,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8858,7 +8855,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B123" s="8">
         <v>46108.75729289352</v>
@@ -8868,16 +8865,16 @@
         <v>46223.59539700231</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H123" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="H123" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="I123" s="8">
         <v>46288</v>
@@ -8895,13 +8892,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="Q123" s="8">
         <v>46288</v>
@@ -8913,15 +8910,15 @@
         <v>0</v>
       </c>
       <c r="T123" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U123" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B124" s="5">
         <v>46111.52857409722</v>
@@ -8931,16 +8928,16 @@
         <v>46223.595359328705</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H124" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="I124" s="5">
         <v>46288</v>
@@ -8958,13 +8955,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8974,7 +8971,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B125" s="8">
         <v>46111.528674016205</v>
@@ -8984,16 +8981,16 @@
         <v>46223.59535869213</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H125" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="H125" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="I125" s="8">
         <v>46288</v>
@@ -9011,13 +9008,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -9027,7 +9024,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B126" s="5">
         <v>46111.531552291664</v>
@@ -9037,16 +9034,16 @@
         <v>46223.59535802083</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H126" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="I126" s="5">
         <v>46288</v>
@@ -9064,13 +9061,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9080,7 +9077,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B127" s="8">
         <v>46111.531603344905</v>
@@ -9090,16 +9087,16 @@
         <v>46223.595357349535</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H127" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="H127" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="I127" s="8">
         <v>46288</v>
@@ -9117,13 +9114,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9133,7 +9130,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B128" s="5">
         <v>46111.531648379634</v>
@@ -9143,16 +9140,16 @@
         <v>46223.59535668981</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H128" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="I128" s="5">
         <v>46288</v>
@@ -9170,13 +9167,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9186,7 +9183,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B129" s="8">
         <v>46111.531705925925</v>
@@ -9196,16 +9193,16 @@
         <v>46223.595356018515</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H129" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="H129" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="I129" s="8">
         <v>46288</v>
@@ -9223,13 +9220,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9239,7 +9236,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B130" s="5">
         <v>46111.533570127314</v>
@@ -9249,16 +9246,16 @@
         <v>46223.59535532407</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H130" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="H130" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="I130" s="5">
         <v>46288</v>
@@ -9276,13 +9273,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9292,7 +9289,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B131" s="8">
         <v>46108.75729930555</v>
@@ -9302,16 +9299,16 @@
         <v>46221.36200443287</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H131" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="H131" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="I131" s="8">
         <v>46293</v>
@@ -9329,13 +9326,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Q131" s="8">
         <v>46293</v>
@@ -9347,15 +9344,15 @@
         <v>0</v>
       </c>
       <c r="T131" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U131" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B132" s="5">
         <v>46111.528799872685</v>
@@ -9365,16 +9362,16 @@
         <v>46114.62931347222</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H132" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9390,13 +9387,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9406,7 +9403,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B133" s="8">
         <v>46111.52885179398</v>
@@ -9416,16 +9413,16 @@
         <v>46114.62931429398</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H133" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="H133" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="I133" s="9"/>
       <c r="J133" s="8">
@@ -9441,13 +9438,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9457,7 +9454,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B134" s="5">
         <v>46111.53215439815</v>
@@ -9467,16 +9464,16 @@
         <v>46114.629315046295</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H134" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9492,13 +9489,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9508,7 +9505,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B135" s="8">
         <v>46111.53220642361</v>
@@ -9518,16 +9515,16 @@
         <v>46114.62931577546</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H135" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="H135" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="I135" s="9"/>
       <c r="J135" s="8">
@@ -9543,13 +9540,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9559,7 +9556,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B136" s="5">
         <v>46111.532258287036</v>
@@ -9569,16 +9566,16 @@
         <v>46114.629316527775</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H136" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="H136" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9594,13 +9591,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9610,7 +9607,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B137" s="8">
         <v>46111.53231001158</v>
@@ -9620,16 +9617,16 @@
         <v>46114.62931729166</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H137" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="H137" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="I137" s="9"/>
       <c r="J137" s="8">
@@ -9645,13 +9642,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -9661,7 +9658,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B138" s="5">
         <v>46111.53368237268</v>
@@ -9671,16 +9668,16 @@
         <v>46114.62931805555</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H138" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="H138" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
@@ -9696,13 +9693,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9712,7 +9709,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B139" s="8">
         <v>46108.757304583334</v>
@@ -9722,16 +9719,16 @@
         <v>46240.71896241898</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H139" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="H139" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="I139" s="8">
         <v>46294</v>
@@ -9749,13 +9746,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="Q139" s="8">
         <v>46294</v>
@@ -9767,15 +9764,15 @@
         <v>0</v>
       </c>
       <c r="T139" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U139" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B140" s="5">
         <v>46111.528945011574</v>
@@ -9785,16 +9782,16 @@
         <v>46114.830281076385</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H140" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="I140" s="5">
         <v>46294</v>
@@ -9812,13 +9809,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9828,7 +9825,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B141" s="8">
         <v>46111.52901092592</v>
@@ -9838,16 +9835,16 @@
         <v>46114.830302789356</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H141" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="H141" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="I141" s="8">
         <v>46294</v>
@@ -9865,13 +9862,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -9881,7 +9878,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B142" s="5">
         <v>46111.53247278935</v>
@@ -9891,16 +9888,16 @@
         <v>46114.830319201385</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H142" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="H142" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="I142" s="5">
         <v>46294</v>
@@ -9918,13 +9915,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9934,7 +9931,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B143" s="8">
         <v>46111.53253350694</v>
@@ -9944,16 +9941,16 @@
         <v>46114.83033574074</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H143" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="H143" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="I143" s="8">
         <v>46294</v>
@@ -9971,13 +9968,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -9987,7 +9984,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B144" s="5">
         <v>46111.532638414355</v>
@@ -9997,16 +9994,16 @@
         <v>46114.83035239583</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H144" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="H144" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="I144" s="5">
         <v>46294</v>
@@ -10024,13 +10021,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10040,7 +10037,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B145" s="8">
         <v>46111.53258112269</v>
@@ -10050,16 +10047,16 @@
         <v>46114.83037114583</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H145" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="H145" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="I145" s="8">
         <v>46294</v>
@@ -10077,13 +10074,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -10093,7 +10090,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B146" s="5">
         <v>46111.53385627315</v>
@@ -10103,16 +10100,16 @@
         <v>46114.83039427083</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H146" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="H146" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="I146" s="5">
         <v>46294</v>
@@ -10130,13 +10127,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10146,7 +10143,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B147" s="8">
         <v>46108.757310497684</v>
@@ -10156,7 +10153,7 @@
         <v>46114.62962797454</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>25</v>
@@ -10180,7 +10177,7 @@
         <v>26</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="P147" s="9" t="s">
         <v>26</v>
@@ -10193,7 +10190,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B148" s="5">
         <v>46108.75731366898</v>
@@ -10203,16 +10200,16 @@
         <v>46114.63764361111</v>
       </c>
       <c r="E148" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="F148" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G148" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="F148" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G148" s="6" t="s">
+      <c r="H148" s="6" t="s">
         <v>434</v>
-      </c>
-      <c r="H148" s="6" t="s">
-        <v>435</v>
       </c>
       <c r="I148" s="5">
         <v>46295</v>
@@ -10230,13 +10227,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="Q148" s="5">
         <v>46295</v>
@@ -10248,15 +10245,15 @@
         <v>0</v>
       </c>
       <c r="T148" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U148" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B149" s="8">
         <v>46108.75732001157</v>
@@ -10266,16 +10263,16 @@
         <v>46119.74841528935</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="H149" s="9" t="s">
         <v>434</v>
-      </c>
-      <c r="H149" s="9" t="s">
-        <v>435</v>
       </c>
       <c r="I149" s="8">
         <v>46295</v>
@@ -10293,13 +10290,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="Q149" s="8">
         <v>46295</v>
@@ -10311,10 +10308,10 @@
         <v>0</v>
       </c>
       <c r="T149" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U149" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="439">
   <si>
     <t>50001525- ZITRON PERU METRO DE LIMA  ESTACION 07</t>
   </si>
@@ -824,6 +824,9 @@
   </si>
   <si>
     <t>Armado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caldereria,Control de calidad Armado </t>
   </si>
   <si>
     <t>1213869987281817</t>
@@ -6351,7 +6354,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46247.95303712963</v>
+        <v>46255.55279185185</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>270</v>
@@ -6387,7 +6390,7 @@
         <v>219</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="Q78" s="5">
         <v>46226</v>
@@ -6407,7 +6410,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B79" s="8">
         <v>46111.52633317129</v>
@@ -6447,10 +6450,10 @@
         <v>270</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6460,7 +6463,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B80" s="5">
         <v>46111.526644375</v>
@@ -6500,10 +6503,10 @@
         <v>270</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6513,7 +6516,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B81" s="8">
         <v>46111.50563458333</v>
@@ -6523,7 +6526,7 @@
         <v>46248.169711875</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6576,7 +6579,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B82" s="5">
         <v>46111.526916469906</v>
@@ -6613,13 +6616,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6629,7 +6632,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B83" s="8">
         <v>46111.52699828704</v>
@@ -6666,13 +6669,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6682,7 +6685,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B84" s="5">
         <v>46108.75714884259</v>
@@ -6692,7 +6695,7 @@
         <v>46221.1155655787</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -6716,7 +6719,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6729,7 +6732,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B85" s="8">
         <v>46108.75715243055</v>
@@ -6739,7 +6742,7 @@
         <v>46185.184959907405</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
@@ -6766,13 +6769,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O85" s="9" t="s">
         <v>147</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q85" s="8">
         <v>46183</v>
@@ -6792,7 +6795,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B86" s="5">
         <v>46108.75715773148</v>
@@ -6829,13 +6832,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>138</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q86" s="5">
         <v>46239</v>
@@ -6855,7 +6858,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B87" s="8">
         <v>46108.75716349537</v>
@@ -6865,7 +6868,7 @@
         <v>46248.16971915509</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
@@ -6892,13 +6895,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O87" s="9" t="s">
         <v>129</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q87" s="8">
         <v>46246</v>
@@ -6918,7 +6921,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B88" s="5">
         <v>46108.75716875</v>
@@ -6928,7 +6931,7 @@
         <v>46111.59782981481</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6955,13 +6958,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>156</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q88" s="5">
         <v>46273</v>
@@ -6981,7 +6984,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B89" s="8">
         <v>46108.75717430556</v>
@@ -6991,7 +6994,7 @@
         <v>46224.18129432871</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -7018,7 +7021,7 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O89" s="9" t="s">
         <v>178</v>
@@ -7044,7 +7047,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B90" s="5">
         <v>46108.75717877314</v>
@@ -7054,7 +7057,7 @@
         <v>46240.16751195602</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -7079,13 +7082,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>245</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q90" s="5">
         <v>46231</v>
@@ -7105,7 +7108,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B91" s="8">
         <v>46108.822037094906</v>
@@ -7115,7 +7118,7 @@
         <v>46185.18495945602</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -7142,13 +7145,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O91" s="9" t="s">
         <v>198</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q91" s="8">
         <v>46183</v>
@@ -7168,7 +7171,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B92" s="5">
         <v>46108.757183124995</v>
@@ -7178,7 +7181,7 @@
         <v>46221.36615074074</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>25</v>
@@ -7202,7 +7205,7 @@
         <v>26</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>26</v>
@@ -7215,7 +7218,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B93" s="8">
         <v>46108.757186296294</v>
@@ -7225,7 +7228,7 @@
         <v>46223.59523664352</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7252,13 +7255,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O93" s="9" t="s">
         <v>219</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q93" s="8">
         <v>46248</v>
@@ -7278,7 +7281,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B94" s="5">
         <v>46111.52720202546</v>
@@ -7315,13 +7318,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7331,7 +7334,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B95" s="8">
         <v>46111.52733795139</v>
@@ -7368,13 +7371,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7384,7 +7387,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B96" s="5">
         <v>46108.75720997685</v>
@@ -7394,7 +7397,7 @@
         <v>46223.595235995366</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7421,13 +7424,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>219</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q96" s="5">
         <v>46268</v>
@@ -7447,7 +7450,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B97" s="8">
         <v>46111.52790079861</v>
@@ -7484,13 +7487,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7500,7 +7503,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B98" s="5">
         <v>46111.52796104166</v>
@@ -7537,13 +7540,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7553,7 +7556,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B99" s="8">
         <v>46108.75719767361</v>
@@ -7563,7 +7566,7 @@
         <v>46223.5952353125</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7590,13 +7593,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O99" s="9" t="s">
         <v>219</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q99" s="8">
         <v>46272</v>
@@ -7616,7 +7619,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B100" s="5">
         <v>46111.52756633102</v>
@@ -7653,13 +7656,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7669,7 +7672,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B101" s="8">
         <v>46111.527622395835</v>
@@ -7706,13 +7709,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7722,7 +7725,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B102" s="5">
         <v>46108.75720341435</v>
@@ -7732,7 +7735,7 @@
         <v>46223.595234629625</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7759,13 +7762,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>219</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q102" s="5">
         <v>46274</v>
@@ -7785,7 +7788,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B103" s="8">
         <v>46111.52775804398</v>
@@ -7822,13 +7825,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -7838,7 +7841,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B104" s="5">
         <v>46111.52780829861</v>
@@ -7875,13 +7878,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7891,7 +7894,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B105" s="8">
         <v>46108.757191412034</v>
@@ -7901,7 +7904,7 @@
         <v>46223.59523400463</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -7928,13 +7931,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O105" s="9" t="s">
         <v>219</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q105" s="8">
         <v>46276</v>
@@ -7954,7 +7957,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B106" s="5">
         <v>46111.527446493055</v>
@@ -7991,13 +7994,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8007,7 +8010,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B107" s="8">
         <v>46111.52746010417</v>
@@ -8044,13 +8047,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -8060,7 +8063,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B108" s="5">
         <v>46108.757217025464</v>
@@ -8070,7 +8073,7 @@
         <v>46245.73985467592</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8097,13 +8100,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>219</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q108" s="5">
         <v>46280</v>
@@ -8123,7 +8126,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B109" s="8">
         <v>46111.528031932874</v>
@@ -8158,13 +8161,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O109" s="9" t="s">
         <v>210</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8174,7 +8177,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B110" s="5">
         <v>46111.52811128472</v>
@@ -8209,13 +8212,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>215</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8225,7 +8228,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B111" s="8">
         <v>46108.75727585648</v>
@@ -8235,7 +8238,7 @@
         <v>46223.595232754626</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8260,13 +8263,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q111" s="8">
         <v>46286</v>
@@ -8286,7 +8289,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B112" s="5">
         <v>46111.5281812037</v>
@@ -8321,13 +8324,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>210</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8337,7 +8340,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B113" s="8">
         <v>46111.528266423615</v>
@@ -8372,13 +8375,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O113" s="9" t="s">
         <v>241</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8388,7 +8391,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B114" s="5">
         <v>46108.757283217594</v>
@@ -8398,7 +8401,7 @@
         <v>46221.10727317129</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>25</v>
@@ -8422,7 +8425,7 @@
         <v>26</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>26</v>
@@ -8435,7 +8438,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B115" s="8">
         <v>46108.757287430555</v>
@@ -8445,16 +8448,16 @@
         <v>46114.63723893519</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I115" s="8">
         <v>46287</v>
@@ -8472,13 +8475,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q115" s="8">
         <v>46287</v>
@@ -8498,7 +8501,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B116" s="5">
         <v>46111.52846596065</v>
@@ -8514,10 +8517,10 @@
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8533,13 +8536,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>210</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8549,7 +8552,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B117" s="8">
         <v>46111.528518067134</v>
@@ -8565,10 +8568,10 @@
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="8">
@@ -8584,13 +8587,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O117" s="9" t="s">
         <v>215</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8600,7 +8603,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B118" s="5">
         <v>46111.531216006944</v>
@@ -8616,10 +8619,10 @@
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I118" s="6"/>
       <c r="J118" s="5">
@@ -8635,13 +8638,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8651,7 +8654,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B119" s="8">
         <v>46111.53129275463</v>
@@ -8667,10 +8670,10 @@
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I119" s="9"/>
       <c r="J119" s="8">
@@ -8686,13 +8689,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O119" s="9" t="s">
         <v>59</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8702,7 +8705,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B120" s="5">
         <v>46111.53134821759</v>
@@ -8712,16 +8715,16 @@
         <v>46114.628886921295</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
@@ -8737,13 +8740,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>62</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8753,7 +8756,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B121" s="8">
         <v>46111.53139942129</v>
@@ -8769,10 +8772,10 @@
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I121" s="9"/>
       <c r="J121" s="8">
@@ -8788,13 +8791,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O121" s="9" t="s">
         <v>65</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8804,7 +8807,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B122" s="5">
         <v>46111.53343819444</v>
@@ -8814,16 +8817,16 @@
         <v>46114.628888437495</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I122" s="6"/>
       <c r="J122" s="5">
@@ -8839,13 +8842,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8855,7 +8858,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B123" s="8">
         <v>46108.75729289352</v>
@@ -8865,7 +8868,7 @@
         <v>46223.59539700231</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -8892,13 +8895,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q123" s="8">
         <v>46288</v>
@@ -8918,7 +8921,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B124" s="5">
         <v>46111.52857409722</v>
@@ -8955,13 +8958,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>210</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8971,7 +8974,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B125" s="8">
         <v>46111.528674016205</v>
@@ -9008,13 +9011,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O125" s="9" t="s">
         <v>215</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -9024,7 +9027,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B126" s="5">
         <v>46111.531552291664</v>
@@ -9061,13 +9064,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9077,7 +9080,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B127" s="8">
         <v>46111.531603344905</v>
@@ -9114,13 +9117,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O127" s="9" t="s">
         <v>59</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9130,7 +9133,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B128" s="5">
         <v>46111.531648379634</v>
@@ -9140,7 +9143,7 @@
         <v>46223.59535668981</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9167,13 +9170,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9183,7 +9186,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B129" s="8">
         <v>46111.531705925925</v>
@@ -9220,13 +9223,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O129" s="9" t="s">
         <v>65</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9236,7 +9239,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B130" s="5">
         <v>46111.533570127314</v>
@@ -9246,7 +9249,7 @@
         <v>46223.59535532407</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9273,13 +9276,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9289,7 +9292,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B131" s="8">
         <v>46108.75729930555</v>
@@ -9299,7 +9302,7 @@
         <v>46221.36200443287</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
@@ -9326,13 +9329,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q131" s="8">
         <v>46293</v>
@@ -9352,7 +9355,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B132" s="5">
         <v>46111.528799872685</v>
@@ -9387,13 +9390,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>210</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9403,7 +9406,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B133" s="8">
         <v>46111.52885179398</v>
@@ -9438,13 +9441,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O133" s="9" t="s">
         <v>215</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9454,7 +9457,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B134" s="5">
         <v>46111.53215439815</v>
@@ -9489,13 +9492,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9505,7 +9508,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B135" s="8">
         <v>46111.53220642361</v>
@@ -9540,13 +9543,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O135" s="9" t="s">
         <v>59</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9556,7 +9559,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B136" s="5">
         <v>46111.532258287036</v>
@@ -9566,7 +9569,7 @@
         <v>46114.629316527775</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9591,13 +9594,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9607,7 +9610,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B137" s="8">
         <v>46111.53231001158</v>
@@ -9642,13 +9645,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O137" s="9" t="s">
         <v>65</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -9658,7 +9661,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B138" s="5">
         <v>46111.53368237268</v>
@@ -9668,7 +9671,7 @@
         <v>46114.62931805555</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9693,13 +9696,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9709,7 +9712,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B139" s="8">
         <v>46108.757304583334</v>
@@ -9719,7 +9722,7 @@
         <v>46240.71896241898</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
@@ -9746,13 +9749,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q139" s="8">
         <v>46294</v>
@@ -9772,7 +9775,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B140" s="5">
         <v>46111.528945011574</v>
@@ -9809,13 +9812,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O140" s="6" t="s">
         <v>210</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9825,7 +9828,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B141" s="8">
         <v>46111.52901092592</v>
@@ -9862,13 +9865,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O141" s="9" t="s">
         <v>215</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -9878,7 +9881,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B142" s="5">
         <v>46111.53247278935</v>
@@ -9915,13 +9918,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9931,7 +9934,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B143" s="8">
         <v>46111.53253350694</v>
@@ -9968,13 +9971,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O143" s="9" t="s">
         <v>59</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -9984,7 +9987,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B144" s="5">
         <v>46111.532638414355</v>
@@ -10021,13 +10024,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>65</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10037,7 +10040,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B145" s="8">
         <v>46111.53258112269</v>
@@ -10047,7 +10050,7 @@
         <v>46114.83037114583</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
@@ -10074,13 +10077,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -10090,7 +10093,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B146" s="5">
         <v>46111.53385627315</v>
@@ -10100,7 +10103,7 @@
         <v>46114.83039427083</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10127,13 +10130,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10143,7 +10146,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B147" s="8">
         <v>46108.757310497684</v>
@@ -10153,7 +10156,7 @@
         <v>46114.62962797454</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>25</v>
@@ -10177,7 +10180,7 @@
         <v>26</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="P147" s="9" t="s">
         <v>26</v>
@@ -10190,7 +10193,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B148" s="5">
         <v>46108.75731366898</v>
@@ -10200,16 +10203,16 @@
         <v>46114.63764361111</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="I148" s="5">
         <v>46295</v>
@@ -10227,13 +10230,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q148" s="5">
         <v>46295</v>
@@ -10253,7 +10256,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B149" s="8">
         <v>46108.75732001157</v>
@@ -10263,16 +10266,16 @@
         <v>46119.74841528935</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="I149" s="8">
         <v>46295</v>
@@ -10290,13 +10293,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q149" s="8">
         <v>46295</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -826,7 +826,7 @@
     <t>Armado</t>
   </si>
   <si>
-    <t xml:space="preserve">Caldereria,Control de calidad Armado </t>
+    <t>Caldereria,Control de calidad Armado  4388</t>
   </si>
   <si>
     <t>1213869987281817</t>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="440">
   <si>
     <t>50001525- ZITRON PERU METRO DE LIMA  ESTACION 07</t>
   </si>
@@ -944,6 +944,9 @@
   </si>
   <si>
     <t>Revestimiento</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1213869987281822</t>
@@ -7225,7 +7228,7 @@
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46223.59523664352</v>
+        <v>46260.19028297454</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>310</v>
@@ -7272,8 +7275,8 @@
       <c r="S93" s="9">
         <v>0</v>
       </c>
-      <c r="T93" s="11" t="s">
-        <v>127</v>
+      <c r="T93" s="12" t="s">
+        <v>311</v>
       </c>
       <c r="U93" s="10" t="s">
         <v>53</v>
@@ -7281,7 +7284,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B94" s="5">
         <v>46111.52720202546</v>
@@ -7321,10 +7324,10 @@
         <v>310</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7334,7 +7337,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B95" s="8">
         <v>46111.52733795139</v>
@@ -7374,10 +7377,10 @@
         <v>310</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7387,7 +7390,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B96" s="5">
         <v>46108.75720997685</v>
@@ -7397,7 +7400,7 @@
         <v>46223.595235995366</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7450,7 +7453,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B97" s="8">
         <v>46111.52790079861</v>
@@ -7487,13 +7490,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7503,7 +7506,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B98" s="5">
         <v>46111.52796104166</v>
@@ -7540,13 +7543,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7556,7 +7559,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B99" s="8">
         <v>46108.75719767361</v>
@@ -7566,7 +7569,7 @@
         <v>46223.5952353125</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7619,7 +7622,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B100" s="5">
         <v>46111.52756633102</v>
@@ -7656,13 +7659,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7672,7 +7675,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B101" s="8">
         <v>46111.527622395835</v>
@@ -7709,13 +7712,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7725,7 +7728,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B102" s="5">
         <v>46108.75720341435</v>
@@ -7735,7 +7738,7 @@
         <v>46223.595234629625</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7788,7 +7791,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B103" s="8">
         <v>46111.52775804398</v>
@@ -7825,13 +7828,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -7841,7 +7844,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B104" s="5">
         <v>46111.52780829861</v>
@@ -7878,13 +7881,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7894,7 +7897,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B105" s="8">
         <v>46108.757191412034</v>
@@ -7904,7 +7907,7 @@
         <v>46223.59523400463</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -7957,7 +7960,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B106" s="5">
         <v>46111.527446493055</v>
@@ -7994,13 +7997,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8010,7 +8013,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B107" s="8">
         <v>46111.52746010417</v>
@@ -8047,13 +8050,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -8063,7 +8066,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B108" s="5">
         <v>46108.757217025464</v>
@@ -8073,7 +8076,7 @@
         <v>46245.73985467592</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8126,7 +8129,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B109" s="8">
         <v>46111.528031932874</v>
@@ -8161,13 +8164,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O109" s="9" t="s">
         <v>210</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8177,7 +8180,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B110" s="5">
         <v>46111.52811128472</v>
@@ -8212,13 +8215,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>215</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8228,7 +8231,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B111" s="8">
         <v>46108.75727585648</v>
@@ -8238,7 +8241,7 @@
         <v>46223.595232754626</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8266,7 +8269,7 @@
         <v>307</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P111" s="9" t="s">
         <v>307</v>
@@ -8289,7 +8292,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B112" s="5">
         <v>46111.5281812037</v>
@@ -8324,13 +8327,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>210</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8340,7 +8343,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B113" s="8">
         <v>46111.528266423615</v>
@@ -8375,13 +8378,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O113" s="9" t="s">
         <v>241</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8391,7 +8394,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B114" s="5">
         <v>46108.757283217594</v>
@@ -8401,7 +8404,7 @@
         <v>46221.10727317129</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>25</v>
@@ -8425,7 +8428,7 @@
         <v>26</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>26</v>
@@ -8438,7 +8441,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B115" s="8">
         <v>46108.757287430555</v>
@@ -8448,16 +8451,16 @@
         <v>46114.63723893519</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I115" s="8">
         <v>46287</v>
@@ -8475,13 +8478,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q115" s="8">
         <v>46287</v>
@@ -8501,7 +8504,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B116" s="5">
         <v>46111.52846596065</v>
@@ -8517,10 +8520,10 @@
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8536,13 +8539,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>210</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8552,7 +8555,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B117" s="8">
         <v>46111.528518067134</v>
@@ -8568,10 +8571,10 @@
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="8">
@@ -8587,13 +8590,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O117" s="9" t="s">
         <v>215</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8603,7 +8606,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B118" s="5">
         <v>46111.531216006944</v>
@@ -8619,10 +8622,10 @@
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I118" s="6"/>
       <c r="J118" s="5">
@@ -8638,13 +8641,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8654,7 +8657,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B119" s="8">
         <v>46111.53129275463</v>
@@ -8670,10 +8673,10 @@
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I119" s="9"/>
       <c r="J119" s="8">
@@ -8689,13 +8692,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O119" s="9" t="s">
         <v>59</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8705,7 +8708,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B120" s="5">
         <v>46111.53134821759</v>
@@ -8715,16 +8718,16 @@
         <v>46114.628886921295</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
@@ -8740,13 +8743,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>62</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8756,7 +8759,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B121" s="8">
         <v>46111.53139942129</v>
@@ -8772,10 +8775,10 @@
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I121" s="9"/>
       <c r="J121" s="8">
@@ -8791,13 +8794,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O121" s="9" t="s">
         <v>65</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8807,7 +8810,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B122" s="5">
         <v>46111.53343819444</v>
@@ -8823,10 +8826,10 @@
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I122" s="6"/>
       <c r="J122" s="5">
@@ -8842,13 +8845,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>304</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8858,7 +8861,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B123" s="8">
         <v>46108.75729289352</v>
@@ -8868,7 +8871,7 @@
         <v>46223.59539700231</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -8895,13 +8898,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q123" s="8">
         <v>46288</v>
@@ -8921,7 +8924,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B124" s="5">
         <v>46111.52857409722</v>
@@ -8958,13 +8961,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>210</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8974,7 +8977,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B125" s="8">
         <v>46111.528674016205</v>
@@ -9011,13 +9014,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O125" s="9" t="s">
         <v>215</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -9027,7 +9030,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B126" s="5">
         <v>46111.531552291664</v>
@@ -9064,13 +9067,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9080,7 +9083,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B127" s="8">
         <v>46111.531603344905</v>
@@ -9117,13 +9120,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O127" s="9" t="s">
         <v>59</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9133,7 +9136,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B128" s="5">
         <v>46111.531648379634</v>
@@ -9143,7 +9146,7 @@
         <v>46223.59535668981</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9170,13 +9173,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9186,7 +9189,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B129" s="8">
         <v>46111.531705925925</v>
@@ -9223,13 +9226,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O129" s="9" t="s">
         <v>65</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9239,7 +9242,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B130" s="5">
         <v>46111.533570127314</v>
@@ -9276,13 +9279,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>305</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9292,7 +9295,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B131" s="8">
         <v>46108.75729930555</v>
@@ -9302,7 +9305,7 @@
         <v>46221.36200443287</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
@@ -9329,13 +9332,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q131" s="8">
         <v>46293</v>
@@ -9355,7 +9358,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B132" s="5">
         <v>46111.528799872685</v>
@@ -9390,13 +9393,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>210</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9406,7 +9409,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B133" s="8">
         <v>46111.52885179398</v>
@@ -9441,13 +9444,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O133" s="9" t="s">
         <v>215</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9457,7 +9460,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B134" s="5">
         <v>46111.53215439815</v>
@@ -9492,13 +9495,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9508,7 +9511,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B135" s="8">
         <v>46111.53220642361</v>
@@ -9543,13 +9546,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O135" s="9" t="s">
         <v>59</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9559,7 +9562,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B136" s="5">
         <v>46111.532258287036</v>
@@ -9569,7 +9572,7 @@
         <v>46114.629316527775</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9594,13 +9597,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9610,7 +9613,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B137" s="8">
         <v>46111.53231001158</v>
@@ -9645,13 +9648,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O137" s="9" t="s">
         <v>65</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -9661,7 +9664,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B138" s="5">
         <v>46111.53368237268</v>
@@ -9671,7 +9674,7 @@
         <v>46114.62931805555</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9696,13 +9699,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O138" s="6" t="s">
         <v>305</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9712,7 +9715,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B139" s="8">
         <v>46108.757304583334</v>
@@ -9722,7 +9725,7 @@
         <v>46240.71896241898</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
@@ -9749,13 +9752,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q139" s="8">
         <v>46294</v>
@@ -9775,7 +9778,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B140" s="5">
         <v>46111.528945011574</v>
@@ -9812,13 +9815,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O140" s="6" t="s">
         <v>210</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9828,7 +9831,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B141" s="8">
         <v>46111.52901092592</v>
@@ -9865,13 +9868,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O141" s="9" t="s">
         <v>215</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -9881,7 +9884,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B142" s="5">
         <v>46111.53247278935</v>
@@ -9918,13 +9921,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9934,7 +9937,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B143" s="8">
         <v>46111.53253350694</v>
@@ -9971,13 +9974,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O143" s="9" t="s">
         <v>59</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -9987,7 +9990,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B144" s="5">
         <v>46111.532638414355</v>
@@ -10024,13 +10027,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>65</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10040,7 +10043,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B145" s="8">
         <v>46111.53258112269</v>
@@ -10050,7 +10053,7 @@
         <v>46114.83037114583</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
@@ -10077,13 +10080,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -10093,7 +10096,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B146" s="5">
         <v>46111.53385627315</v>
@@ -10130,13 +10133,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10146,7 +10149,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B147" s="8">
         <v>46108.757310497684</v>
@@ -10156,7 +10159,7 @@
         <v>46114.62962797454</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>25</v>
@@ -10180,7 +10183,7 @@
         <v>26</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P147" s="9" t="s">
         <v>26</v>
@@ -10193,7 +10196,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B148" s="5">
         <v>46108.75731366898</v>
@@ -10203,16 +10206,16 @@
         <v>46114.63764361111</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="I148" s="5">
         <v>46295</v>
@@ -10230,13 +10233,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q148" s="5">
         <v>46295</v>
@@ -10256,7 +10259,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B149" s="8">
         <v>46108.75732001157</v>
@@ -10266,16 +10269,16 @@
         <v>46119.74841528935</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="I149" s="8">
         <v>46295</v>
@@ -10293,13 +10296,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q149" s="8">
         <v>46295</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1760" uniqueCount="440">
   <si>
     <t>50001525- ZITRON PERU METRO DE LIMA  ESTACION 07</t>
   </si>
@@ -3393,9 +3393,11 @@
       <c r="B28" s="5">
         <v>46108.756897349536</v>
       </c>
-      <c r="C28" s="6"/>
+      <c r="C28" s="5">
+        <v>46260.58066313657</v>
+      </c>
       <c r="D28" s="5">
-        <v>46237.53668097222</v>
+        <v>46260.58066445602</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3651,7 +3653,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46221.115510891206</v>
+        <v>46260.580891192134</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>117</v>
@@ -4519,9 +4521,11 @@
       <c r="B46" s="5">
         <v>46108.75702719907</v>
       </c>
-      <c r="C46" s="6"/>
+      <c r="C46" s="5">
+        <v>46260.58088622685</v>
+      </c>
       <c r="D46" s="5">
-        <v>46211.173315312495</v>
+        <v>46260.58088763889</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>162</v>
@@ -4566,13 +4570,13 @@
         <v>46210</v>
       </c>
       <c r="S46" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T46" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U46" s="10" t="s">
-        <v>53</v>
+      <c r="U46" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -4582,9 +4586,11 @@
       <c r="B47" s="8">
         <v>46108.75703201389</v>
       </c>
-      <c r="C47" s="9"/>
+      <c r="C47" s="8">
+        <v>46260.580722569444</v>
+      </c>
       <c r="D47" s="8">
-        <v>46209.598061192126</v>
+        <v>46260.58072378472</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>107</v>
@@ -4645,9 +4651,11 @@
       <c r="B48" s="5">
         <v>46108.75703761574</v>
       </c>
-      <c r="C48" s="6"/>
+      <c r="C48" s="5">
+        <v>46260.58077260417</v>
+      </c>
       <c r="D48" s="5">
-        <v>46210.16869111111</v>
+        <v>46260.58077393519</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>169</v>
@@ -5007,7 +5015,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46238.167673738426</v>
+        <v>46260.580782777775</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>188</v>
@@ -6070,9 +6078,11 @@
       <c r="B73" s="8">
         <v>46111.50359008102</v>
       </c>
-      <c r="C73" s="9"/>
+      <c r="C73" s="8">
+        <v>46260.580960694446</v>
+      </c>
       <c r="D73" s="8">
-        <v>46114.61935158564</v>
+        <v>46260.58097469907</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>251</v>
@@ -6106,9 +6116,13 @@
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
-      <c r="S73" s="9"/>
+      <c r="S73" s="9">
+        <v>1</v>
+      </c>
       <c r="T73" s="9"/>
-      <c r="U73" s="9"/>
+      <c r="U73" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
@@ -6117,9 +6131,11 @@
       <c r="B74" s="5">
         <v>46111.50404616898</v>
       </c>
-      <c r="C74" s="6"/>
+      <c r="C74" s="5">
+        <v>46260.58055370371</v>
+      </c>
       <c r="D74" s="5">
-        <v>46213.19769318287</v>
+        <v>46260.58079141204</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>254</v>
@@ -6164,13 +6180,13 @@
         <v>46212</v>
       </c>
       <c r="S74" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T74" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U74" s="10" t="s">
-        <v>53</v>
+      <c r="U74" s="12" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -6180,9 +6196,11 @@
       <c r="B75" s="8">
         <v>46111.50406170139</v>
       </c>
-      <c r="C75" s="9"/>
+      <c r="C75" s="8">
+        <v>46260.580943692126</v>
+      </c>
       <c r="D75" s="8">
-        <v>46217.17519608796</v>
+        <v>46260.580961342595</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>259</v>
@@ -6227,13 +6245,13 @@
         <v>46216</v>
       </c>
       <c r="S75" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T75" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U75" s="10" t="s">
-        <v>53</v>
+      <c r="U75" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -6245,7 +6263,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46246.95004469907</v>
+        <v>46260.577887962965</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>262</v>
@@ -6281,7 +6299,9 @@
       <c r="R76" s="6"/>
       <c r="S76" s="6"/>
       <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
+      <c r="U76" s="12" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
@@ -6294,7 +6314,7 @@
         <v>46246.950038807874</v>
       </c>
       <c r="D77" s="8">
-        <v>46246.95005820601</v>
+        <v>46260.58096115741</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>265</v>
@@ -6344,8 +6364,8 @@
       <c r="T77" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U77" s="11" t="s">
-        <v>32</v>
+      <c r="U77" s="12" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -6355,9 +6375,11 @@
       <c r="B78" s="5">
         <v>46111.50560314815</v>
       </c>
-      <c r="C78" s="6"/>
+      <c r="C78" s="5">
+        <v>46260.57748994213</v>
+      </c>
       <c r="D78" s="5">
-        <v>46255.55279185185</v>
+        <v>46260.57750302083</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>270</v>
@@ -6402,13 +6424,13 @@
         <v>46245</v>
       </c>
       <c r="S78" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T78" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U78" s="12" t="s">
-        <v>89</v>
+      <c r="U78" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6418,9 +6440,11 @@
       <c r="B79" s="8">
         <v>46111.52633317129</v>
       </c>
-      <c r="C79" s="9"/>
+      <c r="C79" s="8">
+        <v>46260.57746541667</v>
+      </c>
       <c r="D79" s="8">
-        <v>46246.95004574074</v>
+        <v>46260.57746712963</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>210</v>
@@ -6471,9 +6495,11 @@
       <c r="B80" s="5">
         <v>46111.526644375</v>
       </c>
-      <c r="C80" s="6"/>
+      <c r="C80" s="5">
+        <v>46260.577476342594</v>
+      </c>
       <c r="D80" s="5">
-        <v>46246.95004674769</v>
+        <v>46260.57747775463</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>215</v>
@@ -6524,9 +6550,11 @@
       <c r="B81" s="8">
         <v>46111.50563458333</v>
       </c>
-      <c r="C81" s="9"/>
+      <c r="C81" s="8">
+        <v>46260.57785940972</v>
+      </c>
       <c r="D81" s="8">
-        <v>46248.169711875</v>
+        <v>46260.57788128473</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>278</v>
@@ -6571,13 +6599,13 @@
         <v>46247</v>
       </c>
       <c r="S81" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T81" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U81" s="10" t="s">
-        <v>53</v>
+      <c r="U81" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6587,9 +6615,11 @@
       <c r="B82" s="5">
         <v>46111.526916469906</v>
       </c>
-      <c r="C82" s="6"/>
+      <c r="C82" s="5">
+        <v>46260.57783047453</v>
+      </c>
       <c r="D82" s="5">
-        <v>46247.16738049769</v>
+        <v>46260.57783230324</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>210</v>
@@ -6640,9 +6670,11 @@
       <c r="B83" s="8">
         <v>46111.52699828704</v>
       </c>
-      <c r="C83" s="9"/>
+      <c r="C83" s="8">
+        <v>46260.57784179398</v>
+      </c>
       <c r="D83" s="8">
-        <v>46247.167381701394</v>
+        <v>46260.57784520833</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>215</v>
@@ -7291,7 +7323,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46223.59457288195</v>
+        <v>46260.577836412034</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>210</v>
@@ -7344,7 +7376,7 @@
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46223.594572268514</v>
+        <v>46260.57785292824</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>215</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -7429,7 +7429,7 @@
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46223.595235995366</v>
+        <v>46262.17811915509</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>319</v>
@@ -7476,8 +7476,8 @@
       <c r="S96" s="6">
         <v>0</v>
       </c>
-      <c r="T96" s="11" t="s">
-        <v>127</v>
+      <c r="T96" s="12" t="s">
+        <v>311</v>
       </c>
       <c r="U96" s="10" t="s">
         <v>53</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -469,6 +469,9 @@
     <t>Generación OC motor ot 4287 - 4288,Fabricación motor ot 4287 - 4288,Planos motor proveedor ot 4287 - 4288</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1213833564682558</t>
   </si>
   <si>
@@ -944,9 +947,6 @@
   </si>
   <si>
     <t>Revestimiento</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213869987281822</t>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46211.84653167824</v>
+        <v>46265.17908915509</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>150</v>
@@ -4314,8 +4314,8 @@
       <c r="S42" s="6">
         <v>0</v>
       </c>
-      <c r="T42" s="11" t="s">
-        <v>127</v>
+      <c r="T42" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="U42" s="10" t="s">
         <v>53</v>
@@ -4323,7 +4323,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B43" s="8">
         <v>46108.75700856482</v>
@@ -4335,7 +4335,7 @@
         <v>46182.69343975694</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
@@ -4368,7 +4368,7 @@
         <v>91</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q43" s="8">
         <v>45978</v>
@@ -4388,7 +4388,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B44" s="5">
         <v>46108.757016435186</v>
@@ -4398,7 +4398,7 @@
         <v>46182.69344646991</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
@@ -4428,10 +4428,10 @@
         <v>150</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q44" s="5">
         <v>45999</v>
@@ -4451,7 +4451,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B45" s="8">
         <v>46108.7570218287</v>
@@ -4463,7 +4463,7 @@
         <v>46211.84652803241</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
@@ -4493,10 +4493,10 @@
         <v>150</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q45" s="8">
         <v>45999</v>
@@ -4516,7 +4516,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B46" s="5">
         <v>46108.75702719907</v>
@@ -4528,16 +4528,16 @@
         <v>46260.58088763889</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I46" s="5">
         <v>46195</v>
@@ -4558,7 +4558,7 @@
         <v>117</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>117</v>
@@ -4581,7 +4581,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B47" s="8">
         <v>46108.75703201389</v>
@@ -4599,10 +4599,10 @@
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I47" s="8">
         <v>46195</v>
@@ -4620,13 +4620,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>105</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q47" s="8">
         <v>45985</v>
@@ -4646,7 +4646,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B48" s="5">
         <v>46108.75703761574</v>
@@ -4658,16 +4658,16 @@
         <v>46260.58077393519</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I48" s="5">
         <v>46202</v>
@@ -4685,13 +4685,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>107</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q48" s="5">
         <v>46007</v>
@@ -4711,7 +4711,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B49" s="8">
         <v>46108.75704306713</v>
@@ -4723,16 +4723,16 @@
         <v>46220.16760561343</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I49" s="8">
         <v>46125</v>
@@ -4753,7 +4753,7 @@
         <v>117</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>117</v>
@@ -4776,7 +4776,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B50" s="5">
         <v>46108.75705032407</v>
@@ -4788,16 +4788,16 @@
         <v>46154.86746811343</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I50" s="5">
         <v>46125</v>
@@ -4815,13 +4815,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>109</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4831,7 +4831,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B51" s="8">
         <v>46108.75705728009</v>
@@ -4843,16 +4843,16 @@
         <v>46154.8677641088</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I51" s="8">
         <v>46135</v>
@@ -4870,13 +4870,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4886,7 +4886,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B52" s="5">
         <v>46108.757061435186</v>
@@ -4896,16 +4896,16 @@
         <v>46231.17690494213</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I52" s="5">
         <v>46195</v>
@@ -4926,7 +4926,7 @@
         <v>117</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>117</v>
@@ -4949,7 +4949,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B53" s="8">
         <v>46108.75710696759</v>
@@ -4965,10 +4965,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I53" s="8">
         <v>46195</v>
@@ -4986,13 +4986,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>112</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5008,7 +5008,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B54" s="5">
         <v>46108.757112928244</v>
@@ -5018,16 +5018,16 @@
         <v>46260.580782777775</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I54" s="5">
         <v>46210</v>
@@ -5045,13 +5045,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5061,7 +5061,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B55" s="8">
         <v>46111.50860645833</v>
@@ -5073,7 +5073,7 @@
         <v>46182.69406362269</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
@@ -5103,7 +5103,7 @@
         <v>117</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5126,7 +5126,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B56" s="5">
         <v>46111.508755937495</v>
@@ -5138,7 +5138,7 @@
         <v>46182.69350877315</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -5165,13 +5165,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5181,7 +5181,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B57" s="8">
         <v>46111.508846770834</v>
@@ -5193,7 +5193,7 @@
         <v>46182.69403748843</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
@@ -5220,13 +5220,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5236,7 +5236,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B58" s="5">
         <v>46108.75711900463</v>
@@ -5246,7 +5246,7 @@
         <v>46217.85709320602</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -5270,7 +5270,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5285,7 +5285,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B59" s="8">
         <v>46108.75712325232</v>
@@ -5297,16 +5297,16 @@
         <v>46222.09270599537</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="8">
@@ -5322,13 +5322,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q59" s="8">
         <v>46121</v>
@@ -5348,7 +5348,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B60" s="5">
         <v>46114.552579166666</v>
@@ -5360,16 +5360,16 @@
         <v>46211.84604957176</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I60" s="5">
         <v>46121</v>
@@ -5387,13 +5387,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5403,7 +5403,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B61" s="8">
         <v>46114.552773240735</v>
@@ -5415,16 +5415,16 @@
         <v>46211.846055462964</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I61" s="8">
         <v>46121</v>
@@ -5442,13 +5442,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>77</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5458,7 +5458,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B62" s="5">
         <v>46108.75712855324</v>
@@ -5470,16 +5470,16 @@
         <v>46236.273657928235</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I62" s="5">
         <v>46183</v>
@@ -5497,13 +5497,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q62" s="5">
         <v>46183</v>
@@ -5523,7 +5523,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B63" s="8">
         <v>46114.55286452547</v>
@@ -5535,16 +5535,16 @@
         <v>46217.85704695602</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I63" s="8">
         <v>46183</v>
@@ -5562,13 +5562,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q63" s="9"/>
       <c r="R63" s="9"/>
@@ -5578,7 +5578,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B64" s="5">
         <v>46114.552966620366</v>
@@ -5590,16 +5590,16 @@
         <v>46217.85705476852</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I64" s="5">
         <v>46183</v>
@@ -5617,13 +5617,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5633,7 +5633,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B65" s="8">
         <v>46108.75713383102</v>
@@ -5651,10 +5651,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I65" s="8">
         <v>46190</v>
@@ -5672,13 +5672,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q65" s="8">
         <v>46190</v>
@@ -5698,7 +5698,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B66" s="5">
         <v>46114.55312298611</v>
@@ -5708,16 +5708,16 @@
         <v>46217.85705168982</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="5">
@@ -5736,7 +5736,7 @@
         <v>106</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5749,7 +5749,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B67" s="8">
         <v>46114.553244675924</v>
@@ -5759,16 +5759,16 @@
         <v>46217.85706487269</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="8">
@@ -5787,7 +5787,7 @@
         <v>106</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>26</v>
@@ -5800,7 +5800,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B68" s="5">
         <v>46108.757138761575</v>
@@ -5810,16 +5810,16 @@
         <v>46114.631384050925</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I68" s="5">
         <v>46281</v>
@@ -5837,10 +5837,10 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5863,7 +5863,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B69" s="8">
         <v>46111.55280189815</v>
@@ -5873,16 +5873,16 @@
         <v>46114.62851033565</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -5898,13 +5898,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5914,7 +5914,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B70" s="5">
         <v>46111.55285245371</v>
@@ -5924,16 +5924,16 @@
         <v>46114.62851040509</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -5949,13 +5949,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5965,7 +5965,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B71" s="8">
         <v>46108.75714166666</v>
@@ -5975,7 +5975,7 @@
         <v>46118.545566597226</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -5999,7 +5999,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -6012,7 +6012,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B72" s="5">
         <v>46108.75714454861</v>
@@ -6022,16 +6022,16 @@
         <v>46240.16751462963</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -6047,13 +6047,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q72" s="5">
         <v>46231</v>
@@ -6073,7 +6073,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B73" s="8">
         <v>46111.50359008102</v>
@@ -6085,7 +6085,7 @@
         <v>46260.58097469907</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -6109,7 +6109,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -6126,7 +6126,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B74" s="5">
         <v>46111.50404616898</v>
@@ -6138,16 +6138,16 @@
         <v>46260.58079141204</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I74" s="5">
         <v>46211</v>
@@ -6165,13 +6165,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q74" s="5">
         <v>46211</v>
@@ -6191,7 +6191,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B75" s="8">
         <v>46111.50406170139</v>
@@ -6203,16 +6203,16 @@
         <v>46260.580961342595</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I75" s="8">
         <v>46213</v>
@@ -6230,13 +6230,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q75" s="8">
         <v>46213</v>
@@ -6256,7 +6256,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B76" s="5">
         <v>46111.50543856481</v>
@@ -6266,7 +6266,7 @@
         <v>46260.577887962965</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -6290,7 +6290,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -6305,7 +6305,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B77" s="8">
         <v>46111.505495046295</v>
@@ -6317,16 +6317,16 @@
         <v>46260.58096115741</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I77" s="8">
         <v>46217</v>
@@ -6344,13 +6344,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q77" s="8">
         <v>46217</v>
@@ -6370,7 +6370,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B78" s="5">
         <v>46111.50560314815</v>
@@ -6382,16 +6382,16 @@
         <v>46260.57750302083</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I78" s="5">
         <v>46226</v>
@@ -6409,13 +6409,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q78" s="5">
         <v>46226</v>
@@ -6435,7 +6435,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B79" s="8">
         <v>46111.52633317129</v>
@@ -6447,16 +6447,16 @@
         <v>46260.57746712963</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I79" s="8">
         <v>46226</v>
@@ -6474,13 +6474,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6490,7 +6490,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B80" s="5">
         <v>46111.526644375</v>
@@ -6502,16 +6502,16 @@
         <v>46260.57747775463</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I80" s="5">
         <v>46226</v>
@@ -6529,13 +6529,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6545,7 +6545,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B81" s="8">
         <v>46111.50563458333</v>
@@ -6557,16 +6557,16 @@
         <v>46260.57788128473</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I81" s="8">
         <v>46246</v>
@@ -6584,13 +6584,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q81" s="8">
         <v>46246</v>
@@ -6610,7 +6610,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B82" s="5">
         <v>46111.526916469906</v>
@@ -6622,16 +6622,16 @@
         <v>46260.57783230324</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I82" s="5">
         <v>46246</v>
@@ -6649,13 +6649,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6665,7 +6665,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B83" s="8">
         <v>46111.52699828704</v>
@@ -6677,16 +6677,16 @@
         <v>46260.57784520833</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I83" s="8">
         <v>46246</v>
@@ -6704,13 +6704,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6720,7 +6720,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B84" s="5">
         <v>46108.75714884259</v>
@@ -6730,7 +6730,7 @@
         <v>46221.1155655787</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -6754,7 +6754,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6767,7 +6767,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B85" s="8">
         <v>46108.75715243055</v>
@@ -6777,16 +6777,16 @@
         <v>46185.184959907405</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I85" s="8">
         <v>46183</v>
@@ -6804,13 +6804,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O85" s="9" t="s">
         <v>147</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q85" s="8">
         <v>46183</v>
@@ -6830,7 +6830,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B86" s="5">
         <v>46108.75715773148</v>
@@ -6846,10 +6846,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I86" s="5">
         <v>46239</v>
@@ -6867,13 +6867,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>138</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q86" s="5">
         <v>46239</v>
@@ -6893,7 +6893,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B87" s="8">
         <v>46108.75716349537</v>
@@ -6903,16 +6903,16 @@
         <v>46248.16971915509</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I87" s="8">
         <v>46246</v>
@@ -6930,13 +6930,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O87" s="9" t="s">
         <v>129</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q87" s="8">
         <v>46246</v>
@@ -6956,7 +6956,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B88" s="5">
         <v>46108.75716875</v>
@@ -6966,16 +6966,16 @@
         <v>46111.59782981481</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I88" s="5">
         <v>46273</v>
@@ -6993,13 +6993,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q88" s="5">
         <v>46273</v>
@@ -7019,7 +7019,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B89" s="8">
         <v>46108.75717430556</v>
@@ -7029,16 +7029,16 @@
         <v>46224.18129432871</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I89" s="8">
         <v>46220</v>
@@ -7056,13 +7056,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q89" s="8">
         <v>46220</v>
@@ -7082,7 +7082,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B90" s="5">
         <v>46108.75717877314</v>
@@ -7092,16 +7092,16 @@
         <v>46240.16751195602</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
@@ -7117,13 +7117,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q90" s="5">
         <v>46231</v>
@@ -7143,7 +7143,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B91" s="8">
         <v>46108.822037094906</v>
@@ -7153,16 +7153,16 @@
         <v>46185.18495945602</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I91" s="8">
         <v>46181</v>
@@ -7180,13 +7180,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q91" s="8">
         <v>46183</v>
@@ -7206,7 +7206,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B92" s="5">
         <v>46108.757183124995</v>
@@ -7216,7 +7216,7 @@
         <v>46221.36615074074</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>25</v>
@@ -7240,7 +7240,7 @@
         <v>26</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>26</v>
@@ -7253,7 +7253,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B93" s="8">
         <v>46108.757186296294</v>
@@ -7263,7 +7263,7 @@
         <v>46260.19028297454</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7290,13 +7290,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q93" s="8">
         <v>46248</v>
@@ -7308,7 +7308,7 @@
         <v>0</v>
       </c>
       <c r="T93" s="12" t="s">
-        <v>311</v>
+        <v>152</v>
       </c>
       <c r="U93" s="10" t="s">
         <v>53</v>
@@ -7326,7 +7326,7 @@
         <v>46260.577836412034</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7353,7 +7353,7 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>313</v>
@@ -7379,7 +7379,7 @@
         <v>46260.57785292824</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7406,7 +7406,7 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O95" s="9" t="s">
         <v>316</v>
@@ -7459,13 +7459,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q96" s="5">
         <v>46268</v>
@@ -7477,7 +7477,7 @@
         <v>0</v>
       </c>
       <c r="T96" s="12" t="s">
-        <v>311</v>
+        <v>152</v>
       </c>
       <c r="U96" s="10" t="s">
         <v>53</v>
@@ -7495,7 +7495,7 @@
         <v>46227.72251041667</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7548,7 +7548,7 @@
         <v>46227.72251091435</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7628,13 +7628,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q99" s="8">
         <v>46272</v>
@@ -7664,7 +7664,7 @@
         <v>46227.72251393519</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7717,7 +7717,7 @@
         <v>46227.72251137732</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7797,13 +7797,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q102" s="5">
         <v>46274</v>
@@ -7833,7 +7833,7 @@
         <v>46227.722512928245</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7886,7 +7886,7 @@
         <v>46227.72251365741</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7966,13 +7966,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q105" s="8">
         <v>46276</v>
@@ -8002,7 +8002,7 @@
         <v>46227.722511921296</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -8055,7 +8055,7 @@
         <v>46227.72251247685</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -8135,13 +8135,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q108" s="5">
         <v>46280</v>
@@ -8171,7 +8171,7 @@
         <v>46223.59502533565</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8199,7 +8199,7 @@
         <v>349</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P109" s="9" t="s">
         <v>351</v>
@@ -8222,7 +8222,7 @@
         <v>46223.59502458334</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8250,7 +8250,7 @@
         <v>349</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>353</v>
@@ -8298,13 +8298,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O111" s="9" t="s">
         <v>356</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q111" s="8">
         <v>46286</v>
@@ -8334,7 +8334,7 @@
         <v>46223.595106875</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8362,7 +8362,7 @@
         <v>355</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>358</v>
@@ -8385,7 +8385,7 @@
         <v>46223.59510622685</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8413,7 +8413,7 @@
         <v>355</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P113" s="9" t="s">
         <v>360</v>
@@ -8546,7 +8546,7 @@
         <v>46114.62888387732</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8574,7 +8574,7 @@
         <v>365</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>370</v>
@@ -8597,7 +8597,7 @@
         <v>46114.62888469908</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8625,7 +8625,7 @@
         <v>365</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P117" s="9" t="s">
         <v>372</v>
@@ -8852,7 +8852,7 @@
         <v>46114.628888437495</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8880,7 +8880,7 @@
         <v>365</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>383</v>
@@ -8966,7 +8966,7 @@
         <v>46223.595359328705</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8996,7 +8996,7 @@
         <v>385</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>388</v>
@@ -9019,7 +9019,7 @@
         <v>46223.59535869213</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -9049,7 +9049,7 @@
         <v>385</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P125" s="9" t="s">
         <v>390</v>
@@ -9284,7 +9284,7 @@
         <v>46223.59535532407</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9314,7 +9314,7 @@
         <v>385</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>400</v>
@@ -9343,10 +9343,10 @@
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I131" s="8">
         <v>46293</v>
@@ -9400,16 +9400,16 @@
         <v>46114.62931347222</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9428,7 +9428,7 @@
         <v>402</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>405</v>
@@ -9451,16 +9451,16 @@
         <v>46114.62931429398</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I133" s="9"/>
       <c r="J133" s="8">
@@ -9479,7 +9479,7 @@
         <v>402</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P133" s="9" t="s">
         <v>407</v>
@@ -9508,10 +9508,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9559,10 +9559,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I135" s="9"/>
       <c r="J135" s="8">
@@ -9610,10 +9610,10 @@
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9661,10 +9661,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I137" s="9"/>
       <c r="J137" s="8">
@@ -9712,10 +9712,10 @@
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
@@ -9734,7 +9734,7 @@
         <v>402</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P138" s="6" t="s">
         <v>418</v>
@@ -9763,10 +9763,10 @@
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I139" s="8">
         <v>46294</v>
@@ -9820,16 +9820,16 @@
         <v>46114.830281076385</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I140" s="5">
         <v>46294</v>
@@ -9850,7 +9850,7 @@
         <v>420</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>423</v>
@@ -9873,16 +9873,16 @@
         <v>46114.830302789356</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I141" s="8">
         <v>46294</v>
@@ -9903,7 +9903,7 @@
         <v>420</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P141" s="9" t="s">
         <v>420</v>
@@ -9932,10 +9932,10 @@
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I142" s="5">
         <v>46294</v>
@@ -9985,10 +9985,10 @@
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I143" s="8">
         <v>46294</v>
@@ -10038,10 +10038,10 @@
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I144" s="5">
         <v>46294</v>
@@ -10091,10 +10091,10 @@
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I145" s="8">
         <v>46294</v>
@@ -10138,16 +10138,16 @@
         <v>46114.83039427083</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I146" s="5">
         <v>46294</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -7598,7 +7598,7 @@
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46223.5952353125</v>
+        <v>46266.176813287035</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>327</v>
@@ -7645,8 +7645,8 @@
       <c r="S99" s="9">
         <v>0</v>
       </c>
-      <c r="T99" s="11" t="s">
-        <v>127</v>
+      <c r="T99" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="U99" s="10" t="s">
         <v>53</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -6963,7 +6963,7 @@
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46111.59782981481</v>
+        <v>46267.17843465278</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>298</v>
@@ -7010,8 +7010,8 @@
       <c r="S88" s="6">
         <v>0</v>
       </c>
-      <c r="T88" s="11" t="s">
-        <v>127</v>
+      <c r="T88" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="U88" s="10" t="s">
         <v>53</v>
@@ -7260,7 +7260,7 @@
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46260.19028297454</v>
+        <v>46267.16748222223</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>311</v>
@@ -7323,7 +7323,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46260.577836412034</v>
+        <v>46267.167487708335</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>211</v>
@@ -7376,7 +7376,7 @@
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46260.57785292824</v>
+        <v>46267.167488796294</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>216</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -7260,7 +7260,7 @@
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46267.16748222223</v>
+        <v>46268.17428453703</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>311</v>
@@ -7307,8 +7307,8 @@
       <c r="S93" s="9">
         <v>0</v>
       </c>
-      <c r="T93" s="12" t="s">
-        <v>152</v>
+      <c r="T93" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U93" s="10" t="s">
         <v>53</v>
@@ -7767,7 +7767,7 @@
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46223.595234629625</v>
+        <v>46268.167859270834</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>335</v>
@@ -7814,8 +7814,8 @@
       <c r="S102" s="6">
         <v>0</v>
       </c>
-      <c r="T102" s="11" t="s">
-        <v>127</v>
+      <c r="T102" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="U102" s="10" t="s">
         <v>53</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -7429,7 +7429,7 @@
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46262.17811915509</v>
+        <v>46269.16768288195</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>319</v>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46227.72251041667</v>
+        <v>46269.167690648144</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>211</v>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46227.72251091435</v>
+        <v>46269.16769188657</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>216</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -7429,7 +7429,7 @@
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46269.16768288195</v>
+        <v>46270.18529125</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>319</v>
@@ -7476,8 +7476,8 @@
       <c r="S96" s="6">
         <v>0</v>
       </c>
-      <c r="T96" s="12" t="s">
-        <v>152</v>
+      <c r="T96" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U96" s="10" t="s">
         <v>53</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -4267,7 +4267,7 @@
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46265.17908915509</v>
+        <v>46272.16711635416</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>150</v>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46182.69344646991</v>
+        <v>46272.16711458333</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>157</v>
@@ -7936,7 +7936,7 @@
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46223.59523400463</v>
+        <v>46272.1296174537</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>341</v>
@@ -7983,8 +7983,8 @@
       <c r="S105" s="9">
         <v>0</v>
       </c>
-      <c r="T105" s="11" t="s">
-        <v>127</v>
+      <c r="T105" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="U105" s="10" t="s">
         <v>53</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -469,445 +469,445 @@
     <t>Generación OC motor ot 4287 - 4288,Fabricación motor ot 4287 - 4288,Planos motor proveedor ot 4287 - 4288</t>
   </si>
   <si>
+    <t>1213833564682558</t>
+  </si>
+  <si>
+    <t>Generación OC motor ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>Generación OC motor,Motor ot 4287 - 4288,Fabricación motor ot 4287 - 4288,Planos motor proveedor ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>1213833564685848</t>
+  </si>
+  <si>
+    <t>Fabricación motor ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>Motor ot 4287 - 4288,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1213833564685869</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>Motor ot 4287 - 4288,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>1213833777483152</t>
+  </si>
+  <si>
+    <t>Materiales a codigo // compras locales aprovisionamientomiento: ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC materiales ot 4287 - 4288,Fabricacion a codigo y compras locales ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>1213833777483168</t>
+  </si>
+  <si>
+    <t>Materiales a codigo // compras locales aprovisionamientomiento: ot 4287 - 4288,Fabricacion a codigo y compras locales ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>1213833564688412</t>
+  </si>
+  <si>
+    <t>Fabricacion a codigo y compras locales ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>Materiales a codigo // compras locales aprovisionamientomiento: ot 4287 - 4288,Recepcion materiales a codigos // compras locales aprovisionamiento,Fabricacion estructura proveedor externo ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>1213833763284961</t>
+  </si>
+  <si>
+    <t>Sensores</t>
+  </si>
+  <si>
+    <t>Generacion OC Sensor,Fabricacion Sensores</t>
+  </si>
+  <si>
+    <t>1213833763284977</t>
+  </si>
+  <si>
+    <t>Generacion OC Sensor</t>
+  </si>
+  <si>
+    <t>Sensores,Fabricacion Sensores</t>
+  </si>
+  <si>
+    <t>1213833777489751</t>
+  </si>
+  <si>
+    <t>Fabricacion Sensores</t>
+  </si>
+  <si>
+    <t>Recepción Sensores,Sensores</t>
+  </si>
+  <si>
+    <t>1213833777489767</t>
+  </si>
+  <si>
+    <t>Fabricacion Externa ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Generacion OC Fabricacion Externa ot 4287 - 4288,Fabricacion estructura proveedor externo ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>1213833564667630</t>
+  </si>
+  <si>
+    <t>Fabricacion Externa ot 4287 - 4288,Fabricacion estructura proveedor externo ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>1213833763295351</t>
+  </si>
+  <si>
+    <t>Fabricacion estructura proveedor externo ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>Check Planos,Fabricacion a codigo y compras locales ot 4287 - 4288, Generacion OC Fabricacion Externa ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>Control de calidad Fabricación externa,Fabricacion Externa ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>1213869987281796</t>
+  </si>
+  <si>
+    <t>Atenuador ot 4289</t>
+  </si>
+  <si>
+    <t>Propuesta Atenuadores ,Generacion oc Atenuador  ot 4289,Fabricacion atenuador ot 4289</t>
+  </si>
+  <si>
+    <t>1213869987281797</t>
+  </si>
+  <si>
+    <t>Generacion oc Atenuador  ot 4289</t>
+  </si>
+  <si>
+    <t>Fabricacion atenuador ot 4289,Atenuador ot 4289</t>
+  </si>
+  <si>
+    <t>1213869987281798</t>
+  </si>
+  <si>
+    <t>Fabricacion atenuador ot 4289</t>
+  </si>
+  <si>
+    <t>Atenuadores,Atenuador ot 4289</t>
+  </si>
+  <si>
+    <t>1213833564706217</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1213833564706230</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:,Check Planos</t>
+  </si>
+  <si>
+    <t>1213899500210867</t>
+  </si>
+  <si>
+    <t>OT 4287 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Planos preliminar,OT 4287 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213899500210869</t>
+  </si>
+  <si>
+    <t>OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>Planos preliminar,OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>1213833763300853</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>Check Planos,Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t>1213899500210870</t>
+  </si>
+  <si>
+    <t>OT 4287 ZVR 1-14-42/4,Planos motor proveedor ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>Planos definitivos,OT 4287 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213899500210871</t>
+  </si>
+  <si>
+    <t>OT 4288 ZVR1-14-30/4,Planos motor proveedor ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>Planos definitivos,OT4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>1213833763300879</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Planos preliminar</t>
+  </si>
+  <si>
+    <t>OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,propuesta compras a codigo // aprovisionamiento ot 4287 - 4288,Propuesta Fabricacion Externa ot 4287 - 4288,Fabricacion estructura proveedor externo ot 4287 - 4288</t>
+  </si>
+  <si>
+    <t>1213899500210872</t>
+  </si>
+  <si>
+    <t>1213899500210873</t>
+  </si>
+  <si>
+    <t>OT4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>1213833622855505</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4287 ZVR 1-14-42/4,OT  4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>1213869987281952</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT,OT 4287 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213869987281953</t>
+  </si>
+  <si>
+    <t>OT  4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT,OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>1213833622855516</t>
+  </si>
+  <si>
+    <t>Control de calidad</t>
+  </si>
+  <si>
+    <t>Control de calidad Fabricación externa</t>
+  </si>
+  <si>
+    <t>1213833622855625</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>Control de calidad,Recepcion Fabricacion externa</t>
+  </si>
+  <si>
+    <t>1213840446207872</t>
+  </si>
+  <si>
+    <t>Bodega</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
+  </si>
+  <si>
+    <t>1213840446207876</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamient,Bodega</t>
+  </si>
+  <si>
+    <t>1213840446207878</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
+  </si>
+  <si>
+    <t>Bodega,Preparacion materiales</t>
+  </si>
+  <si>
+    <t>1213869987281780</t>
+  </si>
+  <si>
+    <t>Caldereria</t>
+  </si>
+  <si>
+    <t>Preparacion materiales,Armado,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1213869987281782</t>
+  </si>
+  <si>
+    <t>Preparacion materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>Caldereria,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>1213869987281784</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>Caldereria,Control de calidad Armado  4388</t>
+  </si>
+  <si>
+    <t>1213869987281817</t>
+  </si>
+  <si>
+    <t>Preparacion materiales,Check Planos</t>
+  </si>
+  <si>
+    <t>Armado,OT 4287 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213869987281819</t>
+  </si>
+  <si>
+    <t>Armado,OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>1213869987281786</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1213869987281820</t>
+  </si>
+  <si>
+    <t>OT 4287 ZVR 1-14-42/4,Check Planos</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,OT 4287 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213869987281821</t>
+  </si>
+  <si>
+    <t>OT 4288 ZVR1-14-30/4,Check Planos</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>1213833622855646</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe,Recepcion motor,Recepcion Fabricacion externa,Recepcion Rodete,Recepcion Tableros y componentes electricos</t>
+  </si>
+  <si>
+    <t>1213833763304341</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>Bodega:,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>1213833763304362</t>
+  </si>
+  <si>
+    <t>Bodega:,OT 4290 - TABLERO VDF ABB ACS880-17,OT 4291- TABLERO PLC,OT 4292- TABLERO BOTONERA ,OT 4293-COMPONENTES TABLERO COMPUERTAS</t>
+  </si>
+  <si>
+    <t>1213833806791953</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>Bodega:,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213833564712053</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213833564682558</t>
-  </si>
-  <si>
-    <t>Generación OC motor ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>Generación OC motor,Motor ot 4287 - 4288,Fabricación motor ot 4287 - 4288,Planos motor proveedor ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>1213833564685848</t>
-  </si>
-  <si>
-    <t>Fabricación motor ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>Motor ot 4287 - 4288,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1213833564685869</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>Motor ot 4287 - 4288,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>1213833777483152</t>
-  </si>
-  <si>
-    <t>Materiales a codigo // compras locales aprovisionamientomiento: ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC materiales ot 4287 - 4288,Fabricacion a codigo y compras locales ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>1213833777483168</t>
-  </si>
-  <si>
-    <t>Materiales a codigo // compras locales aprovisionamientomiento: ot 4287 - 4288,Fabricacion a codigo y compras locales ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>1213833564688412</t>
-  </si>
-  <si>
-    <t>Fabricacion a codigo y compras locales ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>Materiales a codigo // compras locales aprovisionamientomiento: ot 4287 - 4288,Recepcion materiales a codigos // compras locales aprovisionamiento,Fabricacion estructura proveedor externo ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>1213833763284961</t>
-  </si>
-  <si>
-    <t>Sensores</t>
-  </si>
-  <si>
-    <t>Generacion OC Sensor,Fabricacion Sensores</t>
-  </si>
-  <si>
-    <t>1213833763284977</t>
-  </si>
-  <si>
-    <t>Generacion OC Sensor</t>
-  </si>
-  <si>
-    <t>Sensores,Fabricacion Sensores</t>
-  </si>
-  <si>
-    <t>1213833777489751</t>
-  </si>
-  <si>
-    <t>Fabricacion Sensores</t>
-  </si>
-  <si>
-    <t>Recepción Sensores,Sensores</t>
-  </si>
-  <si>
-    <t>1213833777489767</t>
-  </si>
-  <si>
-    <t>Fabricacion Externa ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Generacion OC Fabricacion Externa ot 4287 - 4288,Fabricacion estructura proveedor externo ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>1213833564667630</t>
-  </si>
-  <si>
-    <t>Fabricacion Externa ot 4287 - 4288,Fabricacion estructura proveedor externo ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>1213833763295351</t>
-  </si>
-  <si>
-    <t>Fabricacion estructura proveedor externo ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>Check Planos,Fabricacion a codigo y compras locales ot 4287 - 4288, Generacion OC Fabricacion Externa ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>Control de calidad Fabricación externa,Fabricacion Externa ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>1213869987281796</t>
-  </si>
-  <si>
-    <t>Atenuador ot 4289</t>
-  </si>
-  <si>
-    <t>Propuesta Atenuadores ,Generacion oc Atenuador  ot 4289,Fabricacion atenuador ot 4289</t>
-  </si>
-  <si>
-    <t>1213869987281797</t>
-  </si>
-  <si>
-    <t>Generacion oc Atenuador  ot 4289</t>
-  </si>
-  <si>
-    <t>Fabricacion atenuador ot 4289,Atenuador ot 4289</t>
-  </si>
-  <si>
-    <t>1213869987281798</t>
-  </si>
-  <si>
-    <t>Fabricacion atenuador ot 4289</t>
-  </si>
-  <si>
-    <t>Atenuadores,Atenuador ot 4289</t>
-  </si>
-  <si>
-    <t>1213833564706217</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1213833564706230</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:,Check Planos</t>
-  </si>
-  <si>
-    <t>1213899500210867</t>
-  </si>
-  <si>
-    <t>OT 4287 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Planos preliminar,OT 4287 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213899500210869</t>
-  </si>
-  <si>
-    <t>OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>Planos preliminar,OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>1213833763300853</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>Check Planos,Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t>1213899500210870</t>
-  </si>
-  <si>
-    <t>OT 4287 ZVR 1-14-42/4,Planos motor proveedor ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>Planos definitivos,OT 4287 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213899500210871</t>
-  </si>
-  <si>
-    <t>OT 4288 ZVR1-14-30/4,Planos motor proveedor ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>Planos definitivos,OT4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>1213833763300879</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Planos preliminar</t>
-  </si>
-  <si>
-    <t>OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,propuesta compras a codigo // aprovisionamiento ot 4287 - 4288,Propuesta Fabricacion Externa ot 4287 - 4288,Fabricacion estructura proveedor externo ot 4287 - 4288</t>
-  </si>
-  <si>
-    <t>1213899500210872</t>
-  </si>
-  <si>
-    <t>1213899500210873</t>
-  </si>
-  <si>
-    <t>OT4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>1213833622855505</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4287 ZVR 1-14-42/4,OT  4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>1213869987281952</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT,OT 4287 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213869987281953</t>
-  </si>
-  <si>
-    <t>OT  4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT,OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>1213833622855516</t>
-  </si>
-  <si>
-    <t>Control de calidad</t>
-  </si>
-  <si>
-    <t>Control de calidad Fabricación externa</t>
-  </si>
-  <si>
-    <t>1213833622855625</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>Control de calidad,Recepcion Fabricacion externa</t>
-  </si>
-  <si>
-    <t>1213840446207872</t>
-  </si>
-  <si>
-    <t>Bodega</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
-  </si>
-  <si>
-    <t>1213840446207876</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamient,Bodega</t>
-  </si>
-  <si>
-    <t>1213840446207878</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
-  </si>
-  <si>
-    <t>Bodega,Preparacion materiales</t>
-  </si>
-  <si>
-    <t>1213869987281780</t>
-  </si>
-  <si>
-    <t>Caldereria</t>
-  </si>
-  <si>
-    <t>Preparacion materiales,Armado,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1213869987281782</t>
-  </si>
-  <si>
-    <t>Preparacion materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>Caldereria,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>1213869987281784</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>Caldereria,Control de calidad Armado  4388</t>
-  </si>
-  <si>
-    <t>1213869987281817</t>
-  </si>
-  <si>
-    <t>Preparacion materiales,Check Planos</t>
-  </si>
-  <si>
-    <t>Armado,OT 4287 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213869987281819</t>
-  </si>
-  <si>
-    <t>Armado,OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>1213869987281786</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1213869987281820</t>
-  </si>
-  <si>
-    <t>OT 4287 ZVR 1-14-42/4,Check Planos</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,OT 4287 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213869987281821</t>
-  </si>
-  <si>
-    <t>OT 4288 ZVR1-14-30/4,Check Planos</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>1213833622855646</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe,Recepcion motor,Recepcion Fabricacion externa,Recepcion Rodete,Recepcion Tableros y componentes electricos</t>
-  </si>
-  <si>
-    <t>1213833763304341</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>Bodega:,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>1213833763304362</t>
-  </si>
-  <si>
-    <t>Bodega:,OT 4290 - TABLERO VDF ABB ACS880-17,OT 4291- TABLERO PLC,OT 4292- TABLERO BOTONERA ,OT 4293-COMPONENTES TABLERO COMPUERTAS</t>
-  </si>
-  <si>
-    <t>1213833806791953</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>Bodega:,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213833564712053</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
   </si>
   <si>
     <t>1213833564713244</t>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46272.16711635416</v>
+        <v>46273.135429918984</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>150</v>
@@ -4314,8 +4314,8 @@
       <c r="S42" s="6">
         <v>0</v>
       </c>
-      <c r="T42" s="12" t="s">
-        <v>152</v>
+      <c r="T42" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U42" s="10" t="s">
         <v>53</v>
@@ -4323,7 +4323,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B43" s="8">
         <v>46108.75700856482</v>
@@ -4335,7 +4335,7 @@
         <v>46182.69343975694</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
@@ -4368,7 +4368,7 @@
         <v>91</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q43" s="8">
         <v>45978</v>
@@ -4388,7 +4388,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B44" s="5">
         <v>46108.757016435186</v>
@@ -4398,7 +4398,7 @@
         <v>46272.16711458333</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
@@ -4428,10 +4428,10 @@
         <v>150</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q44" s="5">
         <v>45999</v>
@@ -4451,7 +4451,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B45" s="8">
         <v>46108.7570218287</v>
@@ -4463,7 +4463,7 @@
         <v>46211.84652803241</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
@@ -4493,10 +4493,10 @@
         <v>150</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q45" s="8">
         <v>45999</v>
@@ -4516,7 +4516,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B46" s="5">
         <v>46108.75702719907</v>
@@ -4528,16 +4528,16 @@
         <v>46260.58088763889</v>
       </c>
       <c r="E46" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="6" t="s">
+      <c r="H46" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="I46" s="5">
         <v>46195</v>
@@ -4558,7 +4558,7 @@
         <v>117</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>117</v>
@@ -4581,7 +4581,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B47" s="8">
         <v>46108.75703201389</v>
@@ -4599,10 +4599,10 @@
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="H47" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="I47" s="8">
         <v>46195</v>
@@ -4620,13 +4620,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>105</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q47" s="8">
         <v>45985</v>
@@ -4646,7 +4646,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B48" s="5">
         <v>46108.75703761574</v>
@@ -4658,16 +4658,16 @@
         <v>46260.58077393519</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="I48" s="5">
         <v>46202</v>
@@ -4685,13 +4685,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>107</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q48" s="5">
         <v>46007</v>
@@ -4711,7 +4711,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B49" s="8">
         <v>46108.75704306713</v>
@@ -4723,16 +4723,16 @@
         <v>46220.16760561343</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="H49" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="I49" s="8">
         <v>46125</v>
@@ -4753,7 +4753,7 @@
         <v>117</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>117</v>
@@ -4776,7 +4776,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B50" s="5">
         <v>46108.75705032407</v>
@@ -4788,16 +4788,16 @@
         <v>46154.86746811343</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="I50" s="5">
         <v>46125</v>
@@ -4815,13 +4815,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>109</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4831,7 +4831,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B51" s="8">
         <v>46108.75705728009</v>
@@ -4843,16 +4843,16 @@
         <v>46154.8677641088</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="I51" s="8">
         <v>46135</v>
@@ -4870,13 +4870,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4886,7 +4886,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B52" s="5">
         <v>46108.757061435186</v>
@@ -4896,16 +4896,16 @@
         <v>46231.17690494213</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
+      <c r="H52" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="I52" s="5">
         <v>46195</v>
@@ -4926,7 +4926,7 @@
         <v>117</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>117</v>
@@ -4949,7 +4949,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B53" s="8">
         <v>46108.75710696759</v>
@@ -4965,10 +4965,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="H53" s="9" t="s">
         <v>183</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>184</v>
       </c>
       <c r="I53" s="8">
         <v>46195</v>
@@ -4986,13 +4986,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>112</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5008,7 +5008,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B54" s="5">
         <v>46108.757112928244</v>
@@ -5018,16 +5018,16 @@
         <v>46260.580782777775</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="I54" s="5">
         <v>46210</v>
@@ -5045,13 +5045,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O54" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="P54" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="P54" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5061,7 +5061,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B55" s="8">
         <v>46111.50860645833</v>
@@ -5073,7 +5073,7 @@
         <v>46182.69406362269</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
@@ -5103,7 +5103,7 @@
         <v>117</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5126,7 +5126,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B56" s="5">
         <v>46111.508755937495</v>
@@ -5138,7 +5138,7 @@
         <v>46182.69350877315</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -5165,13 +5165,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5181,7 +5181,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B57" s="8">
         <v>46111.508846770834</v>
@@ -5193,7 +5193,7 @@
         <v>46182.69403748843</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
@@ -5220,13 +5220,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5236,7 +5236,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B58" s="5">
         <v>46108.75711900463</v>
@@ -5246,7 +5246,7 @@
         <v>46217.85709320602</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -5270,7 +5270,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5285,7 +5285,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B59" s="8">
         <v>46108.75712325232</v>
@@ -5297,16 +5297,16 @@
         <v>46222.09270599537</v>
       </c>
       <c r="E59" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="F59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="9" t="s">
+      <c r="H59" s="9" t="s">
         <v>206</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>207</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="8">
@@ -5322,13 +5322,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O59" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="P59" s="9" t="s">
         <v>208</v>
-      </c>
-      <c r="P59" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="Q59" s="8">
         <v>46121</v>
@@ -5348,7 +5348,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B60" s="5">
         <v>46114.552579166666</v>
@@ -5360,16 +5360,16 @@
         <v>46211.84604957176</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
+      <c r="H60" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="I60" s="5">
         <v>46121</v>
@@ -5387,13 +5387,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5403,7 +5403,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B61" s="8">
         <v>46114.552773240735</v>
@@ -5415,16 +5415,16 @@
         <v>46211.846055462964</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>213</v>
       </c>
       <c r="I61" s="8">
         <v>46121</v>
@@ -5442,13 +5442,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>77</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5458,7 +5458,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B62" s="5">
         <v>46108.75712855324</v>
@@ -5470,16 +5470,16 @@
         <v>46236.273657928235</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>206</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>207</v>
       </c>
       <c r="I62" s="5">
         <v>46183</v>
@@ -5497,13 +5497,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O62" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="P62" s="6" t="s">
         <v>220</v>
-      </c>
-      <c r="P62" s="6" t="s">
-        <v>221</v>
       </c>
       <c r="Q62" s="5">
         <v>46183</v>
@@ -5523,7 +5523,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B63" s="8">
         <v>46114.55286452547</v>
@@ -5535,16 +5535,16 @@
         <v>46217.85704695602</v>
       </c>
       <c r="E63" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="F63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="9" t="s">
+      <c r="H63" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>213</v>
       </c>
       <c r="I63" s="8">
         <v>46183</v>
@@ -5562,13 +5562,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O63" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="P63" s="9" t="s">
         <v>223</v>
-      </c>
-      <c r="P63" s="9" t="s">
-        <v>224</v>
       </c>
       <c r="Q63" s="9"/>
       <c r="R63" s="9"/>
@@ -5578,7 +5578,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B64" s="5">
         <v>46114.552966620366</v>
@@ -5590,16 +5590,16 @@
         <v>46217.85705476852</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="I64" s="5">
         <v>46183</v>
@@ -5617,13 +5617,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O64" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5633,7 +5633,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B65" s="8">
         <v>46108.75713383102</v>
@@ -5651,10 +5651,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>213</v>
       </c>
       <c r="I65" s="8">
         <v>46190</v>
@@ -5672,13 +5672,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O65" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="P65" s="9" t="s">
         <v>229</v>
-      </c>
-      <c r="P65" s="9" t="s">
-        <v>230</v>
       </c>
       <c r="Q65" s="8">
         <v>46190</v>
@@ -5698,7 +5698,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B66" s="5">
         <v>46114.55312298611</v>
@@ -5708,16 +5708,16 @@
         <v>46217.85705168982</v>
       </c>
       <c r="E66" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G66" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="F66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G66" s="6" t="s">
+      <c r="H66" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="5">
@@ -5736,7 +5736,7 @@
         <v>106</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5749,7 +5749,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B67" s="8">
         <v>46114.553244675924</v>
@@ -5759,16 +5759,16 @@
         <v>46217.85706487269</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>213</v>
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="8">
@@ -5787,7 +5787,7 @@
         <v>106</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>26</v>
@@ -5800,7 +5800,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B68" s="5">
         <v>46108.757138761575</v>
@@ -5810,16 +5810,16 @@
         <v>46114.631384050925</v>
       </c>
       <c r="E68" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G68" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="F68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G68" s="6" t="s">
+      <c r="H68" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="I68" s="5">
         <v>46281</v>
@@ -5837,10 +5837,10 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5863,7 +5863,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B69" s="8">
         <v>46111.55280189815</v>
@@ -5873,16 +5873,16 @@
         <v>46114.62851033565</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -5898,13 +5898,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5914,7 +5914,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B70" s="5">
         <v>46111.55285245371</v>
@@ -5924,16 +5924,16 @@
         <v>46114.62851040509</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -5949,13 +5949,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5965,7 +5965,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B71" s="8">
         <v>46108.75714166666</v>
@@ -5975,7 +5975,7 @@
         <v>46118.545566597226</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -5999,7 +5999,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -6012,7 +6012,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B72" s="5">
         <v>46108.75714454861</v>
@@ -6022,16 +6022,16 @@
         <v>46240.16751462963</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>248</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>249</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -6047,13 +6047,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q72" s="5">
         <v>46231</v>
@@ -6073,7 +6073,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B73" s="8">
         <v>46111.50359008102</v>
@@ -6085,7 +6085,7 @@
         <v>46260.58097469907</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -6109,7 +6109,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -6126,7 +6126,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B74" s="5">
         <v>46111.50404616898</v>
@@ -6138,16 +6138,16 @@
         <v>46260.58079141204</v>
       </c>
       <c r="E74" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G74" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="F74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G74" s="6" t="s">
+      <c r="H74" s="6" t="s">
         <v>256</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>257</v>
       </c>
       <c r="I74" s="5">
         <v>46211</v>
@@ -6165,13 +6165,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q74" s="5">
         <v>46211</v>
@@ -6191,7 +6191,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B75" s="8">
         <v>46111.50406170139</v>
@@ -6203,16 +6203,16 @@
         <v>46260.580961342595</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="H75" s="9" t="s">
         <v>248</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>249</v>
       </c>
       <c r="I75" s="8">
         <v>46213</v>
@@ -6230,13 +6230,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q75" s="8">
         <v>46213</v>
@@ -6256,7 +6256,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B76" s="5">
         <v>46111.50543856481</v>
@@ -6266,7 +6266,7 @@
         <v>46260.577887962965</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -6290,7 +6290,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -6305,7 +6305,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B77" s="8">
         <v>46111.505495046295</v>
@@ -6317,16 +6317,16 @@
         <v>46260.58096115741</v>
       </c>
       <c r="E77" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G77" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="F77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G77" s="9" t="s">
+      <c r="H77" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="I77" s="8">
         <v>46217</v>
@@ -6344,13 +6344,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q77" s="8">
         <v>46217</v>
@@ -6370,7 +6370,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B78" s="5">
         <v>46111.50560314815</v>
@@ -6382,16 +6382,16 @@
         <v>46260.57750302083</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="I78" s="5">
         <v>46226</v>
@@ -6409,13 +6409,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q78" s="5">
         <v>46226</v>
@@ -6435,7 +6435,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B79" s="8">
         <v>46111.52633317129</v>
@@ -6447,16 +6447,16 @@
         <v>46260.57746712963</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H79" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="I79" s="8">
         <v>46226</v>
@@ -6474,13 +6474,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O79" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="P79" s="9" t="s">
         <v>274</v>
-      </c>
-      <c r="P79" s="9" t="s">
-        <v>275</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6490,7 +6490,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B80" s="5">
         <v>46111.526644375</v>
@@ -6502,16 +6502,16 @@
         <v>46260.57747775463</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="I80" s="5">
         <v>46226</v>
@@ -6529,13 +6529,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6545,7 +6545,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B81" s="8">
         <v>46111.50563458333</v>
@@ -6557,16 +6557,16 @@
         <v>46260.57788128473</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="H81" s="9" t="s">
         <v>248</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>249</v>
       </c>
       <c r="I81" s="8">
         <v>46246</v>
@@ -6584,13 +6584,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q81" s="8">
         <v>46246</v>
@@ -6610,7 +6610,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B82" s="5">
         <v>46111.526916469906</v>
@@ -6622,16 +6622,16 @@
         <v>46260.57783230324</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>248</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>249</v>
       </c>
       <c r="I82" s="5">
         <v>46246</v>
@@ -6649,13 +6649,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O82" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="P82" s="6" t="s">
         <v>281</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>282</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6665,7 +6665,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B83" s="8">
         <v>46111.52699828704</v>
@@ -6677,16 +6677,16 @@
         <v>46260.57784520833</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="H83" s="9" t="s">
         <v>248</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>249</v>
       </c>
       <c r="I83" s="8">
         <v>46246</v>
@@ -6704,13 +6704,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O83" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="P83" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="P83" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6720,7 +6720,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B84" s="5">
         <v>46108.75714884259</v>
@@ -6730,7 +6730,7 @@
         <v>46221.1155655787</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -6754,7 +6754,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6767,7 +6767,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B85" s="8">
         <v>46108.75715243055</v>
@@ -6777,16 +6777,16 @@
         <v>46185.184959907405</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="H85" s="9" t="s">
         <v>256</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>257</v>
       </c>
       <c r="I85" s="8">
         <v>46183</v>
@@ -6804,13 +6804,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O85" s="9" t="s">
         <v>147</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q85" s="8">
         <v>46183</v>
@@ -6830,7 +6830,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B86" s="5">
         <v>46108.75715773148</v>
@@ -6846,10 +6846,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>256</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>257</v>
       </c>
       <c r="I86" s="5">
         <v>46239</v>
@@ -6867,13 +6867,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>138</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q86" s="5">
         <v>46239</v>
@@ -6893,7 +6893,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B87" s="8">
         <v>46108.75716349537</v>
@@ -6903,16 +6903,16 @@
         <v>46248.16971915509</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="H87" s="9" t="s">
         <v>256</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>257</v>
       </c>
       <c r="I87" s="8">
         <v>46246</v>
@@ -6930,13 +6930,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O87" s="9" t="s">
         <v>129</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q87" s="8">
         <v>46246</v>
@@ -6956,7 +6956,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B88" s="5">
         <v>46108.75716875</v>
@@ -6966,16 +6966,16 @@
         <v>46267.17843465278</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>256</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>257</v>
       </c>
       <c r="I88" s="5">
         <v>46273</v>
@@ -6993,13 +6993,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q88" s="5">
         <v>46273</v>
@@ -7011,7 +7011,7 @@
         <v>0</v>
       </c>
       <c r="T88" s="12" t="s">
-        <v>152</v>
+        <v>298</v>
       </c>
       <c r="U88" s="10" t="s">
         <v>53</v>
@@ -7035,10 +7035,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="H89" s="9" t="s">
         <v>256</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>257</v>
       </c>
       <c r="I89" s="8">
         <v>46220</v>
@@ -7056,13 +7056,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q89" s="8">
         <v>46220</v>
@@ -7098,10 +7098,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>256</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>257</v>
       </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
@@ -7117,10 +7117,10 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>303</v>
@@ -7159,10 +7159,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="H91" s="9" t="s">
         <v>256</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>257</v>
       </c>
       <c r="I91" s="8">
         <v>46181</v>
@@ -7180,10 +7180,10 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P91" s="9" t="s">
         <v>306</v>
@@ -7293,7 +7293,7 @@
         <v>308</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P93" s="9" t="s">
         <v>308</v>
@@ -7326,7 +7326,7 @@
         <v>46267.167487708335</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7379,7 +7379,7 @@
         <v>46267.167488796294</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7462,7 +7462,7 @@
         <v>308</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>308</v>
@@ -7495,7 +7495,7 @@
         <v>46269.167690648144</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7548,7 +7548,7 @@
         <v>46269.16769188657</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46266.176813287035</v>
+        <v>46273.16745574074</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>327</v>
@@ -7631,7 +7631,7 @@
         <v>308</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P99" s="9" t="s">
         <v>308</v>
@@ -7646,7 +7646,7 @@
         <v>0</v>
       </c>
       <c r="T99" s="12" t="s">
-        <v>152</v>
+        <v>298</v>
       </c>
       <c r="U99" s="10" t="s">
         <v>53</v>
@@ -7661,10 +7661,10 @@
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46227.72251393519</v>
+        <v>46273.16745900463</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7714,10 +7714,10 @@
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46227.72251137732</v>
+        <v>46273.16746020834</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7800,7 +7800,7 @@
         <v>308</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>308</v>
@@ -7815,7 +7815,7 @@
         <v>0</v>
       </c>
       <c r="T102" s="12" t="s">
-        <v>152</v>
+        <v>298</v>
       </c>
       <c r="U102" s="10" t="s">
         <v>53</v>
@@ -7833,7 +7833,7 @@
         <v>46227.722512928245</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7886,7 +7886,7 @@
         <v>46227.72251365741</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7969,7 +7969,7 @@
         <v>308</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P105" s="9" t="s">
         <v>308</v>
@@ -7984,7 +7984,7 @@
         <v>0</v>
       </c>
       <c r="T105" s="12" t="s">
-        <v>152</v>
+        <v>298</v>
       </c>
       <c r="U105" s="10" t="s">
         <v>53</v>
@@ -8002,7 +8002,7 @@
         <v>46227.722511921296</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -8055,7 +8055,7 @@
         <v>46227.72251247685</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46245.73985467592</v>
+        <v>46273.13886990741</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>349</v>
@@ -8138,7 +8138,7 @@
         <v>308</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>308</v>
@@ -8152,8 +8152,8 @@
       <c r="S108" s="6">
         <v>0</v>
       </c>
-      <c r="T108" s="11" t="s">
-        <v>127</v>
+      <c r="T108" s="12" t="s">
+        <v>298</v>
       </c>
       <c r="U108" s="10" t="s">
         <v>53</v>
@@ -8171,7 +8171,7 @@
         <v>46223.59502533565</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8199,7 +8199,7 @@
         <v>349</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P109" s="9" t="s">
         <v>351</v>
@@ -8222,7 +8222,7 @@
         <v>46223.59502458334</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8250,7 +8250,7 @@
         <v>349</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>353</v>
@@ -8334,7 +8334,7 @@
         <v>46223.595106875</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8362,7 +8362,7 @@
         <v>355</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>358</v>
@@ -8385,7 +8385,7 @@
         <v>46223.59510622685</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8413,7 +8413,7 @@
         <v>355</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P113" s="9" t="s">
         <v>360</v>
@@ -8546,7 +8546,7 @@
         <v>46114.62888387732</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8574,7 +8574,7 @@
         <v>365</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>370</v>
@@ -8597,7 +8597,7 @@
         <v>46114.62888469908</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8625,7 +8625,7 @@
         <v>365</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P117" s="9" t="s">
         <v>372</v>
@@ -8966,7 +8966,7 @@
         <v>46223.595359328705</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8996,7 +8996,7 @@
         <v>385</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>388</v>
@@ -9019,7 +9019,7 @@
         <v>46223.59535869213</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -9049,7 +9049,7 @@
         <v>385</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P125" s="9" t="s">
         <v>390</v>
@@ -9343,10 +9343,10 @@
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H131" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="H131" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="I131" s="8">
         <v>46293</v>
@@ -9400,16 +9400,16 @@
         <v>46114.62931347222</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H132" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9428,7 +9428,7 @@
         <v>402</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>405</v>
@@ -9451,16 +9451,16 @@
         <v>46114.62931429398</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H133" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="H133" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="I133" s="9"/>
       <c r="J133" s="8">
@@ -9479,7 +9479,7 @@
         <v>402</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P133" s="9" t="s">
         <v>407</v>
@@ -9508,10 +9508,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H134" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9559,10 +9559,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H135" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="H135" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="I135" s="9"/>
       <c r="J135" s="8">
@@ -9610,10 +9610,10 @@
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H136" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="H136" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9661,10 +9661,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H137" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="H137" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="I137" s="9"/>
       <c r="J137" s="8">
@@ -9712,10 +9712,10 @@
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H138" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="H138" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
@@ -9763,10 +9763,10 @@
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H139" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="H139" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="I139" s="8">
         <v>46294</v>
@@ -9820,16 +9820,16 @@
         <v>46114.830281076385</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H140" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="I140" s="5">
         <v>46294</v>
@@ -9850,7 +9850,7 @@
         <v>420</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>423</v>
@@ -9873,16 +9873,16 @@
         <v>46114.830302789356</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H141" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="H141" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="I141" s="8">
         <v>46294</v>
@@ -9903,7 +9903,7 @@
         <v>420</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P141" s="9" t="s">
         <v>420</v>
@@ -9932,10 +9932,10 @@
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H142" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="H142" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="I142" s="5">
         <v>46294</v>
@@ -9985,10 +9985,10 @@
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H143" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="H143" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="I143" s="8">
         <v>46294</v>
@@ -10038,10 +10038,10 @@
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H144" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="H144" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="I144" s="5">
         <v>46294</v>
@@ -10091,10 +10091,10 @@
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H145" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="H145" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="I145" s="8">
         <v>46294</v>
@@ -10144,10 +10144,10 @@
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H146" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="H146" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="I146" s="5">
         <v>46294</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -727,6 +727,9 @@
     <t>OT 4287 ZVR 1-14-42/4,OT  4288 ZVR1-14-30/4</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1213869987281952</t>
   </si>
   <si>
@@ -905,9 +908,6 @@
   </si>
   <si>
     <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213833564713244</t>
@@ -5807,7 +5807,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46114.631384050925</v>
+        <v>46274.137942905094</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>234</v>
@@ -5854,8 +5854,8 @@
       <c r="S68" s="6">
         <v>0</v>
       </c>
-      <c r="T68" s="11" t="s">
-        <v>127</v>
+      <c r="T68" s="12" t="s">
+        <v>238</v>
       </c>
       <c r="U68" s="10" t="s">
         <v>53</v>
@@ -5863,7 +5863,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B69" s="8">
         <v>46111.55280189815</v>
@@ -5904,7 +5904,7 @@
         <v>210</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5914,7 +5914,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B70" s="5">
         <v>46111.55285245371</v>
@@ -5924,7 +5924,7 @@
         <v>46114.62851040509</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5955,7 +5955,7 @@
         <v>215</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5965,7 +5965,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B71" s="8">
         <v>46108.75714166666</v>
@@ -5975,7 +5975,7 @@
         <v>46118.545566597226</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -5999,7 +5999,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -6012,7 +6012,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B72" s="5">
         <v>46108.75714454861</v>
@@ -6022,16 +6022,16 @@
         <v>46240.16751462963</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -6047,13 +6047,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q72" s="5">
         <v>46231</v>
@@ -6073,7 +6073,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B73" s="8">
         <v>46111.50359008102</v>
@@ -6085,7 +6085,7 @@
         <v>46260.58097469907</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -6109,7 +6109,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -6126,7 +6126,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B74" s="5">
         <v>46111.50404616898</v>
@@ -6138,16 +6138,16 @@
         <v>46260.58079141204</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I74" s="5">
         <v>46211</v>
@@ -6165,13 +6165,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>169</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q74" s="5">
         <v>46211</v>
@@ -6191,7 +6191,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B75" s="8">
         <v>46111.50406170139</v>
@@ -6203,16 +6203,16 @@
         <v>46260.580961342595</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I75" s="8">
         <v>46213</v>
@@ -6230,13 +6230,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q75" s="8">
         <v>46213</v>
@@ -6256,7 +6256,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B76" s="5">
         <v>46111.50543856481</v>
@@ -6266,7 +6266,7 @@
         <v>46260.577887962965</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -6290,7 +6290,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -6305,7 +6305,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B77" s="8">
         <v>46111.505495046295</v>
@@ -6317,16 +6317,16 @@
         <v>46260.58096115741</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I77" s="8">
         <v>46217</v>
@@ -6344,13 +6344,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q77" s="8">
         <v>46217</v>
@@ -6370,7 +6370,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B78" s="5">
         <v>46111.50560314815</v>
@@ -6382,16 +6382,16 @@
         <v>46260.57750302083</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I78" s="5">
         <v>46226</v>
@@ -6409,13 +6409,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>219</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q78" s="5">
         <v>46226</v>
@@ -6435,7 +6435,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B79" s="8">
         <v>46111.52633317129</v>
@@ -6453,10 +6453,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I79" s="8">
         <v>46226</v>
@@ -6474,13 +6474,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6490,7 +6490,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B80" s="5">
         <v>46111.526644375</v>
@@ -6508,10 +6508,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I80" s="5">
         <v>46226</v>
@@ -6529,13 +6529,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6545,7 +6545,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B81" s="8">
         <v>46111.50563458333</v>
@@ -6557,16 +6557,16 @@
         <v>46260.57788128473</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I81" s="8">
         <v>46246</v>
@@ -6584,13 +6584,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O81" s="9" t="s">
         <v>219</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q81" s="8">
         <v>46246</v>
@@ -6610,7 +6610,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B82" s="5">
         <v>46111.526916469906</v>
@@ -6628,10 +6628,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I82" s="5">
         <v>46246</v>
@@ -6649,13 +6649,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6665,7 +6665,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B83" s="8">
         <v>46111.52699828704</v>
@@ -6683,10 +6683,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I83" s="8">
         <v>46246</v>
@@ -6704,13 +6704,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6720,7 +6720,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B84" s="5">
         <v>46108.75714884259</v>
@@ -6730,7 +6730,7 @@
         <v>46221.1155655787</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -6754,7 +6754,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6767,7 +6767,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B85" s="8">
         <v>46108.75715243055</v>
@@ -6777,16 +6777,16 @@
         <v>46185.184959907405</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I85" s="8">
         <v>46183</v>
@@ -6804,13 +6804,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O85" s="9" t="s">
         <v>147</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q85" s="8">
         <v>46183</v>
@@ -6830,7 +6830,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B86" s="5">
         <v>46108.75715773148</v>
@@ -6846,10 +6846,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I86" s="5">
         <v>46239</v>
@@ -6867,13 +6867,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>138</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q86" s="5">
         <v>46239</v>
@@ -6893,7 +6893,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B87" s="8">
         <v>46108.75716349537</v>
@@ -6903,16 +6903,16 @@
         <v>46248.16971915509</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I87" s="8">
         <v>46246</v>
@@ -6930,13 +6930,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O87" s="9" t="s">
         <v>129</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q87" s="8">
         <v>46246</v>
@@ -6956,26 +6956,26 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B88" s="5">
         <v>46108.75716875</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46267.17843465278</v>
+        <v>46274.167405914355</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I88" s="5">
         <v>46273</v>
@@ -6993,13 +6993,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>156</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q88" s="5">
         <v>46273</v>
@@ -7011,7 +7011,7 @@
         <v>0</v>
       </c>
       <c r="T88" s="12" t="s">
-        <v>298</v>
+        <v>238</v>
       </c>
       <c r="U88" s="10" t="s">
         <v>53</v>
@@ -7035,10 +7035,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I89" s="8">
         <v>46220</v>
@@ -7056,7 +7056,7 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O89" s="9" t="s">
         <v>178</v>
@@ -7098,10 +7098,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
@@ -7117,10 +7117,10 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>303</v>
@@ -7159,10 +7159,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I91" s="8">
         <v>46181</v>
@@ -7180,7 +7180,7 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O91" s="9" t="s">
         <v>198</v>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46273.16745574074</v>
+        <v>46274.149059386575</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>327</v>
@@ -7645,8 +7645,8 @@
       <c r="S99" s="9">
         <v>0</v>
       </c>
-      <c r="T99" s="12" t="s">
-        <v>298</v>
+      <c r="T99" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U99" s="10" t="s">
         <v>53</v>
@@ -7815,7 +7815,7 @@
         <v>0</v>
       </c>
       <c r="T102" s="12" t="s">
-        <v>298</v>
+        <v>238</v>
       </c>
       <c r="U102" s="10" t="s">
         <v>53</v>
@@ -7984,7 +7984,7 @@
         <v>0</v>
       </c>
       <c r="T105" s="12" t="s">
-        <v>298</v>
+        <v>238</v>
       </c>
       <c r="U105" s="10" t="s">
         <v>53</v>
@@ -8153,7 +8153,7 @@
         <v>0</v>
       </c>
       <c r="T108" s="12" t="s">
-        <v>298</v>
+        <v>238</v>
       </c>
       <c r="U108" s="10" t="s">
         <v>53</v>
@@ -8413,7 +8413,7 @@
         <v>355</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P113" s="9" t="s">
         <v>360</v>
@@ -9343,10 +9343,10 @@
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I131" s="8">
         <v>46293</v>
@@ -9406,10 +9406,10 @@
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9457,10 +9457,10 @@
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I133" s="9"/>
       <c r="J133" s="8">
@@ -9508,10 +9508,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9559,10 +9559,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I135" s="9"/>
       <c r="J135" s="8">
@@ -9610,10 +9610,10 @@
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9661,10 +9661,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I137" s="9"/>
       <c r="J137" s="8">
@@ -9712,10 +9712,10 @@
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
@@ -9763,10 +9763,10 @@
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I139" s="8">
         <v>46294</v>
@@ -9826,10 +9826,10 @@
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I140" s="5">
         <v>46294</v>
@@ -9879,10 +9879,10 @@
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I141" s="8">
         <v>46294</v>
@@ -9932,10 +9932,10 @@
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I142" s="5">
         <v>46294</v>
@@ -9985,10 +9985,10 @@
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I143" s="8">
         <v>46294</v>
@@ -10038,10 +10038,10 @@
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I144" s="5">
         <v>46294</v>
@@ -10091,10 +10091,10 @@
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I145" s="8">
         <v>46294</v>
@@ -10144,10 +10144,10 @@
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I146" s="5">
         <v>46294</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -6963,7 +6963,7 @@
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46274.167405914355</v>
+        <v>46275.126632685184</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>298</v>
@@ -7010,8 +7010,8 @@
       <c r="S88" s="6">
         <v>0</v>
       </c>
-      <c r="T88" s="12" t="s">
-        <v>238</v>
+      <c r="T88" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U88" s="10" t="s">
         <v>53</v>
@@ -7767,7 +7767,7 @@
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46268.167859270834</v>
+        <v>46275.16746550926</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>335</v>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46227.722512928245</v>
+        <v>46275.16746789352</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>210</v>
@@ -7883,7 +7883,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46227.72251365741</v>
+        <v>46275.16746898148</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>215</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -7767,7 +7767,7 @@
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46275.16746550926</v>
+        <v>46276.143129421296</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>335</v>
@@ -7814,8 +7814,8 @@
       <c r="S102" s="6">
         <v>0</v>
       </c>
-      <c r="T102" s="12" t="s">
-        <v>238</v>
+      <c r="T102" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U102" s="10" t="s">
         <v>53</v>
